--- a/legendas-365.xlsx
+++ b/legendas-365.xlsx
@@ -707,7 +707,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: amor 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #amor</t>
+          <t>Oração da noite: o amor que lança fora o medo 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #amor</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr"/>

--- a/legendas-365.xlsx
+++ b/legendas-365.xlsx
@@ -535,7 +535,7 @@
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: amor 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #amor</t>
+          <t>Oração da noite: amor 🌙 Para fechar o dia com Salmos 36:7. Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #amor</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr"/>
@@ -578,7 +578,7 @@
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: amor 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #amor</t>
+          <t>Oração da noite: amor 🌙 Para fechar o dia com Salmos 63:3. Escreva amém se essa oração é sua também. #oracaodanoite #oracao #fe #amor</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr"/>
@@ -621,7 +621,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: amor 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #amor</t>
+          <t>Oração da noite: amor 🌙 Para fechar o dia com Cantares 8:7. Comente o nome de quem você quer colocar nesta oração. #oracaodanoite #oracao #fe #amor</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr"/>
@@ -750,7 +750,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: amor 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #amor</t>
+          <t>Oração da noite: amor 🌙 Para fechar o dia com Gálatas 5:13-14. Marque alguém que precisa ouvir esta oração. #oracaodanoite #oracao #fe #amor</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr"/>
@@ -793,7 +793,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: amor 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #amor</t>
+          <t>Oração da noite: amor 🌙 Para fechar o dia com João 15:9. Comente seu pedido. Vamos orar juntos. #oracaodanoite #oracao #fe #amor</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr"/>
@@ -836,7 +836,7 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: amor 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #amor</t>
+          <t>Oração da noite: amor 🌙 Para fechar o dia com Efésios 2:4-5. Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #amor</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr"/>
@@ -879,7 +879,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: amor 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #amor</t>
+          <t>Oração da noite: amor 🌙 Para fechar o dia com Romanos 12:9. Escreva amém se essa oração é sua também. #oracaodanoite #oracao #fe #amor</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr"/>
@@ -922,7 +922,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: amor 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #amor</t>
+          <t>Oração da noite: amor 🌙 Para fechar o dia com Provérbios 10:12. Comente o nome de quem você quer colocar nesta oração. #oracaodanoite #oracao #fe #amor</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr"/>
@@ -965,7 +965,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: amor 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #amor</t>
+          <t>Oração da noite: amor 🌙 Para fechar o dia com 1 João 4:20. Conte nos comentários pelo que você quer agradecer hoje. #oracaodanoite #oracao #fe #amor</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr"/>
@@ -1008,7 +1008,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: amor 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #amor</t>
+          <t>Oração da noite: amor 🌙 Para fechar o dia com Salmos 86:15. Deixe nos comentários o que você quer entregar a Deus esta noite. #oracaodanoite #oracao #fe #amor</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr"/>
@@ -1051,7 +1051,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: amor 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #amor</t>
+          <t>Oração da noite: amor 🌙 Para fechar o dia com Oseias 11:4. Marque alguém que precisa ouvir esta oração. #oracaodanoite #oracao #fe #amor</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr"/>
@@ -1094,7 +1094,7 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: amor 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #amor</t>
+          <t>Oração da noite: amor 🌙 Para fechar o dia com Marcos 10:21. Comente seu pedido. Vamos orar juntos. #oracaodanoite #oracao #fe #amor</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr"/>
@@ -1137,7 +1137,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: amor 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #amor</t>
+          <t>Oração da noite: amor 🌙 Para fechar o dia com João 21:17. Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #amor</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr"/>
@@ -1180,7 +1180,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: amor 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #amor</t>
+          <t>Oração da noite: amor 🌙 Para fechar o dia com Tito 3:4-5. Escreva amém se essa oração é sua também. #oracaodanoite #oracao #fe #amor</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr"/>
@@ -1223,7 +1223,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: amor 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #amor</t>
+          <t>Oração da noite: amor 🌙 Para fechar o dia com 1 Coríntios 16:14. Comente o nome de quem você quer colocar nesta oração. #oracaodanoite #oracao #fe #amor</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr"/>
@@ -1266,7 +1266,7 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: oração e confiança 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #oracao</t>
+          <t>Oração da noite: oração e confiança 🌙 Para fechar o dia com Jeremias 33:3. Conte nos comentários pelo que você quer agradecer hoje. #oracaodanoite #oracao #fe #oracao</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr"/>
@@ -1309,7 +1309,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: oração e confiança 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #oracao</t>
+          <t>Oração da noite: oração e confiança 🌙 Para fechar o dia com Mateus 7:7-8. Deixe nos comentários o que você quer entregar a Deus esta noite. #oracaodanoite #oracao #fe #oracao</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr"/>
@@ -1352,7 +1352,7 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: oração e confiança 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #oracao</t>
+          <t>Oração da noite: oração e confiança 🌙 Para fechar o dia com 1 Tessalonicenses 5:17. Marque alguém que precisa ouvir esta oração. #oracaodanoite #oracao #fe #oracao</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr"/>
@@ -1395,7 +1395,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: oração e confiança 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #oracao</t>
+          <t>Oração da noite: oração e confiança 🌙 Para fechar o dia com Filipenses 4:19. Comente seu pedido. Vamos orar juntos. #oracaodanoite #oracao #fe #oracao</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr"/>
@@ -1438,7 +1438,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: oração e confiança 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #oracao</t>
+          <t>Oração da noite: oração e confiança 🌙 Para fechar o dia com Salmos 37:4. Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #oracao</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr"/>
@@ -1481,7 +1481,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: oração e confiança 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #oracao</t>
+          <t>Oração da noite: oração e confiança 🌙 Para fechar o dia com Salmos 56:8. Escreva amém se essa oração é sua também. #oracaodanoite #oracao #fe #oracao</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr"/>
@@ -1524,7 +1524,7 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: oração e confiança 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #oracao</t>
+          <t>Oração da noite: oração e confiança 🌙 Para fechar o dia com Marcos 11:24. Comente o nome de quem você quer colocar nesta oração. #oracaodanoite #oracao #fe #oracao</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr"/>
@@ -1567,7 +1567,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: oração e confiança 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #oracao</t>
+          <t>Oração da noite: oração e confiança 🌙 Para fechar o dia com Salmos 145:18. Conte nos comentários pelo que você quer agradecer hoje. #oracaodanoite #oracao #fe #oracao</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr"/>
@@ -1610,7 +1610,7 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: oração e confiança 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #oracao</t>
+          <t>Oração da noite: oração e confiança 🌙 Para fechar o dia com Mateus 6:6. Deixe nos comentários o que você quer entregar a Deus esta noite. #oracaodanoite #oracao #fe #oracao</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr"/>
@@ -1653,7 +1653,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: oração e confiança 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #oracao</t>
+          <t>Oração da noite: oração e confiança 🌙 Para fechar o dia com Romanos 8:26. Marque alguém que precisa ouvir esta oração. #oracaodanoite #oracao #fe #oracao</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr"/>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: oração e confiança 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #oracao</t>
+          <t>Oração da noite: oração e confiança 🌙 Para fechar o dia com Hebreus 4:16. Comente seu pedido. Vamos orar juntos. #oracaodanoite #oracao #fe #oracao</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr"/>
@@ -1739,7 +1739,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: oração e confiança 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #oracao</t>
+          <t>Oração da noite: oração e confiança 🌙 Para fechar o dia com Salmos 62:8. Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #oracao</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr"/>
@@ -1782,7 +1782,7 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: oração e confiança 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #oracao</t>
+          <t>Oração da noite: oração e confiança 🌙 Para fechar o dia com Tiago 5:16. Escreva amém se essa oração é sua também. #oracaodanoite #oracao #fe #oracao</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr"/>
@@ -1825,7 +1825,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: oração e confiança 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #oracao</t>
+          <t>Oração da noite: oração e confiança 🌙 Para fechar o dia com Mateus 6:9-10. Comente o nome de quem você quer colocar nesta oração. #oracaodanoite #oracao #fe #oracao</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr"/>
@@ -1868,7 +1868,7 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: oração e confiança 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #oracao</t>
+          <t>Oração da noite: oração e confiança 🌙 Para fechar o dia com Salmos 5:3. Conte nos comentários pelo que você quer agradecer hoje. #oracaodanoite #oracao #fe #oracao</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr"/>
@@ -1911,7 +1911,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: oração e confiança 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #oracao</t>
+          <t>Oração da noite: oração e confiança 🌙 Para fechar o dia com Lucas 22:42. Deixe nos comentários o que você quer entregar a Deus esta noite. #oracaodanoite #oracao #fe #oracao</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr"/>
@@ -1954,7 +1954,7 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: oração e confiança 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #oracao</t>
+          <t>Oração da noite: oração e confiança 🌙 Para fechar o dia com 1 João 5:14. Marque alguém que precisa ouvir esta oração. #oracaodanoite #oracao #fe #oracao</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr"/>
@@ -1997,7 +1997,7 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: oração e confiança 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #oracao</t>
+          <t>Oração da noite: oração e confiança 🌙 Para fechar o dia com Salmos 20:7. Comente seu pedido. Vamos orar juntos. #oracaodanoite #oracao #fe #oracao</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr"/>
@@ -2040,7 +2040,7 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: oração e confiança 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #oracao</t>
+          <t>Oração da noite: oração e confiança 🌙 Para fechar o dia com Isaías 65:24. Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #oracao</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr"/>
@@ -2083,7 +2083,7 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: oração e confiança 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #oracao</t>
+          <t>Oração da noite: oração e confiança 🌙 Para fechar o dia com Neemias 1:4. Escreva amém se essa oração é sua também. #oracaodanoite #oracao #fe #oracao</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr"/>
@@ -2126,7 +2126,7 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: oração e confiança 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #oracao</t>
+          <t>Oração da noite: oração e confiança 🌙 Para fechar o dia com Daniel 9:18. Comente o nome de quem você quer colocar nesta oração. #oracaodanoite #oracao #fe #oracao</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr"/>
@@ -2169,7 +2169,7 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: oração e confiança 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #oracao</t>
+          <t>Oração da noite: oração e confiança 🌙 Para fechar o dia com Salmos 37:7. Conte nos comentários pelo que você quer agradecer hoje. #oracaodanoite #oracao #fe #oracao</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr"/>
@@ -2212,7 +2212,7 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: oração e confiança 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #oracao</t>
+          <t>Oração da noite: oração e confiança 🌙 Para fechar o dia com Mateus 21:22. Deixe nos comentários o que você quer entregar a Deus esta noite. #oracaodanoite #oracao #fe #oracao</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr"/>
@@ -2255,7 +2255,7 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: oração e confiança 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #oracao</t>
+          <t>Oração da noite: oração e confiança 🌙 Para fechar o dia com Salmos 141:2. Marque alguém que precisa ouvir esta oração. #oracaodanoite #oracao #fe #oracao</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr"/>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: oração e confiança 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #oracao</t>
+          <t>Oração da noite: oração e confiança 🌙 Para fechar o dia com Isaías 30:15. Comente seu pedido. Vamos orar juntos. #oracaodanoite #oracao #fe #oracao</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr"/>
@@ -2341,7 +2341,7 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: oração e confiança 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #oracao</t>
+          <t>Oração da noite: oração e confiança 🌙 Para fechar o dia com Salmos 9:10. Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #oracao</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr"/>
@@ -2384,7 +2384,7 @@
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: oração e confiança 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #oracao</t>
+          <t>Oração da noite: oração e confiança 🌙 Para fechar o dia com Atos 12:5. Escreva amém se essa oração é sua também. #oracaodanoite #oracao #fe #oracao</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr"/>
@@ -2427,7 +2427,7 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: oração e confiança 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #oracao</t>
+          <t>Oração da noite: oração e confiança 🌙 Para fechar o dia com Lucas 11:9-10. Comente o nome de quem você quer colocar nesta oração. #oracaodanoite #oracao #fe #oracao</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr"/>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: oração e confiança 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #oracao</t>
+          <t>Oração da noite: oração e confiança 🌙 Para fechar o dia com Provérbios 29:25. Conte nos comentários pelo que você quer agradecer hoje. #oracaodanoite #oracao #fe #oracao</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr"/>
@@ -2513,7 +2513,7 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: oração e confiança 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #oracao</t>
+          <t>Oração da noite: oração e confiança 🌙 Para fechar o dia com Salmos 57:1-2. Deixe nos comentários o que você quer entregar a Deus esta noite. #oracaodanoite #oracao #fe #oracao</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr"/>
@@ -2556,7 +2556,7 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: recomeço e promessas 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #recomeco</t>
+          <t>Oração da noite: recomeço e promessas 🌙 Para fechar o dia com Isaías 43:18. Marque alguém que precisa ouvir esta oração. #oracaodanoite #oracao #fe #recomeco</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr"/>
@@ -2599,7 +2599,7 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: recomeço e promessas 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #recomeco</t>
+          <t>Oração da noite: recomeço e promessas 🌙 Para fechar o dia com Filipenses 3:13-14. Comente seu pedido. Vamos orar juntos. #oracaodanoite #oracao #fe #recomeco</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr"/>
@@ -2642,7 +2642,7 @@
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: recomeço e promessas 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #recomeco</t>
+          <t>Oração da noite: recomeço e promessas 🌙 Para fechar o dia com Ezequiel 36:26. Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #recomeco</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr"/>
@@ -2685,7 +2685,7 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: recomeço e promessas 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #recomeco</t>
+          <t>Oração da noite: recomeço e promessas 🌙 Para fechar o dia com Apocalipse 21:5. Escreva amém se essa oração é sua também. #oracaodanoite #oracao #fe #recomeco</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr"/>
@@ -2728,7 +2728,7 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: recomeço e promessas 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #recomeco</t>
+          <t>Oração da noite: recomeço e promessas 🌙 Para fechar o dia com Salmos 40:3. Comente o nome de quem você quer colocar nesta oração. #oracaodanoite #oracao #fe #recomeco</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr"/>
@@ -2771,7 +2771,7 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: recomeço e promessas 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #recomeco</t>
+          <t>Oração da noite: recomeço e promessas 🌙 Para fechar o dia com 2 Coríntios 1:20. Conte nos comentários pelo que você quer agradecer hoje. #oracaodanoite #oracao #fe #recomeco</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr"/>
@@ -2814,7 +2814,7 @@
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: recomeço e promessas 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #recomeco</t>
+          <t>Oração da noite: recomeço e promessas 🌙 Para fechar o dia com Números 23:19. Deixe nos comentários o que você quer entregar a Deus esta noite. #oracaodanoite #oracao #fe #recomeco</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr"/>
@@ -2857,7 +2857,7 @@
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: recomeço e promessas 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #recomeco</t>
+          <t>Oração da noite: recomeço e promessas 🌙 Para fechar o dia com Josué 21:45. Marque alguém que precisa ouvir esta oração. #oracaodanoite #oracao #fe #recomeco</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr"/>
@@ -2900,7 +2900,7 @@
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: recomeço e promessas 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #recomeco</t>
+          <t>Oração da noite: recomeço e promessas 🌙 Para fechar o dia com Lamentações 3:25. Comente seu pedido. Vamos orar juntos. #oracaodanoite #oracao #fe #recomeco</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr"/>
@@ -2943,7 +2943,7 @@
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: recomeço e promessas 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #recomeco</t>
+          <t>Oração da noite: recomeço e promessas 🌙 Para fechar o dia com Isaías 55:10-11. Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #recomeco</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr"/>
@@ -2986,7 +2986,7 @@
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: recomeço e promessas 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #recomeco</t>
+          <t>Oração da noite: recomeço e promessas 🌙 Para fechar o dia com Salmos 37:25. Escreva amém se essa oração é sua também. #oracaodanoite #oracao #fe #recomeco</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr"/>
@@ -3029,7 +3029,7 @@
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: recomeço e promessas 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #recomeco</t>
+          <t>Oração da noite: recomeço e promessas 🌙 Para fechar o dia com Deuteronômio 7:9. Comente o nome de quem você quer colocar nesta oração. #oracaodanoite #oracao #fe #recomeco</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr"/>
@@ -3072,7 +3072,7 @@
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: recomeço e promessas 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #recomeco</t>
+          <t>Oração da noite: recomeço e promessas 🌙 Para fechar o dia com Hebreus 10:23. Conte nos comentários pelo que você quer agradecer hoje. #oracaodanoite #oracao #fe #recomeco</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr"/>
@@ -3115,7 +3115,7 @@
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: recomeço e promessas 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #recomeco</t>
+          <t>Oração da noite: recomeço e promessas 🌙 Para fechar o dia com Jonas 2:10. Deixe nos comentários o que você quer entregar a Deus esta noite. #oracaodanoite #oracao #fe #recomeco</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr"/>
@@ -3158,7 +3158,7 @@
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: recomeço e promessas 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #recomeco</t>
+          <t>Oração da noite: recomeço e promessas 🌙 Para fechar o dia com Jonas 3:1. Marque alguém que precisa ouvir esta oração. #oracaodanoite #oracao #fe #recomeco</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr"/>
@@ -3201,7 +3201,7 @@
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: recomeço e promessas 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #recomeco</t>
+          <t>Oração da noite: recomeço e promessas 🌙 Para fechar o dia com Isaías 58:11. Comente seu pedido. Vamos orar juntos. #oracaodanoite #oracao #fe #recomeco</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr"/>
@@ -3244,7 +3244,7 @@
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: recomeço e promessas 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #recomeco</t>
+          <t>Oração da noite: recomeço e promessas 🌙 Para fechar o dia com Salmos 23:6. Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #recomeco</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr"/>
@@ -3287,7 +3287,7 @@
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: recomeço e promessas 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #recomeco</t>
+          <t>Oração da noite: recomeço e promessas 🌙 Para fechar o dia com Gênesis 28:15. Escreva amém se essa oração é sua também. #oracaodanoite #oracao #fe #recomeco</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr"/>
@@ -3330,7 +3330,7 @@
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: recomeço e promessas 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #recomeco</t>
+          <t>Oração da noite: recomeço e promessas 🌙 Para fechar o dia com Isaías 42:3. Comente o nome de quem você quer colocar nesta oração. #oracaodanoite #oracao #fe #recomeco</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr"/>
@@ -3373,7 +3373,7 @@
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: recomeço e promessas 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #recomeco</t>
+          <t>Oração da noite: recomeço e promessas 🌙 Para fechar o dia com Salmos 145:14. Conte nos comentários pelo que você quer agradecer hoje. #oracaodanoite #oracao #fe #recomeco</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr"/>
@@ -3416,7 +3416,7 @@
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: recomeço e promessas 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #recomeco</t>
+          <t>Oração da noite: recomeço e promessas 🌙 Para fechar o dia com Isaías 60:1. Deixe nos comentários o que você quer entregar a Deus esta noite. #oracaodanoite #oracao #fe #recomeco</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr"/>
@@ -3459,7 +3459,7 @@
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: recomeço e promessas 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #recomeco</t>
+          <t>Oração da noite: recomeço e promessas 🌙 Para fechar o dia com Atos 9:17-18. Marque alguém que precisa ouvir esta oração. #oracaodanoite #oracao #fe #recomeco</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr"/>
@@ -3502,7 +3502,7 @@
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: recomeço e promessas 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #recomeco</t>
+          <t>Oração da noite: recomeço e promessas 🌙 Para fechar o dia com Lucas 5:5-6. Comente seu pedido. Vamos orar juntos. #oracaodanoite #oracao #fe #recomeco</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr"/>
@@ -3545,7 +3545,7 @@
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: recomeço e promessas 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #recomeco</t>
+          <t>Oração da noite: recomeço e promessas 🌙 Para fechar o dia com Oseias 6:3. Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #recomeco</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr"/>
@@ -3588,7 +3588,7 @@
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: recomeço e promessas 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #recomeco</t>
+          <t>Oração da noite: recomeço e promessas 🌙 Para fechar o dia com Ageu 2:9. Escreva amém se essa oração é sua também. #oracaodanoite #oracao #fe #recomeco</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr"/>
@@ -3631,7 +3631,7 @@
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: recomeço e promessas 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #recomeco</t>
+          <t>Oração da noite: recomeço e promessas 🌙 Para fechar o dia com Isaías 54:10. Comente o nome de quem você quer colocar nesta oração. #oracaodanoite #oracao #fe #recomeco</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr"/>
@@ -3674,7 +3674,7 @@
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: recomeço e promessas 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #recomeco</t>
+          <t>Oração da noite: recomeço e promessas 🌙 Para fechar o dia com Salmos 30:11. Conte nos comentários pelo que você quer agradecer hoje. #oracaodanoite #oracao #fe #recomeco</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr"/>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: recomeço e promessas 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #recomeco</t>
+          <t>Oração da noite: recomeço e promessas 🌙 Para fechar o dia com 2 Pedro 3:9. Deixe nos comentários o que você quer entregar a Deus esta noite. #oracaodanoite #oracao #fe #recomeco</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr"/>
@@ -3760,7 +3760,7 @@
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: recomeço e promessas 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #recomeco</t>
+          <t>Oração da noite: recomeço e promessas 🌙 Para fechar o dia com Isaías 46:4. Marque alguém que precisa ouvir esta oração. #oracaodanoite #oracao #fe #recomeco</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr"/>
@@ -3803,7 +3803,7 @@
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: recomeço e promessas 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #recomeco</t>
+          <t>Oração da noite: recomeço e promessas 🌙 Para fechar o dia com Números 6:24-26. Comente seu pedido. Vamos orar juntos. #oracaodanoite #oracao #fe #recomeco</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr"/>
@@ -3846,7 +3846,7 @@
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: recomeço e promessas 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #recomeco</t>
+          <t>Oração da noite: recomeço e promessas 🌙 Para fechar o dia com Judas 1:24-25. Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #recomeco</t>
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr"/>
@@ -3889,7 +3889,7 @@
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: ansiedade e paz 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #ansiedade</t>
+          <t>Oração da noite: ansiedade e paz 🌙 Para fechar o dia com Filipenses 4:6-7. Escreva amém se essa oração é sua também. #oracaodanoite #oracao #fe #ansiedade</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr"/>
@@ -3932,7 +3932,7 @@
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: ansiedade e paz 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #ansiedade</t>
+          <t>Oração da noite: ansiedade e paz 🌙 Para fechar o dia com Mateus 6:34. Comente o nome de quem você quer colocar nesta oração. #oracaodanoite #oracao #fe #ansiedade</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr"/>
@@ -3975,7 +3975,7 @@
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: ansiedade e paz 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #ansiedade</t>
+          <t>Oração da noite: ansiedade e paz 🌙 Para fechar o dia com 1 Pedro 5:7. Conte nos comentários pelo que você quer agradecer hoje. #oracaodanoite #oracao #fe #ansiedade</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr"/>
@@ -4018,7 +4018,7 @@
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: ansiedade e paz 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #ansiedade</t>
+          <t>Oração da noite: ansiedade e paz 🌙 Para fechar o dia com João 14:27. Deixe nos comentários o que você quer entregar a Deus esta noite. #oracaodanoite #oracao #fe #ansiedade</t>
         </is>
       </c>
       <c r="I83" s="2" t="inlineStr"/>
@@ -4061,7 +4061,7 @@
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: ansiedade e paz 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #ansiedade</t>
+          <t>Oração da noite: ansiedade e paz 🌙 Para fechar o dia com Salmos 94:19. Marque alguém que precisa ouvir esta oração. #oracaodanoite #oracao #fe #ansiedade</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr"/>
@@ -4104,7 +4104,7 @@
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: ansiedade e paz 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #ansiedade</t>
+          <t>Oração da noite: ansiedade e paz 🌙 Para fechar o dia com Isaías 26:3. Comente seu pedido. Vamos orar juntos. #oracaodanoite #oracao #fe #ansiedade</t>
         </is>
       </c>
       <c r="I85" s="2" t="inlineStr"/>
@@ -4147,7 +4147,7 @@
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: ansiedade e paz 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #ansiedade</t>
+          <t>Oração da noite: ansiedade e paz 🌙 Para fechar o dia com Salmos 46:10. Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #ansiedade</t>
         </is>
       </c>
       <c r="I86" s="2" t="inlineStr"/>
@@ -4190,7 +4190,7 @@
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: ansiedade e paz 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #ansiedade</t>
+          <t>Oração da noite: ansiedade e paz 🌙 Para fechar o dia com Mateus 11:28-30. Escreva amém se essa oração é sua também. #oracaodanoite #oracao #fe #ansiedade</t>
         </is>
       </c>
       <c r="I87" s="2" t="inlineStr"/>
@@ -4233,7 +4233,7 @@
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: ansiedade e paz 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #ansiedade</t>
+          <t>Oração da noite: ansiedade e paz 🌙 Para fechar o dia com Salmos 55:22. Comente o nome de quem você quer colocar nesta oração. #oracaodanoite #oracao #fe #ansiedade</t>
         </is>
       </c>
       <c r="I88" s="2" t="inlineStr"/>
@@ -4276,7 +4276,7 @@
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: ansiedade e paz 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #ansiedade</t>
+          <t>Oração da noite: ansiedade e paz 🌙 Para fechar o dia com Provérbios 12:25. Conte nos comentários pelo que você quer agradecer hoje. #oracaodanoite #oracao #fe #ansiedade</t>
         </is>
       </c>
       <c r="I89" s="2" t="inlineStr"/>
@@ -4319,7 +4319,7 @@
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: ansiedade e paz 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #ansiedade</t>
+          <t>Oração da noite: ansiedade e paz 🌙 Para fechar o dia com Salmos 4:8. Deixe nos comentários o que você quer entregar a Deus esta noite. #oracaodanoite #oracao #fe #ansiedade</t>
         </is>
       </c>
       <c r="I90" s="2" t="inlineStr"/>
@@ -4362,7 +4362,7 @@
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: ansiedade e paz 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #ansiedade</t>
+          <t>Oração da noite: ansiedade e paz 🌙 Para fechar o dia com Isaías 41:10. Marque alguém que precisa ouvir esta oração. #oracaodanoite #oracao #fe #ansiedade</t>
         </is>
       </c>
       <c r="I91" s="2" t="inlineStr"/>
@@ -4405,7 +4405,7 @@
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: ansiedade e paz 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #ansiedade</t>
+          <t>Oração da noite: ansiedade e paz 🌙 Para fechar o dia com Salmos 23:1-3. Comente seu pedido. Vamos orar juntos. #oracaodanoite #oracao #fe #ansiedade</t>
         </is>
       </c>
       <c r="I92" s="2" t="inlineStr"/>
@@ -4448,7 +4448,7 @@
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: ansiedade e paz 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #ansiedade</t>
+          <t>Oração da noite: ansiedade e paz 🌙 Para fechar o dia com Romanos 8:28. Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #ansiedade</t>
         </is>
       </c>
       <c r="I93" s="2" t="inlineStr"/>
@@ -4491,7 +4491,7 @@
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: ansiedade e paz 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #ansiedade</t>
+          <t>Oração da noite: ansiedade e paz 🌙 Para fechar o dia com 2 Timóteo 1:7. Escreva amém se essa oração é sua também. #oracaodanoite #oracao #fe #ansiedade</t>
         </is>
       </c>
       <c r="I94" s="2" t="inlineStr"/>
@@ -4534,7 +4534,7 @@
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: ansiedade e paz 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #ansiedade</t>
+          <t>Oração da noite: ansiedade e paz 🌙 Para fechar o dia com Salmos 34:4. Comente o nome de quem você quer colocar nesta oração. #oracaodanoite #oracao #fe #ansiedade</t>
         </is>
       </c>
       <c r="I95" s="2" t="inlineStr"/>
@@ -4577,7 +4577,7 @@
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: ansiedade e paz 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #ansiedade</t>
+          <t>Oração da noite: ansiedade e paz 🌙 Para fechar o dia com Salmos 61:2. Conte nos comentários pelo que você quer agradecer hoje. #oracaodanoite #oracao #fe #ansiedade</t>
         </is>
       </c>
       <c r="I96" s="2" t="inlineStr"/>
@@ -4620,7 +4620,7 @@
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: ansiedade e paz 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #ansiedade</t>
+          <t>Oração da noite: ansiedade e paz 🌙 Para fechar o dia com Filipenses 4:8. Deixe nos comentários o que você quer entregar a Deus esta noite. #oracaodanoite #oracao #fe #ansiedade</t>
         </is>
       </c>
       <c r="I97" s="2" t="inlineStr"/>
@@ -4663,7 +4663,7 @@
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: ansiedade e paz 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #ansiedade</t>
+          <t>Oração da noite: ansiedade e paz 🌙 Para fechar o dia com Salmos 139:23-24. Marque alguém que precisa ouvir esta oração. #oracaodanoite #oracao #fe #ansiedade</t>
         </is>
       </c>
       <c r="I98" s="2" t="inlineStr"/>
@@ -4706,7 +4706,7 @@
       </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: ansiedade e paz 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #ansiedade</t>
+          <t>Oração da noite: ansiedade e paz 🌙 Para fechar o dia com Lucas 12:25-26. Comente seu pedido. Vamos orar juntos. #oracaodanoite #oracao #fe #ansiedade</t>
         </is>
       </c>
       <c r="I99" s="2" t="inlineStr"/>
@@ -4749,7 +4749,7 @@
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: ansiedade e paz 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #ansiedade</t>
+          <t>Oração da noite: ansiedade e paz 🌙 Para fechar o dia com Josué 1:9. Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #ansiedade</t>
         </is>
       </c>
       <c r="I100" s="2" t="inlineStr"/>
@@ -4792,7 +4792,7 @@
       </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: ansiedade e paz 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #ansiedade</t>
+          <t>Oração da noite: ansiedade e paz 🌙 Para fechar o dia com Salmos 121:1-2. Escreva amém se essa oração é sua também. #oracaodanoite #oracao #fe #ansiedade</t>
         </is>
       </c>
       <c r="I101" s="2" t="inlineStr"/>
@@ -4835,7 +4835,7 @@
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: ansiedade e paz 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #ansiedade</t>
+          <t>Oração da noite: ansiedade e paz 🌙 Para fechar o dia com Isaías 40:31. Comente o nome de quem você quer colocar nesta oração. #oracaodanoite #oracao #fe #ansiedade</t>
         </is>
       </c>
       <c r="I102" s="2" t="inlineStr"/>
@@ -4878,7 +4878,7 @@
       </c>
       <c r="H103" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: ansiedade e paz 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #ansiedade</t>
+          <t>Oração da noite: ansiedade e paz 🌙 Para fechar o dia com Êxodo 14:14. Conte nos comentários pelo que você quer agradecer hoje. #oracaodanoite #oracao #fe #ansiedade</t>
         </is>
       </c>
       <c r="I103" s="2" t="inlineStr"/>
@@ -4921,7 +4921,7 @@
       </c>
       <c r="H104" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: ansiedade e paz 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #ansiedade</t>
+          <t>Oração da noite: ansiedade e paz 🌙 Para fechar o dia com Salmos 56:3. Deixe nos comentários o que você quer entregar a Deus esta noite. #oracaodanoite #oracao #fe #ansiedade</t>
         </is>
       </c>
       <c r="I104" s="2" t="inlineStr"/>
@@ -4964,7 +4964,7 @@
       </c>
       <c r="H105" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: ansiedade e paz 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #ansiedade</t>
+          <t>Oração da noite: ansiedade e paz 🌙 Para fechar o dia com Mateus 6:26. Marque alguém que precisa ouvir esta oração. #oracaodanoite #oracao #fe #ansiedade</t>
         </is>
       </c>
       <c r="I105" s="2" t="inlineStr"/>
@@ -5007,7 +5007,7 @@
       </c>
       <c r="H106" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: ansiedade e paz 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #ansiedade</t>
+          <t>Oração da noite: ansiedade e paz 🌙 Para fechar o dia com Salmos 3:3. Comente seu pedido. Vamos orar juntos. #oracaodanoite #oracao #fe #ansiedade</t>
         </is>
       </c>
       <c r="I106" s="2" t="inlineStr"/>
@@ -5050,7 +5050,7 @@
       </c>
       <c r="H107" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: ansiedade e paz 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #ansiedade</t>
+          <t>Oração da noite: ansiedade e paz 🌙 Para fechar o dia com Sofonias 3:17. Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #ansiedade</t>
         </is>
       </c>
       <c r="I107" s="2" t="inlineStr"/>
@@ -5093,7 +5093,7 @@
       </c>
       <c r="H108" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: ansiedade e paz 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #ansiedade</t>
+          <t>Oração da noite: ansiedade e paz 🌙 Para fechar o dia com João 16:33. Escreva amém se essa oração é sua também. #oracaodanoite #oracao #fe #ansiedade</t>
         </is>
       </c>
       <c r="I108" s="2" t="inlineStr"/>
@@ -5136,7 +5136,7 @@
       </c>
       <c r="H109" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: ansiedade e paz 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #ansiedade</t>
+          <t>Oração da noite: ansiedade e paz 🌙 Para fechar o dia com Salmos 16:8. Comente o nome de quem você quer colocar nesta oração. #oracaodanoite #oracao #fe #ansiedade</t>
         </is>
       </c>
       <c r="I109" s="2" t="inlineStr"/>
@@ -5179,7 +5179,7 @@
       </c>
       <c r="H110" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: ansiedade e paz 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #ansiedade</t>
+          <t>Oração da noite: ansiedade e paz 🌙 Para fechar o dia com Salmos 27:1. Conte nos comentários pelo que você quer agradecer hoje. #oracaodanoite #oracao #fe #ansiedade</t>
         </is>
       </c>
       <c r="I110" s="2" t="inlineStr"/>
@@ -5222,7 +5222,7 @@
       </c>
       <c r="H111" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: medo e coragem 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #medo</t>
+          <t>Oração da noite: medo e coragem 🌙 Para fechar o dia com Deuteronômio 31:6. Deixe nos comentários o que você quer entregar a Deus esta noite. #oracaodanoite #oracao #fe #medo</t>
         </is>
       </c>
       <c r="I111" s="2" t="inlineStr"/>
@@ -5265,7 +5265,7 @@
       </c>
       <c r="H112" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: medo e coragem 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #medo</t>
+          <t>Oração da noite: medo e coragem 🌙 Para fechar o dia com Salmos 118:6. Marque alguém que precisa ouvir esta oração. #oracaodanoite #oracao #fe #medo</t>
         </is>
       </c>
       <c r="I112" s="2" t="inlineStr"/>
@@ -5308,7 +5308,7 @@
       </c>
       <c r="H113" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: medo e coragem 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #medo</t>
+          <t>Oração da noite: medo e coragem 🌙 Para fechar o dia com Isaías 43:1-2. Comente seu pedido. Vamos orar juntos. #oracaodanoite #oracao #fe #medo</t>
         </is>
       </c>
       <c r="I113" s="2" t="inlineStr"/>
@@ -5351,7 +5351,7 @@
       </c>
       <c r="H114" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: medo e coragem 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #medo</t>
+          <t>Oração da noite: medo e coragem 🌙 Para fechar o dia com Salmos 23:4. Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #medo</t>
         </is>
       </c>
       <c r="I114" s="2" t="inlineStr"/>
@@ -5394,7 +5394,7 @@
       </c>
       <c r="H115" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: medo e coragem 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #medo</t>
+          <t>Oração da noite: medo e coragem 🌙 Para fechar o dia com Romanos 8:31. Escreva amém se essa oração é sua também. #oracaodanoite #oracao #fe #medo</t>
         </is>
       </c>
       <c r="I115" s="2" t="inlineStr"/>
@@ -5437,7 +5437,7 @@
       </c>
       <c r="H116" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: medo e coragem 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #medo</t>
+          <t>Oração da noite: medo e coragem 🌙 Para fechar o dia com Hebreus 13:6. Comente o nome de quem você quer colocar nesta oração. #oracaodanoite #oracao #fe #medo</t>
         </is>
       </c>
       <c r="I116" s="2" t="inlineStr"/>
@@ -5480,7 +5480,7 @@
       </c>
       <c r="H117" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: medo e coragem 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #medo</t>
+          <t>Oração da noite: medo e coragem 🌙 Para fechar o dia com Provérbios 28:1. Conte nos comentários pelo que você quer agradecer hoje. #oracaodanoite #oracao #fe #medo</t>
         </is>
       </c>
       <c r="I117" s="2" t="inlineStr"/>
@@ -5523,7 +5523,7 @@
       </c>
       <c r="H118" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: medo e coragem 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #medo</t>
+          <t>Oração da noite: medo e coragem 🌙 Para fechar o dia com Salmos 91:1-2. Deixe nos comentários o que você quer entregar a Deus esta noite. #oracaodanoite #oracao #fe #medo</t>
         </is>
       </c>
       <c r="I118" s="2" t="inlineStr"/>
@@ -5566,7 +5566,7 @@
       </c>
       <c r="H119" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: medo e coragem 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #medo</t>
+          <t>Oração da noite: medo e coragem 🌙 Para fechar o dia com Josué 1:7. Marque alguém que precisa ouvir esta oração. #oracaodanoite #oracao #fe #medo</t>
         </is>
       </c>
       <c r="I119" s="2" t="inlineStr"/>
@@ -5609,7 +5609,7 @@
       </c>
       <c r="H120" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: medo e coragem 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #medo</t>
+          <t>Oração da noite: medo e coragem 🌙 Para fechar o dia com 1 Samuel 17:45. Comente seu pedido. Vamos orar juntos. #oracaodanoite #oracao #fe #medo</t>
         </is>
       </c>
       <c r="I120" s="2" t="inlineStr"/>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="H121" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: medo e coragem 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #medo</t>
+          <t>Oração da noite: medo e coragem 🌙 Para fechar o dia com Salmos 27:14. Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #medo</t>
         </is>
       </c>
       <c r="I121" s="2" t="inlineStr"/>
@@ -5695,7 +5695,7 @@
       </c>
       <c r="H122" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: medo e coragem 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #medo</t>
+          <t>Oração da noite: medo e coragem 🌙 Para fechar o dia com Isaías 12:2. Escreva amém se essa oração é sua também. #oracaodanoite #oracao #fe #medo</t>
         </is>
       </c>
       <c r="I122" s="2" t="inlineStr"/>
@@ -5738,7 +5738,7 @@
       </c>
       <c r="H123" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: medo e coragem 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #medo</t>
+          <t>Oração da noite: medo e coragem 🌙 Para fechar o dia com 2 Crônicas 20:15. Comente o nome de quem você quer colocar nesta oração. #oracaodanoite #oracao #fe #medo</t>
         </is>
       </c>
       <c r="I123" s="2" t="inlineStr"/>
@@ -5781,7 +5781,7 @@
       </c>
       <c r="H124" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: medo e coragem 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #medo</t>
+          <t>Oração da noite: medo e coragem 🌙 Para fechar o dia com Salmos 46:1-2. Conte nos comentários pelo que você quer agradecer hoje. #oracaodanoite #oracao #fe #medo</t>
         </is>
       </c>
       <c r="I124" s="2" t="inlineStr"/>
@@ -5824,7 +5824,7 @@
       </c>
       <c r="H125" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: medo e coragem 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #medo</t>
+          <t>Oração da noite: medo e coragem 🌙 Para fechar o dia com Marcos 4:39-40. Deixe nos comentários o que você quer entregar a Deus esta noite. #oracaodanoite #oracao #fe #medo</t>
         </is>
       </c>
       <c r="I125" s="2" t="inlineStr"/>
@@ -5867,7 +5867,7 @@
       </c>
       <c r="H126" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: medo e coragem 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #medo</t>
+          <t>Oração da noite: medo e coragem 🌙 Para fechar o dia com Mateus 14:29-31. Marque alguém que precisa ouvir esta oração. #oracaodanoite #oracao #fe #medo</t>
         </is>
       </c>
       <c r="I126" s="2" t="inlineStr"/>
@@ -5910,7 +5910,7 @@
       </c>
       <c r="H127" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: medo e coragem 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #medo</t>
+          <t>Oração da noite: medo e coragem 🌙 Para fechar o dia com Salmos 112:7. Comente seu pedido. Vamos orar juntos. #oracaodanoite #oracao #fe #medo</t>
         </is>
       </c>
       <c r="I127" s="2" t="inlineStr"/>
@@ -5953,7 +5953,7 @@
       </c>
       <c r="H128" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: medo e coragem 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #medo</t>
+          <t>Oração da noite: medo e coragem 🌙 Para fechar o dia com Lucas 1:37. Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #medo</t>
         </is>
       </c>
       <c r="I128" s="2" t="inlineStr"/>
@@ -5996,7 +5996,7 @@
       </c>
       <c r="H129" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: medo e coragem 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #medo</t>
+          <t>Oração da noite: medo e coragem 🌙 Para fechar o dia com Juízes 6:12. Escreva amém se essa oração é sua também. #oracaodanoite #oracao #fe #medo</t>
         </is>
       </c>
       <c r="I129" s="2" t="inlineStr"/>
@@ -6039,7 +6039,7 @@
       </c>
       <c r="H130" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: medo e coragem 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #medo</t>
+          <t>Oração da noite: medo e coragem 🌙 Para fechar o dia com Salmos 31:24. Comente o nome de quem você quer colocar nesta oração. #oracaodanoite #oracao #fe #medo</t>
         </is>
       </c>
       <c r="I130" s="2" t="inlineStr"/>
@@ -6082,7 +6082,7 @@
       </c>
       <c r="H131" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: medo e coragem 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #medo</t>
+          <t>Oração da noite: medo e coragem 🌙 Para fechar o dia com Ester 4:14. Conte nos comentários pelo que você quer agradecer hoje. #oracaodanoite #oracao #fe #medo</t>
         </is>
       </c>
       <c r="I131" s="2" t="inlineStr"/>
@@ -6125,7 +6125,7 @@
       </c>
       <c r="H132" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: medo e coragem 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #medo</t>
+          <t>Oração da noite: medo e coragem 🌙 Para fechar o dia com Daniel 3:17-18. Deixe nos comentários o que você quer entregar a Deus esta noite. #oracaodanoite #oracao #fe #medo</t>
         </is>
       </c>
       <c r="I132" s="2" t="inlineStr"/>
@@ -6168,7 +6168,7 @@
       </c>
       <c r="H133" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: medo e coragem 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #medo</t>
+          <t>Oração da noite: medo e coragem 🌙 Para fechar o dia com Atos 18:9-10. Marque alguém que precisa ouvir esta oração. #oracaodanoite #oracao #fe #medo</t>
         </is>
       </c>
       <c r="I133" s="2" t="inlineStr"/>
@@ -6211,7 +6211,7 @@
       </c>
       <c r="H134" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: medo e coragem 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #medo</t>
+          <t>Oração da noite: medo e coragem 🌙 Para fechar o dia com Salmos 138:3. Comente seu pedido. Vamos orar juntos. #oracaodanoite #oracao #fe #medo</t>
         </is>
       </c>
       <c r="I134" s="2" t="inlineStr"/>
@@ -6254,7 +6254,7 @@
       </c>
       <c r="H135" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: medo e coragem 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #medo</t>
+          <t>Oração da noite: medo e coragem 🌙 Para fechar o dia com Isaías 54:17. Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #medo</t>
         </is>
       </c>
       <c r="I135" s="2" t="inlineStr"/>
@@ -6297,7 +6297,7 @@
       </c>
       <c r="H136" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: medo e coragem 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #medo</t>
+          <t>Oração da noite: medo e coragem 🌙 Para fechar o dia com Provérbios 3:25-26. Escreva amém se essa oração é sua também. #oracaodanoite #oracao #fe #medo</t>
         </is>
       </c>
       <c r="I136" s="2" t="inlineStr"/>
@@ -6340,7 +6340,7 @@
       </c>
       <c r="H137" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: medo e coragem 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #medo</t>
+          <t>Oração da noite: medo e coragem 🌙 Para fechar o dia com Neemias 4:14. Comente o nome de quem você quer colocar nesta oração. #oracaodanoite #oracao #fe #medo</t>
         </is>
       </c>
       <c r="I137" s="2" t="inlineStr"/>
@@ -6383,7 +6383,7 @@
       </c>
       <c r="H138" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: medo e coragem 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #medo</t>
+          <t>Oração da noite: medo e coragem 🌙 Para fechar o dia com 2 Coríntios 12:9-10. Conte nos comentários pelo que você quer agradecer hoje. #oracaodanoite #oracao #fe #medo</t>
         </is>
       </c>
       <c r="I138" s="2" t="inlineStr"/>
@@ -6426,7 +6426,7 @@
       </c>
       <c r="H139" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: esperança em tempos difíceis 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #esperanca</t>
+          <t>Oração da noite: esperança em tempos difíceis 🌙 Para fechar o dia com Lamentações 3:22-23. Deixe nos comentários o que você quer entregar a Deus esta noite. #oracaodanoite #oracao #fe #esperanca</t>
         </is>
       </c>
       <c r="I139" s="2" t="inlineStr"/>
@@ -6469,7 +6469,7 @@
       </c>
       <c r="H140" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: esperança em tempos difíceis 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #esperanca</t>
+          <t>Oração da noite: esperança em tempos difíceis 🌙 Para fechar o dia com Jeremias 29:11. Marque alguém que precisa ouvir esta oração. #oracaodanoite #oracao #fe #esperanca</t>
         </is>
       </c>
       <c r="I140" s="2" t="inlineStr"/>
@@ -6512,7 +6512,7 @@
       </c>
       <c r="H141" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: esperança em tempos difíceis 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #esperanca</t>
+          <t>Oração da noite: esperança em tempos difíceis 🌙 Para fechar o dia com Romanos 15:13. Comente seu pedido. Vamos orar juntos. #oracaodanoite #oracao #fe #esperanca</t>
         </is>
       </c>
       <c r="I141" s="2" t="inlineStr"/>
@@ -6555,7 +6555,7 @@
       </c>
       <c r="H142" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: esperança em tempos difíceis 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #esperanca</t>
+          <t>Oração da noite: esperança em tempos difíceis 🌙 Para fechar o dia com Salmos 42:11. Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #esperanca</t>
         </is>
       </c>
       <c r="I142" s="2" t="inlineStr"/>
@@ -6598,7 +6598,7 @@
       </c>
       <c r="H143" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: esperança em tempos difíceis 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #esperanca</t>
+          <t>Oração da noite: esperança em tempos difíceis 🌙 Para fechar o dia com Isaías 43:19. Escreva amém se essa oração é sua também. #oracaodanoite #oracao #fe #esperanca</t>
         </is>
       </c>
       <c r="I143" s="2" t="inlineStr"/>
@@ -6641,7 +6641,7 @@
       </c>
       <c r="H144" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: esperança em tempos difíceis 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #esperanca</t>
+          <t>Oração da noite: esperança em tempos difíceis 🌙 Para fechar o dia com Romanos 5:3-5. Comente o nome de quem você quer colocar nesta oração. #oracaodanoite #oracao #fe #esperanca</t>
         </is>
       </c>
       <c r="I144" s="2" t="inlineStr"/>
@@ -6684,7 +6684,7 @@
       </c>
       <c r="H145" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: esperança em tempos difíceis 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #esperanca</t>
+          <t>Oração da noite: esperança em tempos difíceis 🌙 Para fechar o dia com 2 Coríntios 4:16-18. Conte nos comentários pelo que você quer agradecer hoje. #oracaodanoite #oracao #fe #esperanca</t>
         </is>
       </c>
       <c r="I145" s="2" t="inlineStr"/>
@@ -6727,7 +6727,7 @@
       </c>
       <c r="H146" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: esperança em tempos difíceis 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #esperanca</t>
+          <t>Oração da noite: esperança em tempos difíceis 🌙 Para fechar o dia com Salmos 30:5. Deixe nos comentários o que você quer entregar a Deus esta noite. #oracaodanoite #oracao #fe #esperanca</t>
         </is>
       </c>
       <c r="I146" s="2" t="inlineStr"/>
@@ -6770,7 +6770,7 @@
       </c>
       <c r="H147" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: esperança em tempos difíceis 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #esperanca</t>
+          <t>Oração da noite: esperança em tempos difíceis 🌙 Para fechar o dia com Habacuque 3:17-18. Marque alguém que precisa ouvir esta oração. #oracaodanoite #oracao #fe #esperanca</t>
         </is>
       </c>
       <c r="I147" s="2" t="inlineStr"/>
@@ -6813,7 +6813,7 @@
       </c>
       <c r="H148" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: esperança em tempos difíceis 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #esperanca</t>
+          <t>Oração da noite: esperança em tempos difíceis 🌙 Para fechar o dia com Hebreus 6:19. Comente seu pedido. Vamos orar juntos. #oracaodanoite #oracao #fe #esperanca</t>
         </is>
       </c>
       <c r="I148" s="2" t="inlineStr"/>
@@ -6856,7 +6856,7 @@
       </c>
       <c r="H149" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: esperança em tempos difíceis 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #esperanca</t>
+          <t>Oração da noite: esperança em tempos difíceis 🌙 Para fechar o dia com Salmos 40:1-2. Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #esperanca</t>
         </is>
       </c>
       <c r="I149" s="2" t="inlineStr"/>
@@ -6899,7 +6899,7 @@
       </c>
       <c r="H150" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: esperança em tempos difíceis 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #esperanca</t>
+          <t>Oração da noite: esperança em tempos difíceis 🌙 Para fechar o dia com Isaías 61:3. Escreva amém se essa oração é sua também. #oracaodanoite #oracao #fe #esperanca</t>
         </is>
       </c>
       <c r="I150" s="2" t="inlineStr"/>
@@ -6942,7 +6942,7 @@
       </c>
       <c r="H151" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: esperança em tempos difíceis 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #esperanca</t>
+          <t>Oração da noite: esperança em tempos difíceis 🌙 Para fechar o dia com Romanos 8:18. Comente o nome de quem você quer colocar nesta oração. #oracaodanoite #oracao #fe #esperanca</t>
         </is>
       </c>
       <c r="I151" s="2" t="inlineStr"/>
@@ -6985,7 +6985,7 @@
       </c>
       <c r="H152" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: esperança em tempos difíceis 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #esperanca</t>
+          <t>Oração da noite: esperança em tempos difíceis 🌙 Para fechar o dia com Miqueias 7:8. Conte nos comentários pelo que você quer agradecer hoje. #oracaodanoite #oracao #fe #esperanca</t>
         </is>
       </c>
       <c r="I152" s="2" t="inlineStr"/>
@@ -7028,7 +7028,7 @@
       </c>
       <c r="H153" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: esperança em tempos difíceis 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #esperanca</t>
+          <t>Oração da noite: esperança em tempos difíceis 🌙 Para fechar o dia com Salmos 147:3. Deixe nos comentários o que você quer entregar a Deus esta noite. #oracaodanoite #oracao #fe #esperanca</t>
         </is>
       </c>
       <c r="I153" s="2" t="inlineStr"/>
@@ -7071,7 +7071,7 @@
       </c>
       <c r="H154" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: esperança em tempos difíceis 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #esperanca</t>
+          <t>Oração da noite: esperança em tempos difíceis 🌙 Para fechar o dia com Joel 2:25. Marque alguém que precisa ouvir esta oração. #oracaodanoite #oracao #fe #esperanca</t>
         </is>
       </c>
       <c r="I154" s="2" t="inlineStr"/>
@@ -7114,7 +7114,7 @@
       </c>
       <c r="H155" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: esperança em tempos difíceis 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #esperanca</t>
+          <t>Oração da noite: esperança em tempos difíceis 🌙 Para fechar o dia com Jó 42:10. Comente seu pedido. Vamos orar juntos. #oracaodanoite #oracao #fe #esperanca</t>
         </is>
       </c>
       <c r="I155" s="2" t="inlineStr"/>
@@ -7157,7 +7157,7 @@
       </c>
       <c r="H156" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: esperança em tempos difíceis 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #esperanca</t>
+          <t>Oração da noite: esperança em tempos difíceis 🌙 Para fechar o dia com Salmos 34:18. Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #esperanca</t>
         </is>
       </c>
       <c r="I156" s="2" t="inlineStr"/>
@@ -7200,7 +7200,7 @@
       </c>
       <c r="H157" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: esperança em tempos difíceis 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #esperanca</t>
+          <t>Oração da noite: esperança em tempos difíceis 🌙 Para fechar o dia com Apocalipse 21:4. Escreva amém se essa oração é sua também. #oracaodanoite #oracao #fe #esperanca</t>
         </is>
       </c>
       <c r="I157" s="2" t="inlineStr"/>
@@ -7243,7 +7243,7 @@
       </c>
       <c r="H158" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: esperança em tempos difíceis 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #esperanca</t>
+          <t>Oração da noite: esperança em tempos difíceis 🌙 Para fechar o dia com Romanos 12:12. Comente o nome de quem você quer colocar nesta oração. #oracaodanoite #oracao #fe #esperanca</t>
         </is>
       </c>
       <c r="I158" s="2" t="inlineStr"/>
@@ -7286,7 +7286,7 @@
       </c>
       <c r="H159" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: esperança em tempos difíceis 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #esperanca</t>
+          <t>Oração da noite: esperança em tempos difíceis 🌙 Para fechar o dia com Isaías 40:29. Conte nos comentários pelo que você quer agradecer hoje. #oracaodanoite #oracao #fe #esperanca</t>
         </is>
       </c>
       <c r="I159" s="2" t="inlineStr"/>
@@ -7329,7 +7329,7 @@
       </c>
       <c r="H160" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: esperança em tempos difíceis 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #esperanca</t>
+          <t>Oração da noite: esperança em tempos difíceis 🌙 Para fechar o dia com Salmos 71:20. Deixe nos comentários o que você quer entregar a Deus esta noite. #oracaodanoite #oracao #fe #esperanca</t>
         </is>
       </c>
       <c r="I160" s="2" t="inlineStr"/>
@@ -7372,7 +7372,7 @@
       </c>
       <c r="H161" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: esperança em tempos difíceis 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #esperanca</t>
+          <t>Oração da noite: esperança em tempos difíceis 🌙 Para fechar o dia com 1 Pedro 1:3. Marque alguém que precisa ouvir esta oração. #oracaodanoite #oracao #fe #esperanca</t>
         </is>
       </c>
       <c r="I161" s="2" t="inlineStr"/>
@@ -7415,7 +7415,7 @@
       </c>
       <c r="H162" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: esperança em tempos difíceis 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #esperanca</t>
+          <t>Oração da noite: esperança em tempos difíceis 🌙 Para fechar o dia com Gênesis 50:20. Comente seu pedido. Vamos orar juntos. #oracaodanoite #oracao #fe #esperanca</t>
         </is>
       </c>
       <c r="I162" s="2" t="inlineStr"/>
@@ -7458,7 +7458,7 @@
       </c>
       <c r="H163" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: esperança em tempos difíceis 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #esperanca</t>
+          <t>Oração da noite: esperança em tempos difíceis 🌙 Para fechar o dia com Salmos 126:5-6. Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #esperanca</t>
         </is>
       </c>
       <c r="I163" s="2" t="inlineStr"/>
@@ -7501,7 +7501,7 @@
       </c>
       <c r="H164" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: esperança em tempos difíceis 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #esperanca</t>
+          <t>Oração da noite: esperança em tempos difíceis 🌙 Para fechar o dia com Isaías 9:2. Escreva amém se essa oração é sua também. #oracaodanoite #oracao #fe #esperanca</t>
         </is>
       </c>
       <c r="I164" s="2" t="inlineStr"/>
@@ -7544,7 +7544,7 @@
       </c>
       <c r="H165" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: esperança em tempos difíceis 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #esperanca</t>
+          <t>Oração da noite: esperança em tempos difíceis 🌙 Para fechar o dia com Salmos 62:5. Comente o nome de quem você quer colocar nesta oração. #oracaodanoite #oracao #fe #esperanca</t>
         </is>
       </c>
       <c r="I165" s="2" t="inlineStr"/>
@@ -7587,7 +7587,7 @@
       </c>
       <c r="H166" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: esperança em tempos difíceis 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #esperanca</t>
+          <t>Oração da noite: esperança em tempos difíceis 🌙 Para fechar o dia com Isaías 35:3-4. Conte nos comentários pelo que você quer agradecer hoje. #oracaodanoite #oracao #fe #esperanca</t>
         </is>
       </c>
       <c r="I166" s="2" t="inlineStr"/>
@@ -7630,7 +7630,7 @@
       </c>
       <c r="H167" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: esperança em tempos difíceis 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #esperanca</t>
+          <t>Oração da noite: esperança em tempos difíceis 🌙 Para fechar o dia com 2 Coríntios 4:8-9. Deixe nos comentários o que você quer entregar a Deus esta noite. #oracaodanoite #oracao #fe #esperanca</t>
         </is>
       </c>
       <c r="I167" s="2" t="inlineStr"/>
@@ -7673,7 +7673,7 @@
       </c>
       <c r="H168" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: esperança em tempos difíceis 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #esperanca</t>
+          <t>Oração da noite: esperança em tempos difíceis 🌙 Para fechar o dia com Salmos 33:20-22. Marque alguém que precisa ouvir esta oração. #oracaodanoite #oracao #fe #esperanca</t>
         </is>
       </c>
       <c r="I168" s="2" t="inlineStr"/>
@@ -7716,7 +7716,7 @@
       </c>
       <c r="H169" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: esperança em tempos difíceis 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #esperanca</t>
+          <t>Oração da noite: esperança em tempos difíceis 🌙 Para fechar o dia com Mateus 28:20. Comente seu pedido. Vamos orar juntos. #oracaodanoite #oracao #fe #esperanca</t>
         </is>
       </c>
       <c r="I169" s="2" t="inlineStr"/>
@@ -7759,7 +7759,7 @@
       </c>
       <c r="H170" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: perdão 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #perdao</t>
+          <t>Oração da noite: perdão 🌙 Para fechar o dia com Efésios 4:32. Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #perdao</t>
         </is>
       </c>
       <c r="I170" s="2" t="inlineStr"/>
@@ -7802,7 +7802,7 @@
       </c>
       <c r="H171" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: perdão 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #perdao</t>
+          <t>Oração da noite: perdão 🌙 Para fechar o dia com Colossenses 3:13. Escreva amém se essa oração é sua também. #oracaodanoite #oracao #fe #perdao</t>
         </is>
       </c>
       <c r="I171" s="2" t="inlineStr"/>
@@ -7845,7 +7845,7 @@
       </c>
       <c r="H172" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: perdão 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #perdao</t>
+          <t>Oração da noite: perdão 🌙 Para fechar o dia com Mateus 6:14-15. Comente o nome de quem você quer colocar nesta oração. #oracaodanoite #oracao #fe #perdao</t>
         </is>
       </c>
       <c r="I172" s="2" t="inlineStr"/>
@@ -7888,7 +7888,7 @@
       </c>
       <c r="H173" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: perdão 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #perdao</t>
+          <t>Oração da noite: perdão 🌙 Para fechar o dia com Mateus 18:21-22. Conte nos comentários pelo que você quer agradecer hoje. #oracaodanoite #oracao #fe #perdao</t>
         </is>
       </c>
       <c r="I173" s="2" t="inlineStr"/>
@@ -7931,7 +7931,7 @@
       </c>
       <c r="H174" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: perdão 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #perdao</t>
+          <t>Oração da noite: perdão 🌙 Para fechar o dia com 1 João 1:9. Deixe nos comentários o que você quer entregar a Deus esta noite. #oracaodanoite #oracao #fe #perdao</t>
         </is>
       </c>
       <c r="I174" s="2" t="inlineStr"/>
@@ -7974,7 +7974,7 @@
       </c>
       <c r="H175" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: perdão 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #perdao</t>
+          <t>Oração da noite: perdão 🌙 Para fechar o dia com Salmos 103:12. Marque alguém que precisa ouvir esta oração. #oracaodanoite #oracao #fe #perdao</t>
         </is>
       </c>
       <c r="I175" s="2" t="inlineStr"/>
@@ -8017,7 +8017,7 @@
       </c>
       <c r="H176" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: perdão 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #perdao</t>
+          <t>Oração da noite: perdão 🌙 Para fechar o dia com Isaías 1:18. Comente seu pedido. Vamos orar juntos. #oracaodanoite #oracao #fe #perdao</t>
         </is>
       </c>
       <c r="I176" s="2" t="inlineStr"/>
@@ -8060,7 +8060,7 @@
       </c>
       <c r="H177" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: perdão 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #perdao</t>
+          <t>Oração da noite: perdão 🌙 Para fechar o dia com Lucas 15:20. Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #perdao</t>
         </is>
       </c>
       <c r="I177" s="2" t="inlineStr"/>
@@ -8103,7 +8103,7 @@
       </c>
       <c r="H178" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: perdão 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #perdao</t>
+          <t>Oração da noite: perdão 🌙 Para fechar o dia com Lucas 23:34. Escreva amém se essa oração é sua também. #oracaodanoite #oracao #fe #perdao</t>
         </is>
       </c>
       <c r="I178" s="2" t="inlineStr"/>
@@ -8146,7 +8146,7 @@
       </c>
       <c r="H179" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: perdão 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #perdao</t>
+          <t>Oração da noite: perdão 🌙 Para fechar o dia com Miqueias 7:18-19. Comente o nome de quem você quer colocar nesta oração. #oracaodanoite #oracao #fe #perdao</t>
         </is>
       </c>
       <c r="I179" s="2" t="inlineStr"/>
@@ -8189,7 +8189,7 @@
       </c>
       <c r="H180" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: perdão 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #perdao</t>
+          <t>Oração da noite: perdão 🌙 Para fechar o dia com Romanos 12:17-19. Conte nos comentários pelo que você quer agradecer hoje. #oracaodanoite #oracao #fe #perdao</t>
         </is>
       </c>
       <c r="I180" s="2" t="inlineStr"/>
@@ -8232,7 +8232,7 @@
       </c>
       <c r="H181" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: perdão 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #perdao</t>
+          <t>Oração da noite: perdão 🌙 Para fechar o dia com Salmos 32:1-2. Deixe nos comentários o que você quer entregar a Deus esta noite. #oracaodanoite #oracao #fe #perdao</t>
         </is>
       </c>
       <c r="I181" s="2" t="inlineStr"/>
@@ -8275,7 +8275,7 @@
       </c>
       <c r="H182" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: perdão 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #perdao</t>
+          <t>Oração da noite: perdão 🌙 Para fechar o dia com Marcos 11:25. Marque alguém que precisa ouvir esta oração. #oracaodanoite #oracao #fe #perdao</t>
         </is>
       </c>
       <c r="I182" s="2" t="inlineStr"/>
@@ -8318,7 +8318,7 @@
       </c>
       <c r="H183" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: perdão 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #perdao</t>
+          <t>Oração da noite: perdão 🌙 Para fechar o dia com Hebreus 8:12. Comente seu pedido. Vamos orar juntos. #oracaodanoite #oracao #fe #perdao</t>
         </is>
       </c>
       <c r="I183" s="2" t="inlineStr"/>
@@ -8361,7 +8361,7 @@
       </c>
       <c r="H184" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: perdão 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #perdao</t>
+          <t>Oração da noite: perdão 🌙 Para fechar o dia com Gênesis 45:4-5. Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #perdao</t>
         </is>
       </c>
       <c r="I184" s="2" t="inlineStr"/>
@@ -8404,7 +8404,7 @@
       </c>
       <c r="H185" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: perdão 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #perdao</t>
+          <t>Oração da noite: perdão 🌙 Para fechar o dia com Provérbios 19:11. Escreva amém se essa oração é sua também. #oracaodanoite #oracao #fe #perdao</t>
         </is>
       </c>
       <c r="I185" s="2" t="inlineStr"/>
@@ -8447,7 +8447,7 @@
       </c>
       <c r="H186" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: perdão 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #perdao</t>
+          <t>Oração da noite: perdão 🌙 Para fechar o dia com 2 Coríntios 5:17. Comente o nome de quem você quer colocar nesta oração. #oracaodanoite #oracao #fe #perdao</t>
         </is>
       </c>
       <c r="I186" s="2" t="inlineStr"/>
@@ -8490,7 +8490,7 @@
       </c>
       <c r="H187" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: perdão 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #perdao</t>
+          <t>Oração da noite: perdão 🌙 Para fechar o dia com Romanos 8:1. Conte nos comentários pelo que você quer agradecer hoje. #oracaodanoite #oracao #fe #perdao</t>
         </is>
       </c>
       <c r="I187" s="2" t="inlineStr"/>
@@ -8533,7 +8533,7 @@
       </c>
       <c r="H188" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: perdão 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #perdao</t>
+          <t>Oração da noite: perdão 🌙 Para fechar o dia com Lucas 6:37. Deixe nos comentários o que você quer entregar a Deus esta noite. #oracaodanoite #oracao #fe #perdao</t>
         </is>
       </c>
       <c r="I188" s="2" t="inlineStr"/>
@@ -8576,7 +8576,7 @@
       </c>
       <c r="H189" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: perdão 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #perdao</t>
+          <t>Oração da noite: perdão 🌙 Para fechar o dia com Salmos 51:10. Marque alguém que precisa ouvir esta oração. #oracaodanoite #oracao #fe #perdao</t>
         </is>
       </c>
       <c r="I189" s="2" t="inlineStr"/>
@@ -8619,7 +8619,7 @@
       </c>
       <c r="H190" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: perdão 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #perdao</t>
+          <t>Oração da noite: perdão 🌙 Para fechar o dia com Atos 3:19. Comente seu pedido. Vamos orar juntos. #oracaodanoite #oracao #fe #perdao</t>
         </is>
       </c>
       <c r="I190" s="2" t="inlineStr"/>
@@ -8662,7 +8662,7 @@
       </c>
       <c r="H191" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: perdão 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #perdao</t>
+          <t>Oração da noite: perdão 🌙 Para fechar o dia com Mateus 5:23-24. Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #perdao</t>
         </is>
       </c>
       <c r="I191" s="2" t="inlineStr"/>
@@ -8705,7 +8705,7 @@
       </c>
       <c r="H192" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: perdão 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #perdao</t>
+          <t>Oração da noite: perdão 🌙 Para fechar o dia com Efésios 4:26-27. Escreva amém se essa oração é sua também. #oracaodanoite #oracao #fe #perdao</t>
         </is>
       </c>
       <c r="I192" s="2" t="inlineStr"/>
@@ -8748,7 +8748,7 @@
       </c>
       <c r="H193" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: perdão 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #perdao</t>
+          <t>Oração da noite: perdão 🌙 Para fechar o dia com Lucas 7:47. Comente o nome de quem você quer colocar nesta oração. #oracaodanoite #oracao #fe #perdao</t>
         </is>
       </c>
       <c r="I193" s="2" t="inlineStr"/>
@@ -8791,7 +8791,7 @@
       </c>
       <c r="H194" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: perdão 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #perdao</t>
+          <t>Oração da noite: perdão 🌙 Para fechar o dia com João 8:10-11. Conte nos comentários pelo que você quer agradecer hoje. #oracaodanoite #oracao #fe #perdao</t>
         </is>
       </c>
       <c r="I194" s="2" t="inlineStr"/>
@@ -8834,7 +8834,7 @@
       </c>
       <c r="H195" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: perdão 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #perdao</t>
+          <t>Oração da noite: perdão 🌙 Para fechar o dia com Isaías 43:25. Deixe nos comentários o que você quer entregar a Deus esta noite. #oracaodanoite #oracao #fe #perdao</t>
         </is>
       </c>
       <c r="I195" s="2" t="inlineStr"/>
@@ -8877,7 +8877,7 @@
       </c>
       <c r="H196" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: perdão 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #perdao</t>
+          <t>Oração da noite: perdão 🌙 Para fechar o dia com Salmos 130:3-4. Marque alguém que precisa ouvir esta oração. #oracaodanoite #oracao #fe #perdao</t>
         </is>
       </c>
       <c r="I196" s="2" t="inlineStr"/>
@@ -8920,7 +8920,7 @@
       </c>
       <c r="H197" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: perdão 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #perdao</t>
+          <t>Oração da noite: perdão 🌙 Para fechar o dia com Colossenses 2:13-14. Comente seu pedido. Vamos orar juntos. #oracaodanoite #oracao #fe #perdao</t>
         </is>
       </c>
       <c r="I197" s="2" t="inlineStr"/>
@@ -8963,7 +8963,7 @@
       </c>
       <c r="H198" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: perdão 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #perdao</t>
+          <t>Oração da noite: perdão 🌙 Para fechar o dia com 1 Pedro 3:9. Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #perdao</t>
         </is>
       </c>
       <c r="I198" s="2" t="inlineStr"/>
@@ -9006,7 +9006,7 @@
       </c>
       <c r="H199" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: perdão 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #perdao</t>
+          <t>Oração da noite: perdão 🌙 Para fechar o dia com Lucas 17:3-4. Escreva amém se essa oração é sua também. #oracaodanoite #oracao #fe #perdao</t>
         </is>
       </c>
       <c r="I199" s="2" t="inlineStr"/>
@@ -9049,7 +9049,7 @@
       </c>
       <c r="H200" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: família e relacionamentos 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #familia</t>
+          <t>Oração da noite: família e relacionamentos 🌙 Para fechar o dia com Josué 24:15. Comente o nome de quem você quer colocar nesta oração. #oracaodanoite #oracao #fe #familia</t>
         </is>
       </c>
       <c r="I200" s="2" t="inlineStr"/>
@@ -9092,7 +9092,7 @@
       </c>
       <c r="H201" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: família e relacionamentos 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #familia</t>
+          <t>Oração da noite: família e relacionamentos 🌙 Para fechar o dia com Salmos 127:1. Conte nos comentários pelo que você quer agradecer hoje. #oracaodanoite #oracao #fe #familia</t>
         </is>
       </c>
       <c r="I201" s="2" t="inlineStr"/>
@@ -9135,7 +9135,7 @@
       </c>
       <c r="H202" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: família e relacionamentos 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #familia</t>
+          <t>Oração da noite: família e relacionamentos 🌙 Para fechar o dia com Provérbios 22:6. Deixe nos comentários o que você quer entregar a Deus esta noite. #oracaodanoite #oracao #fe #familia</t>
         </is>
       </c>
       <c r="I202" s="2" t="inlineStr"/>
@@ -9178,7 +9178,7 @@
       </c>
       <c r="H203" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: família e relacionamentos 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #familia</t>
+          <t>Oração da noite: família e relacionamentos 🌙 Para fechar o dia com Efésios 6:1-3. Marque alguém que precisa ouvir esta oração. #oracaodanoite #oracao #fe #familia</t>
         </is>
       </c>
       <c r="I203" s="2" t="inlineStr"/>
@@ -9221,7 +9221,7 @@
       </c>
       <c r="H204" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: família e relacionamentos 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #familia</t>
+          <t>Oração da noite: família e relacionamentos 🌙 Para fechar o dia com Eclesiastes 4:9-10. Comente seu pedido. Vamos orar juntos. #oracaodanoite #oracao #fe #familia</t>
         </is>
       </c>
       <c r="I204" s="2" t="inlineStr"/>
@@ -9264,7 +9264,7 @@
       </c>
       <c r="H205" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: família e relacionamentos 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #familia</t>
+          <t>Oração da noite: família e relacionamentos 🌙 Para fechar o dia com Eclesiastes 4:12. Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #familia</t>
         </is>
       </c>
       <c r="I205" s="2" t="inlineStr"/>
@@ -9307,7 +9307,7 @@
       </c>
       <c r="H206" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: família e relacionamentos 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #familia</t>
+          <t>Oração da noite: família e relacionamentos 🌙 Para fechar o dia com Rute 1:16-17. Escreva amém se essa oração é sua também. #oracaodanoite #oracao #fe #familia</t>
         </is>
       </c>
       <c r="I206" s="2" t="inlineStr"/>
@@ -9350,7 +9350,7 @@
       </c>
       <c r="H207" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: família e relacionamentos 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #familia</t>
+          <t>Oração da noite: família e relacionamentos 🌙 Para fechar o dia com Provérbios 17:17. Comente o nome de quem você quer colocar nesta oração. #oracaodanoite #oracao #fe #familia</t>
         </is>
       </c>
       <c r="I207" s="2" t="inlineStr"/>
@@ -9393,7 +9393,7 @@
       </c>
       <c r="H208" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: família e relacionamentos 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #familia</t>
+          <t>Oração da noite: família e relacionamentos 🌙 Para fechar o dia com Colossenses 3:14. Conte nos comentários pelo que você quer agradecer hoje. #oracaodanoite #oracao #fe #familia</t>
         </is>
       </c>
       <c r="I208" s="2" t="inlineStr"/>
@@ -9436,7 +9436,7 @@
       </c>
       <c r="H209" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: família e relacionamentos 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #familia</t>
+          <t>Oração da noite: família e relacionamentos 🌙 Para fechar o dia com 1 Coríntios 13:4-5. Deixe nos comentários o que você quer entregar a Deus esta noite. #oracaodanoite #oracao #fe #familia</t>
         </is>
       </c>
       <c r="I209" s="2" t="inlineStr"/>
@@ -9479,7 +9479,7 @@
       </c>
       <c r="H210" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: família e relacionamentos 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #familia</t>
+          <t>Oração da noite: família e relacionamentos 🌙 Para fechar o dia com Gênesis 2:24. Marque alguém que precisa ouvir esta oração. #oracaodanoite #oracao #fe #familia</t>
         </is>
       </c>
       <c r="I210" s="2" t="inlineStr"/>
@@ -9522,7 +9522,7 @@
       </c>
       <c r="H211" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: família e relacionamentos 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #familia</t>
+          <t>Oração da noite: família e relacionamentos 🌙 Para fechar o dia com Provérbios 31:10-11. Comente seu pedido. Vamos orar juntos. #oracaodanoite #oracao #fe #familia</t>
         </is>
       </c>
       <c r="I211" s="2" t="inlineStr"/>
@@ -9565,7 +9565,7 @@
       </c>
       <c r="H212" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: família e relacionamentos 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #familia</t>
+          <t>Oração da noite: família e relacionamentos 🌙 Para fechar o dia com Efésios 5:25. Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #familia</t>
         </is>
       </c>
       <c r="I212" s="2" t="inlineStr"/>
@@ -9608,7 +9608,7 @@
       </c>
       <c r="H213" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: família e relacionamentos 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #familia</t>
+          <t>Oração da noite: família e relacionamentos 🌙 Para fechar o dia com Salmos 133:1. Escreva amém se essa oração é sua também. #oracaodanoite #oracao #fe #familia</t>
         </is>
       </c>
       <c r="I213" s="2" t="inlineStr"/>
@@ -9651,7 +9651,7 @@
       </c>
       <c r="H214" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: família e relacionamentos 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #familia</t>
+          <t>Oração da noite: família e relacionamentos 🌙 Para fechar o dia com Provérbios 15:1. Comente o nome de quem você quer colocar nesta oração. #oracaodanoite #oracao #fe #familia</t>
         </is>
       </c>
       <c r="I214" s="2" t="inlineStr"/>
@@ -9694,7 +9694,7 @@
       </c>
       <c r="H215" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: família e relacionamentos 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #familia</t>
+          <t>Oração da noite: família e relacionamentos 🌙 Para fechar o dia com Tiago 1:19. Conte nos comentários pelo que você quer agradecer hoje. #oracaodanoite #oracao #fe #familia</t>
         </is>
       </c>
       <c r="I215" s="2" t="inlineStr"/>
@@ -9737,7 +9737,7 @@
       </c>
       <c r="H216" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: família e relacionamentos 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #familia</t>
+          <t>Oração da noite: família e relacionamentos 🌙 Para fechar o dia com 1 Pedro 4:8. Deixe nos comentários o que você quer entregar a Deus esta noite. #oracaodanoite #oracao #fe #familia</t>
         </is>
       </c>
       <c r="I216" s="2" t="inlineStr"/>
@@ -9780,7 +9780,7 @@
       </c>
       <c r="H217" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: família e relacionamentos 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #familia</t>
+          <t>Oração da noite: família e relacionamentos 🌙 Para fechar o dia com Malaquias 4:6. Marque alguém que precisa ouvir esta oração. #oracaodanoite #oracao #fe #familia</t>
         </is>
       </c>
       <c r="I217" s="2" t="inlineStr"/>
@@ -9823,7 +9823,7 @@
       </c>
       <c r="H218" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: família e relacionamentos 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #familia</t>
+          <t>Oração da noite: família e relacionamentos 🌙 Para fechar o dia com Salmos 68:6. Comente seu pedido. Vamos orar juntos. #oracaodanoite #oracao #fe #familia</t>
         </is>
       </c>
       <c r="I218" s="2" t="inlineStr"/>
@@ -9866,7 +9866,7 @@
       </c>
       <c r="H219" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: família e relacionamentos 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #familia</t>
+          <t>Oração da noite: família e relacionamentos 🌙 Para fechar o dia com Provérbios 27:17. Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #familia</t>
         </is>
       </c>
       <c r="I219" s="2" t="inlineStr"/>
@@ -9909,7 +9909,7 @@
       </c>
       <c r="H220" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: família e relacionamentos 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #familia</t>
+          <t>Oração da noite: família e relacionamentos 🌙 Para fechar o dia com Romanos 12:10. Escreva amém se essa oração é sua também. #oracaodanoite #oracao #fe #familia</t>
         </is>
       </c>
       <c r="I220" s="2" t="inlineStr"/>
@@ -9952,7 +9952,7 @@
       </c>
       <c r="H221" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: família e relacionamentos 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #familia</t>
+          <t>Oração da noite: família e relacionamentos 🌙 Para fechar o dia com 1 Tessalonicenses 5:11. Comente o nome de quem você quer colocar nesta oração. #oracaodanoite #oracao #fe #familia</t>
         </is>
       </c>
       <c r="I221" s="2" t="inlineStr"/>
@@ -9995,7 +9995,7 @@
       </c>
       <c r="H222" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: família e relacionamentos 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #familia</t>
+          <t>Oração da noite: família e relacionamentos 🌙 Para fechar o dia com Lucas 2:51-52. Conte nos comentários pelo que você quer agradecer hoje. #oracaodanoite #oracao #fe #familia</t>
         </is>
       </c>
       <c r="I222" s="2" t="inlineStr"/>
@@ -10038,7 +10038,7 @@
       </c>
       <c r="H223" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: família e relacionamentos 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #familia</t>
+          <t>Oração da noite: família e relacionamentos 🌙 Para fechar o dia com Provérbios 18:24. Deixe nos comentários o que você quer entregar a Deus esta noite. #oracaodanoite #oracao #fe #familia</t>
         </is>
       </c>
       <c r="I223" s="2" t="inlineStr"/>
@@ -10081,7 +10081,7 @@
       </c>
       <c r="H224" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: família e relacionamentos 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #familia</t>
+          <t>Oração da noite: família e relacionamentos 🌙 Para fechar o dia com João 15:13. Marque alguém que precisa ouvir esta oração. #oracaodanoite #oracao #fe #familia</t>
         </is>
       </c>
       <c r="I224" s="2" t="inlineStr"/>
@@ -10124,7 +10124,7 @@
       </c>
       <c r="H225" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: família e relacionamentos 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #familia</t>
+          <t>Oração da noite: família e relacionamentos 🌙 Para fechar o dia com Gálatas 6:2. Comente seu pedido. Vamos orar juntos. #oracaodanoite #oracao #fe #familia</t>
         </is>
       </c>
       <c r="I225" s="2" t="inlineStr"/>
@@ -10167,7 +10167,7 @@
       </c>
       <c r="H226" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: família e relacionamentos 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #familia</t>
+          <t>Oração da noite: família e relacionamentos 🌙 Para fechar o dia com Filipenses 2:3-4. Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #familia</t>
         </is>
       </c>
       <c r="I226" s="2" t="inlineStr"/>
@@ -10210,7 +10210,7 @@
       </c>
       <c r="H227" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: família e relacionamentos 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #familia</t>
+          <t>Oração da noite: família e relacionamentos 🌙 Para fechar o dia com Salmos 103:13. Escreva amém se essa oração é sua também. #oracaodanoite #oracao #fe #familia</t>
         </is>
       </c>
       <c r="I227" s="2" t="inlineStr"/>
@@ -10253,7 +10253,7 @@
       </c>
       <c r="H228" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: família e relacionamentos 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #familia</t>
+          <t>Oração da noite: família e relacionamentos 🌙 Para fechar o dia com Isaías 49:15. Comente o nome de quem você quer colocar nesta oração. #oracaodanoite #oracao #fe #familia</t>
         </is>
       </c>
       <c r="I228" s="2" t="inlineStr"/>
@@ -10296,7 +10296,7 @@
       </c>
       <c r="H229" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: família e relacionamentos 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #familia</t>
+          <t>Oração da noite: família e relacionamentos 🌙 Para fechar o dia com 1 João 4:11. Conte nos comentários pelo que você quer agradecer hoje. #oracaodanoite #oracao #fe #familia</t>
         </is>
       </c>
       <c r="I229" s="2" t="inlineStr"/>
@@ -10339,7 +10339,7 @@
       </c>
       <c r="H230" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: família e relacionamentos 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #familia</t>
+          <t>Oração da noite: família e relacionamentos 🌙 Para fechar o dia com Hebreus 13:1. Deixe nos comentários o que você quer entregar a Deus esta noite. #oracaodanoite #oracao #fe #familia</t>
         </is>
       </c>
       <c r="I230" s="2" t="inlineStr"/>
@@ -10382,7 +10382,7 @@
       </c>
       <c r="H231" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: gratidão 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #gratidao</t>
+          <t>Oração da noite: gratidão 🌙 Para fechar o dia com 1 Tessalonicenses 5:18. Marque alguém que precisa ouvir esta oração. #oracaodanoite #oracao #fe #gratidao</t>
         </is>
       </c>
       <c r="I231" s="2" t="inlineStr"/>
@@ -10425,7 +10425,7 @@
       </c>
       <c r="H232" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: gratidão 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #gratidao</t>
+          <t>Oração da noite: gratidão 🌙 Para fechar o dia com Salmos 118:24. Comente seu pedido. Vamos orar juntos. #oracaodanoite #oracao #fe #gratidao</t>
         </is>
       </c>
       <c r="I232" s="2" t="inlineStr"/>
@@ -10468,7 +10468,7 @@
       </c>
       <c r="H233" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: gratidão 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #gratidao</t>
+          <t>Oração da noite: gratidão 🌙 Para fechar o dia com Salmos 100:4. Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #gratidao</t>
         </is>
       </c>
       <c r="I233" s="2" t="inlineStr"/>
@@ -10511,7 +10511,7 @@
       </c>
       <c r="H234" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: gratidão 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #gratidao</t>
+          <t>Oração da noite: gratidão 🌙 Para fechar o dia com Colossenses 3:15. Escreva amém se essa oração é sua também. #oracaodanoite #oracao #fe #gratidao</t>
         </is>
       </c>
       <c r="I234" s="2" t="inlineStr"/>
@@ -10554,7 +10554,7 @@
       </c>
       <c r="H235" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: gratidão 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #gratidao</t>
+          <t>Oração da noite: gratidão 🌙 Para fechar o dia com Salmos 103:2. Comente o nome de quem você quer colocar nesta oração. #oracaodanoite #oracao #fe #gratidao</t>
         </is>
       </c>
       <c r="I235" s="2" t="inlineStr"/>
@@ -10597,7 +10597,7 @@
       </c>
       <c r="H236" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: gratidão 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #gratidao</t>
+          <t>Oração da noite: gratidão 🌙 Para fechar o dia com Lucas 17:15-16. Conte nos comentários pelo que você quer agradecer hoje. #oracaodanoite #oracao #fe #gratidao</t>
         </is>
       </c>
       <c r="I236" s="2" t="inlineStr"/>
@@ -10640,7 +10640,7 @@
       </c>
       <c r="H237" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: gratidão 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #gratidao</t>
+          <t>Oração da noite: gratidão 🌙 Para fechar o dia com Tiago 1:17. Deixe nos comentários o que você quer entregar a Deus esta noite. #oracaodanoite #oracao #fe #gratidao</t>
         </is>
       </c>
       <c r="I237" s="2" t="inlineStr"/>
@@ -10683,7 +10683,7 @@
       </c>
       <c r="H238" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: gratidão 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #gratidao</t>
+          <t>Oração da noite: gratidão 🌙 Para fechar o dia com Salmos 136:1. Marque alguém que precisa ouvir esta oração. #oracaodanoite #oracao #fe #gratidao</t>
         </is>
       </c>
       <c r="I238" s="2" t="inlineStr"/>
@@ -10726,7 +10726,7 @@
       </c>
       <c r="H239" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: gratidão 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #gratidao</t>
+          <t>Oração da noite: gratidão 🌙 Para fechar o dia com Filipenses 4:11-12. Comente seu pedido. Vamos orar juntos. #oracaodanoite #oracao #fe #gratidao</t>
         </is>
       </c>
       <c r="I239" s="2" t="inlineStr"/>
@@ -10769,7 +10769,7 @@
       </c>
       <c r="H240" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: gratidão 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #gratidao</t>
+          <t>Oração da noite: gratidão 🌙 Para fechar o dia com Salmos 9:1. Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #gratidao</t>
         </is>
       </c>
       <c r="I240" s="2" t="inlineStr"/>
@@ -10812,7 +10812,7 @@
       </c>
       <c r="H241" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: gratidão 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #gratidao</t>
+          <t>Oração da noite: gratidão 🌙 Para fechar o dia com Salmos 107:1. Escreva amém se essa oração é sua também. #oracaodanoite #oracao #fe #gratidao</t>
         </is>
       </c>
       <c r="I241" s="2" t="inlineStr"/>
@@ -10855,7 +10855,7 @@
       </c>
       <c r="H242" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: gratidão 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #gratidao</t>
+          <t>Oração da noite: gratidão 🌙 Para fechar o dia com Efésios 5:20. Comente o nome de quem você quer colocar nesta oração. #oracaodanoite #oracao #fe #gratidao</t>
         </is>
       </c>
       <c r="I242" s="2" t="inlineStr"/>
@@ -10898,7 +10898,7 @@
       </c>
       <c r="H243" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: gratidão 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #gratidao</t>
+          <t>Oração da noite: gratidão 🌙 Para fechar o dia com Hebreus 12:28. Conte nos comentários pelo que você quer agradecer hoje. #oracaodanoite #oracao #fe #gratidao</t>
         </is>
       </c>
       <c r="I243" s="2" t="inlineStr"/>
@@ -10941,7 +10941,7 @@
       </c>
       <c r="H244" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: gratidão 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #gratidao</t>
+          <t>Oração da noite: gratidão 🌙 Para fechar o dia com Salmos 92:1-2. Deixe nos comentários o que você quer entregar a Deus esta noite. #oracaodanoite #oracao #fe #gratidao</t>
         </is>
       </c>
       <c r="I244" s="2" t="inlineStr"/>
@@ -10984,7 +10984,7 @@
       </c>
       <c r="H245" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: gratidão 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #gratidao</t>
+          <t>Oração da noite: gratidão 🌙 Para fechar o dia com 1 Crônicas 16:34. Marque alguém que precisa ouvir esta oração. #oracaodanoite #oracao #fe #gratidao</t>
         </is>
       </c>
       <c r="I245" s="2" t="inlineStr"/>
@@ -11027,7 +11027,7 @@
       </c>
       <c r="H246" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: gratidão 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #gratidao</t>
+          <t>Oração da noite: gratidão 🌙 Para fechar o dia com 2 Coríntios 9:15. Comente seu pedido. Vamos orar juntos. #oracaodanoite #oracao #fe #gratidao</t>
         </is>
       </c>
       <c r="I246" s="2" t="inlineStr"/>
@@ -11070,7 +11070,7 @@
       </c>
       <c r="H247" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: gratidão 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #gratidao</t>
+          <t>Oração da noite: gratidão 🌙 Para fechar o dia com Salmos 34:1. Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #gratidao</t>
         </is>
       </c>
       <c r="I247" s="2" t="inlineStr"/>
@@ -11113,7 +11113,7 @@
       </c>
       <c r="H248" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: gratidão 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #gratidao</t>
+          <t>Oração da noite: gratidão 🌙 Para fechar o dia com Daniel 6:10. Escreva amém se essa oração é sua também. #oracaodanoite #oracao #fe #gratidao</t>
         </is>
       </c>
       <c r="I248" s="2" t="inlineStr"/>
@@ -11156,7 +11156,7 @@
       </c>
       <c r="H249" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: gratidão 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #gratidao</t>
+          <t>Oração da noite: gratidão 🌙 Para fechar o dia com Salmos 50:23. Comente o nome de quem você quer colocar nesta oração. #oracaodanoite #oracao #fe #gratidao</t>
         </is>
       </c>
       <c r="I249" s="2" t="inlineStr"/>
@@ -11199,7 +11199,7 @@
       </c>
       <c r="H250" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: gratidão 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #gratidao</t>
+          <t>Oração da noite: gratidão 🌙 Para fechar o dia com Romanos 1:21. Conte nos comentários pelo que você quer agradecer hoje. #oracaodanoite #oracao #fe #gratidao</t>
         </is>
       </c>
       <c r="I250" s="2" t="inlineStr"/>
@@ -11242,7 +11242,7 @@
       </c>
       <c r="H251" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: gratidão 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #gratidao</t>
+          <t>Oração da noite: gratidão 🌙 Para fechar o dia com Salmos 16:6. Deixe nos comentários o que você quer entregar a Deus esta noite. #oracaodanoite #oracao #fe #gratidao</t>
         </is>
       </c>
       <c r="I251" s="2" t="inlineStr"/>
@@ -11285,7 +11285,7 @@
       </c>
       <c r="H252" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: gratidão 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #gratidao</t>
+          <t>Oração da noite: gratidão 🌙 Para fechar o dia com Salmos 145:9. Marque alguém que precisa ouvir esta oração. #oracaodanoite #oracao #fe #gratidao</t>
         </is>
       </c>
       <c r="I252" s="2" t="inlineStr"/>
@@ -11328,7 +11328,7 @@
       </c>
       <c r="H253" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: gratidão 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #gratidao</t>
+          <t>Oração da noite: gratidão 🌙 Para fechar o dia com João 6:11. Comente seu pedido. Vamos orar juntos. #oracaodanoite #oracao #fe #gratidao</t>
         </is>
       </c>
       <c r="I253" s="2" t="inlineStr"/>
@@ -11371,7 +11371,7 @@
       </c>
       <c r="H254" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: gratidão 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #gratidao</t>
+          <t>Oração da noite: gratidão 🌙 Para fechar o dia com Salmos 95:2. Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #gratidao</t>
         </is>
       </c>
       <c r="I254" s="2" t="inlineStr"/>
@@ -11414,7 +11414,7 @@
       </c>
       <c r="H255" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: gratidão 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #gratidao</t>
+          <t>Oração da noite: gratidão 🌙 Para fechar o dia com Lamentações 3:24. Escreva amém se essa oração é sua também. #oracaodanoite #oracao #fe #gratidao</t>
         </is>
       </c>
       <c r="I255" s="2" t="inlineStr"/>
@@ -11457,7 +11457,7 @@
       </c>
       <c r="H256" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: gratidão 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #gratidao</t>
+          <t>Oração da noite: gratidão 🌙 Para fechar o dia com Salmos 116:12. Comente o nome de quem você quer colocar nesta oração. #oracaodanoite #oracao #fe #gratidao</t>
         </is>
       </c>
       <c r="I256" s="2" t="inlineStr"/>
@@ -11500,7 +11500,7 @@
       </c>
       <c r="H257" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: gratidão 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #gratidao</t>
+          <t>Oração da noite: gratidão 🌙 Para fechar o dia com Atos 16:25. Conte nos comentários pelo que você quer agradecer hoje. #oracaodanoite #oracao #fe #gratidao</t>
         </is>
       </c>
       <c r="I257" s="2" t="inlineStr"/>
@@ -11543,7 +11543,7 @@
       </c>
       <c r="H258" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: gratidão 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #gratidao</t>
+          <t>Oração da noite: gratidão 🌙 Para fechar o dia com Salmos 103:3-5. Deixe nos comentários o que você quer entregar a Deus esta noite. #oracaodanoite #oracao #fe #gratidao</t>
         </is>
       </c>
       <c r="I258" s="2" t="inlineStr"/>
@@ -11586,7 +11586,7 @@
       </c>
       <c r="H259" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: gratidão 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #gratidao</t>
+          <t>Oração da noite: gratidão 🌙 Para fechar o dia com Salmos 65:11. Marque alguém que precisa ouvir esta oração. #oracaodanoite #oracao #fe #gratidao</t>
         </is>
       </c>
       <c r="I259" s="2" t="inlineStr"/>
@@ -11629,7 +11629,7 @@
       </c>
       <c r="H260" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: gratidão 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #gratidao</t>
+          <t>Oração da noite: gratidão 🌙 Para fechar o dia com Neemias 8:10. Comente seu pedido. Vamos orar juntos. #oracaodanoite #oracao #fe #gratidao</t>
         </is>
       </c>
       <c r="I260" s="2" t="inlineStr"/>
@@ -11672,7 +11672,7 @@
       </c>
       <c r="H261" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: propósito e trabalho 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #proposito</t>
+          <t>Oração da noite: propósito e trabalho 🌙 Para fechar o dia com Colossenses 3:23. Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #proposito</t>
         </is>
       </c>
       <c r="I261" s="2" t="inlineStr"/>
@@ -11715,7 +11715,7 @@
       </c>
       <c r="H262" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: propósito e trabalho 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #proposito</t>
+          <t>Oração da noite: propósito e trabalho 🌙 Para fechar o dia com Provérbios 16:3. Escreva amém se essa oração é sua também. #oracaodanoite #oracao #fe #proposito</t>
         </is>
       </c>
       <c r="I262" s="2" t="inlineStr"/>
@@ -11758,7 +11758,7 @@
       </c>
       <c r="H263" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: propósito e trabalho 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #proposito</t>
+          <t>Oração da noite: propósito e trabalho 🌙 Para fechar o dia com Efésios 2:10. Comente o nome de quem você quer colocar nesta oração. #oracaodanoite #oracao #fe #proposito</t>
         </is>
       </c>
       <c r="I263" s="2" t="inlineStr"/>
@@ -11801,7 +11801,7 @@
       </c>
       <c r="H264" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: propósito e trabalho 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #proposito</t>
+          <t>Oração da noite: propósito e trabalho 🌙 Para fechar o dia com Jeremias 1:5. Conte nos comentários pelo que você quer agradecer hoje. #oracaodanoite #oracao #fe #proposito</t>
         </is>
       </c>
       <c r="I264" s="2" t="inlineStr"/>
@@ -11844,7 +11844,7 @@
       </c>
       <c r="H265" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: propósito e trabalho 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #proposito</t>
+          <t>Oração da noite: propósito e trabalho 🌙 Para fechar o dia com Provérbios 14:23. Deixe nos comentários o que você quer entregar a Deus esta noite. #oracaodanoite #oracao #fe #proposito</t>
         </is>
       </c>
       <c r="I265" s="2" t="inlineStr"/>
@@ -11887,7 +11887,7 @@
       </c>
       <c r="H266" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: propósito e trabalho 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #proposito</t>
+          <t>Oração da noite: propósito e trabalho 🌙 Para fechar o dia com Eclesiastes 9:10. Marque alguém que precisa ouvir esta oração. #oracaodanoite #oracao #fe #proposito</t>
         </is>
       </c>
       <c r="I266" s="2" t="inlineStr"/>
@@ -11930,7 +11930,7 @@
       </c>
       <c r="H267" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: propósito e trabalho 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #proposito</t>
+          <t>Oração da noite: propósito e trabalho 🌙 Para fechar o dia com Provérbios 22:29. Comente seu pedido. Vamos orar juntos. #oracaodanoite #oracao #fe #proposito</t>
         </is>
       </c>
       <c r="I267" s="2" t="inlineStr"/>
@@ -11973,7 +11973,7 @@
       </c>
       <c r="H268" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: propósito e trabalho 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #proposito</t>
+          <t>Oração da noite: propósito e trabalho 🌙 Para fechar o dia com Filipenses 1:6. Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #proposito</t>
         </is>
       </c>
       <c r="I268" s="2" t="inlineStr"/>
@@ -12016,7 +12016,7 @@
       </c>
       <c r="H269" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: propósito e trabalho 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #proposito</t>
+          <t>Oração da noite: propósito e trabalho 🌙 Para fechar o dia com Gálatas 6:9. Escreva amém se essa oração é sua também. #oracaodanoite #oracao #fe #proposito</t>
         </is>
       </c>
       <c r="I269" s="2" t="inlineStr"/>
@@ -12059,7 +12059,7 @@
       </c>
       <c r="H270" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: propósito e trabalho 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #proposito</t>
+          <t>Oração da noite: propósito e trabalho 🌙 Para fechar o dia com Salmos 90:17. Comente o nome de quem você quer colocar nesta oração. #oracaodanoite #oracao #fe #proposito</t>
         </is>
       </c>
       <c r="I270" s="2" t="inlineStr"/>
@@ -12102,7 +12102,7 @@
       </c>
       <c r="H271" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: propósito e trabalho 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #proposito</t>
+          <t>Oração da noite: propósito e trabalho 🌙 Para fechar o dia com Romanos 12:6-8. Conte nos comentários pelo que você quer agradecer hoje. #oracaodanoite #oracao #fe #proposito</t>
         </is>
       </c>
       <c r="I271" s="2" t="inlineStr"/>
@@ -12145,7 +12145,7 @@
       </c>
       <c r="H272" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: propósito e trabalho 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #proposito</t>
+          <t>Oração da noite: propósito e trabalho 🌙 Para fechar o dia com 1 Pedro 4:10. Deixe nos comentários o que você quer entregar a Deus esta noite. #oracaodanoite #oracao #fe #proposito</t>
         </is>
       </c>
       <c r="I272" s="2" t="inlineStr"/>
@@ -12188,7 +12188,7 @@
       </c>
       <c r="H273" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: propósito e trabalho 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #proposito</t>
+          <t>Oração da noite: propósito e trabalho 🌙 Para fechar o dia com Provérbios 6:6-8. Marque alguém que precisa ouvir esta oração. #oracaodanoite #oracao #fe #proposito</t>
         </is>
       </c>
       <c r="I273" s="2" t="inlineStr"/>
@@ -12231,7 +12231,7 @@
       </c>
       <c r="H274" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: propósito e trabalho 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #proposito</t>
+          <t>Oração da noite: propósito e trabalho 🌙 Para fechar o dia com Mateus 25:21. Comente seu pedido. Vamos orar juntos. #oracaodanoite #oracao #fe #proposito</t>
         </is>
       </c>
       <c r="I274" s="2" t="inlineStr"/>
@@ -12274,7 +12274,7 @@
       </c>
       <c r="H275" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: propósito e trabalho 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #proposito</t>
+          <t>Oração da noite: propósito e trabalho 🌙 Para fechar o dia com Neemias 2:20. Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #proposito</t>
         </is>
       </c>
       <c r="I275" s="2" t="inlineStr"/>
@@ -12317,7 +12317,7 @@
       </c>
       <c r="H276" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: propósito e trabalho 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #proposito</t>
+          <t>Oração da noite: propósito e trabalho 🌙 Para fechar o dia com Provérbios 13:4. Escreva amém se essa oração é sua também. #oracaodanoite #oracao #fe #proposito</t>
         </is>
       </c>
       <c r="I276" s="2" t="inlineStr"/>
@@ -12360,7 +12360,7 @@
       </c>
       <c r="H277" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: propósito e trabalho 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #proposito</t>
+          <t>Oração da noite: propósito e trabalho 🌙 Para fechar o dia com Mateus 5:14-16. Comente o nome de quem você quer colocar nesta oração. #oracaodanoite #oracao #fe #proposito</t>
         </is>
       </c>
       <c r="I277" s="2" t="inlineStr"/>
@@ -12403,7 +12403,7 @@
       </c>
       <c r="H278" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: propósito e trabalho 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #proposito</t>
+          <t>Oração da noite: propósito e trabalho 🌙 Para fechar o dia com 1 Coríntios 15:58. Conte nos comentários pelo que você quer agradecer hoje. #oracaodanoite #oracao #fe #proposito</t>
         </is>
       </c>
       <c r="I278" s="2" t="inlineStr"/>
@@ -12446,7 +12446,7 @@
       </c>
       <c r="H279" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: propósito e trabalho 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #proposito</t>
+          <t>Oração da noite: propósito e trabalho 🌙 Para fechar o dia com Deuteronômio 8:18. Deixe nos comentários o que você quer entregar a Deus esta noite. #oracaodanoite #oracao #fe #proposito</t>
         </is>
       </c>
       <c r="I279" s="2" t="inlineStr"/>
@@ -12489,7 +12489,7 @@
       </c>
       <c r="H280" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: propósito e trabalho 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #proposito</t>
+          <t>Oração da noite: propósito e trabalho 🌙 Para fechar o dia com Provérbios 10:4. Marque alguém que precisa ouvir esta oração. #oracaodanoite #oracao #fe #proposito</t>
         </is>
       </c>
       <c r="I280" s="2" t="inlineStr"/>
@@ -12532,7 +12532,7 @@
       </c>
       <c r="H281" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: propósito e trabalho 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #proposito</t>
+          <t>Oração da noite: propósito e trabalho 🌙 Para fechar o dia com Eclesiastes 3:1. Comente seu pedido. Vamos orar juntos. #oracaodanoite #oracao #fe #proposito</t>
         </is>
       </c>
       <c r="I281" s="2" t="inlineStr"/>
@@ -12575,7 +12575,7 @@
       </c>
       <c r="H282" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: propósito e trabalho 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #proposito</t>
+          <t>Oração da noite: propósito e trabalho 🌙 Para fechar o dia com 2 Tessalonicenses 3:10-13. Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #proposito</t>
         </is>
       </c>
       <c r="I282" s="2" t="inlineStr"/>
@@ -12618,7 +12618,7 @@
       </c>
       <c r="H283" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: propósito e trabalho 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #proposito</t>
+          <t>Oração da noite: propósito e trabalho 🌙 Para fechar o dia com Isaías 64:8. Escreva amém se essa oração é sua também. #oracaodanoite #oracao #fe #proposito</t>
         </is>
       </c>
       <c r="I283" s="2" t="inlineStr"/>
@@ -12661,7 +12661,7 @@
       </c>
       <c r="H284" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: propósito e trabalho 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #proposito</t>
+          <t>Oração da noite: propósito e trabalho 🌙 Para fechar o dia com Atos 20:35. Comente o nome de quem você quer colocar nesta oração. #oracaodanoite #oracao #fe #proposito</t>
         </is>
       </c>
       <c r="I284" s="2" t="inlineStr"/>
@@ -12704,7 +12704,7 @@
       </c>
       <c r="H285" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: propósito e trabalho 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #proposito</t>
+          <t>Oração da noite: propósito e trabalho 🌙 Para fechar o dia com Provérbios 16:9. Conte nos comentários pelo que você quer agradecer hoje. #oracaodanoite #oracao #fe #proposito</t>
         </is>
       </c>
       <c r="I285" s="2" t="inlineStr"/>
@@ -12747,7 +12747,7 @@
       </c>
       <c r="H286" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: propósito e trabalho 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #proposito</t>
+          <t>Oração da noite: propósito e trabalho 🌙 Para fechar o dia com Habacuque 2:2-3. Deixe nos comentários o que você quer entregar a Deus esta noite. #oracaodanoite #oracao #fe #proposito</t>
         </is>
       </c>
       <c r="I286" s="2" t="inlineStr"/>
@@ -12790,7 +12790,7 @@
       </c>
       <c r="H287" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: propósito e trabalho 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #proposito</t>
+          <t>Oração da noite: propósito e trabalho 🌙 Para fechar o dia com Gênesis 39:2-3. Marque alguém que precisa ouvir esta oração. #oracaodanoite #oracao #fe #proposito</t>
         </is>
       </c>
       <c r="I287" s="2" t="inlineStr"/>
@@ -12833,7 +12833,7 @@
       </c>
       <c r="H288" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: propósito e trabalho 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #proposito</t>
+          <t>Oração da noite: propósito e trabalho 🌙 Para fechar o dia com 1 Coríntios 10:31. Comente seu pedido. Vamos orar juntos. #oracaodanoite #oracao #fe #proposito</t>
         </is>
       </c>
       <c r="I288" s="2" t="inlineStr"/>
@@ -12876,7 +12876,7 @@
       </c>
       <c r="H289" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: propósito e trabalho 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #proposito</t>
+          <t>Oração da noite: propósito e trabalho 🌙 Para fechar o dia com Salmos 37:5. Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #proposito</t>
         </is>
       </c>
       <c r="I289" s="2" t="inlineStr"/>
@@ -12919,7 +12919,7 @@
       </c>
       <c r="H290" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: propósito e trabalho 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #proposito</t>
+          <t>Oração da noite: propósito e trabalho 🌙 Para fechar o dia com Zacarias 4:10. Escreva amém se essa oração é sua também. #oracaodanoite #oracao #fe #proposito</t>
         </is>
       </c>
       <c r="I290" s="2" t="inlineStr"/>
@@ -12962,7 +12962,7 @@
       </c>
       <c r="H291" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: propósito e trabalho 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #proposito</t>
+          <t>Oração da noite: propósito e trabalho 🌙 Para fechar o dia com Mateus 6:33. Comente o nome de quem você quer colocar nesta oração. #oracaodanoite #oracao #fe #proposito</t>
         </is>
       </c>
       <c r="I291" s="2" t="inlineStr"/>
@@ -13005,7 +13005,7 @@
       </c>
       <c r="H292" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: sabedoria e decisões 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #sabedoria</t>
+          <t>Oração da noite: sabedoria e decisões 🌙 Para fechar o dia com Tiago 1:5. Conte nos comentários pelo que você quer agradecer hoje. #oracaodanoite #oracao #fe #sabedoria</t>
         </is>
       </c>
       <c r="I292" s="2" t="inlineStr"/>
@@ -13048,7 +13048,7 @@
       </c>
       <c r="H293" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: sabedoria e decisões 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #sabedoria</t>
+          <t>Oração da noite: sabedoria e decisões 🌙 Para fechar o dia com Provérbios 3:5-6. Deixe nos comentários o que você quer entregar a Deus esta noite. #oracaodanoite #oracao #fe #sabedoria</t>
         </is>
       </c>
       <c r="I293" s="2" t="inlineStr"/>
@@ -13091,7 +13091,7 @@
       </c>
       <c r="H294" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: sabedoria e decisões 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #sabedoria</t>
+          <t>Oração da noite: sabedoria e decisões 🌙 Para fechar o dia com Salmos 119:105. Marque alguém que precisa ouvir esta oração. #oracaodanoite #oracao #fe #sabedoria</t>
         </is>
       </c>
       <c r="I294" s="2" t="inlineStr"/>
@@ -13134,7 +13134,7 @@
       </c>
       <c r="H295" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: sabedoria e decisões 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #sabedoria</t>
+          <t>Oração da noite: sabedoria e decisões 🌙 Para fechar o dia com Provérbios 1:7. Comente seu pedido. Vamos orar juntos. #oracaodanoite #oracao #fe #sabedoria</t>
         </is>
       </c>
       <c r="I295" s="2" t="inlineStr"/>
@@ -13177,7 +13177,7 @@
       </c>
       <c r="H296" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: sabedoria e decisões 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #sabedoria</t>
+          <t>Oração da noite: sabedoria e decisões 🌙 Para fechar o dia com Provérbios 11:14. Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #sabedoria</t>
         </is>
       </c>
       <c r="I296" s="2" t="inlineStr"/>
@@ -13220,7 +13220,7 @@
       </c>
       <c r="H297" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: sabedoria e decisões 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #sabedoria</t>
+          <t>Oração da noite: sabedoria e decisões 🌙 Para fechar o dia com Salmos 32:8. Escreva amém se essa oração é sua também. #oracaodanoite #oracao #fe #sabedoria</t>
         </is>
       </c>
       <c r="I297" s="2" t="inlineStr"/>
@@ -13263,7 +13263,7 @@
       </c>
       <c r="H298" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: sabedoria e decisões 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #sabedoria</t>
+          <t>Oração da noite: sabedoria e decisões 🌙 Para fechar o dia com Provérbios 4:23. Comente o nome de quem você quer colocar nesta oração. #oracaodanoite #oracao #fe #sabedoria</t>
         </is>
       </c>
       <c r="I298" s="2" t="inlineStr"/>
@@ -13306,7 +13306,7 @@
       </c>
       <c r="H299" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: sabedoria e decisões 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #sabedoria</t>
+          <t>Oração da noite: sabedoria e decisões 🌙 Para fechar o dia com Isaías 30:21. Conte nos comentários pelo que você quer agradecer hoje. #oracaodanoite #oracao #fe #sabedoria</t>
         </is>
       </c>
       <c r="I299" s="2" t="inlineStr"/>
@@ -13349,7 +13349,7 @@
       </c>
       <c r="H300" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: sabedoria e decisões 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #sabedoria</t>
+          <t>Oração da noite: sabedoria e decisões 🌙 Para fechar o dia com Provérbios 2:6. Deixe nos comentários o que você quer entregar a Deus esta noite. #oracaodanoite #oracao #fe #sabedoria</t>
         </is>
       </c>
       <c r="I300" s="2" t="inlineStr"/>
@@ -13392,7 +13392,7 @@
       </c>
       <c r="H301" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: sabedoria e decisões 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #sabedoria</t>
+          <t>Oração da noite: sabedoria e decisões 🌙 Para fechar o dia com Tiago 3:17. Marque alguém que precisa ouvir esta oração. #oracaodanoite #oracao #fe #sabedoria</t>
         </is>
       </c>
       <c r="I301" s="2" t="inlineStr"/>
@@ -13435,7 +13435,7 @@
       </c>
       <c r="H302" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: sabedoria e decisões 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #sabedoria</t>
+          <t>Oração da noite: sabedoria e decisões 🌙 Para fechar o dia com Provérbios 15:22. Comente seu pedido. Vamos orar juntos. #oracaodanoite #oracao #fe #sabedoria</t>
         </is>
       </c>
       <c r="I302" s="2" t="inlineStr"/>
@@ -13478,7 +13478,7 @@
       </c>
       <c r="H303" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: sabedoria e decisões 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #sabedoria</t>
+          <t>Oração da noite: sabedoria e decisões 🌙 Para fechar o dia com Salmos 25:4-5. Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #sabedoria</t>
         </is>
       </c>
       <c r="I303" s="2" t="inlineStr"/>
@@ -13521,7 +13521,7 @@
       </c>
       <c r="H304" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: sabedoria e decisões 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #sabedoria</t>
+          <t>Oração da noite: sabedoria e decisões 🌙 Para fechar o dia com Provérbios 16:16. Escreva amém se essa oração é sua também. #oracaodanoite #oracao #fe #sabedoria</t>
         </is>
       </c>
       <c r="I304" s="2" t="inlineStr"/>
@@ -13564,7 +13564,7 @@
       </c>
       <c r="H305" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: sabedoria e decisões 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #sabedoria</t>
+          <t>Oração da noite: sabedoria e decisões 🌙 Para fechar o dia com Colossenses 3:16. Comente o nome de quem você quer colocar nesta oração. #oracaodanoite #oracao #fe #sabedoria</t>
         </is>
       </c>
       <c r="I305" s="2" t="inlineStr"/>
@@ -13607,7 +13607,7 @@
       </c>
       <c r="H306" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: sabedoria e decisões 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #sabedoria</t>
+          <t>Oração da noite: sabedoria e decisões 🌙 Para fechar o dia com Provérbios 14:12. Conte nos comentários pelo que você quer agradecer hoje. #oracaodanoite #oracao #fe #sabedoria</t>
         </is>
       </c>
       <c r="I306" s="2" t="inlineStr"/>
@@ -13650,7 +13650,7 @@
       </c>
       <c r="H307" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: sabedoria e decisões 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #sabedoria</t>
+          <t>Oração da noite: sabedoria e decisões 🌙 Para fechar o dia com 1 Reis 3:9. Deixe nos comentários o que você quer entregar a Deus esta noite. #oracaodanoite #oracao #fe #sabedoria</t>
         </is>
       </c>
       <c r="I307" s="2" t="inlineStr"/>
@@ -13693,7 +13693,7 @@
       </c>
       <c r="H308" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: sabedoria e decisões 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #sabedoria</t>
+          <t>Oração da noite: sabedoria e decisões 🌙 Para fechar o dia com Provérbios 19:21. Marque alguém que precisa ouvir esta oração. #oracaodanoite #oracao #fe #sabedoria</t>
         </is>
       </c>
       <c r="I308" s="2" t="inlineStr"/>
@@ -13736,7 +13736,7 @@
       </c>
       <c r="H309" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: sabedoria e decisões 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #sabedoria</t>
+          <t>Oração da noite: sabedoria e decisões 🌙 Para fechar o dia com Romanos 12:2. Comente seu pedido. Vamos orar juntos. #oracaodanoite #oracao #fe #sabedoria</t>
         </is>
       </c>
       <c r="I309" s="2" t="inlineStr"/>
@@ -13779,7 +13779,7 @@
       </c>
       <c r="H310" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: sabedoria e decisões 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #sabedoria</t>
+          <t>Oração da noite: sabedoria e decisões 🌙 Para fechar o dia com Salmos 1:1-3. Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #sabedoria</t>
         </is>
       </c>
       <c r="I310" s="2" t="inlineStr"/>
@@ -13822,7 +13822,7 @@
       </c>
       <c r="H311" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: sabedoria e decisões 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #sabedoria</t>
+          <t>Oração da noite: sabedoria e decisões 🌙 Para fechar o dia com Provérbios 13:20. Escreva amém se essa oração é sua também. #oracaodanoite #oracao #fe #sabedoria</t>
         </is>
       </c>
       <c r="I311" s="2" t="inlineStr"/>
@@ -13865,7 +13865,7 @@
       </c>
       <c r="H312" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: sabedoria e decisões 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #sabedoria</t>
+          <t>Oração da noite: sabedoria e decisões 🌙 Para fechar o dia com Eclesiastes 7:8. Comente o nome de quem você quer colocar nesta oração. #oracaodanoite #oracao #fe #sabedoria</t>
         </is>
       </c>
       <c r="I312" s="2" t="inlineStr"/>
@@ -13908,7 +13908,7 @@
       </c>
       <c r="H313" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: sabedoria e decisões 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #sabedoria</t>
+          <t>Oração da noite: sabedoria e decisões 🌙 Para fechar o dia com Provérbios 12:15. Conte nos comentários pelo que você quer agradecer hoje. #oracaodanoite #oracao #fe #sabedoria</t>
         </is>
       </c>
       <c r="I313" s="2" t="inlineStr"/>
@@ -13951,7 +13951,7 @@
       </c>
       <c r="H314" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: sabedoria e decisões 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #sabedoria</t>
+          <t>Oração da noite: sabedoria e decisões 🌙 Para fechar o dia com Salmos 37:23. Deixe nos comentários o que você quer entregar a Deus esta noite. #oracaodanoite #oracao #fe #sabedoria</t>
         </is>
       </c>
       <c r="I314" s="2" t="inlineStr"/>
@@ -13994,7 +13994,7 @@
       </c>
       <c r="H315" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: sabedoria e decisões 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #sabedoria</t>
+          <t>Oração da noite: sabedoria e decisões 🌙 Para fechar o dia com Provérbios 21:5. Marque alguém que precisa ouvir esta oração. #oracaodanoite #oracao #fe #sabedoria</t>
         </is>
       </c>
       <c r="I315" s="2" t="inlineStr"/>
@@ -14037,7 +14037,7 @@
       </c>
       <c r="H316" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: sabedoria e decisões 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #sabedoria</t>
+          <t>Oração da noite: sabedoria e decisões 🌙 Para fechar o dia com Filipenses 1:9-10. Comente seu pedido. Vamos orar juntos. #oracaodanoite #oracao #fe #sabedoria</t>
         </is>
       </c>
       <c r="I316" s="2" t="inlineStr"/>
@@ -14080,7 +14080,7 @@
       </c>
       <c r="H317" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: sabedoria e decisões 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #sabedoria</t>
+          <t>Oração da noite: sabedoria e decisões 🌙 Para fechar o dia com Provérbios 18:13. Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #sabedoria</t>
         </is>
       </c>
       <c r="I317" s="2" t="inlineStr"/>
@@ -14123,7 +14123,7 @@
       </c>
       <c r="H318" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: sabedoria e decisões 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #sabedoria</t>
+          <t>Oração da noite: sabedoria e decisões 🌙 Para fechar o dia com Mateus 7:24-25. Escreva amém se essa oração é sua também. #oracaodanoite #oracao #fe #sabedoria</t>
         </is>
       </c>
       <c r="I318" s="2" t="inlineStr"/>
@@ -14166,7 +14166,7 @@
       </c>
       <c r="H319" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: sabedoria e decisões 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #sabedoria</t>
+          <t>Oração da noite: sabedoria e decisões 🌙 Para fechar o dia com Salmos 111:10. Comente o nome de quem você quer colocar nesta oração. #oracaodanoite #oracao #fe #sabedoria</t>
         </is>
       </c>
       <c r="I319" s="2" t="inlineStr"/>
@@ -14209,7 +14209,7 @@
       </c>
       <c r="H320" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: sabedoria e decisões 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #sabedoria</t>
+          <t>Oração da noite: sabedoria e decisões 🌙 Para fechar o dia com Provérbios 27:12. Conte nos comentários pelo que você quer agradecer hoje. #oracaodanoite #oracao #fe #sabedoria</t>
         </is>
       </c>
       <c r="I320" s="2" t="inlineStr"/>
@@ -14252,7 +14252,7 @@
       </c>
       <c r="H321" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: sabedoria e decisões 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #sabedoria</t>
+          <t>Oração da noite: sabedoria e decisões 🌙 Para fechar o dia com Eclesiastes 12:13. Deixe nos comentários o que você quer entregar a Deus esta noite. #oracaodanoite #oracao #fe #sabedoria</t>
         </is>
       </c>
       <c r="I321" s="2" t="inlineStr"/>
@@ -14295,7 +14295,7 @@
       </c>
       <c r="H322" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: sabedoria e decisões 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #sabedoria</t>
+          <t>Oração da noite: sabedoria e decisões 🌙 Para fechar o dia com Daniel 2:20-21. Marque alguém que precisa ouvir esta oração. #oracaodanoite #oracao #fe #sabedoria</t>
         </is>
       </c>
       <c r="I322" s="2" t="inlineStr"/>
@@ -14338,7 +14338,7 @@
       </c>
       <c r="H323" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: força e perseverança 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #forca</t>
+          <t>Oração da noite: força e perseverança 🌙 Para fechar o dia com Filipenses 4:13. Comente seu pedido. Vamos orar juntos. #oracaodanoite #oracao #fe #forca</t>
         </is>
       </c>
       <c r="I323" s="2" t="inlineStr"/>
@@ -14381,7 +14381,7 @@
       </c>
       <c r="H324" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: força e perseverança 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #forca</t>
+          <t>Oração da noite: força e perseverança 🌙 Para fechar o dia com Hebreus 12:1-2. Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #forca</t>
         </is>
       </c>
       <c r="I324" s="2" t="inlineStr"/>
@@ -14424,7 +14424,7 @@
       </c>
       <c r="H325" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: força e perseverança 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #forca</t>
+          <t>Oração da noite: força e perseverança 🌙 Para fechar o dia com Salmos 27:13. Escreva amém se essa oração é sua também. #oracaodanoite #oracao #fe #forca</t>
         </is>
       </c>
       <c r="I325" s="2" t="inlineStr"/>
@@ -14467,7 +14467,7 @@
       </c>
       <c r="H326" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: força e perseverança 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #forca</t>
+          <t>Oração da noite: força e perseverança 🌙 Para fechar o dia com Tiago 1:2-4. Comente o nome de quem você quer colocar nesta oração. #oracaodanoite #oracao #fe #forca</t>
         </is>
       </c>
       <c r="I326" s="2" t="inlineStr"/>
@@ -14510,7 +14510,7 @@
       </c>
       <c r="H327" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: força e perseverança 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #forca</t>
+          <t>Oração da noite: força e perseverança 🌙 Para fechar o dia com Provérbios 24:16. Conte nos comentários pelo que você quer agradecer hoje. #oracaodanoite #oracao #fe #forca</t>
         </is>
       </c>
       <c r="I327" s="2" t="inlineStr"/>
@@ -14553,7 +14553,7 @@
       </c>
       <c r="H328" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: força e perseverança 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #forca</t>
+          <t>Oração da noite: força e perseverança 🌙 Para fechar o dia com 2 Timóteo 4:7. Deixe nos comentários o que você quer entregar a Deus esta noite. #oracaodanoite #oracao #fe #forca</t>
         </is>
       </c>
       <c r="I328" s="2" t="inlineStr"/>
@@ -14596,7 +14596,7 @@
       </c>
       <c r="H329" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: força e perseverança 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #forca</t>
+          <t>Oração da noite: força e perseverança 🌙 Para fechar o dia com Salmos 18:32. Marque alguém que precisa ouvir esta oração. #oracaodanoite #oracao #fe #forca</t>
         </is>
       </c>
       <c r="I329" s="2" t="inlineStr"/>
@@ -14639,7 +14639,7 @@
       </c>
       <c r="H330" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: força e perseverança 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #forca</t>
+          <t>Oração da noite: força e perseverança 🌙 Para fechar o dia com Salmos 66:10-12. Comente seu pedido. Vamos orar juntos. #oracaodanoite #oracao #fe #forca</t>
         </is>
       </c>
       <c r="I330" s="2" t="inlineStr"/>
@@ -14682,7 +14682,7 @@
       </c>
       <c r="H331" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: força e perseverança 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #forca</t>
+          <t>Oração da noite: força e perseverança 🌙 Para fechar o dia com Salmos 73:26. Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #forca</t>
         </is>
       </c>
       <c r="I331" s="2" t="inlineStr"/>
@@ -14725,7 +14725,7 @@
       </c>
       <c r="H332" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: força e perseverança 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #forca</t>
+          <t>Oração da noite: força e perseverança 🌙 Para fechar o dia com Isaías 41:13. Escreva amém se essa oração é sua também. #oracaodanoite #oracao #fe #forca</t>
         </is>
       </c>
       <c r="I332" s="2" t="inlineStr"/>
@@ -14768,7 +14768,7 @@
       </c>
       <c r="H333" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: força e perseverança 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #forca</t>
+          <t>Oração da noite: força e perseverança 🌙 Para fechar o dia com 1 Coríntios 16:13. Comente o nome de quem você quer colocar nesta oração. #oracaodanoite #oracao #fe #forca</t>
         </is>
       </c>
       <c r="I333" s="2" t="inlineStr"/>
@@ -14811,7 +14811,7 @@
       </c>
       <c r="H334" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: força e perseverança 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #forca</t>
+          <t>Oração da noite: força e perseverança 🌙 Para fechar o dia com Efésios 6:10. Conte nos comentários pelo que você quer agradecer hoje. #oracaodanoite #oracao #fe #forca</t>
         </is>
       </c>
       <c r="I334" s="2" t="inlineStr"/>
@@ -14854,7 +14854,7 @@
       </c>
       <c r="H335" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: força e perseverança 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #forca</t>
+          <t>Oração da noite: força e perseverança 🌙 Para fechar o dia com Salmos 28:7. Deixe nos comentários o que você quer entregar a Deus esta noite. #oracaodanoite #oracao #fe #forca</t>
         </is>
       </c>
       <c r="I335" s="2" t="inlineStr"/>
@@ -14897,7 +14897,7 @@
       </c>
       <c r="H336" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: força e perseverança 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #forca</t>
+          <t>Oração da noite: força e perseverança 🌙 Para fechar o dia com Hebreus 10:36. Marque alguém que precisa ouvir esta oração. #oracaodanoite #oracao #fe #forca</t>
         </is>
       </c>
       <c r="I336" s="2" t="inlineStr"/>
@@ -14940,7 +14940,7 @@
       </c>
       <c r="H337" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: força e perseverança 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #forca</t>
+          <t>Oração da noite: força e perseverança 🌙 Para fechar o dia com Zacarias 4:6. Comente seu pedido. Vamos orar juntos. #oracaodanoite #oracao #fe #forca</t>
         </is>
       </c>
       <c r="I337" s="2" t="inlineStr"/>
@@ -14983,7 +14983,7 @@
       </c>
       <c r="H338" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: força e perseverança 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #forca</t>
+          <t>Oração da noite: força e perseverança 🌙 Para fechar o dia com Isaías 50:7. Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #forca</t>
         </is>
       </c>
       <c r="I338" s="2" t="inlineStr"/>
@@ -15026,7 +15026,7 @@
       </c>
       <c r="H339" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: força e perseverança 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #forca</t>
+          <t>Oração da noite: força e perseverança 🌙 Para fechar o dia com Salmos 138:7. Escreva amém se essa oração é sua também. #oracaodanoite #oracao #fe #forca</t>
         </is>
       </c>
       <c r="I339" s="2" t="inlineStr"/>
@@ -15069,7 +15069,7 @@
       </c>
       <c r="H340" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: força e perseverança 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #forca</t>
+          <t>Oração da noite: força e perseverança 🌙 Para fechar o dia com Neemias 6:3. Comente o nome de quem você quer colocar nesta oração. #oracaodanoite #oracao #fe #forca</t>
         </is>
       </c>
       <c r="I340" s="2" t="inlineStr"/>
@@ -15112,7 +15112,7 @@
       </c>
       <c r="H341" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: força e perseverança 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #forca</t>
+          <t>Oração da noite: força e perseverança 🌙 Para fechar o dia com Tiago 1:12. Conte nos comentários pelo que você quer agradecer hoje. #oracaodanoite #oracao #fe #forca</t>
         </is>
       </c>
       <c r="I341" s="2" t="inlineStr"/>
@@ -15155,7 +15155,7 @@
       </c>
       <c r="H342" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: força e perseverança 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #forca</t>
+          <t>Oração da noite: força e perseverança 🌙 Para fechar o dia com Salmos 46:5. Deixe nos comentários o que você quer entregar a Deus esta noite. #oracaodanoite #oracao #fe #forca</t>
         </is>
       </c>
       <c r="I342" s="2" t="inlineStr"/>
@@ -15198,7 +15198,7 @@
       </c>
       <c r="H343" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: força e perseverança 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #forca</t>
+          <t>Oração da noite: força e perseverança 🌙 Para fechar o dia com Hebreus 12:11. Marque alguém que precisa ouvir esta oração. #oracaodanoite #oracao #fe #forca</t>
         </is>
       </c>
       <c r="I343" s="2" t="inlineStr"/>
@@ -15241,7 +15241,7 @@
       </c>
       <c r="H344" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: força e perseverança 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #forca</t>
+          <t>Oração da noite: força e perseverança 🌙 Para fechar o dia com Lucas 18:1. Comente seu pedido. Vamos orar juntos. #oracaodanoite #oracao #fe #forca</t>
         </is>
       </c>
       <c r="I344" s="2" t="inlineStr"/>
@@ -15284,7 +15284,7 @@
       </c>
       <c r="H345" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: força e perseverança 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #forca</t>
+          <t>Oração da noite: força e perseverança 🌙 Para fechar o dia com Salmos 37:24. Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #forca</t>
         </is>
       </c>
       <c r="I345" s="2" t="inlineStr"/>
@@ -15327,7 +15327,7 @@
       </c>
       <c r="H346" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: força e perseverança 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #forca</t>
+          <t>Oração da noite: força e perseverança 🌙 Para fechar o dia com 2 Coríntios 4:7. Escreva amém se essa oração é sua também. #oracaodanoite #oracao #fe #forca</t>
         </is>
       </c>
       <c r="I346" s="2" t="inlineStr"/>
@@ -15370,7 +15370,7 @@
       </c>
       <c r="H347" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: força e perseverança 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #forca</t>
+          <t>Oração da noite: força e perseverança 🌙 Para fechar o dia com Josué 14:11. Comente o nome de quem você quer colocar nesta oração. #oracaodanoite #oracao #fe #forca</t>
         </is>
       </c>
       <c r="I347" s="2" t="inlineStr"/>
@@ -15413,7 +15413,7 @@
       </c>
       <c r="H348" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: força e perseverança 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #forca</t>
+          <t>Oração da noite: força e perseverança 🌙 Para fechar o dia com Isaías 40:28. Conte nos comentários pelo que você quer agradecer hoje. #oracaodanoite #oracao #fe #forca</t>
         </is>
       </c>
       <c r="I348" s="2" t="inlineStr"/>
@@ -15456,7 +15456,7 @@
       </c>
       <c r="H349" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: força e perseverança 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #forca</t>
+          <t>Oração da noite: força e perseverança 🌙 Para fechar o dia com Romanos 8:37. Deixe nos comentários o que você quer entregar a Deus esta noite. #oracaodanoite #oracao #fe #forca</t>
         </is>
       </c>
       <c r="I349" s="2" t="inlineStr"/>
@@ -15499,7 +15499,7 @@
       </c>
       <c r="H350" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: força e perseverança 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #forca</t>
+          <t>Oração da noite: força e perseverança 🌙 Para fechar o dia com Habacuque 3:19. Marque alguém que precisa ouvir esta oração. #oracaodanoite #oracao #fe #forca</t>
         </is>
       </c>
       <c r="I350" s="2" t="inlineStr"/>
@@ -15542,7 +15542,7 @@
       </c>
       <c r="H351" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: força e perseverança 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #forca</t>
+          <t>Oração da noite: força e perseverança 🌙 Para fechar o dia com Apocalipse 2:10. Comente seu pedido. Vamos orar juntos. #oracaodanoite #oracao #fe #forca</t>
         </is>
       </c>
       <c r="I351" s="2" t="inlineStr"/>
@@ -15585,7 +15585,7 @@
       </c>
       <c r="H352" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: força e perseverança 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #forca</t>
+          <t>Oração da noite: força e perseverança 🌙 Para fechar o dia com 2 Crônicas 15:7. Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #forca</t>
         </is>
       </c>
       <c r="I352" s="2" t="inlineStr"/>
@@ -15628,7 +15628,7 @@
       </c>
       <c r="H353" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: amor 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #amor</t>
+          <t>Oração da noite: amor 🌙 Para fechar o dia com João 3:16. Escreva amém se essa oração é sua também. #oracaodanoite #oracao #fe #amor</t>
         </is>
       </c>
       <c r="I353" s="2" t="inlineStr"/>
@@ -15671,7 +15671,7 @@
       </c>
       <c r="H354" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: amor 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #amor</t>
+          <t>Oração da noite: amor 🌙 Para fechar o dia com 1 João 4:8. Comente o nome de quem você quer colocar nesta oração. #oracaodanoite #oracao #fe #amor</t>
         </is>
       </c>
       <c r="I354" s="2" t="inlineStr"/>
@@ -15714,7 +15714,7 @@
       </c>
       <c r="H355" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: amor 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #amor</t>
+          <t>Oração da noite: amor 🌙 Para fechar o dia com Romanos 5:8. Conte nos comentários pelo que você quer agradecer hoje. #oracaodanoite #oracao #fe #amor</t>
         </is>
       </c>
       <c r="I355" s="2" t="inlineStr"/>
@@ -15757,7 +15757,7 @@
       </c>
       <c r="H356" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: amor 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #amor</t>
+          <t>Oração da noite: amor 🌙 Para fechar o dia com Romanos 8:38-39. Deixe nos comentários o que você quer entregar a Deus esta noite. #oracaodanoite #oracao #fe #amor</t>
         </is>
       </c>
       <c r="I356" s="2" t="inlineStr"/>
@@ -15800,7 +15800,7 @@
       </c>
       <c r="H357" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: amor 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #amor</t>
+          <t>Oração da noite: amor 🌙 Para fechar o dia com 1 João 4:19. Marque alguém que precisa ouvir esta oração. #oracaodanoite #oracao #fe #amor</t>
         </is>
       </c>
       <c r="I357" s="2" t="inlineStr"/>
@@ -15843,7 +15843,7 @@
       </c>
       <c r="H358" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: amor 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #amor</t>
+          <t>Oração da noite: amor 🌙 Para fechar o dia com Jeremias 31:3. Comente seu pedido. Vamos orar juntos. #oracaodanoite #oracao #fe #amor</t>
         </is>
       </c>
       <c r="I358" s="2" t="inlineStr"/>
@@ -15886,7 +15886,7 @@
       </c>
       <c r="H359" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: amor 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #amor</t>
+          <t>Oração da noite: amor 🌙 Para fechar o dia com 1 Coríntios 13:7. Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #amor</t>
         </is>
       </c>
       <c r="I359" s="2" t="inlineStr"/>
@@ -15929,7 +15929,7 @@
       </c>
       <c r="H360" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: amor 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #amor</t>
+          <t>Oração da noite: amor 🌙 Para fechar o dia com 1 Coríntios 13:13. Escreva amém se essa oração é sua também. #oracaodanoite #oracao #fe #amor</t>
         </is>
       </c>
       <c r="I360" s="2" t="inlineStr"/>
@@ -15972,7 +15972,7 @@
       </c>
       <c r="H361" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: amor 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #amor</t>
+          <t>Oração da noite: amor 🌙 Para fechar o dia com Mateus 22:37-39. Comente o nome de quem você quer colocar nesta oração. #oracaodanoite #oracao #fe #amor</t>
         </is>
       </c>
       <c r="I361" s="2" t="inlineStr"/>
@@ -16015,7 +16015,7 @@
       </c>
       <c r="H362" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: amor 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #amor</t>
+          <t>Oração da noite: amor 🌙 Para fechar o dia com João 13:34-35. Conte nos comentários pelo que você quer agradecer hoje. #oracaodanoite #oracao #fe #amor</t>
         </is>
       </c>
       <c r="I362" s="2" t="inlineStr"/>
@@ -16058,7 +16058,7 @@
       </c>
       <c r="H363" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: amor 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #amor</t>
+          <t>Oração da noite: amor 🌙 Para fechar o dia com Lucas 6:27-28. Deixe nos comentários o que você quer entregar a Deus esta noite. #oracaodanoite #oracao #fe #amor</t>
         </is>
       </c>
       <c r="I363" s="2" t="inlineStr"/>
@@ -16101,7 +16101,7 @@
       </c>
       <c r="H364" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: amor 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #amor</t>
+          <t>Oração da noite: amor 🌙 Para fechar o dia com Efésios 3:17-19. Marque alguém que precisa ouvir esta oração. #oracaodanoite #oracao #fe #amor</t>
         </is>
       </c>
       <c r="I364" s="2" t="inlineStr"/>
@@ -16144,7 +16144,7 @@
       </c>
       <c r="H365" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: amor 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #amor</t>
+          <t>Oração da noite: amor 🌙 Para fechar o dia com 1 João 3:18. Comente seu pedido. Vamos orar juntos. #oracaodanoite #oracao #fe #amor</t>
         </is>
       </c>
       <c r="I365" s="2" t="inlineStr"/>
@@ -16187,7 +16187,7 @@
       </c>
       <c r="H366" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: amor 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #amor</t>
+          <t>Oração da noite: amor 🌙 Para fechar o dia com Romanos 13:10. Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #amor</t>
         </is>
       </c>
       <c r="I366" s="2" t="inlineStr"/>

--- a/legendas-365.xlsx
+++ b/legendas-365.xlsx
@@ -773,7 +773,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Dia 294 de 365. João 15:9: Permanecei no meu amor. #fe #amordedeus #amor #palavradodia</t>
+          <t>Dia 7 de 365. João 15:9: Permanecei no meu amor. #fe #amordedeus #amor #palavradodia</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -816,7 +816,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Dia 295 de 365. Efésios 2:4-5: Rico em misericórdia. #fe #amordedeus #amor #palavradodia</t>
+          <t>Dia 8 de 365. Efésios 2:4-5: Rico em misericórdia. #fe #amordedeus #amor #palavradodia</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Dia 296 de 365. Romanos 12:9: O amor seja sem fingimento. #fe #amordedeus #amor #palavradodia</t>
+          <t>Dia 9 de 365. Romanos 12:9: O amor seja sem fingimento. #fe #amordedeus #amor #palavradodia</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -902,7 +902,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Dia 297 de 365. Provérbios 10:12: O ódio provoca brigas. #fe #amordedeus #amor #palavradodia</t>
+          <t>Dia 10 de 365. Provérbios 10:12: O ódio provoca brigas. #fe #amordedeus #amor #palavradodia</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -945,7 +945,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Dia 298 de 365. 1 João 4:20: Quem diz que ama a Deus. #fe #amordedeus #amor #palavradodia</t>
+          <t>Dia 11 de 365. 1 João 4:20: Quem diz que ama a Deus. #fe #amordedeus #amor #palavradodia</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -988,7 +988,7 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Dia 299 de 365. Salmos 86:15: Lento para a ira, grande em amor. #fe #amordedeus #amor #palavradodia</t>
+          <t>Dia 12 de 365. Salmos 86:15: Lento para a ira, grande em amor. #fe #amordedeus #amor #palavradodia</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1031,7 +1031,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Dia 300 de 365. Oseias 11:4: Atraí-os com cordas de amor. #fe #amordedeus #amor #palavradodia</t>
+          <t>Dia 13 de 365. Oseias 11:4: Atraí-os com cordas de amor. #fe #amordedeus #amor #palavradodia</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -1074,7 +1074,7 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Dia 301 de 365. Marcos 10:21: Jesus olhou para ele e o amou. #fe #amordedeus #amor #palavradodia</t>
+          <t>Dia 14 de 365. Marcos 10:21: Jesus olhou para ele e o amou. #fe #amordedeus #amor #palavradodia</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1117,7 +1117,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Dia 302 de 365. João 21:17: Tu sabes que eu te amo. #fe #amordedeus #amor #palavradodia</t>
+          <t>Dia 15 de 365. João 21:17: Tu sabes que eu te amo. #fe #amordedeus #amor #palavradodia</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1160,7 +1160,7 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>Dia 303 de 365. Tito 3:4-5: A bondade e o amor de Deus apareceram. #fe #amordedeus #amor #palavradodia</t>
+          <t>Dia 16 de 365. Tito 3:4-5: A bondade e o amor de Deus apareceram. #fe #amordedeus #amor #palavradodia</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -1203,7 +1203,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Dia 304 de 365. 1 Coríntios 16:14: Todas as vossas coisas sejam feitas com amor. #fe #amordedeus #amor #palavradodia</t>
+          <t>Dia 17 de 365. 1 Coríntios 16:14: Todas as vossas coisas sejam feitas com amor. #fe #amordedeus #amor #palavradodia</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -1246,7 +1246,7 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>Dia 305 de 365. Jeremias 33:3: Clama a mim, e responder-te-ei. #fe #oracao #confianca #palavradodia</t>
+          <t>Dia 18 de 365. Jeremias 33:3: Clama a mim, e responder-te-ei. #fe #oracao #confianca #palavradodia</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -1289,7 +1289,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Dia 306 de 365. Mateus 7:7-8: Pedi, buscai, batei. #fe #oracao #confianca #palavradodia</t>
+          <t>Dia 19 de 365. Mateus 7:7-8: Pedi, buscai, batei. #fe #oracao #confianca #palavradodia</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -1332,7 +1332,7 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>Dia 307 de 365. 1 Tessalonicenses 5:17: Orai sem cessar. #fe #oracao #confianca #palavradodia</t>
+          <t>Dia 20 de 365. 1 Tessalonicenses 5:17: Orai sem cessar. #fe #oracao #confianca #palavradodia</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -1375,7 +1375,7 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>Dia 308 de 365. Filipenses 4:19: O meu Deus suprirá. #fe #oracao #confianca #palavradodia</t>
+          <t>Dia 21 de 365. Filipenses 4:19: O meu Deus suprirá. #fe #oracao #confianca #palavradodia</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>Dia 309 de 365. Salmos 37:4: Deleita-te no Senhor. #fe #oracao #confianca #palavradodia</t>
+          <t>Dia 22 de 365. Salmos 37:4: Deleita-te no Senhor. #fe #oracao #confianca #palavradodia</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
@@ -1461,7 +1461,7 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>Dia 310 de 365. Salmos 56:8: Deus guarda as suas lágrimas. #fe #oracao #confianca #palavradodia</t>
+          <t>Dia 23 de 365. Salmos 56:8: Deus guarda as suas lágrimas. #fe #oracao #confianca #palavradodia</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
@@ -1504,7 +1504,7 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>Dia 311 de 365. Marcos 11:24: Crede que recebestes. #fe #oracao #confianca #palavradodia</t>
+          <t>Dia 24 de 365. Marcos 11:24: Crede que recebestes. #fe #oracao #confianca #palavradodia</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>Dia 312 de 365. Salmos 145:18: Perto está o Senhor. #fe #oracao #confianca #palavradodia</t>
+          <t>Dia 25 de 365. Salmos 145:18: Perto está o Senhor. #fe #oracao #confianca #palavradodia</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -1590,7 +1590,7 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>Dia 313 de 365. Mateus 6:6: Entre no seu quarto e feche a porta. #fe #oracao #confianca #palavradodia</t>
+          <t>Dia 26 de 365. Mateus 6:6: Entre no seu quarto e feche a porta. #fe #oracao #confianca #palavradodia</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
@@ -1633,7 +1633,7 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>Dia 314 de 365. Romanos 8:26: Quando você não sabe o que orar. #fe #oracao #confianca #palavradodia</t>
+          <t>Dia 27 de 365. Romanos 8:26: Quando você não sabe o que orar. #fe #oracao #confianca #palavradodia</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>Dia 315 de 365. Hebreus 4:16: Cheguemos com confiança ao trono da graça. #fe #oracao #confianca #palavradodia</t>
+          <t>Dia 28 de 365. Hebreus 4:16: Cheguemos com confiança ao trono da graça. #fe #oracao #confianca #palavradodia</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
@@ -1719,7 +1719,7 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>Dia 316 de 365. Salmos 62:8: Derramai perante Ele o vosso coração. #fe #oracao #confianca #palavradodia</t>
+          <t>Dia 29 de 365. Salmos 62:8: Derramai perante Ele o vosso coração. #fe #oracao #confianca #palavradodia</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
@@ -1762,7 +1762,7 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>Dia 317 de 365. Tiago 5:16: A oração do justo pode muito. #fe #oracao #confianca #palavradodia</t>
+          <t>Dia 30 de 365. Tiago 5:16: A oração do justo pode muito. #fe #oracao #confianca #palavradodia</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
@@ -1805,7 +1805,7 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>Dia 318 de 365. Mateus 6:9-10: A oração que Jesus ensinou. #fe #oracao #confianca #palavradodia</t>
+          <t>Dia 31 de 365. Mateus 6:9-10: A oração que Jesus ensinou. #fe #oracao #confianca #palavradodia</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
@@ -1848,7 +1848,7 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>Dia 319 de 365. Salmos 5:3: De manhã ouvirás a minha voz. #fe #oracao #confianca #palavradodia</t>
+          <t>Dia 32 de 365. Salmos 5:3: De manhã ouvirás a minha voz. #fe #oracao #confianca #palavradodia</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
@@ -1891,7 +1891,7 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>Dia 320 de 365. Lucas 22:42: Não a minha vontade, mas a tua. #fe #oracao #confianca #palavradodia</t>
+          <t>Dia 33 de 365. Lucas 22:42: Não a minha vontade, mas a tua. #fe #oracao #confianca #palavradodia</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
@@ -1934,7 +1934,7 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>Dia 321 de 365. 1 João 5:14: Se pedirmos segundo a sua vontade. #fe #oracao #confianca #palavradodia</t>
+          <t>Dia 34 de 365. 1 João 5:14: Se pedirmos segundo a sua vontade. #fe #oracao #confianca #palavradodia</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
@@ -1977,7 +1977,7 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>Dia 322 de 365. Salmos 20:7: Uns confiam em carros, outros em cavalos. #fe #oracao #confianca #palavradodia</t>
+          <t>Dia 35 de 365. Salmos 20:7: Uns confiam em carros, outros em cavalos. #fe #oracao #confianca #palavradodia</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
@@ -2020,7 +2020,7 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>Dia 323 de 365. Isaías 65:24: Antes que clamem, eu responderei. #fe #oracao #confianca #palavradodia</t>
+          <t>Dia 36 de 365. Isaías 65:24: Antes que clamem, eu responderei. #fe #oracao #confianca #palavradodia</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
@@ -2063,7 +2063,7 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>Dia 324 de 365. Neemias 1:4: Neemias chorou, jejuou e orou. #fe #oracao #confianca #palavradodia</t>
+          <t>Dia 37 de 365. Neemias 1:4: Neemias chorou, jejuou e orou. #fe #oracao #confianca #palavradodia</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>Dia 325 de 365. Daniel 9:18: Não por nossas justiças. #fe #oracao #confianca #palavradodia</t>
+          <t>Dia 38 de 365. Daniel 9:18: Não por nossas justiças. #fe #oracao #confianca #palavradodia</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
@@ -2149,7 +2149,7 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>Dia 326 de 365. Salmos 37:7: Descansa no Senhor e espera nEle. #fe #oracao #confianca #palavradodia</t>
+          <t>Dia 39 de 365. Salmos 37:7: Descansa no Senhor e espera nEle. #fe #oracao #confianca #palavradodia</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
@@ -2192,7 +2192,7 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>Dia 327 de 365. Mateus 21:22: Tudo o que pedirdes em oração, crendo. #fe #oracao #confianca #palavradodia</t>
+          <t>Dia 40 de 365. Mateus 21:22: Tudo o que pedirdes em oração, crendo. #fe #oracao #confianca #palavradodia</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
@@ -2235,7 +2235,7 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>Dia 328 de 365. Salmos 141:2: Minha oração como incenso. #fe #oracao #confianca #palavradodia</t>
+          <t>Dia 41 de 365. Salmos 141:2: Minha oração como incenso. #fe #oracao #confianca #palavradodia</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
@@ -2278,7 +2278,7 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>Dia 329 de 365. Isaías 30:15: Na tranquilidade e na confiança. #fe #oracao #confianca #palavradodia</t>
+          <t>Dia 42 de 365. Isaías 30:15: Na tranquilidade e na confiança. #fe #oracao #confianca #palavradodia</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>Dia 330 de 365. Salmos 9:10: Os que conhecem o teu nome confiarão em ti. #fe #oracao #confianca #palavradodia</t>
+          <t>Dia 43 de 365. Salmos 9:10: Os que conhecem o teu nome confiarão em ti. #fe #oracao #confianca #palavradodia</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
@@ -2364,7 +2364,7 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>Dia 331 de 365. Atos 12:5: A igreja orava por Pedro. #fe #oracao #confianca #palavradodia</t>
+          <t>Dia 44 de 365. Atos 12:5: A igreja orava por Pedro. #fe #oracao #confianca #palavradodia</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
@@ -2407,7 +2407,7 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>Dia 332 de 365. Lucas 11:9-10: Batei, e abrir-se-vos-á. #fe #oracao #confianca #palavradodia</t>
+          <t>Dia 45 de 365. Lucas 11:9-10: Batei, e abrir-se-vos-á. #fe #oracao #confianca #palavradodia</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
@@ -2450,7 +2450,7 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>Dia 333 de 365. Provérbios 29:25: O medo dos homens é um laço. #fe #oracao #confianca #palavradodia</t>
+          <t>Dia 46 de 365. Provérbios 29:25: O medo dos homens é um laço. #fe #oracao #confianca #palavradodia</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
@@ -2493,7 +2493,7 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>Dia 334 de 365. Salmos 57:1-2: À sombra das tuas asas. #fe #oracao #confianca #palavradodia</t>
+          <t>Dia 47 de 365. Salmos 57:1-2: À sombra das tuas asas. #fe #oracao #confianca #palavradodia</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
@@ -2536,7 +2536,7 @@
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>Dia 335 de 365. Isaías 43:18: Não vos lembreis das coisas passadas. #fe #recomeco #promessas #palavradodia</t>
+          <t>Dia 48 de 365. Isaías 43:18: Não vos lembreis das coisas passadas. #fe #recomeco #promessas #palavradodia</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
@@ -2579,7 +2579,7 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>Dia 336 de 365. Filipenses 3:13-14: Esquecendo o que fica para trás. #fe #recomeco #promessas #palavradodia</t>
+          <t>Dia 49 de 365. Filipenses 3:13-14: Esquecendo o que fica para trás. #fe #recomeco #promessas #palavradodia</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
@@ -2622,7 +2622,7 @@
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>Dia 337 de 365. Ezequiel 36:26: Um coração novo. #fe #recomeco #promessas #palavradodia</t>
+          <t>Dia 50 de 365. Ezequiel 36:26: Um coração novo. #fe #recomeco #promessas #palavradodia</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
@@ -2665,7 +2665,7 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>Dia 338 de 365. Apocalipse 21:5: Eis que faço novas todas as coisas. #fe #recomeco #promessas #palavradodia</t>
+          <t>Dia 51 de 365. Apocalipse 21:5: Eis que faço novas todas as coisas. #fe #recomeco #promessas #palavradodia</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
@@ -2708,7 +2708,7 @@
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>Dia 339 de 365. Salmos 40:3: Um cântico novo. #fe #recomeco #promessas #palavradodia</t>
+          <t>Dia 52 de 365. Salmos 40:3: Um cântico novo. #fe #recomeco #promessas #palavradodia</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
@@ -2751,7 +2751,7 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>Dia 340 de 365. 2 Coríntios 1:20: Todas as promessas têm o sim nEle. #fe #recomeco #promessas #palavradodia</t>
+          <t>Dia 53 de 365. 2 Coríntios 1:20: Todas as promessas têm o sim nEle. #fe #recomeco #promessas #palavradodia</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
@@ -2794,7 +2794,7 @@
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>Dia 341 de 365. Números 23:19: Deus não é homem para que minta. #fe #recomeco #promessas #palavradodia</t>
+          <t>Dia 54 de 365. Números 23:19: Deus não é homem para que minta. #fe #recomeco #promessas #palavradodia</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
@@ -2837,7 +2837,7 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>Dia 342 de 365. Josué 21:45: Nenhuma palavra falhou. #fe #recomeco #promessas #palavradodia</t>
+          <t>Dia 55 de 365. Josué 21:45: Nenhuma palavra falhou. #fe #recomeco #promessas #palavradodia</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
@@ -2880,7 +2880,7 @@
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>Dia 343 de 365. Lamentações 3:25: Bom é o Senhor para os que esperam por Ele. #fe #recomeco #promessas #palavradodia</t>
+          <t>Dia 56 de 365. Lamentações 3:25: Bom é o Senhor para os que esperam por Ele. #fe #recomeco #promessas #palavradodia</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
@@ -2923,7 +2923,7 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>Dia 344 de 365. Isaías 55:10-11: A palavra de Deus não volta vazia. #fe #recomeco #promessas #palavradodia</t>
+          <t>Dia 57 de 365. Isaías 55:10-11: A palavra de Deus não volta vazia. #fe #recomeco #promessas #palavradodia</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
@@ -2966,7 +2966,7 @@
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>Dia 345 de 365. Salmos 37:25: Nunca vi o justo desamparado. #fe #recomeco #promessas #palavradodia</t>
+          <t>Dia 58 de 365. Salmos 37:25: Nunca vi o justo desamparado. #fe #recomeco #promessas #palavradodia</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
@@ -3009,7 +3009,7 @@
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>Dia 346 de 365. Deuteronômio 7:9: O Deus fiel. #fe #recomeco #promessas #palavradodia</t>
+          <t>Dia 59 de 365. Deuteronômio 7:9: O Deus fiel. #fe #recomeco #promessas #palavradodia</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
@@ -3052,7 +3052,7 @@
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>Dia 347 de 365. Hebreus 10:23: Retenhamos firme a confissão da esperança. #fe #recomeco #promessas #palavradodia</t>
+          <t>Dia 60 de 365. Hebreus 10:23: Retenhamos firme a confissão da esperança. #fe #recomeco #promessas #palavradodia</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
@@ -3095,7 +3095,7 @@
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>Dia 348 de 365. Jonas 2:10: Do fundo do peixe para a terra seca. #fe #recomeco #promessas #palavradodia</t>
+          <t>Dia 61 de 365. Jonas 2:10: Do fundo do peixe para a terra seca. #fe #recomeco #promessas #palavradodia</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
@@ -3138,7 +3138,7 @@
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>Dia 349 de 365. Jonas 3:1: A palavra veio pela segunda vez. #fe #recomeco #promessas #palavradodia</t>
+          <t>Dia 62 de 365. Jonas 3:1: A palavra veio pela segunda vez. #fe #recomeco #promessas #palavradodia</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>Dia 350 de 365. Isaías 58:11: Como jardim regado. #fe #recomeco #promessas #palavradodia</t>
+          <t>Dia 63 de 365. Isaías 58:11: Como jardim regado. #fe #recomeco #promessas #palavradodia</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
@@ -3224,7 +3224,7 @@
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>Dia 351 de 365. Salmos 23:6: Bondade e misericórdia me seguirão. #fe #recomeco #promessas #palavradodia</t>
+          <t>Dia 64 de 365. Salmos 23:6: Bondade e misericórdia me seguirão. #fe #recomeco #promessas #palavradodia</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
@@ -3267,7 +3267,7 @@
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>Dia 352 de 365. Gênesis 28:15: Eis que estou contigo. #fe #recomeco #promessas #palavradodia</t>
+          <t>Dia 65 de 365. Gênesis 28:15: Eis que estou contigo. #fe #recomeco #promessas #palavradodia</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
@@ -3310,7 +3310,7 @@
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>Dia 353 de 365. Isaías 42:3: A cana quebrada Ele não esmagará. #fe #recomeco #promessas #palavradodia</t>
+          <t>Dia 66 de 365. Isaías 42:3: A cana quebrada Ele não esmagará. #fe #recomeco #promessas #palavradodia</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">

--- a/legendas-365.xlsx
+++ b/legendas-365.xlsx
@@ -3353,7 +3353,7 @@
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>Dia 354 de 365. Salmos 145:14: O Senhor sustenta os que caem. #fe #recomeco #promessas #palavradodia</t>
+          <t>Dia 67 de 365. Salmos 145:14: O Senhor sustenta os que caem. #fe #recomeco #promessas #palavradodia</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
@@ -3396,7 +3396,7 @@
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>Dia 355 de 365. Isaías 60:1: Levanta-te, resplandece. #fe #recomeco #promessas #palavradodia</t>
+          <t>Dia 68 de 365. Isaías 60:1: Levanta-te, resplandece. #fe #recomeco #promessas #palavradodia</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
@@ -3439,7 +3439,7 @@
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>Dia 356 de 365. Atos 9:17-18: Saulo voltou a ver. #fe #recomeco #promessas #palavradodia</t>
+          <t>Dia 69 de 365. Atos 9:17-18: Saulo voltou a ver. #fe #recomeco #promessas #palavradodia</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
@@ -3482,7 +3482,7 @@
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>Dia 357 de 365. Lucas 5:5-6: Sobre a tua palavra, lançarei as redes. #fe #recomeco #promessas #palavradodia</t>
+          <t>Dia 70 de 365. Lucas 5:5-6: Sobre a tua palavra, lançarei as redes. #fe #recomeco #promessas #palavradodia</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
@@ -3525,7 +3525,7 @@
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>Dia 358 de 365. Oseias 6:3: Como a alva, a sua vinda é certa. #fe #recomeco #promessas #palavradodia</t>
+          <t>Dia 71 de 365. Oseias 6:3: Como a alva, a sua vinda é certa. #fe #recomeco #promessas #palavradodia</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
@@ -3568,7 +3568,7 @@
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>Dia 359 de 365. Ageu 2:9: A glória desta última casa será maior. #fe #recomeco #promessas #palavradodia</t>
+          <t>Dia 72 de 365. Ageu 2:9: A glória desta última casa será maior. #fe #recomeco #promessas #palavradodia</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
@@ -3611,7 +3611,7 @@
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>Dia 360 de 365. Isaías 54:10: Os montes se retirarão. #fe #recomeco #promessas #palavradodia</t>
+          <t>Dia 73 de 365. Isaías 54:10: Os montes se retirarão. #fe #recomeco #promessas #palavradodia</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
@@ -3654,7 +3654,7 @@
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>Dia 361 de 365. Salmos 30:11: Tornaste o meu pranto em dança. #fe #recomeco #promessas #palavradodia</t>
+          <t>Dia 74 de 365. Salmos 30:11: Tornaste o meu pranto em dança. #fe #recomeco #promessas #palavradodia</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
@@ -3697,7 +3697,7 @@
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>Dia 362 de 365. 2 Pedro 3:9: O Senhor não retarda a promessa. #fe #recomeco #promessas #palavradodia</t>
+          <t>Dia 75 de 365. 2 Pedro 3:9: O Senhor não retarda a promessa. #fe #recomeco #promessas #palavradodia</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
@@ -3740,7 +3740,7 @@
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>Dia 363 de 365. Isaías 46:4: Até a velhice eu te carregarei. #fe #recomeco #promessas #palavradodia</t>
+          <t>Dia 76 de 365. Isaías 46:4: Até a velhice eu te carregarei. #fe #recomeco #promessas #palavradodia</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
@@ -3783,7 +3783,7 @@
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>Dia 364 de 365. Números 6:24-26: O Senhor te abençoe e te guarde. #fe #recomeco #promessas #palavradodia</t>
+          <t>Dia 77 de 365. Números 6:24-26: O Senhor te abençoe e te guarde. #fe #recomeco #promessas #palavradodia</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
@@ -3826,7 +3826,7 @@
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>Dia 365 de 365. Judas 1:24-25: Àquele que é poderoso para vos guardar. #fe #recomeco #promessas #palavradodia</t>
+          <t>Dia 78 de 365. Judas 1:24-25: Àquele que é poderoso para vos guardar. #fe #recomeco #promessas #palavradodia</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
@@ -3869,7 +3869,7 @@
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>Dia 1 de 365. Filipenses 4:6-7: Se a ansiedade te acordou hoje, ouça isso antes de começar o dia. #fe #ansiedade #paz #palavradodia</t>
+          <t>Dia 79 de 365. Filipenses 4:6-7: Se a ansiedade te acordou hoje, ouça isso antes de começar o dia. #fe #ansiedade #paz #palavradodia</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
@@ -3912,7 +3912,7 @@
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>Dia 2 de 365. Mateus 6:34: Você está sofrendo hoje por algo que ainda nem aconteceu? #fe #ansiedade #paz #palavradodia</t>
+          <t>Dia 80 de 365. Mateus 6:34: Você está sofrendo hoje por algo que ainda nem aconteceu? #fe #ansiedade #paz #palavradodia</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
@@ -3955,7 +3955,7 @@
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>Dia 3 de 365. 1 Pedro 5:7: Tem uma coisa que você não contou para ninguém. Deus já sabe. #fe #ansiedade #paz #palavradodia</t>
+          <t>Dia 81 de 365. 1 Pedro 5:7: Tem uma coisa que você não contou para ninguém. Deus já sabe. #fe #ansiedade #paz #palavradodia</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
@@ -3998,7 +3998,7 @@
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>Dia 4 de 365. João 14:27: A paz que o mundo vende acaba. Essa não. #fe #ansiedade #paz #palavradodia</t>
+          <t>Dia 82 de 365. João 14:27: A paz que o mundo vende acaba. Essa não. #fe #ansiedade #paz #palavradodia</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
@@ -4041,7 +4041,7 @@
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>Dia 5 de 365. Salmos 94:19: Quando os pensamentos não param, leia isso. #fe #ansiedade #paz #palavradodia</t>
+          <t>Dia 83 de 365. Salmos 94:19: Quando os pensamentos não param, leia isso. #fe #ansiedade #paz #palavradodia</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
@@ -4084,7 +4084,7 @@
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>Dia 6 de 365. Isaías 26:3: Existe um tipo de paz que só vem de um lugar. #fe #ansiedade #paz #palavradodia</t>
+          <t>Dia 84 de 365. Isaías 26:3: Existe um tipo de paz que só vem de um lugar. #fe #ansiedade #paz #palavradodia</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr">
@@ -4127,7 +4127,7 @@
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>Dia 7 de 365. Salmos 46:10: Às vezes a resposta é parar. #fe #ansiedade #paz #palavradodia</t>
+          <t>Dia 85 de 365. Salmos 46:10: Às vezes a resposta é parar. #fe #ansiedade #paz #palavradodia</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
@@ -4170,7 +4170,7 @@
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>Dia 8 de 365. Mateus 11:28-30: Cansado de carregar tudo sozinho? #fe #ansiedade #paz #palavradodia</t>
+          <t>Dia 86 de 365. Mateus 11:28-30: Cansado de carregar tudo sozinho? #fe #ansiedade #paz #palavradodia</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr">
@@ -4213,7 +4213,7 @@
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>Dia 9 de 365. Salmos 55:22: O que você está carregando que não é seu para carregar? #fe #ansiedade #paz #palavradodia</t>
+          <t>Dia 87 de 365. Salmos 55:22: O que você está carregando que não é seu para carregar? #fe #ansiedade #paz #palavradodia</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
@@ -4256,7 +4256,7 @@
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t>Dia 10 de 365. Provérbios 12:25: Uma palavra boa muda o dia de alguém. Inclusive o seu. #fe #ansiedade #paz #palavradodia</t>
+          <t>Dia 88 de 365. Provérbios 12:25: Uma palavra boa muda o dia de alguém. Inclusive o seu. #fe #ansiedade #paz #palavradodia</t>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr">
@@ -4299,7 +4299,7 @@
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>Dia 11 de 365. Salmos 4:8: Para quem não consegue dormir de preocupação. #fe #ansiedade #paz #palavradodia</t>
+          <t>Dia 89 de 365. Salmos 4:8: Para quem não consegue dormir de preocupação. #fe #ansiedade #paz #palavradodia</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
@@ -4342,7 +4342,7 @@
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>Dia 12 de 365. Isaías 41:10: Se o medo de hoje parece maior que você, ouça isso. #fe #ansiedade #paz #palavradodia</t>
+          <t>Dia 90 de 365. Isaías 41:10: Se o medo de hoje parece maior que você, ouça isso. #fe #ansiedade #paz #palavradodia</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr">
@@ -4385,7 +4385,7 @@
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>Dia 13 de 365. Salmos 23:1-3: O salmo que milhões repetem quando a vida aperta. #fe #ansiedade #paz #palavradodia</t>
+          <t>Dia 91 de 365. Salmos 23:1-3: O salmo que milhões repetem quando a vida aperta. #fe #ansiedade #paz #palavradodia</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
@@ -4428,7 +4428,7 @@
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>Dia 14 de 365. Romanos 8:28: Nem tudo que acontece é bom. Mas veja o que este versículo diz. #fe #ansiedade #paz #palavradodia</t>
+          <t>Dia 92 de 365. Romanos 8:28: Nem tudo que acontece é bom. Mas veja o que este versículo diz. #fe #ansiedade #paz #palavradodia</t>
         </is>
       </c>
       <c r="E93" s="2" t="inlineStr">
@@ -4471,7 +4471,7 @@
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>Dia 15 de 365. 2 Timóteo 1:7: O medo não veio de Deus. #fe #ansiedade #paz #palavradodia</t>
+          <t>Dia 93 de 365. 2 Timóteo 1:7: O medo não veio de Deus. #fe #ansiedade #paz #palavradodia</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">

--- a/legendas-365.xlsx
+++ b/legendas-365.xlsx
@@ -4514,7 +4514,7 @@
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>Dia 16 de 365. Salmos 34:4: Busquei, e Ele respondeu. #fe #ansiedade #paz #palavradodia</t>
+          <t>Dia 94 de 365. Salmos 34:4: Busquei, e Ele respondeu. #fe #ansiedade #paz #palavradodia</t>
         </is>
       </c>
       <c r="E95" s="2" t="inlineStr">
@@ -4557,7 +4557,7 @@
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>Dia 17 de 365. Salmos 61:2: Quando o coração desfalece, para onde você corre? #fe #ansiedade #paz #palavradodia</t>
+          <t>Dia 95 de 365. Salmos 61:2: Quando o coração desfalece, para onde você corre? #fe #ansiedade #paz #palavradodia</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
@@ -4600,7 +4600,7 @@
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t>Dia 18 de 365. Filipenses 4:8: Mude o que você alimenta na mente e o dia muda. #fe #ansiedade #paz #palavradodia</t>
+          <t>Dia 96 de 365. Filipenses 4:8: Mude o que você alimenta na mente e o dia muda. #fe #ansiedade #paz #palavradodia</t>
         </is>
       </c>
       <c r="E97" s="2" t="inlineStr">
@@ -4643,7 +4643,7 @@
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>Dia 19 de 365. Salmos 139:23-24: Uma oração para quem está com o coração inquieto. #fe #ansiedade #paz #palavradodia</t>
+          <t>Dia 97 de 365. Salmos 139:23-24: Uma oração para quem está com o coração inquieto. #fe #ansiedade #paz #palavradodia</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr">
@@ -4686,7 +4686,7 @@
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t>Dia 20 de 365. Lucas 12:25-26: Preocupação já resolveu algum problema seu? #fe #ansiedade #paz #palavradodia</t>
+          <t>Dia 98 de 365. Lucas 12:25-26: Preocupação já resolveu algum problema seu? #fe #ansiedade #paz #palavradodia</t>
         </is>
       </c>
       <c r="E99" s="2" t="inlineStr">
@@ -4729,7 +4729,7 @@
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>Dia 21 de 365. Josué 1:9: Uma ordem e uma promessa no mesmo versículo. #fe #ansiedade #paz #palavradodia</t>
+          <t>Dia 99 de 365. Josué 1:9: Uma ordem e uma promessa no mesmo versículo. #fe #ansiedade #paz #palavradodia</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr">
@@ -4772,7 +4772,7 @@
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t>Dia 22 de 365. Salmos 121:1-2: De onde vem o seu socorro? #fe #ansiedade #paz #palavradodia</t>
+          <t>Dia 100 de 365. Salmos 121:1-2: De onde vem o seu socorro? #fe #ansiedade #paz #palavradodia</t>
         </is>
       </c>
       <c r="E101" s="2" t="inlineStr">
@@ -4815,7 +4815,7 @@
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>Dia 23 de 365. Isaías 40:31: Para quem está sem forças para continuar. #fe #ansiedade #paz #palavradodia</t>
+          <t>Dia 101 de 365. Isaías 40:31: Para quem está sem forças para continuar. #fe #ansiedade #paz #palavradodia</t>
         </is>
       </c>
       <c r="E102" s="2" t="inlineStr">
@@ -4858,7 +4858,7 @@
       </c>
       <c r="D103" s="2" t="inlineStr">
         <is>
-          <t>Dia 24 de 365. Êxodo 14:14: Tem batalhas que não são suas para lutar. #fe #ansiedade #paz #palavradodia</t>
+          <t>Dia 102 de 365. Êxodo 14:14: Tem batalhas que não são suas para lutar. #fe #ansiedade #paz #palavradodia</t>
         </is>
       </c>
       <c r="E103" s="2" t="inlineStr">
@@ -4901,7 +4901,7 @@
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>Dia 25 de 365. Salmos 56:3: Uma frase curta para repetir quando o medo chegar. #fe #ansiedade #paz #palavradodia</t>
+          <t>Dia 103 de 365. Salmos 56:3: Uma frase curta para repetir quando o medo chegar. #fe #ansiedade #paz #palavradodia</t>
         </is>
       </c>
       <c r="E104" s="2" t="inlineStr">
@@ -4944,7 +4944,7 @@
       </c>
       <c r="D105" s="2" t="inlineStr">
         <is>
-          <t>Dia 26 de 365. Mateus 6:26: Olhe os pássaros lá fora. #fe #ansiedade #paz #palavradodia</t>
+          <t>Dia 104 de 365. Mateus 6:26: Olhe os pássaros lá fora. #fe #ansiedade #paz #palavradodia</t>
         </is>
       </c>
       <c r="E105" s="2" t="inlineStr">
@@ -4987,7 +4987,7 @@
       </c>
       <c r="D106" s="2" t="inlineStr">
         <is>
-          <t>Dia 27 de 365. Salmos 3:3: Quando você está de cabeça baixa. #fe #ansiedade #paz #palavradodia</t>
+          <t>Dia 105 de 365. Salmos 3:3: Quando você está de cabeça baixa. #fe #ansiedade #paz #palavradodia</t>
         </is>
       </c>
       <c r="E106" s="2" t="inlineStr">
@@ -5030,7 +5030,7 @@
       </c>
       <c r="D107" s="2" t="inlineStr">
         <is>
-          <t>Dia 28 de 365. Sofonias 3:17: Deus se alegra com você. Já pensou nisso? #fe #ansiedade #paz #palavradodia</t>
+          <t>Dia 106 de 365. Sofonias 3:17: Deus se alegra com você. Já pensou nisso? #fe #ansiedade #paz #palavradodia</t>
         </is>
       </c>
       <c r="E107" s="2" t="inlineStr">
@@ -5073,7 +5073,7 @@
       </c>
       <c r="D108" s="2" t="inlineStr">
         <is>
-          <t>Dia 29 de 365. João 16:33: Jesus nunca prometeu uma vida sem problemas. #fe #ansiedade #paz #palavradodia</t>
+          <t>Dia 107 de 365. João 16:33: Jesus nunca prometeu uma vida sem problemas. #fe #ansiedade #paz #palavradodia</t>
         </is>
       </c>
       <c r="E108" s="2" t="inlineStr">
@@ -5116,7 +5116,7 @@
       </c>
       <c r="D109" s="2" t="inlineStr">
         <is>
-          <t>Dia 30 de 365. Salmos 16:8: O segredo de quem não é abalado. #fe #ansiedade #paz #palavradodia</t>
+          <t>Dia 108 de 365. Salmos 16:8: O segredo de quem não é abalado. #fe #ansiedade #paz #palavradodia</t>
         </is>
       </c>
       <c r="E109" s="2" t="inlineStr">
@@ -5159,7 +5159,7 @@
       </c>
       <c r="D110" s="2" t="inlineStr">
         <is>
-          <t>Dia 31 de 365. Salmos 27:1: Se Deus é sua luz, de quem você vai ter medo? #fe #ansiedade #paz #palavradodia</t>
+          <t>Dia 109 de 365. Salmos 27:1: Se Deus é sua luz, de quem você vai ter medo? #fe #ansiedade #paz #palavradodia</t>
         </is>
       </c>
       <c r="E110" s="2" t="inlineStr">
@@ -5202,7 +5202,7 @@
       </c>
       <c r="D111" s="2" t="inlineStr">
         <is>
-          <t>Dia 32 de 365. Deuteronômio 31:6: Você não vai enfrentar isso sozinho. #fe #coragem #medo #palavradodia</t>
+          <t>Dia 110 de 365. Deuteronômio 31:6: Você não vai enfrentar isso sozinho. #fe #coragem #medo #palavradodia</t>
         </is>
       </c>
       <c r="E111" s="2" t="inlineStr">
@@ -5245,7 +5245,7 @@
       </c>
       <c r="D112" s="2" t="inlineStr">
         <is>
-          <t>Dia 33 de 365. Salmos 118:6: Uma pergunta para quem tem medo do que os outros vão fazer. #fe #coragem #medo #palavradodia</t>
+          <t>Dia 111 de 365. Salmos 118:6: Uma pergunta para quem tem medo do que os outros vão fazer. #fe #coragem #medo #palavradodia</t>
         </is>
       </c>
       <c r="E112" s="2" t="inlineStr">
@@ -5288,7 +5288,7 @@
       </c>
       <c r="D113" s="2" t="inlineStr">
         <is>
-          <t>Dia 34 de 365. Isaías 43:1-2: Você passou pelas águas e não se afogou. #fe #coragem #medo #palavradodia</t>
+          <t>Dia 112 de 365. Isaías 43:1-2: Você passou pelas águas e não se afogou. #fe #coragem #medo #palavradodia</t>
         </is>
       </c>
       <c r="E113" s="2" t="inlineStr">
@@ -5331,7 +5331,7 @@
       </c>
       <c r="D114" s="2" t="inlineStr">
         <is>
-          <t>Dia 35 de 365. Salmos 23:4: Para quem está atravessando um vale escuro. #fe #coragem #medo #palavradodia</t>
+          <t>Dia 113 de 365. Salmos 23:4: Para quem está atravessando um vale escuro. #fe #coragem #medo #palavradodia</t>
         </is>
       </c>
       <c r="E114" s="2" t="inlineStr">
@@ -5374,7 +5374,7 @@
       </c>
       <c r="D115" s="2" t="inlineStr">
         <is>
-          <t>Dia 36 de 365. Romanos 8:31: Se Deus é por você, quem será contra? #fe #coragem #medo #palavradodia</t>
+          <t>Dia 114 de 365. Romanos 8:31: Se Deus é por você, quem será contra? #fe #coragem #medo #palavradodia</t>
         </is>
       </c>
       <c r="E115" s="2" t="inlineStr">
@@ -5417,7 +5417,7 @@
       </c>
       <c r="D116" s="2" t="inlineStr">
         <is>
-          <t>Dia 37 de 365. Hebreus 13:6: Diga em voz alta: o Senhor é o meu ajudador. #fe #coragem #medo #palavradodia</t>
+          <t>Dia 115 de 365. Hebreus 13:6: Diga em voz alta: o Senhor é o meu ajudador. #fe #coragem #medo #palavradodia</t>
         </is>
       </c>
       <c r="E116" s="2" t="inlineStr">
@@ -5460,7 +5460,7 @@
       </c>
       <c r="D117" s="2" t="inlineStr">
         <is>
-          <t>Dia 38 de 365. Provérbios 28:1: Por que algumas pessoas parecem não ter medo? #fe #coragem #medo #palavradodia</t>
+          <t>Dia 116 de 365. Provérbios 28:1: Por que algumas pessoas parecem não ter medo? #fe #coragem #medo #palavradodia</t>
         </is>
       </c>
       <c r="E117" s="2" t="inlineStr">
@@ -5503,7 +5503,7 @@
       </c>
       <c r="D118" s="2" t="inlineStr">
         <is>
-          <t>Dia 39 de 365. Salmos 91:1-2: O salmo da proteção. #fe #coragem #medo #palavradodia</t>
+          <t>Dia 117 de 365. Salmos 91:1-2: O salmo da proteção. #fe #coragem #medo #palavradodia</t>
         </is>
       </c>
       <c r="E118" s="2" t="inlineStr">
@@ -5546,7 +5546,7 @@
       </c>
       <c r="D119" s="2" t="inlineStr">
         <is>
-          <t>Dia 40 de 365. Josué 1:7: Coragem para fazer o certo, não só o fácil. #fe #coragem #medo #palavradodia</t>
+          <t>Dia 118 de 365. Josué 1:7: Coragem para fazer o certo, não só o fácil. #fe #coragem #medo #palavradodia</t>
         </is>
       </c>
       <c r="E119" s="2" t="inlineStr">
@@ -5589,7 +5589,7 @@
       </c>
       <c r="D120" s="2" t="inlineStr">
         <is>
-          <t>Dia 41 de 365. 1 Samuel 17:45: Davi diante do gigante. #fe #coragem #medo #palavradodia</t>
+          <t>Dia 119 de 365. 1 Samuel 17:45: Davi diante do gigante. #fe #coragem #medo #palavradodia</t>
         </is>
       </c>
       <c r="E120" s="2" t="inlineStr">
@@ -5632,7 +5632,7 @@
       </c>
       <c r="D121" s="2" t="inlineStr">
         <is>
-          <t>Dia 42 de 365. Salmos 27:14: Coragem também é saber esperar. #fe #coragem #medo #palavradodia</t>
+          <t>Dia 120 de 365. Salmos 27:14: Coragem também é saber esperar. #fe #coragem #medo #palavradodia</t>
         </is>
       </c>
       <c r="E121" s="2" t="inlineStr">
@@ -5675,7 +5675,7 @@
       </c>
       <c r="D122" s="2" t="inlineStr">
         <is>
-          <t>Dia 43 de 365. Isaías 12:2: Confiar sem medo. Dá para treinar isso? #fe #coragem #medo #palavradodia</t>
+          <t>Dia 121 de 365. Isaías 12:2: Confiar sem medo. Dá para treinar isso? #fe #coragem #medo #palavradodia</t>
         </is>
       </c>
       <c r="E122" s="2" t="inlineStr">
@@ -5718,7 +5718,7 @@
       </c>
       <c r="D123" s="2" t="inlineStr">
         <is>
-          <t>Dia 44 de 365. 2 Crônicas 20:15: A batalha não é sua. #fe #coragem #medo #palavradodia</t>
+          <t>Dia 122 de 365. 2 Crônicas 20:15: A batalha não é sua. #fe #coragem #medo #palavradodia</t>
         </is>
       </c>
       <c r="E123" s="2" t="inlineStr">
@@ -5761,7 +5761,7 @@
       </c>
       <c r="D124" s="2" t="inlineStr">
         <is>
-          <t>Dia 45 de 365. Salmos 46:1-2: Mesmo que tudo desabe. #fe #coragem #medo #palavradodia</t>
+          <t>Dia 123 de 365. Salmos 46:1-2: Mesmo que tudo desabe. #fe #coragem #medo #palavradodia</t>
         </is>
       </c>
       <c r="E124" s="2" t="inlineStr">
@@ -5804,7 +5804,7 @@
       </c>
       <c r="D125" s="2" t="inlineStr">
         <is>
-          <t>Dia 46 de 365. Marcos 4:39-40: Jesus dormia no meio da tempestade. #fe #coragem #medo #palavradodia</t>
+          <t>Dia 124 de 365. Marcos 4:39-40: Jesus dormia no meio da tempestade. #fe #coragem #medo #palavradodia</t>
         </is>
       </c>
       <c r="E125" s="2" t="inlineStr">
@@ -5847,7 +5847,7 @@
       </c>
       <c r="D126" s="2" t="inlineStr">
         <is>
-          <t>Dia 47 de 365. Mateus 14:29-31: Pedro andou sobre as águas. Até olhar para o vento. #fe #coragem #medo #palavradodia</t>
+          <t>Dia 125 de 365. Mateus 14:29-31: Pedro andou sobre as águas. Até olhar para o vento. #fe #coragem #medo #palavradodia</t>
         </is>
       </c>
       <c r="E126" s="2" t="inlineStr">
@@ -5890,7 +5890,7 @@
       </c>
       <c r="D127" s="2" t="inlineStr">
         <is>
-          <t>Dia 48 de 365. Salmos 112:7: Medo de notícia ruim? #fe #coragem #medo #palavradodia</t>
+          <t>Dia 126 de 365. Salmos 112:7: Medo de notícia ruim? #fe #coragem #medo #palavradodia</t>
         </is>
       </c>
       <c r="E127" s="2" t="inlineStr">
@@ -5933,7 +5933,7 @@
       </c>
       <c r="D128" s="2" t="inlineStr">
         <is>
-          <t>Dia 49 de 365. Lucas 1:37: Para quem acha que é tarde demais. #fe #coragem #medo #palavradodia</t>
+          <t>Dia 127 de 365. Lucas 1:37: Para quem acha que é tarde demais. #fe #coragem #medo #palavradodia</t>
         </is>
       </c>
       <c r="E128" s="2" t="inlineStr">
@@ -5976,7 +5976,7 @@
       </c>
       <c r="D129" s="2" t="inlineStr">
         <is>
-          <t>Dia 50 de 365. Juízes 6:12: Deus chamou de valente um homem escondido. #fe #coragem #medo #palavradodia</t>
+          <t>Dia 128 de 365. Juízes 6:12: Deus chamou de valente um homem escondido. #fe #coragem #medo #palavradodia</t>
         </is>
       </c>
       <c r="E129" s="2" t="inlineStr">
@@ -6019,7 +6019,7 @@
       </c>
       <c r="D130" s="2" t="inlineStr">
         <is>
-          <t>Dia 51 de 365. Salmos 31:24: Uma palavra para todos que esperam no Senhor. #fe #coragem #medo #palavradodia</t>
+          <t>Dia 129 de 365. Salmos 31:24: Uma palavra para todos que esperam no Senhor. #fe #coragem #medo #palavradodia</t>
         </is>
       </c>
       <c r="E130" s="2" t="inlineStr">
@@ -6062,7 +6062,7 @@
       </c>
       <c r="D131" s="2" t="inlineStr">
         <is>
-          <t>Dia 52 de 365. Ester 4:14: Talvez você esteja exatamente onde precisa estar. #fe #coragem #medo #palavradodia</t>
+          <t>Dia 130 de 365. Ester 4:14: Talvez você esteja exatamente onde precisa estar. #fe #coragem #medo #palavradodia</t>
         </is>
       </c>
       <c r="E131" s="2" t="inlineStr">
@@ -6105,7 +6105,7 @@
       </c>
       <c r="D132" s="2" t="inlineStr">
         <is>
-          <t>Dia 53 de 365. Daniel 3:17-18: Fé que não depende do resultado. #fe #coragem #medo #palavradodia</t>
+          <t>Dia 131 de 365. Daniel 3:17-18: Fé que não depende do resultado. #fe #coragem #medo #palavradodia</t>
         </is>
       </c>
       <c r="E132" s="2" t="inlineStr">
@@ -6148,7 +6148,7 @@
       </c>
       <c r="D133" s="2" t="inlineStr">
         <is>
-          <t>Dia 54 de 365. Atos 18:9-10: Não se cale. Eu estou com você. #fe #coragem #medo #palavradodia</t>
+          <t>Dia 132 de 365. Atos 18:9-10: Não se cale. Eu estou com você. #fe #coragem #medo #palavradodia</t>
         </is>
       </c>
       <c r="E133" s="2" t="inlineStr">
@@ -6191,7 +6191,7 @@
       </c>
       <c r="D134" s="2" t="inlineStr">
         <is>
-          <t>Dia 55 de 365. Salmos 138:3: Ele respondeu no dia em que você clamou. #fe #coragem #medo #palavradodia</t>
+          <t>Dia 133 de 365. Salmos 138:3: Ele respondeu no dia em que você clamou. #fe #coragem #medo #palavradodia</t>
         </is>
       </c>
       <c r="E134" s="2" t="inlineStr">
@@ -6234,7 +6234,7 @@
       </c>
       <c r="D135" s="2" t="inlineStr">
         <is>
-          <t>Dia 56 de 365. Isaías 54:17: Nenhuma arma forjada contra você prosperará. #fe #coragem #medo #palavradodia</t>
+          <t>Dia 134 de 365. Isaías 54:17: Nenhuma arma forjada contra você prosperará. #fe #coragem #medo #palavradodia</t>
         </is>
       </c>
       <c r="E135" s="2" t="inlineStr">
@@ -6277,7 +6277,7 @@
       </c>
       <c r="D136" s="2" t="inlineStr">
         <is>
-          <t>Dia 57 de 365. Provérbios 3:25-26: Não tema o pavor repentino. #fe #coragem #medo #palavradodia</t>
+          <t>Dia 135 de 365. Provérbios 3:25-26: Não tema o pavor repentino. #fe #coragem #medo #palavradodia</t>
         </is>
       </c>
       <c r="E136" s="2" t="inlineStr">
@@ -6320,7 +6320,7 @@
       </c>
       <c r="D137" s="2" t="inlineStr">
         <is>
-          <t>Dia 58 de 365. Neemias 4:14: Lembre-se de quem é o Senhor. #fe #coragem #medo #palavradodia</t>
+          <t>Dia 136 de 365. Neemias 4:14: Lembre-se de quem é o Senhor. #fe #coragem #medo #palavradodia</t>
         </is>
       </c>
       <c r="E137" s="2" t="inlineStr">
@@ -6363,7 +6363,7 @@
       </c>
       <c r="D138" s="2" t="inlineStr">
         <is>
-          <t>Dia 59 de 365. 2 Coríntios 12:9-10: Quando você é fraco, aí é que é forte. #fe #coragem #medo #palavradodia</t>
+          <t>Dia 137 de 365. 2 Coríntios 12:9-10: Quando você é fraco, aí é que é forte. #fe #coragem #medo #palavradodia</t>
         </is>
       </c>
       <c r="E138" s="2" t="inlineStr">
@@ -6406,7 +6406,7 @@
       </c>
       <c r="D139" s="2" t="inlineStr">
         <is>
-          <t>Dia 60 de 365. Lamentações 3:22-23: As misericórdias se renovam toda manhã. Inclusive nesta. #fe #esperanca #forca #palavradodia</t>
+          <t>Dia 138 de 365. Lamentações 3:22-23: As misericórdias se renovam toda manhã. Inclusive nesta. #fe #esperanca #forca #palavradodia</t>
         </is>
       </c>
       <c r="E139" s="2" t="inlineStr">
@@ -6449,7 +6449,7 @@
       </c>
       <c r="D140" s="2" t="inlineStr">
         <is>
-          <t>Dia 61 de 365. Jeremias 29:11: Deus tem planos para você. Bons. #fe #esperanca #forca #palavradodia</t>
+          <t>Dia 139 de 365. Jeremias 29:11: Deus tem planos para você. Bons. #fe #esperanca #forca #palavradodia</t>
         </is>
       </c>
       <c r="E140" s="2" t="inlineStr">
@@ -6492,7 +6492,7 @@
       </c>
       <c r="D141" s="2" t="inlineStr">
         <is>
-          <t>Dia 62 de 365. Romanos 15:13: Uma bênção para quem perdeu a esperança. #fe #esperanca #forca #palavradodia</t>
+          <t>Dia 140 de 365. Romanos 15:13: Uma bênção para quem perdeu a esperança. #fe #esperanca #forca #palavradodia</t>
         </is>
       </c>
       <c r="E141" s="2" t="inlineStr">
@@ -6535,7 +6535,7 @@
       </c>
       <c r="D142" s="2" t="inlineStr">
         <is>
-          <t>Dia 63 de 365. Salmos 42:11: Por que estás abatida, ó minha alma? #fe #esperanca #forca #palavradodia</t>
+          <t>Dia 141 de 365. Salmos 42:11: Por que estás abatida, ó minha alma? #fe #esperanca #forca #palavradodia</t>
         </is>
       </c>
       <c r="E142" s="2" t="inlineStr">
@@ -6578,7 +6578,7 @@
       </c>
       <c r="D143" s="2" t="inlineStr">
         <is>
-          <t>Dia 64 de 365. Isaías 43:19: Deus está fazendo algo novo. Você não percebe? #fe #esperanca #forca #palavradodia</t>
+          <t>Dia 142 de 365. Isaías 43:19: Deus está fazendo algo novo. Você não percebe? #fe #esperanca #forca #palavradodia</t>
         </is>
       </c>
       <c r="E143" s="2" t="inlineStr">
@@ -6621,7 +6621,7 @@
       </c>
       <c r="D144" s="2" t="inlineStr">
         <is>
-          <t>Dia 65 de 365. Romanos 5:3-5: A dor não é o fim da história. #fe #esperanca #forca #palavradodia</t>
+          <t>Dia 143 de 365. Romanos 5:3-5: A dor não é o fim da história. #fe #esperanca #forca #palavradodia</t>
         </is>
       </c>
       <c r="E144" s="2" t="inlineStr">
@@ -6664,7 +6664,7 @@
       </c>
       <c r="D145" s="2" t="inlineStr">
         <is>
-          <t>Dia 66 de 365. 2 Coríntios 4:16-18: Por fora você cansa. Por dentro, algo se renova. #fe #esperanca #forca #palavradodia</t>
+          <t>Dia 144 de 365. 2 Coríntios 4:16-18: Por fora você cansa. Por dentro, algo se renova. #fe #esperanca #forca #palavradodia</t>
         </is>
       </c>
       <c r="E145" s="2" t="inlineStr">
@@ -6707,7 +6707,7 @@
       </c>
       <c r="D146" s="2" t="inlineStr">
         <is>
-          <t>Dia 67 de 365. Salmos 30:5: O choro pode durar uma noite. #fe #esperanca #forca #palavradodia</t>
+          <t>Dia 145 de 365. Salmos 30:5: O choro pode durar uma noite. #fe #esperanca #forca #palavradodia</t>
         </is>
       </c>
       <c r="E146" s="2" t="inlineStr">
@@ -6750,7 +6750,7 @@
       </c>
       <c r="D147" s="2" t="inlineStr">
         <is>
-          <t>Dia 68 de 365. Habacuque 3:17-18: Mesmo que nada dê certo. #fe #esperanca #forca #palavradodia</t>
+          <t>Dia 146 de 365. Habacuque 3:17-18: Mesmo que nada dê certo. #fe #esperanca #forca #palavradodia</t>
         </is>
       </c>
       <c r="E147" s="2" t="inlineStr">
@@ -6793,7 +6793,7 @@
       </c>
       <c r="D148" s="2" t="inlineStr">
         <is>
-          <t>Dia 69 de 365. Hebreus 6:19: Uma âncora para a alma. #fe #esperanca #forca #palavradodia</t>
+          <t>Dia 147 de 365. Hebreus 6:19: Uma âncora para a alma. #fe #esperanca #forca #palavradodia</t>
         </is>
       </c>
       <c r="E148" s="2" t="inlineStr">
@@ -6836,7 +6836,7 @@
       </c>
       <c r="D149" s="2" t="inlineStr">
         <is>
-          <t>Dia 70 de 365. Salmos 40:1-2: Esperei com paciência. #fe #esperanca #forca #palavradodia</t>
+          <t>Dia 148 de 365. Salmos 40:1-2: Esperei com paciência. #fe #esperanca #forca #palavradodia</t>
         </is>
       </c>
       <c r="E149" s="2" t="inlineStr">
@@ -6879,7 +6879,7 @@
       </c>
       <c r="D150" s="2" t="inlineStr">
         <is>
-          <t>Dia 71 de 365. Isaías 61:3: Coroa em vez de cinzas. #fe #esperanca #forca #palavradodia</t>
+          <t>Dia 149 de 365. Isaías 61:3: Coroa em vez de cinzas. #fe #esperanca #forca #palavradodia</t>
         </is>
       </c>
       <c r="E150" s="2" t="inlineStr">
@@ -6922,7 +6922,7 @@
       </c>
       <c r="D151" s="2" t="inlineStr">
         <is>
-          <t>Dia 72 de 365. Romanos 8:18: O que vem é maior do que o que dói. #fe #esperanca #forca #palavradodia</t>
+          <t>Dia 150 de 365. Romanos 8:18: O que vem é maior do que o que dói. #fe #esperanca #forca #palavradodia</t>
         </is>
       </c>
       <c r="E151" s="2" t="inlineStr">
@@ -6965,7 +6965,7 @@
       </c>
       <c r="D152" s="2" t="inlineStr">
         <is>
-          <t>Dia 73 de 365. Miqueias 7:8: Caí, mas vou me levantar. #fe #esperanca #forca #palavradodia</t>
+          <t>Dia 151 de 365. Miqueias 7:8: Caí, mas vou me levantar. #fe #esperanca #forca #palavradodia</t>
         </is>
       </c>
       <c r="E152" s="2" t="inlineStr">
@@ -7008,7 +7008,7 @@
       </c>
       <c r="D153" s="2" t="inlineStr">
         <is>
-          <t>Dia 74 de 365. Salmos 147:3: Para quem está de coração partido. #fe #esperanca #forca #palavradodia</t>
+          <t>Dia 152 de 365. Salmos 147:3: Para quem está de coração partido. #fe #esperanca #forca #palavradodia</t>
         </is>
       </c>
       <c r="E153" s="2" t="inlineStr">
@@ -7051,7 +7051,7 @@
       </c>
       <c r="D154" s="2" t="inlineStr">
         <is>
-          <t>Dia 75 de 365. Joel 2:25: Deus pode restituir os anos perdidos. #fe #esperanca #forca #palavradodia</t>
+          <t>Dia 153 de 365. Joel 2:25: Deus pode restituir os anos perdidos. #fe #esperanca #forca #palavradodia</t>
         </is>
       </c>
       <c r="E154" s="2" t="inlineStr">
@@ -7094,7 +7094,7 @@
       </c>
       <c r="D155" s="2" t="inlineStr">
         <is>
-          <t>Dia 76 de 365. Jó 42:10: A história de Jó não termina na perda. #fe #esperanca #forca #palavradodia</t>
+          <t>Dia 154 de 365. Jó 42:10: A história de Jó não termina na perda. #fe #esperanca #forca #palavradodia</t>
         </is>
       </c>
       <c r="E155" s="2" t="inlineStr">
@@ -7137,7 +7137,7 @@
       </c>
       <c r="D156" s="2" t="inlineStr">
         <is>
-          <t>Dia 77 de 365. Salmos 34:18: Deus está perto. Especialmente agora. #fe #esperanca #forca #palavradodia</t>
+          <t>Dia 155 de 365. Salmos 34:18: Deus está perto. Especialmente agora. #fe #esperanca #forca #palavradodia</t>
         </is>
       </c>
       <c r="E156" s="2" t="inlineStr">
@@ -7180,7 +7180,7 @@
       </c>
       <c r="D157" s="2" t="inlineStr">
         <is>
-          <t>Dia 78 de 365. Apocalipse 21:4: Um dia sem lágrimas. #fe #esperanca #forca #palavradodia</t>
+          <t>Dia 156 de 365. Apocalipse 21:4: Um dia sem lágrimas. #fe #esperanca #forca #palavradodia</t>
         </is>
       </c>
       <c r="E157" s="2" t="inlineStr">
@@ -7223,7 +7223,7 @@
       </c>
       <c r="D158" s="2" t="inlineStr">
         <is>
-          <t>Dia 79 de 365. Romanos 12:12: Três atitudes para dias difíceis. #fe #esperanca #forca #palavradodia</t>
+          <t>Dia 157 de 365. Romanos 12:12: Três atitudes para dias difíceis. #fe #esperanca #forca #palavradodia</t>
         </is>
       </c>
       <c r="E158" s="2" t="inlineStr">
@@ -7266,7 +7266,7 @@
       </c>
       <c r="D159" s="2" t="inlineStr">
         <is>
-          <t>Dia 80 de 365. Isaías 40:29: Ele dá força ao cansado. #fe #esperanca #forca #palavradodia</t>
+          <t>Dia 158 de 365. Isaías 40:29: Ele dá força ao cansado. #fe #esperanca #forca #palavradodia</t>
         </is>
       </c>
       <c r="E159" s="2" t="inlineStr">
@@ -7309,7 +7309,7 @@
       </c>
       <c r="D160" s="2" t="inlineStr">
         <is>
-          <t>Dia 81 de 365. Salmos 71:20: Você vai voltar a viver. #fe #esperanca #forca #palavradodia</t>
+          <t>Dia 159 de 365. Salmos 71:20: Você vai voltar a viver. #fe #esperanca #forca #palavradodia</t>
         </is>
       </c>
       <c r="E160" s="2" t="inlineStr">
@@ -7352,7 +7352,7 @@
       </c>
       <c r="D161" s="2" t="inlineStr">
         <is>
-          <t>Dia 82 de 365. 1 Pedro 1:3: Uma esperança viva. #fe #esperanca #forca #palavradodia</t>
+          <t>Dia 160 de 365. 1 Pedro 1:3: Uma esperança viva. #fe #esperanca #forca #palavradodia</t>
         </is>
       </c>
       <c r="E161" s="2" t="inlineStr">
@@ -7395,7 +7395,7 @@
       </c>
       <c r="D162" s="2" t="inlineStr">
         <is>
-          <t>Dia 83 de 365. Gênesis 50:20: O mal que planejaram contra você. #fe #esperanca #forca #palavradodia</t>
+          <t>Dia 161 de 365. Gênesis 50:20: O mal que planejaram contra você. #fe #esperanca #forca #palavradodia</t>
         </is>
       </c>
       <c r="E162" s="2" t="inlineStr">
@@ -7438,7 +7438,7 @@
       </c>
       <c r="D163" s="2" t="inlineStr">
         <is>
-          <t>Dia 84 de 365. Salmos 126:5-6: Quem semeia com lágrimas. #fe #esperanca #forca #palavradodia</t>
+          <t>Dia 162 de 365. Salmos 126:5-6: Quem semeia com lágrimas. #fe #esperanca #forca #palavradodia</t>
         </is>
       </c>
       <c r="E163" s="2" t="inlineStr">
@@ -7481,7 +7481,7 @@
       </c>
       <c r="D164" s="2" t="inlineStr">
         <is>
-          <t>Dia 85 de 365. Isaías 9:2: Uma luz no meio da escuridão. #fe #esperanca #forca #palavradodia</t>
+          <t>Dia 163 de 365. Isaías 9:2: Uma luz no meio da escuridão. #fe #esperanca #forca #palavradodia</t>
         </is>
       </c>
       <c r="E164" s="2" t="inlineStr">
@@ -7524,7 +7524,7 @@
       </c>
       <c r="D165" s="2" t="inlineStr">
         <is>
-          <t>Dia 86 de 365. Salmos 62:5: Descanse, ó minha alma. #fe #esperanca #forca #palavradodia</t>
+          <t>Dia 164 de 365. Salmos 62:5: Descanse, ó minha alma. #fe #esperanca #forca #palavradodia</t>
         </is>
       </c>
       <c r="E165" s="2" t="inlineStr">
@@ -7567,7 +7567,7 @@
       </c>
       <c r="D166" s="2" t="inlineStr">
         <is>
-          <t>Dia 87 de 365. Isaías 35:3-4: Fortalecei as mãos fracas. #fe #esperanca #forca #palavradodia</t>
+          <t>Dia 165 de 365. Isaías 35:3-4: Fortalecei as mãos fracas. #fe #esperanca #forca #palavradodia</t>
         </is>
       </c>
       <c r="E166" s="2" t="inlineStr">
@@ -7610,7 +7610,7 @@
       </c>
       <c r="D167" s="2" t="inlineStr">
         <is>
-          <t>Dia 88 de 365. 2 Coríntios 4:8-9: Apertado, mas não esmagado. #fe #esperanca #forca #palavradodia</t>
+          <t>Dia 166 de 365. 2 Coríntios 4:8-9: Apertado, mas não esmagado. #fe #esperanca #forca #palavradodia</t>
         </is>
       </c>
       <c r="E167" s="2" t="inlineStr">
@@ -7653,7 +7653,7 @@
       </c>
       <c r="D168" s="2" t="inlineStr">
         <is>
-          <t>Dia 89 de 365. Salmos 33:20-22: Nossa alma espera no Senhor. #fe #esperanca #forca #palavradodia</t>
+          <t>Dia 167 de 365. Salmos 33:20-22: Nossa alma espera no Senhor. #fe #esperanca #forca #palavradodia</t>
         </is>
       </c>
       <c r="E168" s="2" t="inlineStr">
@@ -7696,7 +7696,7 @@
       </c>
       <c r="D169" s="2" t="inlineStr">
         <is>
-          <t>Dia 90 de 365. Mateus 28:20: Até o fim. Todos os dias. #fe #esperanca #forca #palavradodia</t>
+          <t>Dia 168 de 365. Mateus 28:20: Até o fim. Todos os dias. #fe #esperanca #forca #palavradodia</t>
         </is>
       </c>
       <c r="E169" s="2" t="inlineStr">
@@ -7739,7 +7739,7 @@
       </c>
       <c r="D170" s="2" t="inlineStr">
         <is>
-          <t>Dia 91 de 365. Efésios 4:32: Perdoar não é dizer que não doeu. #fe #perdao #graca #palavradodia</t>
+          <t>Dia 169 de 365. Efésios 4:32: Perdoar não é dizer que não doeu. #fe #perdao #graca #palavradodia</t>
         </is>
       </c>
       <c r="E170" s="2" t="inlineStr">
@@ -7782,7 +7782,7 @@
       </c>
       <c r="D171" s="2" t="inlineStr">
         <is>
-          <t>Dia 92 de 365. Colossenses 3:13: Tem alguém que você ainda não perdoou? #fe #perdao #graca #palavradodia</t>
+          <t>Dia 170 de 365. Colossenses 3:13: Tem alguém que você ainda não perdoou? #fe #perdao #graca #palavradodia</t>
         </is>
       </c>
       <c r="E171" s="2" t="inlineStr">
@@ -7868,7 +7868,7 @@
       </c>
       <c r="D173" s="2" t="inlineStr">
         <is>
-          <t>Dia 94 de 365. Mateus 18:21-22: Quantas vezes eu tenho que perdoar? #fe #perdao #graca #palavradodia</t>
+          <t>Dia 172 de 365. Mateus 18:21-22: Quantas vezes eu tenho que perdoar? #fe #perdao #graca #palavradodia</t>
         </is>
       </c>
       <c r="E173" s="2" t="inlineStr">
@@ -7911,7 +7911,7 @@
       </c>
       <c r="D174" s="2" t="inlineStr">
         <is>
-          <t>Dia 95 de 365. 1 João 1:9: Para quem acha que errou demais. #fe #perdao #graca #palavradodia</t>
+          <t>Dia 173 de 365. 1 João 1:9: Para quem acha que errou demais. #fe #perdao #graca #palavradodia</t>
         </is>
       </c>
       <c r="E174" s="2" t="inlineStr">
@@ -7954,7 +7954,7 @@
       </c>
       <c r="D175" s="2" t="inlineStr">
         <is>
-          <t>Dia 96 de 365. Salmos 103:12: Até onde Deus jogou os seus erros? #fe #perdao #graca #palavradodia</t>
+          <t>Dia 174 de 365. Salmos 103:12: Até onde Deus jogou os seus erros? #fe #perdao #graca #palavradodia</t>
         </is>
       </c>
       <c r="E175" s="2" t="inlineStr">
@@ -7997,7 +7997,7 @@
       </c>
       <c r="D176" s="2" t="inlineStr">
         <is>
-          <t>Dia 97 de 365. Isaías 1:18: Ainda que seus pecados sejam como escarlate. #fe #perdao #graca #palavradodia</t>
+          <t>Dia 175 de 365. Isaías 1:18: Ainda que seus pecados sejam como escarlate. #fe #perdao #graca #palavradodia</t>
         </is>
       </c>
       <c r="E176" s="2" t="inlineStr">
@@ -8040,7 +8040,7 @@
       </c>
       <c r="D177" s="2" t="inlineStr">
         <is>
-          <t>Dia 98 de 365. Lucas 15:20: O pai correu. #fe #perdao #graca #palavradodia</t>
+          <t>Dia 176 de 365. Lucas 15:20: O pai correu. #fe #perdao #graca #palavradodia</t>
         </is>
       </c>
       <c r="E177" s="2" t="inlineStr">
@@ -8083,7 +8083,7 @@
       </c>
       <c r="D178" s="2" t="inlineStr">
         <is>
-          <t>Dia 99 de 365. Lucas 23:34: Jesus perdoou enquanto ainda doía. #fe #perdao #graca #palavradodia</t>
+          <t>Dia 177 de 365. Lucas 23:34: Jesus perdoou enquanto ainda doía. #fe #perdao #graca #palavradodia</t>
         </is>
       </c>
       <c r="E178" s="2" t="inlineStr">
@@ -8126,7 +8126,7 @@
       </c>
       <c r="D179" s="2" t="inlineStr">
         <is>
-          <t>Dia 100 de 365. Miqueias 7:18-19: Deus lança os pecados no fundo do mar. #fe #perdao #graca #palavradodia</t>
+          <t>Dia 178 de 365. Miqueias 7:18-19: Deus lança os pecados no fundo do mar. #fe #perdao #graca #palavradodia</t>
         </is>
       </c>
       <c r="E179" s="2" t="inlineStr">
@@ -8169,7 +8169,7 @@
       </c>
       <c r="D180" s="2" t="inlineStr">
         <is>
-          <t>Dia 101 de 365. Romanos 12:17-19: Não pague o mal com mal. #fe #perdao #graca #palavradodia</t>
+          <t>Dia 179 de 365. Romanos 12:17-19: Não pague o mal com mal. #fe #perdao #graca #palavradodia</t>
         </is>
       </c>
       <c r="E180" s="2" t="inlineStr">
@@ -8212,7 +8212,7 @@
       </c>
       <c r="D181" s="2" t="inlineStr">
         <is>
-          <t>Dia 102 de 365. Salmos 32:1-2: Feliz é quem foi perdoado. #fe #perdao #graca #palavradodia</t>
+          <t>Dia 180 de 365. Salmos 32:1-2: Feliz é quem foi perdoado. #fe #perdao #graca #palavradodia</t>
         </is>
       </c>
       <c r="E181" s="2" t="inlineStr">
@@ -8255,7 +8255,7 @@
       </c>
       <c r="D182" s="2" t="inlineStr">
         <is>
-          <t>Dia 103 de 365. Marcos 11:25: Antes de orar, solte. #fe #perdao #graca #palavradodia</t>
+          <t>Dia 181 de 365. Marcos 11:25: Antes de orar, solte. #fe #perdao #graca #palavradodia</t>
         </is>
       </c>
       <c r="E182" s="2" t="inlineStr">
@@ -8298,7 +8298,7 @@
       </c>
       <c r="D183" s="2" t="inlineStr">
         <is>
-          <t>Dia 104 de 365. Hebreus 8:12: Deus decide esquecer. #fe #perdao #graca #palavradodia</t>
+          <t>Dia 182 de 365. Hebreus 8:12: Deus decide esquecer. #fe #perdao #graca #palavradodia</t>
         </is>
       </c>
       <c r="E183" s="2" t="inlineStr">
@@ -8341,7 +8341,7 @@
       </c>
       <c r="D184" s="2" t="inlineStr">
         <is>
-          <t>Dia 105 de 365. Gênesis 45:4-5: José perdoou os irmãos que o venderam. #fe #perdao #graca #palavradodia</t>
+          <t>Dia 183 de 365. Gênesis 45:4-5: José perdoou os irmãos que o venderam. #fe #perdao #graca #palavradodia</t>
         </is>
       </c>
       <c r="E184" s="2" t="inlineStr">
@@ -8384,7 +8384,7 @@
       </c>
       <c r="D185" s="2" t="inlineStr">
         <is>
-          <t>Dia 106 de 365. Provérbios 19:11: Saber deixar passar é sabedoria. #fe #perdao #graca #palavradodia</t>
+          <t>Dia 184 de 365. Provérbios 19:11: Saber deixar passar é sabedoria. #fe #perdao #graca #palavradodia</t>
         </is>
       </c>
       <c r="E185" s="2" t="inlineStr">
@@ -8427,7 +8427,7 @@
       </c>
       <c r="D186" s="2" t="inlineStr">
         <is>
-          <t>Dia 107 de 365. 2 Coríntios 5:17: Você não é mais quem era. #fe #perdao #graca #palavradodia</t>
+          <t>Dia 185 de 365. 2 Coríntios 5:17: Você não é mais quem era. #fe #perdao #graca #palavradodia</t>
         </is>
       </c>
       <c r="E186" s="2" t="inlineStr">
@@ -8470,7 +8470,7 @@
       </c>
       <c r="D187" s="2" t="inlineStr">
         <is>
-          <t>Dia 108 de 365. Romanos 8:1: Nenhuma condenação. #fe #perdao #graca #palavradodia</t>
+          <t>Dia 186 de 365. Romanos 8:1: Nenhuma condenação. #fe #perdao #graca #palavradodia</t>
         </is>
       </c>
       <c r="E187" s="2" t="inlineStr">
@@ -8513,7 +8513,7 @@
       </c>
       <c r="D188" s="2" t="inlineStr">
         <is>
-          <t>Dia 109 de 365. Lucas 6:37: Não julgue, e não será julgado. #fe #perdao #graca #palavradodia</t>
+          <t>Dia 187 de 365. Lucas 6:37: Não julgue, e não será julgado. #fe #perdao #graca #palavradodia</t>
         </is>
       </c>
       <c r="E188" s="2" t="inlineStr">
@@ -8556,7 +8556,7 @@
       </c>
       <c r="D189" s="2" t="inlineStr">
         <is>
-          <t>Dia 110 de 365. Salmos 51:10: Uma oração para recomeçar por dentro. #fe #perdao #graca #palavradodia</t>
+          <t>Dia 188 de 365. Salmos 51:10: Uma oração para recomeçar por dentro. #fe #perdao #graca #palavradodia</t>
         </is>
       </c>
       <c r="E189" s="2" t="inlineStr">
@@ -8599,7 +8599,7 @@
       </c>
       <c r="D190" s="2" t="inlineStr">
         <is>
-          <t>Dia 111 de 365. Atos 3:19: Arrepender e ser renovado. #fe #perdao #graca #palavradodia</t>
+          <t>Dia 189 de 365. Atos 3:19: Arrepender e ser renovado. #fe #perdao #graca #palavradodia</t>
         </is>
       </c>
       <c r="E190" s="2" t="inlineStr">
@@ -8642,7 +8642,7 @@
       </c>
       <c r="D191" s="2" t="inlineStr">
         <is>
-          <t>Dia 112 de 365. Mateus 5:23-24: Antes da oferta, a reconciliação. #fe #perdao #graca #palavradodia</t>
+          <t>Dia 190 de 365. Mateus 5:23-24: Antes da oferta, a reconciliação. #fe #perdao #graca #palavradodia</t>
         </is>
       </c>
       <c r="E191" s="2" t="inlineStr">
@@ -8685,7 +8685,7 @@
       </c>
       <c r="D192" s="2" t="inlineStr">
         <is>
-          <t>Dia 113 de 365. Efésios 4:26-27: Não deixe o sol se pôr sobre a sua ira. #fe #perdao #graca #palavradodia</t>
+          <t>Dia 191 de 365. Efésios 4:26-27: Não deixe o sol se pôr sobre a sua ira. #fe #perdao #graca #palavradodia</t>
         </is>
       </c>
       <c r="E192" s="2" t="inlineStr">
@@ -8728,7 +8728,7 @@
       </c>
       <c r="D193" s="2" t="inlineStr">
         <is>
-          <t>Dia 114 de 365. Lucas 7:47: Quem foi muito perdoado, ama muito. #fe #perdao #graca #palavradodia</t>
+          <t>Dia 192 de 365. Lucas 7:47: Quem foi muito perdoado, ama muito. #fe #perdao #graca #palavradodia</t>
         </is>
       </c>
       <c r="E193" s="2" t="inlineStr">
@@ -8771,7 +8771,7 @@
       </c>
       <c r="D194" s="2" t="inlineStr">
         <is>
-          <t>Dia 115 de 365. João 8:10-11: Nem eu te condeno. #fe #perdao #graca #palavradodia</t>
+          <t>Dia 193 de 365. João 8:10-11: Nem eu te condeno. #fe #perdao #graca #palavradodia</t>
         </is>
       </c>
       <c r="E194" s="2" t="inlineStr">
@@ -8814,7 +8814,7 @@
       </c>
       <c r="D195" s="2" t="inlineStr">
         <is>
-          <t>Dia 116 de 365. Isaías 43:25: Deus apaga por amor a si mesmo. #fe #perdao #graca #palavradodia</t>
+          <t>Dia 194 de 365. Isaías 43:25: Deus apaga por amor a si mesmo. #fe #perdao #graca #palavradodia</t>
         </is>
       </c>
       <c r="E195" s="2" t="inlineStr">
@@ -8857,7 +8857,7 @@
       </c>
       <c r="D196" s="2" t="inlineStr">
         <is>
-          <t>Dia 117 de 365. Salmos 130:3-4: Se Deus guardasse a lista. #fe #perdao #graca #palavradodia</t>
+          <t>Dia 195 de 365. Salmos 130:3-4: Se Deus guardasse a lista. #fe #perdao #graca #palavradodia</t>
         </is>
       </c>
       <c r="E196" s="2" t="inlineStr">
@@ -8900,7 +8900,7 @@
       </c>
       <c r="D197" s="2" t="inlineStr">
         <is>
-          <t>Dia 118 de 365. Colossenses 2:13-14: A dívida foi pregada na cruz. #fe #perdao #graca #palavradodia</t>
+          <t>Dia 196 de 365. Colossenses 2:13-14: A dívida foi pregada na cruz. #fe #perdao #graca #palavradodia</t>
         </is>
       </c>
       <c r="E197" s="2" t="inlineStr">
@@ -8943,7 +8943,7 @@
       </c>
       <c r="D198" s="2" t="inlineStr">
         <is>
-          <t>Dia 119 de 365. 1 Pedro 3:9: Responda com bênção. #fe #perdao #graca #palavradodia</t>
+          <t>Dia 197 de 365. 1 Pedro 3:9: Responda com bênção. #fe #perdao #graca #palavradodia</t>
         </is>
       </c>
       <c r="E198" s="2" t="inlineStr">
@@ -8986,7 +8986,7 @@
       </c>
       <c r="D199" s="2" t="inlineStr">
         <is>
-          <t>Dia 120 de 365. Lucas 17:3-4: Perdoar também quando se repete. #fe #perdao #graca #palavradodia</t>
+          <t>Dia 198 de 365. Lucas 17:3-4: Perdoar também quando se repete. #fe #perdao #graca #palavradodia</t>
         </is>
       </c>
       <c r="E199" s="2" t="inlineStr">
@@ -9029,7 +9029,7 @@
       </c>
       <c r="D200" s="2" t="inlineStr">
         <is>
-          <t>Dia 121 de 365. Josué 24:15: Eu e a minha casa serviremos ao Senhor. #fe #familia #relacionamentos #palavradodia</t>
+          <t>Dia 199 de 365. Josué 24:15: Eu e a minha casa serviremos ao Senhor. #fe #familia #relacionamentos #palavradodia</t>
         </is>
       </c>
       <c r="E200" s="2" t="inlineStr">
@@ -9072,7 +9072,7 @@
       </c>
       <c r="D201" s="2" t="inlineStr">
         <is>
-          <t>Dia 122 de 365. Salmos 127:1: Se o Senhor não edificar a casa. #fe #familia #relacionamentos #palavradodia</t>
+          <t>Dia 200 de 365. Salmos 127:1: Se o Senhor não edificar a casa. #fe #familia #relacionamentos #palavradodia</t>
         </is>
       </c>
       <c r="E201" s="2" t="inlineStr">
@@ -9115,7 +9115,7 @@
       </c>
       <c r="D202" s="2" t="inlineStr">
         <is>
-          <t>Dia 123 de 365. Provérbios 22:6: Ensina a criança no caminho. #fe #familia #relacionamentos #palavradodia</t>
+          <t>Dia 201 de 365. Provérbios 22:6: Ensina a criança no caminho. #fe #familia #relacionamentos #palavradodia</t>
         </is>
       </c>
       <c r="E202" s="2" t="inlineStr">
@@ -9158,7 +9158,7 @@
       </c>
       <c r="D203" s="2" t="inlineStr">
         <is>
-          <t>Dia 124 de 365. Efésios 6:1-3: Honrar pai e mãe tem uma promessa. #fe #familia #relacionamentos #palavradodia</t>
+          <t>Dia 202 de 365. Efésios 6:1-3: Honrar pai e mãe tem uma promessa. #fe #familia #relacionamentos #palavradodia</t>
         </is>
       </c>
       <c r="E203" s="2" t="inlineStr">
@@ -9201,7 +9201,7 @@
       </c>
       <c r="D204" s="2" t="inlineStr">
         <is>
-          <t>Dia 125 de 365. Eclesiastes 4:9-10: Dois são melhores que um. #fe #familia #relacionamentos #palavradodia</t>
+          <t>Dia 203 de 365. Eclesiastes 4:9-10: Dois são melhores que um. #fe #familia #relacionamentos #palavradodia</t>
         </is>
       </c>
       <c r="E204" s="2" t="inlineStr">
@@ -9244,7 +9244,7 @@
       </c>
       <c r="D205" s="2" t="inlineStr">
         <is>
-          <t>Dia 126 de 365. Eclesiastes 4:12: O cordão de três dobras. #fe #familia #relacionamentos #palavradodia</t>
+          <t>Dia 204 de 365. Eclesiastes 4:12: O cordão de três dobras. #fe #familia #relacionamentos #palavradodia</t>
         </is>
       </c>
       <c r="E205" s="2" t="inlineStr">
@@ -9287,7 +9287,7 @@
       </c>
       <c r="D206" s="2" t="inlineStr">
         <is>
-          <t>Dia 127 de 365. Rute 1:16-17: Aonde quer que fores, irei. #fe #familia #relacionamentos #palavradodia</t>
+          <t>Dia 205 de 365. Rute 1:16-17: Aonde quer que fores, irei. #fe #familia #relacionamentos #palavradodia</t>
         </is>
       </c>
       <c r="E206" s="2" t="inlineStr">
@@ -9330,7 +9330,7 @@
       </c>
       <c r="D207" s="2" t="inlineStr">
         <is>
-          <t>Dia 128 de 365. Provérbios 17:17: O amigo ama em todo tempo. #fe #familia #relacionamentos #palavradodia</t>
+          <t>Dia 206 de 365. Provérbios 17:17: O amigo ama em todo tempo. #fe #familia #relacionamentos #palavradodia</t>
         </is>
       </c>
       <c r="E207" s="2" t="inlineStr">
@@ -9373,7 +9373,7 @@
       </c>
       <c r="D208" s="2" t="inlineStr">
         <is>
-          <t>Dia 129 de 365. Colossenses 3:14: Acima de tudo, o amor. #fe #familia #relacionamentos #palavradodia</t>
+          <t>Dia 207 de 365. Colossenses 3:14: Acima de tudo, o amor. #fe #familia #relacionamentos #palavradodia</t>
         </is>
       </c>
       <c r="E208" s="2" t="inlineStr">
@@ -9459,7 +9459,7 @@
       </c>
       <c r="D210" s="2" t="inlineStr">
         <is>
-          <t>Dia 131 de 365. Gênesis 2:24: Deixar e unir. #fe #familia #relacionamentos #palavradodia</t>
+          <t>Dia 209 de 365. Gênesis 2:24: Deixar e unir. #fe #familia #relacionamentos #palavradodia</t>
         </is>
       </c>
       <c r="E210" s="2" t="inlineStr">
@@ -9502,7 +9502,7 @@
       </c>
       <c r="D211" s="2" t="inlineStr">
         <is>
-          <t>Dia 132 de 365. Provérbios 31:10-11: Quem achará uma mulher virtuosa? #fe #familia #relacionamentos #palavradodia</t>
+          <t>Dia 210 de 365. Provérbios 31:10-11: Quem achará uma mulher virtuosa? #fe #familia #relacionamentos #palavradodia</t>
         </is>
       </c>
       <c r="E211" s="2" t="inlineStr">
@@ -9545,7 +9545,7 @@
       </c>
       <c r="D212" s="2" t="inlineStr">
         <is>
-          <t>Dia 133 de 365. Efésios 5:25: Amar como Cristo amou a igreja. #fe #familia #relacionamentos #palavradodia</t>
+          <t>Dia 211 de 365. Efésios 5:25: Amar como Cristo amou a igreja. #fe #familia #relacionamentos #palavradodia</t>
         </is>
       </c>
       <c r="E212" s="2" t="inlineStr">
@@ -9588,7 +9588,7 @@
       </c>
       <c r="D213" s="2" t="inlineStr">
         <is>
-          <t>Dia 134 de 365. Salmos 133:1: Como é bom viver em união. #fe #familia #relacionamentos #palavradodia</t>
+          <t>Dia 212 de 365. Salmos 133:1: Como é bom viver em união. #fe #familia #relacionamentos #palavradodia</t>
         </is>
       </c>
       <c r="E213" s="2" t="inlineStr">
@@ -9631,7 +9631,7 @@
       </c>
       <c r="D214" s="2" t="inlineStr">
         <is>
-          <t>Dia 135 de 365. Provérbios 15:1: A resposta branda desvia o furor. #fe #familia #relacionamentos #palavradodia</t>
+          <t>Dia 213 de 365. Provérbios 15:1: A resposta branda desvia o furor. #fe #familia #relacionamentos #palavradodia</t>
         </is>
       </c>
       <c r="E214" s="2" t="inlineStr">
@@ -9674,7 +9674,7 @@
       </c>
       <c r="D215" s="2" t="inlineStr">
         <is>
-          <t>Dia 136 de 365. Tiago 1:19: Ouvir mais, falar menos. #fe #familia #relacionamentos #palavradodia</t>
+          <t>Dia 214 de 365. Tiago 1:19: Ouvir mais, falar menos. #fe #familia #relacionamentos #palavradodia</t>
         </is>
       </c>
       <c r="E215" s="2" t="inlineStr">
@@ -9717,7 +9717,7 @@
       </c>
       <c r="D216" s="2" t="inlineStr">
         <is>
-          <t>Dia 137 de 365. 1 Pedro 4:8: O amor cobre muitos pecados. #fe #familia #relacionamentos #palavradodia</t>
+          <t>Dia 215 de 365. 1 Pedro 4:8: O amor cobre muitos pecados. #fe #familia #relacionamentos #palavradodia</t>
         </is>
       </c>
       <c r="E216" s="2" t="inlineStr">
@@ -9760,7 +9760,7 @@
       </c>
       <c r="D217" s="2" t="inlineStr">
         <is>
-          <t>Dia 138 de 365. Malaquias 4:6: Corações que voltam. #fe #familia #relacionamentos #palavradodia</t>
+          <t>Dia 216 de 365. Malaquias 4:6: Corações que voltam. #fe #familia #relacionamentos #palavradodia</t>
         </is>
       </c>
       <c r="E217" s="2" t="inlineStr">
@@ -9803,7 +9803,7 @@
       </c>
       <c r="D218" s="2" t="inlineStr">
         <is>
-          <t>Dia 139 de 365. Salmos 68:6: Deus faz o solitário habitar em família. #fe #familia #relacionamentos #palavradodia</t>
+          <t>Dia 217 de 365. Salmos 68:6: Deus faz o solitário habitar em família. #fe #familia #relacionamentos #palavradodia</t>
         </is>
       </c>
       <c r="E218" s="2" t="inlineStr">
@@ -9846,7 +9846,7 @@
       </c>
       <c r="D219" s="2" t="inlineStr">
         <is>
-          <t>Dia 140 de 365. Provérbios 27:17: Ferro afia ferro. #fe #familia #relacionamentos #palavradodia</t>
+          <t>Dia 218 de 365. Provérbios 27:17: Ferro afia ferro. #fe #familia #relacionamentos #palavradodia</t>
         </is>
       </c>
       <c r="E219" s="2" t="inlineStr">
@@ -9889,7 +9889,7 @@
       </c>
       <c r="D220" s="2" t="inlineStr">
         <is>
-          <t>Dia 141 de 365. Romanos 12:10: Amai-vos cordialmente. #fe #familia #relacionamentos #palavradodia</t>
+          <t>Dia 219 de 365. Romanos 12:10: Amai-vos cordialmente. #fe #familia #relacionamentos #palavradodia</t>
         </is>
       </c>
       <c r="E220" s="2" t="inlineStr">
@@ -9932,7 +9932,7 @@
       </c>
       <c r="D221" s="2" t="inlineStr">
         <is>
-          <t>Dia 142 de 365. 1 Tessalonicenses 5:11: Encorajem uns aos outros. #fe #familia #relacionamentos #palavradodia</t>
+          <t>Dia 220 de 365. 1 Tessalonicenses 5:11: Encorajem uns aos outros. #fe #familia #relacionamentos #palavradodia</t>
         </is>
       </c>
       <c r="E221" s="2" t="inlineStr">
@@ -9975,7 +9975,7 @@
       </c>
       <c r="D222" s="2" t="inlineStr">
         <is>
-          <t>Dia 143 de 365. Lucas 2:51-52: Jesus também viveu em família. #fe #familia #relacionamentos #palavradodia</t>
+          <t>Dia 221 de 365. Lucas 2:51-52: Jesus também viveu em família. #fe #familia #relacionamentos #palavradodia</t>
         </is>
       </c>
       <c r="E222" s="2" t="inlineStr">
@@ -10018,7 +10018,7 @@
       </c>
       <c r="D223" s="2" t="inlineStr">
         <is>
-          <t>Dia 144 de 365. Provérbios 18:24: Há amigo mais chegado que um irmão. #fe #familia #relacionamentos #palavradodia</t>
+          <t>Dia 222 de 365. Provérbios 18:24: Há amigo mais chegado que um irmão. #fe #familia #relacionamentos #palavradodia</t>
         </is>
       </c>
       <c r="E223" s="2" t="inlineStr">
@@ -10061,7 +10061,7 @@
       </c>
       <c r="D224" s="2" t="inlineStr">
         <is>
-          <t>Dia 145 de 365. João 15:13: Maior amor não há. #fe #familia #relacionamentos #palavradodia</t>
+          <t>Dia 223 de 365. João 15:13: Maior amor não há. #fe #familia #relacionamentos #palavradodia</t>
         </is>
       </c>
       <c r="E224" s="2" t="inlineStr">
@@ -10104,7 +10104,7 @@
       </c>
       <c r="D225" s="2" t="inlineStr">
         <is>
-          <t>Dia 146 de 365. Gálatas 6:2: Levai as cargas uns dos outros. #fe #familia #relacionamentos #palavradodia</t>
+          <t>Dia 224 de 365. Gálatas 6:2: Levai as cargas uns dos outros. #fe #familia #relacionamentos #palavradodia</t>
         </is>
       </c>
       <c r="E225" s="2" t="inlineStr">
@@ -10147,7 +10147,7 @@
       </c>
       <c r="D226" s="2" t="inlineStr">
         <is>
-          <t>Dia 147 de 365. Filipenses 2:3-4: Considere os outros superiores a si mesmo. #fe #familia #relacionamentos #palavradodia</t>
+          <t>Dia 225 de 365. Filipenses 2:3-4: Considere os outros superiores a si mesmo. #fe #familia #relacionamentos #palavradodia</t>
         </is>
       </c>
       <c r="E226" s="2" t="inlineStr">
@@ -10190,7 +10190,7 @@
       </c>
       <c r="D227" s="2" t="inlineStr">
         <is>
-          <t>Dia 148 de 365. Salmos 103:13: Como um pai se compadece dos filhos. #fe #familia #relacionamentos #palavradodia</t>
+          <t>Dia 226 de 365. Salmos 103:13: Como um pai se compadece dos filhos. #fe #familia #relacionamentos #palavradodia</t>
         </is>
       </c>
       <c r="E227" s="2" t="inlineStr">
@@ -10233,7 +10233,7 @@
       </c>
       <c r="D228" s="2" t="inlineStr">
         <is>
-          <t>Dia 149 de 365. Isaías 49:15: Uma mãe pode esquecer o filho? #fe #familia #relacionamentos #palavradodia</t>
+          <t>Dia 227 de 365. Isaías 49:15: Uma mãe pode esquecer o filho? #fe #familia #relacionamentos #palavradodia</t>
         </is>
       </c>
       <c r="E228" s="2" t="inlineStr">
@@ -10276,7 +10276,7 @@
       </c>
       <c r="D229" s="2" t="inlineStr">
         <is>
-          <t>Dia 150 de 365. 1 João 4:11: Se Deus nos amou assim. #fe #familia #relacionamentos #palavradodia</t>
+          <t>Dia 228 de 365. 1 João 4:11: Se Deus nos amou assim. #fe #familia #relacionamentos #palavradodia</t>
         </is>
       </c>
       <c r="E229" s="2" t="inlineStr">
@@ -10319,7 +10319,7 @@
       </c>
       <c r="D230" s="2" t="inlineStr">
         <is>
-          <t>Dia 151 de 365. Hebreus 13:1: Permaneça o amor fraternal. #fe #familia #relacionamentos #palavradodia</t>
+          <t>Dia 229 de 365. Hebreus 13:1: Permaneça o amor fraternal. #fe #familia #relacionamentos #palavradodia</t>
         </is>
       </c>
       <c r="E230" s="2" t="inlineStr">
@@ -10362,7 +10362,7 @@
       </c>
       <c r="D231" s="2" t="inlineStr">
         <is>
-          <t>Dia 152 de 365. 1 Tessalonicenses 5:18: Em tudo dai graças. #fe #gratidao #louvor #palavradodia</t>
+          <t>Dia 230 de 365. 1 Tessalonicenses 5:18: Em tudo dai graças. #fe #gratidao #louvor #palavradodia</t>
         </is>
       </c>
       <c r="E231" s="2" t="inlineStr">
@@ -10405,7 +10405,7 @@
       </c>
       <c r="D232" s="2" t="inlineStr">
         <is>
-          <t>Dia 153 de 365. Salmos 118:24: Este é o dia que o Senhor fez. #fe #gratidao #louvor #palavradodia</t>
+          <t>Dia 231 de 365. Salmos 118:24: Este é o dia que o Senhor fez. #fe #gratidao #louvor #palavradodia</t>
         </is>
       </c>
       <c r="E232" s="2" t="inlineStr">
@@ -10448,7 +10448,7 @@
       </c>
       <c r="D233" s="2" t="inlineStr">
         <is>
-          <t>Dia 154 de 365. Salmos 100:4: Entre pelas portas com ação de graças. #fe #gratidao #louvor #palavradodia</t>
+          <t>Dia 232 de 365. Salmos 100:4: Entre pelas portas com ação de graças. #fe #gratidao #louvor #palavradodia</t>
         </is>
       </c>
       <c r="E233" s="2" t="inlineStr">
@@ -10491,7 +10491,7 @@
       </c>
       <c r="D234" s="2" t="inlineStr">
         <is>
-          <t>Dia 155 de 365. Colossenses 3:15: E sede agradecidos. #fe #gratidao #louvor #palavradodia</t>
+          <t>Dia 233 de 365. Colossenses 3:15: E sede agradecidos. #fe #gratidao #louvor #palavradodia</t>
         </is>
       </c>
       <c r="E234" s="2" t="inlineStr">
@@ -10534,7 +10534,7 @@
       </c>
       <c r="D235" s="2" t="inlineStr">
         <is>
-          <t>Dia 156 de 365. Salmos 103:2: Não te esqueças de nenhum dos seus benefícios. #fe #gratidao #louvor #palavradodia</t>
+          <t>Dia 234 de 365. Salmos 103:2: Não te esqueças de nenhum dos seus benefícios. #fe #gratidao #louvor #palavradodia</t>
         </is>
       </c>
       <c r="E235" s="2" t="inlineStr">
@@ -10577,7 +10577,7 @@
       </c>
       <c r="D236" s="2" t="inlineStr">
         <is>
-          <t>Dia 157 de 365. Lucas 17:15-16: Dos dez curados, só um voltou para agradecer. #fe #gratidao #louvor #palavradodia</t>
+          <t>Dia 235 de 365. Lucas 17:15-16: Dos dez curados, só um voltou para agradecer. #fe #gratidao #louvor #palavradodia</t>
         </is>
       </c>
       <c r="E236" s="2" t="inlineStr">
@@ -10620,7 +10620,7 @@
       </c>
       <c r="D237" s="2" t="inlineStr">
         <is>
-          <t>Dia 158 de 365. Tiago 1:17: Todo bem vem do alto. #fe #gratidao #louvor #palavradodia</t>
+          <t>Dia 236 de 365. Tiago 1:17: Todo bem vem do alto. #fe #gratidao #louvor #palavradodia</t>
         </is>
       </c>
       <c r="E237" s="2" t="inlineStr">
@@ -10663,7 +10663,7 @@
       </c>
       <c r="D238" s="2" t="inlineStr">
         <is>
-          <t>Dia 159 de 365. Salmos 136:1: A misericórdia dEle dura para sempre. #fe #gratidao #louvor #palavradodia</t>
+          <t>Dia 237 de 365. Salmos 136:1: A misericórdia dEle dura para sempre. #fe #gratidao #louvor #palavradodia</t>
         </is>
       </c>
       <c r="E238" s="2" t="inlineStr">
@@ -10706,7 +10706,7 @@
       </c>
       <c r="D239" s="2" t="inlineStr">
         <is>
-          <t>Dia 160 de 365. Filipenses 4:11-12: Aprendi a contentar-me. #fe #gratidao #louvor #palavradodia</t>
+          <t>Dia 238 de 365. Filipenses 4:11-12: Aprendi a contentar-me. #fe #gratidao #louvor #palavradodia</t>
         </is>
       </c>
       <c r="E239" s="2" t="inlineStr">
@@ -10749,7 +10749,7 @@
       </c>
       <c r="D240" s="2" t="inlineStr">
         <is>
-          <t>Dia 161 de 365. Salmos 9:1: De todo o coração. #fe #gratidao #louvor #palavradodia</t>
+          <t>Dia 239 de 365. Salmos 9:1: De todo o coração. #fe #gratidao #louvor #palavradodia</t>
         </is>
       </c>
       <c r="E240" s="2" t="inlineStr">
@@ -10792,7 +10792,7 @@
       </c>
       <c r="D241" s="2" t="inlineStr">
         <is>
-          <t>Dia 162 de 365. Salmos 107:1: Dai graças ao Senhor, porque Ele é bom. #fe #gratidao #louvor #palavradodia</t>
+          <t>Dia 240 de 365. Salmos 107:1: Dai graças ao Senhor, porque Ele é bom. #fe #gratidao #louvor #palavradodia</t>
         </is>
       </c>
       <c r="E241" s="2" t="inlineStr">
@@ -10835,7 +10835,7 @@
       </c>
       <c r="D242" s="2" t="inlineStr">
         <is>
-          <t>Dia 163 de 365. Efésios 5:20: Dando sempre graças por tudo. #fe #gratidao #louvor #palavradodia</t>
+          <t>Dia 241 de 365. Efésios 5:20: Dando sempre graças por tudo. #fe #gratidao #louvor #palavradodia</t>
         </is>
       </c>
       <c r="E242" s="2" t="inlineStr">
@@ -10878,7 +10878,7 @@
       </c>
       <c r="D243" s="2" t="inlineStr">
         <is>
-          <t>Dia 164 de 365. Hebreus 12:28: Um reino que não pode ser abalado. #fe #gratidao #louvor #palavradodia</t>
+          <t>Dia 242 de 365. Hebreus 12:28: Um reino que não pode ser abalado. #fe #gratidao #louvor #palavradodia</t>
         </is>
       </c>
       <c r="E243" s="2" t="inlineStr">
@@ -10921,7 +10921,7 @@
       </c>
       <c r="D244" s="2" t="inlineStr">
         <is>
-          <t>Dia 165 de 365. Salmos 92:1-2: Bom é render graças de manhã e de noite. #fe #gratidao #louvor #palavradodia</t>
+          <t>Dia 243 de 365. Salmos 92:1-2: Bom é render graças de manhã e de noite. #fe #gratidao #louvor #palavradodia</t>
         </is>
       </c>
       <c r="E244" s="2" t="inlineStr">
@@ -10964,7 +10964,7 @@
       </c>
       <c r="D245" s="2" t="inlineStr">
         <is>
-          <t>Dia 166 de 365. 1 Crônicas 16:34: Rendei graças ao Senhor. #fe #gratidao #louvor #palavradodia</t>
+          <t>Dia 244 de 365. 1 Crônicas 16:34: Rendei graças ao Senhor. #fe #gratidao #louvor #palavradodia</t>
         </is>
       </c>
       <c r="E245" s="2" t="inlineStr">
@@ -11007,7 +11007,7 @@
       </c>
       <c r="D246" s="2" t="inlineStr">
         <is>
-          <t>Dia 167 de 365. 2 Coríntios 9:15: Graças a Deus pelo seu dom inefável. #fe #gratidao #louvor #palavradodia</t>
+          <t>Dia 245 de 365. 2 Coríntios 9:15: Graças a Deus pelo seu dom inefável. #fe #gratidao #louvor #palavradodia</t>
         </is>
       </c>
       <c r="E246" s="2" t="inlineStr">
@@ -11050,7 +11050,7 @@
       </c>
       <c r="D247" s="2" t="inlineStr">
         <is>
-          <t>Dia 168 de 365. Salmos 34:1: Bendirei o Senhor em todo o tempo. #fe #gratidao #louvor #palavradodia</t>
+          <t>Dia 246 de 365. Salmos 34:1: Bendirei o Senhor em todo o tempo. #fe #gratidao #louvor #palavradodia</t>
         </is>
       </c>
       <c r="E247" s="2" t="inlineStr">
@@ -11093,7 +11093,7 @@
       </c>
       <c r="D248" s="2" t="inlineStr">
         <is>
-          <t>Dia 169 de 365. Daniel 6:10: Daniel orava e dava graças três vezes ao dia. #fe #gratidao #louvor #palavradodia</t>
+          <t>Dia 247 de 365. Daniel 6:10: Daniel orava e dava graças três vezes ao dia. #fe #gratidao #louvor #palavradodia</t>
         </is>
       </c>
       <c r="E248" s="2" t="inlineStr">

--- a/legendas-365.xlsx
+++ b/legendas-365.xlsx
@@ -515,7 +515,7 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Dia 288 de 365. Salmos 36:7: Quão preciosa é a tua benignidade. #fe #amordedeus #amor #palavradodia</t>
+          <t>Dia 1 de 365. Salmos 36:7: Quão preciosa é a tua benignidade. #fe #amordedeus #amor #palavradodia</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -558,7 +558,7 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Dia 289 de 365. Salmos 63:3: O teu amor é melhor do que a vida. #fe #amordedeus #amor #palavradodia</t>
+          <t>Dia 2 de 365. Salmos 63:3: O teu amor é melhor do que a vida. #fe #amordedeus #amor #palavradodia</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
@@ -601,7 +601,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Dia 290 de 365. Cantares 8:7: As muitas águas não podem apagar o amor. #fe #amordedeus #amor #palavradodia</t>
+          <t>Dia 3 de 365. Cantares 8:7: As muitas águas não podem apagar o amor. #fe #amordedeus #amor #palavradodia</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -644,7 +644,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Dia 291 de 365. Lucas 10:33-34: O bom samaritano parou. #fe #amordedeus #amor #palavradodia</t>
+          <t>Dia 4 de 365. Lucas 10:33-34: O bom samaritano parou. #fe #amordedeus #amor #palavradodia</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -730,7 +730,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Dia 293 de 365. Gálatas 5:13-14: Sirvam uns aos outros pelo amor. #fe #amordedeus #amor #palavradodia</t>
+          <t>Dia 6 de 365. Gálatas 5:13-14: Sirvam uns aos outros pelo amor. #fe #amordedeus #amor #palavradodia</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -11136,7 +11136,7 @@
       </c>
       <c r="D249" s="2" t="inlineStr">
         <is>
-          <t>Dia 170 de 365. Salmos 50:23: A gratidão honra a Deus. #fe #gratidao #louvor #palavradodia</t>
+          <t>Dia 248 de 365. Salmos 50:23: A gratidão honra a Deus. #fe #gratidao #louvor #palavradodia</t>
         </is>
       </c>
       <c r="E249" s="2" t="inlineStr">
@@ -11179,7 +11179,7 @@
       </c>
       <c r="D250" s="2" t="inlineStr">
         <is>
-          <t>Dia 171 de 365. Romanos 1:21: O perigo de esquecer de agradecer. #fe #gratidao #louvor #palavradodia</t>
+          <t>Dia 249 de 365. Romanos 1:21: O perigo de esquecer de agradecer. #fe #gratidao #louvor #palavradodia</t>
         </is>
       </c>
       <c r="E250" s="2" t="inlineStr">
@@ -11222,7 +11222,7 @@
       </c>
       <c r="D251" s="2" t="inlineStr">
         <is>
-          <t>Dia 172 de 365. Salmos 16:6: As cordas caíram em lugares deliciosos. #fe #gratidao #louvor #palavradodia</t>
+          <t>Dia 250 de 365. Salmos 16:6: As cordas caíram em lugares deliciosos. #fe #gratidao #louvor #palavradodia</t>
         </is>
       </c>
       <c r="E251" s="2" t="inlineStr">
@@ -11265,7 +11265,7 @@
       </c>
       <c r="D252" s="2" t="inlineStr">
         <is>
-          <t>Dia 173 de 365. Salmos 145:9: O Senhor é bom para todos. #fe #gratidao #louvor #palavradodia</t>
+          <t>Dia 251 de 365. Salmos 145:9: O Senhor é bom para todos. #fe #gratidao #louvor #palavradodia</t>
         </is>
       </c>
       <c r="E252" s="2" t="inlineStr">
@@ -11308,7 +11308,7 @@
       </c>
       <c r="D253" s="2" t="inlineStr">
         <is>
-          <t>Dia 174 de 365. João 6:11: Jesus deu graças antes do milagre. #fe #gratidao #louvor #palavradodia</t>
+          <t>Dia 252 de 365. João 6:11: Jesus deu graças antes do milagre. #fe #gratidao #louvor #palavradodia</t>
         </is>
       </c>
       <c r="E253" s="2" t="inlineStr">
@@ -11351,7 +11351,7 @@
       </c>
       <c r="D254" s="2" t="inlineStr">
         <is>
-          <t>Dia 175 de 365. Salmos 95:2: Cheguemos com ações de graças. #fe #gratidao #louvor #palavradodia</t>
+          <t>Dia 253 de 365. Salmos 95:2: Cheguemos com ações de graças. #fe #gratidao #louvor #palavradodia</t>
         </is>
       </c>
       <c r="E254" s="2" t="inlineStr">
@@ -11394,7 +11394,7 @@
       </c>
       <c r="D255" s="2" t="inlineStr">
         <is>
-          <t>Dia 176 de 365. Lamentações 3:24: A minha porção é o Senhor. #fe #gratidao #louvor #palavradodia</t>
+          <t>Dia 254 de 365. Lamentações 3:24: A minha porção é o Senhor. #fe #gratidao #louvor #palavradodia</t>
         </is>
       </c>
       <c r="E255" s="2" t="inlineStr">
@@ -11437,7 +11437,7 @@
       </c>
       <c r="D256" s="2" t="inlineStr">
         <is>
-          <t>Dia 177 de 365. Salmos 116:12: Que darei ao Senhor por todos os benefícios? #fe #gratidao #louvor #palavradodia</t>
+          <t>Dia 255 de 365. Salmos 116:12: Que darei ao Senhor por todos os benefícios? #fe #gratidao #louvor #palavradodia</t>
         </is>
       </c>
       <c r="E256" s="2" t="inlineStr">
@@ -11480,7 +11480,7 @@
       </c>
       <c r="D257" s="2" t="inlineStr">
         <is>
-          <t>Dia 178 de 365. Atos 16:25: Paulo e Silas cantavam presos. #fe #gratidao #louvor #palavradodia</t>
+          <t>Dia 256 de 365. Atos 16:25: Paulo e Silas cantavam presos. #fe #gratidao #louvor #palavradodia</t>
         </is>
       </c>
       <c r="E257" s="2" t="inlineStr">
@@ -11523,7 +11523,7 @@
       </c>
       <c r="D258" s="2" t="inlineStr">
         <is>
-          <t>Dia 179 de 365. Salmos 103:3-5: Ele perdoa, sara, resgata, coroa, farta. #fe #gratidao #louvor #palavradodia</t>
+          <t>Dia 257 de 365. Salmos 103:3-5: Ele perdoa, sara, resgata, coroa, farta. #fe #gratidao #louvor #palavradodia</t>
         </is>
       </c>
       <c r="E258" s="2" t="inlineStr">
@@ -11566,7 +11566,7 @@
       </c>
       <c r="D259" s="2" t="inlineStr">
         <is>
-          <t>Dia 180 de 365. Salmos 65:11: Coroas o ano com a tua bondade. #fe #gratidao #louvor #palavradodia</t>
+          <t>Dia 258 de 365. Salmos 65:11: Coroas o ano com a tua bondade. #fe #gratidao #louvor #palavradodia</t>
         </is>
       </c>
       <c r="E259" s="2" t="inlineStr">
@@ -11609,7 +11609,7 @@
       </c>
       <c r="D260" s="2" t="inlineStr">
         <is>
-          <t>Dia 181 de 365. Neemias 8:10: A alegria do Senhor é a vossa força. #fe #gratidao #louvor #palavradodia</t>
+          <t>Dia 259 de 365. Neemias 8:10: A alegria do Senhor é a vossa força. #fe #gratidao #louvor #palavradodia</t>
         </is>
       </c>
       <c r="E260" s="2" t="inlineStr">
@@ -11652,7 +11652,7 @@
       </c>
       <c r="D261" s="2" t="inlineStr">
         <is>
-          <t>Dia 182 de 365. Colossenses 3:23: Trabalhe como se fosse para Deus. #fe #proposito #trabalho #palavradodia</t>
+          <t>Dia 260 de 365. Colossenses 3:23: Trabalhe como se fosse para Deus. #fe #proposito #trabalho #palavradodia</t>
         </is>
       </c>
       <c r="E261" s="2" t="inlineStr">
@@ -11695,7 +11695,7 @@
       </c>
       <c r="D262" s="2" t="inlineStr">
         <is>
-          <t>Dia 183 de 365. Provérbios 16:3: Entregue ao Senhor as suas obras. #fe #proposito #trabalho #palavradodia</t>
+          <t>Dia 261 de 365. Provérbios 16:3: Entregue ao Senhor as suas obras. #fe #proposito #trabalho #palavradodia</t>
         </is>
       </c>
       <c r="E262" s="2" t="inlineStr">
@@ -11738,7 +11738,7 @@
       </c>
       <c r="D263" s="2" t="inlineStr">
         <is>
-          <t>Dia 184 de 365. Efésios 2:10: Você foi feito com propósito. #fe #proposito #trabalho #palavradodia</t>
+          <t>Dia 262 de 365. Efésios 2:10: Você foi feito com propósito. #fe #proposito #trabalho #palavradodia</t>
         </is>
       </c>
       <c r="E263" s="2" t="inlineStr">
@@ -11781,7 +11781,7 @@
       </c>
       <c r="D264" s="2" t="inlineStr">
         <is>
-          <t>Dia 185 de 365. Jeremias 1:5: Antes de te formar, eu te conheci. #fe #proposito #trabalho #palavradodia</t>
+          <t>Dia 263 de 365. Jeremias 1:5: Antes de te formar, eu te conheci. #fe #proposito #trabalho #palavradodia</t>
         </is>
       </c>
       <c r="E264" s="2" t="inlineStr">
@@ -11824,7 +11824,7 @@
       </c>
       <c r="D265" s="2" t="inlineStr">
         <is>
-          <t>Dia 186 de 365. Provérbios 14:23: Em todo trabalho há proveito. #fe #proposito #trabalho #palavradodia</t>
+          <t>Dia 264 de 365. Provérbios 14:23: Em todo trabalho há proveito. #fe #proposito #trabalho #palavradodia</t>
         </is>
       </c>
       <c r="E265" s="2" t="inlineStr">
@@ -11867,7 +11867,7 @@
       </c>
       <c r="D266" s="2" t="inlineStr">
         <is>
-          <t>Dia 187 de 365. Eclesiastes 9:10: Faça com todas as suas forças. #fe #proposito #trabalho #palavradodia</t>
+          <t>Dia 265 de 365. Eclesiastes 9:10: Faça com todas as suas forças. #fe #proposito #trabalho #palavradodia</t>
         </is>
       </c>
       <c r="E266" s="2" t="inlineStr">
@@ -11910,7 +11910,7 @@
       </c>
       <c r="D267" s="2" t="inlineStr">
         <is>
-          <t>Dia 188 de 365. Provérbios 22:29: O diligente servirá diante de reis. #fe #proposito #trabalho #palavradodia</t>
+          <t>Dia 266 de 365. Provérbios 22:29: O diligente servirá diante de reis. #fe #proposito #trabalho #palavradodia</t>
         </is>
       </c>
       <c r="E267" s="2" t="inlineStr">
@@ -11953,7 +11953,7 @@
       </c>
       <c r="D268" s="2" t="inlineStr">
         <is>
-          <t>Dia 189 de 365. Filipenses 1:6: Deus termina o que começa. #fe #proposito #trabalho #palavradodia</t>
+          <t>Dia 267 de 365. Filipenses 1:6: Deus termina o que começa. #fe #proposito #trabalho #palavradodia</t>
         </is>
       </c>
       <c r="E268" s="2" t="inlineStr">
@@ -11996,7 +11996,7 @@
       </c>
       <c r="D269" s="2" t="inlineStr">
         <is>
-          <t>Dia 190 de 365. Gálatas 6:9: Não se canse de fazer o bem. #fe #proposito #trabalho #palavradodia</t>
+          <t>Dia 268 de 365. Gálatas 6:9: Não se canse de fazer o bem. #fe #proposito #trabalho #palavradodia</t>
         </is>
       </c>
       <c r="E269" s="2" t="inlineStr">
@@ -12039,7 +12039,7 @@
       </c>
       <c r="D270" s="2" t="inlineStr">
         <is>
-          <t>Dia 191 de 365. Salmos 90:17: Confirma a obra das nossas mãos. #fe #proposito #trabalho #palavradodia</t>
+          <t>Dia 269 de 365. Salmos 90:17: Confirma a obra das nossas mãos. #fe #proposito #trabalho #palavradodia</t>
         </is>
       </c>
       <c r="E270" s="2" t="inlineStr">
@@ -12082,7 +12082,7 @@
       </c>
       <c r="D271" s="2" t="inlineStr">
         <is>
-          <t>Dia 192 de 365. Romanos 12:6-8: Cada um tem um dom diferente. #fe #proposito #trabalho #palavradodia</t>
+          <t>Dia 270 de 365. Romanos 12:6-8: Cada um tem um dom diferente. #fe #proposito #trabalho #palavradodia</t>
         </is>
       </c>
       <c r="E271" s="2" t="inlineStr">
@@ -12125,7 +12125,7 @@
       </c>
       <c r="D272" s="2" t="inlineStr">
         <is>
-          <t>Dia 193 de 365. 1 Pedro 4:10: Seu dom é para servir. #fe #proposito #trabalho #palavradodia</t>
+          <t>Dia 271 de 365. 1 Pedro 4:10: Seu dom é para servir. #fe #proposito #trabalho #palavradodia</t>
         </is>
       </c>
       <c r="E272" s="2" t="inlineStr">
@@ -12168,7 +12168,7 @@
       </c>
       <c r="D273" s="2" t="inlineStr">
         <is>
-          <t>Dia 194 de 365. Provérbios 6:6-8: Olhe para a formiga. #fe #proposito #trabalho #palavradodia</t>
+          <t>Dia 272 de 365. Provérbios 6:6-8: Olhe para a formiga. #fe #proposito #trabalho #palavradodia</t>
         </is>
       </c>
       <c r="E273" s="2" t="inlineStr">
@@ -12211,7 +12211,7 @@
       </c>
       <c r="D274" s="2" t="inlineStr">
         <is>
-          <t>Dia 195 de 365. Mateus 25:21: Fiel no pouco. #fe #proposito #trabalho #palavradodia</t>
+          <t>Dia 273 de 365. Mateus 25:21: Fiel no pouco. #fe #proposito #trabalho #palavradodia</t>
         </is>
       </c>
       <c r="E274" s="2" t="inlineStr">
@@ -12254,7 +12254,7 @@
       </c>
       <c r="D275" s="2" t="inlineStr">
         <is>
-          <t>Dia 196 de 365. Neemias 2:20: O Deus dos céus nos fará prosperar. #fe #proposito #trabalho #palavradodia</t>
+          <t>Dia 274 de 365. Neemias 2:20: O Deus dos céus nos fará prosperar. #fe #proposito #trabalho #palavradodia</t>
         </is>
       </c>
       <c r="E275" s="2" t="inlineStr">
@@ -12297,7 +12297,7 @@
       </c>
       <c r="D276" s="2" t="inlineStr">
         <is>
-          <t>Dia 197 de 365. Provérbios 13:4: O desejo do preguiçoso não se realiza. #fe #proposito #trabalho #palavradodia</t>
+          <t>Dia 275 de 365. Provérbios 13:4: O desejo do preguiçoso não se realiza. #fe #proposito #trabalho #palavradodia</t>
         </is>
       </c>
       <c r="E276" s="2" t="inlineStr">
@@ -12340,7 +12340,7 @@
       </c>
       <c r="D277" s="2" t="inlineStr">
         <is>
-          <t>Dia 198 de 365. Mateus 5:14-16: Você é a luz do mundo. #fe #proposito #trabalho #palavradodia</t>
+          <t>Dia 276 de 365. Mateus 5:14-16: Você é a luz do mundo. #fe #proposito #trabalho #palavradodia</t>
         </is>
       </c>
       <c r="E277" s="2" t="inlineStr">
@@ -12383,7 +12383,7 @@
       </c>
       <c r="D278" s="2" t="inlineStr">
         <is>
-          <t>Dia 199 de 365. 1 Coríntios 15:58: Seu trabalho no Senhor não é em vão. #fe #proposito #trabalho #palavradodia</t>
+          <t>Dia 277 de 365. 1 Coríntios 15:58: Seu trabalho no Senhor não é em vão. #fe #proposito #trabalho #palavradodia</t>
         </is>
       </c>
       <c r="E278" s="2" t="inlineStr">
@@ -12426,7 +12426,7 @@
       </c>
       <c r="D279" s="2" t="inlineStr">
         <is>
-          <t>Dia 200 de 365. Deuteronômio 8:18: É Ele quem dá força para conquistar. #fe #proposito #trabalho #palavradodia</t>
+          <t>Dia 278 de 365. Deuteronômio 8:18: É Ele quem dá força para conquistar. #fe #proposito #trabalho #palavradodia</t>
         </is>
       </c>
       <c r="E279" s="2" t="inlineStr">
@@ -12469,7 +12469,7 @@
       </c>
       <c r="D280" s="2" t="inlineStr">
         <is>
-          <t>Dia 201 de 365. Provérbios 10:4: A mão diligente enriquece. #fe #proposito #trabalho #palavradodia</t>
+          <t>Dia 279 de 365. Provérbios 10:4: A mão diligente enriquece. #fe #proposito #trabalho #palavradodia</t>
         </is>
       </c>
       <c r="E280" s="2" t="inlineStr">
@@ -12512,7 +12512,7 @@
       </c>
       <c r="D281" s="2" t="inlineStr">
         <is>
-          <t>Dia 202 de 365. Eclesiastes 3:1: Tudo tem o seu tempo. #fe #proposito #trabalho #palavradodia</t>
+          <t>Dia 280 de 365. Eclesiastes 3:1: Tudo tem o seu tempo. #fe #proposito #trabalho #palavradodia</t>
         </is>
       </c>
       <c r="E281" s="2" t="inlineStr">
@@ -12555,7 +12555,7 @@
       </c>
       <c r="D282" s="2" t="inlineStr">
         <is>
-          <t>Dia 203 de 365. 2 Tessalonicenses 3:10-13: Não vos canseis de fazer o bem. #fe #proposito #trabalho #palavradodia</t>
+          <t>Dia 281 de 365. 2 Tessalonicenses 3:10-13: Não vos canseis de fazer o bem. #fe #proposito #trabalho #palavradodia</t>
         </is>
       </c>
       <c r="E282" s="2" t="inlineStr">
@@ -12598,7 +12598,7 @@
       </c>
       <c r="D283" s="2" t="inlineStr">
         <is>
-          <t>Dia 204 de 365. Isaías 64:8: Somos o barro, Tu és o oleiro. #fe #proposito #trabalho #palavradodia</t>
+          <t>Dia 282 de 365. Isaías 64:8: Somos o barro, Tu és o oleiro. #fe #proposito #trabalho #palavradodia</t>
         </is>
       </c>
       <c r="E283" s="2" t="inlineStr">
@@ -12641,7 +12641,7 @@
       </c>
       <c r="D284" s="2" t="inlineStr">
         <is>
-          <t>Dia 205 de 365. Atos 20:35: Mais bem-aventurado é dar. #fe #proposito #trabalho #palavradodia</t>
+          <t>Dia 283 de 365. Atos 20:35: Mais bem-aventurado é dar. #fe #proposito #trabalho #palavradodia</t>
         </is>
       </c>
       <c r="E284" s="2" t="inlineStr">
@@ -12684,7 +12684,7 @@
       </c>
       <c r="D285" s="2" t="inlineStr">
         <is>
-          <t>Dia 206 de 365. Provérbios 16:9: Você planeja, Deus dirige. #fe #proposito #trabalho #palavradodia</t>
+          <t>Dia 284 de 365. Provérbios 16:9: Você planeja, Deus dirige. #fe #proposito #trabalho #palavradodia</t>
         </is>
       </c>
       <c r="E285" s="2" t="inlineStr">
@@ -12727,7 +12727,7 @@
       </c>
       <c r="D286" s="2" t="inlineStr">
         <is>
-          <t>Dia 207 de 365. Habacuque 2:2-3: Escreva a visão. #fe #proposito #trabalho #palavradodia</t>
+          <t>Dia 285 de 365. Habacuque 2:2-3: Escreva a visão. #fe #proposito #trabalho #palavradodia</t>
         </is>
       </c>
       <c r="E286" s="2" t="inlineStr">
@@ -12770,7 +12770,7 @@
       </c>
       <c r="D287" s="2" t="inlineStr">
         <is>
-          <t>Dia 208 de 365. Gênesis 39:2-3: O Senhor estava com José. #fe #proposito #trabalho #palavradodia</t>
+          <t>Dia 286 de 365. Gênesis 39:2-3: O Senhor estava com José. #fe #proposito #trabalho #palavradodia</t>
         </is>
       </c>
       <c r="E287" s="2" t="inlineStr">
@@ -12813,7 +12813,7 @@
       </c>
       <c r="D288" s="2" t="inlineStr">
         <is>
-          <t>Dia 209 de 365. 1 Coríntios 10:31: Para a glória de Deus. #fe #proposito #trabalho #palavradodia</t>
+          <t>Dia 287 de 365. 1 Coríntios 10:31: Para a glória de Deus. #fe #proposito #trabalho #palavradodia</t>
         </is>
       </c>
       <c r="E288" s="2" t="inlineStr">
@@ -12856,7 +12856,7 @@
       </c>
       <c r="D289" s="2" t="inlineStr">
         <is>
-          <t>Dia 210 de 365. Salmos 37:5: Entrega o teu caminho. #fe #proposito #trabalho #palavradodia</t>
+          <t>Dia 288 de 365. Salmos 37:5: Entrega o teu caminho. #fe #proposito #trabalho #palavradodia</t>
         </is>
       </c>
       <c r="E289" s="2" t="inlineStr">
@@ -12899,7 +12899,7 @@
       </c>
       <c r="D290" s="2" t="inlineStr">
         <is>
-          <t>Dia 211 de 365. Zacarias 4:10: Não despreze os pequenos começos. #fe #proposito #trabalho #palavradodia</t>
+          <t>Dia 289 de 365. Zacarias 4:10: Não despreze os pequenos começos. #fe #proposito #trabalho #palavradodia</t>
         </is>
       </c>
       <c r="E290" s="2" t="inlineStr">
@@ -12942,7 +12942,7 @@
       </c>
       <c r="D291" s="2" t="inlineStr">
         <is>
-          <t>Dia 212 de 365. Mateus 6:33: Busque primeiro. #fe #proposito #trabalho #palavradodia</t>
+          <t>Dia 290 de 365. Mateus 6:33: Busque primeiro. #fe #proposito #trabalho #palavradodia</t>
         </is>
       </c>
       <c r="E291" s="2" t="inlineStr">
@@ -12985,7 +12985,7 @@
       </c>
       <c r="D292" s="2" t="inlineStr">
         <is>
-          <t>Dia 213 de 365. Tiago 1:5: Precisa decidir algo e não sabe o quê? #fe #sabedoria #decisoes #palavradodia</t>
+          <t>Dia 291 de 365. Tiago 1:5: Precisa decidir algo e não sabe o quê? #fe #sabedoria #decisoes #palavradodia</t>
         </is>
       </c>
       <c r="E292" s="2" t="inlineStr">
@@ -13028,7 +13028,7 @@
       </c>
       <c r="D293" s="2" t="inlineStr">
         <is>
-          <t>Dia 214 de 365. Provérbios 3:5-6: Não se apoie só no seu entendimento. #fe #sabedoria #decisoes #palavradodia</t>
+          <t>Dia 292 de 365. Provérbios 3:5-6: Não se apoie só no seu entendimento. #fe #sabedoria #decisoes #palavradodia</t>
         </is>
       </c>
       <c r="E293" s="2" t="inlineStr">
@@ -13071,7 +13071,7 @@
       </c>
       <c r="D294" s="2" t="inlineStr">
         <is>
-          <t>Dia 215 de 365. Salmos 119:105: Uma lâmpada para os pés. #fe #sabedoria #decisoes #palavradodia</t>
+          <t>Dia 293 de 365. Salmos 119:105: Uma lâmpada para os pés. #fe #sabedoria #decisoes #palavradodia</t>
         </is>
       </c>
       <c r="E294" s="2" t="inlineStr">
@@ -13114,7 +13114,7 @@
       </c>
       <c r="D295" s="2" t="inlineStr">
         <is>
-          <t>Dia 216 de 365. Provérbios 1:7: Onde a sabedoria começa. #fe #sabedoria #decisoes #palavradodia</t>
+          <t>Dia 294 de 365. Provérbios 1:7: Onde a sabedoria começa. #fe #sabedoria #decisoes #palavradodia</t>
         </is>
       </c>
       <c r="E295" s="2" t="inlineStr">
@@ -13157,7 +13157,7 @@
       </c>
       <c r="D296" s="2" t="inlineStr">
         <is>
-          <t>Dia 217 de 365. Provérbios 11:14: Na multidão de conselheiros há segurança. #fe #sabedoria #decisoes #palavradodia</t>
+          <t>Dia 295 de 365. Provérbios 11:14: Na multidão de conselheiros há segurança. #fe #sabedoria #decisoes #palavradodia</t>
         </is>
       </c>
       <c r="E296" s="2" t="inlineStr">
@@ -13200,7 +13200,7 @@
       </c>
       <c r="D297" s="2" t="inlineStr">
         <is>
-          <t>Dia 218 de 365. Salmos 32:8: Eu te instruirei. #fe #sabedoria #decisoes #palavradodia</t>
+          <t>Dia 296 de 365. Salmos 32:8: Eu te instruirei. #fe #sabedoria #decisoes #palavradodia</t>
         </is>
       </c>
       <c r="E297" s="2" t="inlineStr">
@@ -13243,7 +13243,7 @@
       </c>
       <c r="D298" s="2" t="inlineStr">
         <is>
-          <t>Dia 219 de 365. Provérbios 4:23: Guarde o coração. #fe #sabedoria #decisoes #palavradodia</t>
+          <t>Dia 297 de 365. Provérbios 4:23: Guarde o coração. #fe #sabedoria #decisoes #palavradodia</t>
         </is>
       </c>
       <c r="E298" s="2" t="inlineStr">
@@ -13286,7 +13286,7 @@
       </c>
       <c r="D299" s="2" t="inlineStr">
         <is>
-          <t>Dia 220 de 365. Isaías 30:21: Este é o caminho, andai nele. #fe #sabedoria #decisoes #palavradodia</t>
+          <t>Dia 298 de 365. Isaías 30:21: Este é o caminho, andai nele. #fe #sabedoria #decisoes #palavradodia</t>
         </is>
       </c>
       <c r="E299" s="2" t="inlineStr">
@@ -13329,7 +13329,7 @@
       </c>
       <c r="D300" s="2" t="inlineStr">
         <is>
-          <t>Dia 221 de 365. Provérbios 2:6: O Senhor dá a sabedoria. #fe #sabedoria #decisoes #palavradodia</t>
+          <t>Dia 299 de 365. Provérbios 2:6: O Senhor dá a sabedoria. #fe #sabedoria #decisoes #palavradodia</t>
         </is>
       </c>
       <c r="E300" s="2" t="inlineStr">
@@ -13372,7 +13372,7 @@
       </c>
       <c r="D301" s="2" t="inlineStr">
         <is>
-          <t>Dia 222 de 365. Tiago 3:17: Como reconhecer a sabedoria que vem do alto. #fe #sabedoria #decisoes #palavradodia</t>
+          <t>Dia 300 de 365. Tiago 3:17: Como reconhecer a sabedoria que vem do alto. #fe #sabedoria #decisoes #palavradodia</t>
         </is>
       </c>
       <c r="E301" s="2" t="inlineStr">
@@ -13415,7 +13415,7 @@
       </c>
       <c r="D302" s="2" t="inlineStr">
         <is>
-          <t>Dia 223 de 365. Provérbios 15:22: Sem conselho, os planos falham. #fe #sabedoria #decisoes #palavradodia</t>
+          <t>Dia 301 de 365. Provérbios 15:22: Sem conselho, os planos falham. #fe #sabedoria #decisoes #palavradodia</t>
         </is>
       </c>
       <c r="E302" s="2" t="inlineStr">
@@ -13458,7 +13458,7 @@
       </c>
       <c r="D303" s="2" t="inlineStr">
         <is>
-          <t>Dia 224 de 365. Salmos 25:4-5: Mostra-me os teus caminhos. #fe #sabedoria #decisoes #palavradodia</t>
+          <t>Dia 302 de 365. Salmos 25:4-5: Mostra-me os teus caminhos. #fe #sabedoria #decisoes #palavradodia</t>
         </is>
       </c>
       <c r="E303" s="2" t="inlineStr">
@@ -13501,7 +13501,7 @@
       </c>
       <c r="D304" s="2" t="inlineStr">
         <is>
-          <t>Dia 225 de 365. Provérbios 16:16: Melhor que ouro. #fe #sabedoria #decisoes #palavradodia</t>
+          <t>Dia 303 de 365. Provérbios 16:16: Melhor que ouro. #fe #sabedoria #decisoes #palavradodia</t>
         </is>
       </c>
       <c r="E304" s="2" t="inlineStr">
@@ -13544,7 +13544,7 @@
       </c>
       <c r="D305" s="2" t="inlineStr">
         <is>
-          <t>Dia 226 de 365. Colossenses 3:16: Que a Palavra habite em você ricamente. #fe #sabedoria #decisoes #palavradodia</t>
+          <t>Dia 304 de 365. Colossenses 3:16: Que a Palavra habite em você ricamente. #fe #sabedoria #decisoes #palavradodia</t>
         </is>
       </c>
       <c r="E305" s="2" t="inlineStr">
@@ -13587,7 +13587,7 @@
       </c>
       <c r="D306" s="2" t="inlineStr">
         <is>
-          <t>Dia 227 de 365. Provérbios 14:12: Há caminho que parece direito. #fe #sabedoria #decisoes #palavradodia</t>
+          <t>Dia 305 de 365. Provérbios 14:12: Há caminho que parece direito. #fe #sabedoria #decisoes #palavradodia</t>
         </is>
       </c>
       <c r="E306" s="2" t="inlineStr">
@@ -13630,7 +13630,7 @@
       </c>
       <c r="D307" s="2" t="inlineStr">
         <is>
-          <t>Dia 228 de 365. 1 Reis 3:9: O pedido de Salomão. #fe #sabedoria #decisoes #palavradodia</t>
+          <t>Dia 306 de 365. 1 Reis 3:9: O pedido de Salomão. #fe #sabedoria #decisoes #palavradodia</t>
         </is>
       </c>
       <c r="E307" s="2" t="inlineStr">
@@ -13673,7 +13673,7 @@
       </c>
       <c r="D308" s="2" t="inlineStr">
         <is>
-          <t>Dia 229 de 365. Provérbios 19:21: Muitos planos, um propósito. #fe #sabedoria #decisoes #palavradodia</t>
+          <t>Dia 307 de 365. Provérbios 19:21: Muitos planos, um propósito. #fe #sabedoria #decisoes #palavradodia</t>
         </is>
       </c>
       <c r="E308" s="2" t="inlineStr">
@@ -13716,7 +13716,7 @@
       </c>
       <c r="D309" s="2" t="inlineStr">
         <is>
-          <t>Dia 230 de 365. Romanos 12:2: Não se conforme com este mundo. #fe #sabedoria #decisoes #palavradodia</t>
+          <t>Dia 308 de 365. Romanos 12:2: Não se conforme com este mundo. #fe #sabedoria #decisoes #palavradodia</t>
         </is>
       </c>
       <c r="E309" s="2" t="inlineStr">
@@ -13759,7 +13759,7 @@
       </c>
       <c r="D310" s="2" t="inlineStr">
         <is>
-          <t>Dia 231 de 365. Salmos 1:1-3: Feliz quem não segue o conselho dos ímpios. #fe #sabedoria #decisoes #palavradodia</t>
+          <t>Dia 309 de 365. Salmos 1:1-3: Feliz quem não segue o conselho dos ímpios. #fe #sabedoria #decisoes #palavradodia</t>
         </is>
       </c>
       <c r="E310" s="2" t="inlineStr">
@@ -13802,7 +13802,7 @@
       </c>
       <c r="D311" s="2" t="inlineStr">
         <is>
-          <t>Dia 232 de 365. Provérbios 13:20: Ande com os sábios. #fe #sabedoria #decisoes #palavradodia</t>
+          <t>Dia 310 de 365. Provérbios 13:20: Ande com os sábios. #fe #sabedoria #decisoes #palavradodia</t>
         </is>
       </c>
       <c r="E311" s="2" t="inlineStr">
@@ -13845,7 +13845,7 @@
       </c>
       <c r="D312" s="2" t="inlineStr">
         <is>
-          <t>Dia 233 de 365. Eclesiastes 7:8: Melhor é o fim do que o começo. #fe #sabedoria #decisoes #palavradodia</t>
+          <t>Dia 311 de 365. Eclesiastes 7:8: Melhor é o fim do que o começo. #fe #sabedoria #decisoes #palavradodia</t>
         </is>
       </c>
       <c r="E312" s="2" t="inlineStr">
@@ -13888,7 +13888,7 @@
       </c>
       <c r="D313" s="2" t="inlineStr">
         <is>
-          <t>Dia 234 de 365. Provérbios 12:15: O tolo acha que está sempre certo. #fe #sabedoria #decisoes #palavradodia</t>
+          <t>Dia 312 de 365. Provérbios 12:15: O tolo acha que está sempre certo. #fe #sabedoria #decisoes #palavradodia</t>
         </is>
       </c>
       <c r="E313" s="2" t="inlineStr">
@@ -13931,7 +13931,7 @@
       </c>
       <c r="D314" s="2" t="inlineStr">
         <is>
-          <t>Dia 235 de 365. Salmos 37:23: O Senhor firma os passos do homem bom. #fe #sabedoria #decisoes #palavradodia</t>
+          <t>Dia 313 de 365. Salmos 37:23: O Senhor firma os passos do homem bom. #fe #sabedoria #decisoes #palavradodia</t>
         </is>
       </c>
       <c r="E314" s="2" t="inlineStr">
@@ -13974,7 +13974,7 @@
       </c>
       <c r="D315" s="2" t="inlineStr">
         <is>
-          <t>Dia 236 de 365. Provérbios 21:5: Os planos do diligente levam à fartura. #fe #sabedoria #decisoes #palavradodia</t>
+          <t>Dia 314 de 365. Provérbios 21:5: Os planos do diligente levam à fartura. #fe #sabedoria #decisoes #palavradodia</t>
         </is>
       </c>
       <c r="E315" s="2" t="inlineStr">
@@ -14017,7 +14017,7 @@
       </c>
       <c r="D316" s="2" t="inlineStr">
         <is>
-          <t>Dia 237 de 365. Filipenses 1:9-10: Discernir o que é excelente. #fe #sabedoria #decisoes #palavradodia</t>
+          <t>Dia 315 de 365. Filipenses 1:9-10: Discernir o que é excelente. #fe #sabedoria #decisoes #palavradodia</t>
         </is>
       </c>
       <c r="E316" s="2" t="inlineStr">
@@ -14060,7 +14060,7 @@
       </c>
       <c r="D317" s="2" t="inlineStr">
         <is>
-          <t>Dia 238 de 365. Provérbios 18:13: Responder antes de ouvir é tolice. #fe #sabedoria #decisoes #palavradodia</t>
+          <t>Dia 316 de 365. Provérbios 18:13: Responder antes de ouvir é tolice. #fe #sabedoria #decisoes #palavradodia</t>
         </is>
       </c>
       <c r="E317" s="2" t="inlineStr">
@@ -14103,7 +14103,7 @@
       </c>
       <c r="D318" s="2" t="inlineStr">
         <is>
-          <t>Dia 239 de 365. Mateus 7:24-25: Construa sobre a rocha. #fe #sabedoria #decisoes #palavradodia</t>
+          <t>Dia 317 de 365. Mateus 7:24-25: Construa sobre a rocha. #fe #sabedoria #decisoes #palavradodia</t>
         </is>
       </c>
       <c r="E318" s="2" t="inlineStr">
@@ -14146,7 +14146,7 @@
       </c>
       <c r="D319" s="2" t="inlineStr">
         <is>
-          <t>Dia 240 de 365. Salmos 111:10: O temor do Senhor é o princípio da sabedoria. #fe #sabedoria #decisoes #palavradodia</t>
+          <t>Dia 318 de 365. Salmos 111:10: O temor do Senhor é o princípio da sabedoria. #fe #sabedoria #decisoes #palavradodia</t>
         </is>
       </c>
       <c r="E319" s="2" t="inlineStr">
@@ -14189,7 +14189,7 @@
       </c>
       <c r="D320" s="2" t="inlineStr">
         <is>
-          <t>Dia 241 de 365. Provérbios 27:12: O prudente vê o perigo e se esconde. #fe #sabedoria #decisoes #palavradodia</t>
+          <t>Dia 319 de 365. Provérbios 27:12: O prudente vê o perigo e se esconde. #fe #sabedoria #decisoes #palavradodia</t>
         </is>
       </c>
       <c r="E320" s="2" t="inlineStr">
@@ -14232,7 +14232,7 @@
       </c>
       <c r="D321" s="2" t="inlineStr">
         <is>
-          <t>Dia 242 de 365. Eclesiastes 12:13: A conclusão de tudo. #fe #sabedoria #decisoes #palavradodia</t>
+          <t>Dia 320 de 365. Eclesiastes 12:13: A conclusão de tudo. #fe #sabedoria #decisoes #palavradodia</t>
         </is>
       </c>
       <c r="E321" s="2" t="inlineStr">
@@ -14275,7 +14275,7 @@
       </c>
       <c r="D322" s="2" t="inlineStr">
         <is>
-          <t>Dia 243 de 365. Daniel 2:20-21: Ele dá sabedoria aos sábios. #fe #sabedoria #decisoes #palavradodia</t>
+          <t>Dia 321 de 365. Daniel 2:20-21: Ele dá sabedoria aos sábios. #fe #sabedoria #decisoes #palavradodia</t>
         </is>
       </c>
       <c r="E322" s="2" t="inlineStr">
@@ -14318,7 +14318,7 @@
       </c>
       <c r="D323" s="2" t="inlineStr">
         <is>
-          <t>Dia 244 de 365. Filipenses 4:13: Tudo posso naquele que me fortalece. #fe #perseveranca #forca #palavradodia</t>
+          <t>Dia 322 de 365. Filipenses 4:13: Tudo posso naquele que me fortalece. #fe #perseveranca #forca #palavradodia</t>
         </is>
       </c>
       <c r="E323" s="2" t="inlineStr">
@@ -14361,7 +14361,7 @@
       </c>
       <c r="D324" s="2" t="inlineStr">
         <is>
-          <t>Dia 245 de 365. Hebreus 12:1-2: Corra com perseverança. #fe #perseveranca #forca #palavradodia</t>
+          <t>Dia 323 de 365. Hebreus 12:1-2: Corra com perseverança. #fe #perseveranca #forca #palavradodia</t>
         </is>
       </c>
       <c r="E324" s="2" t="inlineStr">
@@ -14404,7 +14404,7 @@
       </c>
       <c r="D325" s="2" t="inlineStr">
         <is>
-          <t>Dia 246 de 365. Salmos 27:13: Eu creio que verei a bondade do Senhor. #fe #perseveranca #forca #palavradodia</t>
+          <t>Dia 324 de 365. Salmos 27:13: Eu creio que verei a bondade do Senhor. #fe #perseveranca #forca #palavradodia</t>
         </is>
       </c>
       <c r="E325" s="2" t="inlineStr">
@@ -14447,7 +14447,7 @@
       </c>
       <c r="D326" s="2" t="inlineStr">
         <is>
-          <t>Dia 247 de 365. Tiago 1:2-4: Alegria nas provações? #fe #perseveranca #forca #palavradodia</t>
+          <t>Dia 325 de 365. Tiago 1:2-4: Alegria nas provações? #fe #perseveranca #forca #palavradodia</t>
         </is>
       </c>
       <c r="E326" s="2" t="inlineStr">
@@ -14490,7 +14490,7 @@
       </c>
       <c r="D327" s="2" t="inlineStr">
         <is>
-          <t>Dia 248 de 365. Provérbios 24:16: O justo cai sete vezes e se levanta. #fe #perseveranca #forca #palavradodia</t>
+          <t>Dia 326 de 365. Provérbios 24:16: O justo cai sete vezes e se levanta. #fe #perseveranca #forca #palavradodia</t>
         </is>
       </c>
       <c r="E327" s="2" t="inlineStr">
@@ -14533,7 +14533,7 @@
       </c>
       <c r="D328" s="2" t="inlineStr">
         <is>
-          <t>Dia 249 de 365. 2 Timóteo 4:7: Combati o bom combate. #fe #perseveranca #forca #palavradodia</t>
+          <t>Dia 327 de 365. 2 Timóteo 4:7: Combati o bom combate. #fe #perseveranca #forca #palavradodia</t>
         </is>
       </c>
       <c r="E328" s="2" t="inlineStr">
@@ -14576,7 +14576,7 @@
       </c>
       <c r="D329" s="2" t="inlineStr">
         <is>
-          <t>Dia 250 de 365. Salmos 18:32: Deus me reveste de força. #fe #perseveranca #forca #palavradodia</t>
+          <t>Dia 328 de 365. Salmos 18:32: Deus me reveste de força. #fe #perseveranca #forca #palavradodia</t>
         </is>
       </c>
       <c r="E329" s="2" t="inlineStr">
@@ -14619,7 +14619,7 @@
       </c>
       <c r="D330" s="2" t="inlineStr">
         <is>
-          <t>Dia 251 de 365. Salmos 66:10-12: Passamos pelo fogo e pela água. #fe #perseveranca #forca #palavradodia</t>
+          <t>Dia 329 de 365. Salmos 66:10-12: Passamos pelo fogo e pela água. #fe #perseveranca #forca #palavradodia</t>
         </is>
       </c>
       <c r="E330" s="2" t="inlineStr">
@@ -14662,7 +14662,7 @@
       </c>
       <c r="D331" s="2" t="inlineStr">
         <is>
-          <t>Dia 252 de 365. Salmos 73:26: Quando o corpo e o coração falham. #fe #perseveranca #forca #palavradodia</t>
+          <t>Dia 330 de 365. Salmos 73:26: Quando o corpo e o coração falham. #fe #perseveranca #forca #palavradodia</t>
         </is>
       </c>
       <c r="E331" s="2" t="inlineStr">
@@ -14705,7 +14705,7 @@
       </c>
       <c r="D332" s="2" t="inlineStr">
         <is>
-          <t>Dia 253 de 365. Isaías 41:13: Eu te ajudo. #fe #perseveranca #forca #palavradodia</t>
+          <t>Dia 331 de 365. Isaías 41:13: Eu te ajudo. #fe #perseveranca #forca #palavradodia</t>
         </is>
       </c>
       <c r="E332" s="2" t="inlineStr">
@@ -14748,7 +14748,7 @@
       </c>
       <c r="D333" s="2" t="inlineStr">
         <is>
-          <t>Dia 254 de 365. 1 Coríntios 16:13: Sede fortes. #fe #perseveranca #forca #palavradodia</t>
+          <t>Dia 332 de 365. 1 Coríntios 16:13: Sede fortes. #fe #perseveranca #forca #palavradodia</t>
         </is>
       </c>
       <c r="E333" s="2" t="inlineStr">
@@ -14791,7 +14791,7 @@
       </c>
       <c r="D334" s="2" t="inlineStr">
         <is>
-          <t>Dia 255 de 365. Efésios 6:10: Fortalecei-vos no Senhor. #fe #perseveranca #forca #palavradodia</t>
+          <t>Dia 333 de 365. Efésios 6:10: Fortalecei-vos no Senhor. #fe #perseveranca #forca #palavradodia</t>
         </is>
       </c>
       <c r="E334" s="2" t="inlineStr">
@@ -14834,7 +14834,7 @@
       </c>
       <c r="D335" s="2" t="inlineStr">
         <is>
-          <t>Dia 256 de 365. Salmos 28:7: O Senhor é a minha força e o meu escudo. #fe #perseveranca #forca #palavradodia</t>
+          <t>Dia 334 de 365. Salmos 28:7: O Senhor é a minha força e o meu escudo. #fe #perseveranca #forca #palavradodia</t>
         </is>
       </c>
       <c r="E335" s="2" t="inlineStr">
@@ -14877,7 +14877,7 @@
       </c>
       <c r="D336" s="2" t="inlineStr">
         <is>
-          <t>Dia 257 de 365. Hebreus 10:36: Vocês precisam de perseverança. #fe #perseveranca #forca #palavradodia</t>
+          <t>Dia 335 de 365. Hebreus 10:36: Vocês precisam de perseverança. #fe #perseveranca #forca #palavradodia</t>
         </is>
       </c>
       <c r="E336" s="2" t="inlineStr">
@@ -14920,7 +14920,7 @@
       </c>
       <c r="D337" s="2" t="inlineStr">
         <is>
-          <t>Dia 258 de 365. Zacarias 4:6: Não por força, nem por violência. #fe #perseveranca #forca #palavradodia</t>
+          <t>Dia 336 de 365. Zacarias 4:6: Não por força, nem por violência. #fe #perseveranca #forca #palavradodia</t>
         </is>
       </c>
       <c r="E337" s="2" t="inlineStr">
@@ -14963,7 +14963,7 @@
       </c>
       <c r="D338" s="2" t="inlineStr">
         <is>
-          <t>Dia 259 de 365. Isaías 50:7: Pus o meu rosto como pedra. #fe #perseveranca #forca #palavradodia</t>
+          <t>Dia 337 de 365. Isaías 50:7: Pus o meu rosto como pedra. #fe #perseveranca #forca #palavradodia</t>
         </is>
       </c>
       <c r="E338" s="2" t="inlineStr">
@@ -15006,7 +15006,7 @@
       </c>
       <c r="D339" s="2" t="inlineStr">
         <is>
-          <t>Dia 260 de 365. Salmos 138:7: Ainda que eu ande no meio da angústia. #fe #perseveranca #forca #palavradodia</t>
+          <t>Dia 338 de 365. Salmos 138:7: Ainda que eu ande no meio da angústia. #fe #perseveranca #forca #palavradodia</t>
         </is>
       </c>
       <c r="E339" s="2" t="inlineStr">
@@ -15049,7 +15049,7 @@
       </c>
       <c r="D340" s="2" t="inlineStr">
         <is>
-          <t>Dia 261 de 365. Neemias 6:3: Estou fazendo uma grande obra. #fe #perseveranca #forca #palavradodia</t>
+          <t>Dia 339 de 365. Neemias 6:3: Estou fazendo uma grande obra. #fe #perseveranca #forca #palavradodia</t>
         </is>
       </c>
       <c r="E340" s="2" t="inlineStr">
@@ -15092,7 +15092,7 @@
       </c>
       <c r="D341" s="2" t="inlineStr">
         <is>
-          <t>Dia 262 de 365. Tiago 1:12: Feliz o que suporta a provação. #fe #perseveranca #forca #palavradodia</t>
+          <t>Dia 340 de 365. Tiago 1:12: Feliz o que suporta a provação. #fe #perseveranca #forca #palavradodia</t>
         </is>
       </c>
       <c r="E341" s="2" t="inlineStr">
@@ -15135,7 +15135,7 @@
       </c>
       <c r="D342" s="2" t="inlineStr">
         <is>
-          <t>Dia 263 de 365. Salmos 46:5: Deus está no meio dela. #fe #perseveranca #forca #palavradodia</t>
+          <t>Dia 341 de 365. Salmos 46:5: Deus está no meio dela. #fe #perseveranca #forca #palavradodia</t>
         </is>
       </c>
       <c r="E342" s="2" t="inlineStr">
@@ -15178,7 +15178,7 @@
       </c>
       <c r="D343" s="2" t="inlineStr">
         <is>
-          <t>Dia 264 de 365. Hebreus 12:11: A disciplina dói, depois dá fruto. #fe #perseveranca #forca #palavradodia</t>
+          <t>Dia 342 de 365. Hebreus 12:11: A disciplina dói, depois dá fruto. #fe #perseveranca #forca #palavradodia</t>
         </is>
       </c>
       <c r="E343" s="2" t="inlineStr">
@@ -15221,7 +15221,7 @@
       </c>
       <c r="D344" s="2" t="inlineStr">
         <is>
-          <t>Dia 265 de 365. Lucas 18:1: Orar sempre e nunca desistir. #fe #perseveranca #forca #palavradodia</t>
+          <t>Dia 343 de 365. Lucas 18:1: Orar sempre e nunca desistir. #fe #perseveranca #forca #palavradodia</t>
         </is>
       </c>
       <c r="E344" s="2" t="inlineStr">
@@ -15264,7 +15264,7 @@
       </c>
       <c r="D345" s="2" t="inlineStr">
         <is>
-          <t>Dia 266 de 365. Salmos 37:24: Ainda que caia, não ficará prostrado. #fe #perseveranca #forca #palavradodia</t>
+          <t>Dia 344 de 365. Salmos 37:24: Ainda que caia, não ficará prostrado. #fe #perseveranca #forca #palavradodia</t>
         </is>
       </c>
       <c r="E345" s="2" t="inlineStr">
@@ -15307,7 +15307,7 @@
       </c>
       <c r="D346" s="2" t="inlineStr">
         <is>
-          <t>Dia 267 de 365. 2 Coríntios 4:7: Um tesouro em vasos de barro. #fe #perseveranca #forca #palavradodia</t>
+          <t>Dia 345 de 365. 2 Coríntios 4:7: Um tesouro em vasos de barro. #fe #perseveranca #forca #palavradodia</t>
         </is>
       </c>
       <c r="E346" s="2" t="inlineStr">
@@ -15350,7 +15350,7 @@
       </c>
       <c r="D347" s="2" t="inlineStr">
         <is>
-          <t>Dia 268 de 365. Josué 14:11: Calebe com 85 anos. #fe #perseveranca #forca #palavradodia</t>
+          <t>Dia 346 de 365. Josué 14:11: Calebe com 85 anos. #fe #perseveranca #forca #palavradodia</t>
         </is>
       </c>
       <c r="E347" s="2" t="inlineStr">
@@ -15393,7 +15393,7 @@
       </c>
       <c r="D348" s="2" t="inlineStr">
         <is>
-          <t>Dia 269 de 365. Isaías 40:28: Deus não se cansa. #fe #perseveranca #forca #palavradodia</t>
+          <t>Dia 347 de 365. Isaías 40:28: Deus não se cansa. #fe #perseveranca #forca #palavradodia</t>
         </is>
       </c>
       <c r="E348" s="2" t="inlineStr">
@@ -15436,7 +15436,7 @@
       </c>
       <c r="D349" s="2" t="inlineStr">
         <is>
-          <t>Dia 270 de 365. Romanos 8:37: Mais que vencedores. #fe #perseveranca #forca #palavradodia</t>
+          <t>Dia 348 de 365. Romanos 8:37: Mais que vencedores. #fe #perseveranca #forca #palavradodia</t>
         </is>
       </c>
       <c r="E349" s="2" t="inlineStr">
@@ -15479,7 +15479,7 @@
       </c>
       <c r="D350" s="2" t="inlineStr">
         <is>
-          <t>Dia 271 de 365. Habacuque 3:19: Pés como os das corças. #fe #perseveranca #forca #palavradodia</t>
+          <t>Dia 349 de 365. Habacuque 3:19: Pés como os das corças. #fe #perseveranca #forca #palavradodia</t>
         </is>
       </c>
       <c r="E350" s="2" t="inlineStr">
@@ -15522,7 +15522,7 @@
       </c>
       <c r="D351" s="2" t="inlineStr">
         <is>
-          <t>Dia 272 de 365. Apocalipse 2:10: Sê fiel até a morte. #fe #perseveranca #forca #palavradodia</t>
+          <t>Dia 350 de 365. Apocalipse 2:10: Sê fiel até a morte. #fe #perseveranca #forca #palavradodia</t>
         </is>
       </c>
       <c r="E351" s="2" t="inlineStr">
@@ -15565,7 +15565,7 @@
       </c>
       <c r="D352" s="2" t="inlineStr">
         <is>
-          <t>Dia 273 de 365. 2 Crônicas 15:7: Não desfaleçam as vossas mãos. #fe #perseveranca #forca #palavradodia</t>
+          <t>Dia 351 de 365. 2 Crônicas 15:7: Não desfaleçam as vossas mãos. #fe #perseveranca #forca #palavradodia</t>
         </is>
       </c>
       <c r="E352" s="2" t="inlineStr">
@@ -15608,7 +15608,7 @@
       </c>
       <c r="D353" s="2" t="inlineStr">
         <is>
-          <t>Dia 274 de 365. João 3:16: O versículo mais conhecido da Bíblia. #fe #amordedeus #amor #palavradodia</t>
+          <t>Dia 352 de 365. João 3:16: O versículo mais conhecido da Bíblia. #fe #amordedeus #amor #palavradodia</t>
         </is>
       </c>
       <c r="E353" s="2" t="inlineStr">
@@ -15651,7 +15651,7 @@
       </c>
       <c r="D354" s="2" t="inlineStr">
         <is>
-          <t>Dia 275 de 365. 1 João 4:8: Deus é amor. #fe #amordedeus #amor #palavradodia</t>
+          <t>Dia 353 de 365. 1 João 4:8: Deus é amor. #fe #amordedeus #amor #palavradodia</t>
         </is>
       </c>
       <c r="E354" s="2" t="inlineStr">
@@ -15694,7 +15694,7 @@
       </c>
       <c r="D355" s="2" t="inlineStr">
         <is>
-          <t>Dia 276 de 365. Romanos 5:8: Ele te amou no seu pior momento. #fe #amordedeus #amor #palavradodia</t>
+          <t>Dia 354 de 365. Romanos 5:8: Ele te amou no seu pior momento. #fe #amordedeus #amor #palavradodia</t>
         </is>
       </c>
       <c r="E355" s="2" t="inlineStr">
@@ -15737,7 +15737,7 @@
       </c>
       <c r="D356" s="2" t="inlineStr">
         <is>
-          <t>Dia 277 de 365. Romanos 8:38-39: Nada pode te separar. #fe #amordedeus #amor #palavradodia</t>
+          <t>Dia 355 de 365. Romanos 8:38-39: Nada pode te separar. #fe #amordedeus #amor #palavradodia</t>
         </is>
       </c>
       <c r="E356" s="2" t="inlineStr">
@@ -15780,7 +15780,7 @@
       </c>
       <c r="D357" s="2" t="inlineStr">
         <is>
-          <t>Dia 278 de 365. 1 João 4:19: Nós amamos porque Ele nos amou primeiro. #fe #amordedeus #amor #palavradodia</t>
+          <t>Dia 356 de 365. 1 João 4:19: Nós amamos porque Ele nos amou primeiro. #fe #amordedeus #amor #palavradodia</t>
         </is>
       </c>
       <c r="E357" s="2" t="inlineStr">
@@ -15823,7 +15823,7 @@
       </c>
       <c r="D358" s="2" t="inlineStr">
         <is>
-          <t>Dia 279 de 365. Jeremias 31:3: Com amor eterno eu te amei. #fe #amordedeus #amor #palavradodia</t>
+          <t>Dia 357 de 365. Jeremias 31:3: Com amor eterno eu te amei. #fe #amordedeus #amor #palavradodia</t>
         </is>
       </c>
       <c r="E358" s="2" t="inlineStr">
@@ -15866,7 +15866,7 @@
       </c>
       <c r="D359" s="2" t="inlineStr">
         <is>
-          <t>Dia 280 de 365. 1 Coríntios 13:7: Tudo sofre, tudo crê, tudo espera, tudo suporta. #fe #amordedeus #amor #palavradodia</t>
+          <t>Dia 358 de 365. 1 Coríntios 13:7: Tudo sofre, tudo crê, tudo espera, tudo suporta. #fe #amordedeus #amor #palavradodia</t>
         </is>
       </c>
       <c r="E359" s="2" t="inlineStr">
@@ -15909,7 +15909,7 @@
       </c>
       <c r="D360" s="2" t="inlineStr">
         <is>
-          <t>Dia 281 de 365. 1 Coríntios 13:13: O maior deles é o amor. #fe #amordedeus #amor #palavradodia</t>
+          <t>Dia 359 de 365. 1 Coríntios 13:13: O maior deles é o amor. #fe #amordedeus #amor #palavradodia</t>
         </is>
       </c>
       <c r="E360" s="2" t="inlineStr">
@@ -15952,7 +15952,7 @@
       </c>
       <c r="D361" s="2" t="inlineStr">
         <is>
-          <t>Dia 282 de 365. Mateus 22:37-39: Os dois maiores mandamentos. #fe #amordedeus #amor #palavradodia</t>
+          <t>Dia 360 de 365. Mateus 22:37-39: Os dois maiores mandamentos. #fe #amordedeus #amor #palavradodia</t>
         </is>
       </c>
       <c r="E361" s="2" t="inlineStr">
@@ -15995,7 +15995,7 @@
       </c>
       <c r="D362" s="2" t="inlineStr">
         <is>
-          <t>Dia 283 de 365. João 13:34-35: Um mandamento novo. #fe #amordedeus #amor #palavradodia</t>
+          <t>Dia 361 de 365. João 13:34-35: Um mandamento novo. #fe #amordedeus #amor #palavradodia</t>
         </is>
       </c>
       <c r="E362" s="2" t="inlineStr">
@@ -16038,7 +16038,7 @@
       </c>
       <c r="D363" s="2" t="inlineStr">
         <is>
-          <t>Dia 284 de 365. Lucas 6:27-28: Amai os vossos inimigos. #fe #amordedeus #amor #palavradodia</t>
+          <t>Dia 362 de 365. Lucas 6:27-28: Amai os vossos inimigos. #fe #amordedeus #amor #palavradodia</t>
         </is>
       </c>
       <c r="E363" s="2" t="inlineStr">
@@ -16081,7 +16081,7 @@
       </c>
       <c r="D364" s="2" t="inlineStr">
         <is>
-          <t>Dia 285 de 365. Efésios 3:17-19: Largura, comprimento, altura e profundidade. #fe #amordedeus #amor #palavradodia</t>
+          <t>Dia 363 de 365. Efésios 3:17-19: Largura, comprimento, altura e profundidade. #fe #amordedeus #amor #palavradodia</t>
         </is>
       </c>
       <c r="E364" s="2" t="inlineStr">
@@ -16124,7 +16124,7 @@
       </c>
       <c r="D365" s="2" t="inlineStr">
         <is>
-          <t>Dia 286 de 365. 1 João 3:18: Amor de verdade aparece em ações. #fe #amordedeus #amor #palavradodia</t>
+          <t>Dia 364 de 365. 1 João 3:18: Amor de verdade aparece em ações. #fe #amordedeus #amor #palavradodia</t>
         </is>
       </c>
       <c r="E365" s="2" t="inlineStr">
@@ -16167,7 +16167,7 @@
       </c>
       <c r="D366" s="2" t="inlineStr">
         <is>
-          <t>Dia 287 de 365. Romanos 13:10: O amor não faz mal ao próximo. #fe #amordedeus #amor #palavradodia</t>
+          <t>Dia 365 de 365. Romanos 13:10: O amor não faz mal ao próximo. #fe #amordedeus #amor #palavradodia</t>
         </is>
       </c>
       <c r="E366" s="2" t="inlineStr">

--- a/legendas-365.xlsx
+++ b/legendas-365.xlsx
@@ -515,7 +515,7 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Dia 1 de 365. Salmos 36:7: Quão preciosa é a tua benignidade. #fe #amordedeus #amor #palavradodia</t>
+          <t>Dia 1 de 365. Salmos 36:7: Quão preciosa é a tua benignidade. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -525,7 +525,7 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ Salmos 103:17. Amor eterno. #versiculododia #fe #amor #oracao</t>
+          <t>Pausa do meio-dia ☀️ Salmos 103:17. Amor eterno. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -535,7 +535,7 @@
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: amor 🌙 Para fechar o dia com Salmos 36:7. Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #amor</t>
+          <t>Oração da noite: amor 🌙 Para fechar o dia com Salmos 36:7. Deixe seu pedido de oração nos comentários. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr"/>
@@ -558,7 +558,7 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Dia 2 de 365. Salmos 63:3: O teu amor é melhor do que a vida. #fe #amordedeus #amor #palavradodia</t>
+          <t>Dia 2 de 365. Salmos 63:3: O teu amor é melhor do que a vida. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
@@ -568,7 +568,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ Isaías 66:13. Amor que consola. #versiculododia #fe #amor #oracao</t>
+          <t>Pausa do meio-dia ☀️ Isaías 66:13. Amor que consola. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -578,7 +578,7 @@
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: amor 🌙 Para fechar o dia com Salmos 63:3. Escreva amém se essa oração é sua também. #oracaodanoite #oracao #fe #amor</t>
+          <t>Oração da noite: amor 🌙 Para fechar o dia com Salmos 63:3. Escreva amém se essa oração é sua também. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr"/>
@@ -601,7 +601,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Dia 3 de 365. Cantares 8:7: As muitas águas não podem apagar o amor. #fe #amordedeus #amor #palavradodia</t>
+          <t>Dia 3 de 365. Cantares 8:7: As muitas águas não podem apagar o amor. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -611,7 +611,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ Efésios 4:29. Amor nas palavras. #versiculododia #fe #amor #oracao</t>
+          <t>Pausa do meio-dia ☀️ Efésios 4:29. Amor nas palavras. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -621,7 +621,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: amor 🌙 Para fechar o dia com Cantares 8:7. Comente o nome de quem você quer colocar nesta oração. #oracaodanoite #oracao #fe #amor</t>
+          <t>Oração da noite: amor 🌙 Para fechar o dia com Cantares 8:7. Comente o nome de quem você quer colocar nesta oração. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr"/>
@@ -644,7 +644,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Dia 4 de 365. Lucas 10:33-34: O bom samaritano parou. #fe #amordedeus #amor #palavradodia</t>
+          <t>Dia 4 de 365. Lucas 10:33-34: O bom samaritano parou. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -654,7 +654,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ Salmos 85:10. Amor e verdade. #versiculododia #fe #amor #oracao</t>
+          <t>Pausa do meio-dia ☀️ Salmos 85:10. Amor e verdade. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: amor 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #amor</t>
+          <t>Oração da noite: amor 🌙 Deixe seu pedido de oração nos comentários. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr"/>
@@ -687,7 +687,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Dia 292 de 365. 1 João 4:18: O perfeito amor lança fora o medo. #fe #amordedeus #amor #palavradodia</t>
+          <t>Dia 292 de 365. 1 João 4:18: O perfeito amor lança fora o medo. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -697,7 +697,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ 2 Coríntios 9:7. Amor que dá. #versiculododia #fe #amor #oracao</t>
+          <t>Pausa do meio-dia ☀️ 2 Coríntios 9:7. Amor que dá. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -707,7 +707,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: o amor que lança fora o medo 🌙 Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #amor</t>
+          <t>Oração da noite: o amor que lança fora o medo 🌙 Deixe seu pedido de oração nos comentários. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr"/>
@@ -730,7 +730,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Dia 6 de 365. Gálatas 5:13-14: Sirvam uns aos outros pelo amor. #fe #amordedeus #amor #palavradodia</t>
+          <t>Dia 6 de 365. Gálatas 5:13-14: Sirvam uns aos outros pelo amor. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -740,7 +740,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ 1 João 3:1. Amor de Pai. #versiculododia #fe #amor #oracao</t>
+          <t>Pausa do meio-dia ☀️ 1 João 3:1. Amor de Pai. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -750,7 +750,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: amor 🌙 Para fechar o dia com Gálatas 5:13-14. Marque alguém que precisa ouvir esta oração. #oracaodanoite #oracao #fe #amor</t>
+          <t>Oração da noite: amor 🌙 Para fechar o dia com Gálatas 5:13-14. Marque alguém que precisa ouvir esta oração. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr"/>
@@ -773,7 +773,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Dia 7 de 365. João 15:9: Permanecei no meu amor. #fe #amordedeus #amor #palavradodia</t>
+          <t>Dia 7 de 365. João 15:9: Permanecei no meu amor. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -783,7 +783,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ 1 Coríntios 13:8. Amor que nunca falha. #versiculododia #fe #amor #oracao</t>
+          <t>Pausa do meio-dia ☀️ 1 Coríntios 13:8. Amor que nunca falha. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -793,7 +793,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: amor 🌙 Para fechar o dia com João 15:9. Comente seu pedido. Vamos orar juntos. #oracaodanoite #oracao #fe #amor</t>
+          <t>Oração da noite: amor 🌙 Para fechar o dia com João 15:9. Comente seu pedido. Vamos orar juntos. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr"/>
@@ -816,7 +816,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Dia 8 de 365. Efésios 2:4-5: Rico em misericórdia. #fe #amordedeus #amor #palavradodia</t>
+          <t>Dia 8 de 365. Efésios 2:4-5: Rico em misericórdia. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -826,7 +826,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ Deuteronômio 6:5. O maior mandamento. #versiculododia #fe #amor #oracao</t>
+          <t>Pausa do meio-dia ☀️ Deuteronômio 6:5. O maior mandamento. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -836,7 +836,7 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: amor 🌙 Para fechar o dia com Efésios 2:4-5. Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #amor</t>
+          <t>Oração da noite: amor 🌙 Para fechar o dia com Efésios 2:4-5. Deixe seu pedido de oração nos comentários. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr"/>
@@ -859,7 +859,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Dia 9 de 365. Romanos 12:9: O amor seja sem fingimento. #fe #amordedeus #amor #palavradodia</t>
+          <t>Dia 9 de 365. Romanos 12:9: O amor seja sem fingimento. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ Deuteronômio 10:19. Amor ao estrangeiro. #versiculododia #fe #amor #oracao</t>
+          <t>Pausa do meio-dia ☀️ Deuteronômio 10:19. Amor ao estrangeiro. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -879,7 +879,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: amor 🌙 Para fechar o dia com Romanos 12:9. Escreva amém se essa oração é sua também. #oracaodanoite #oracao #fe #amor</t>
+          <t>Oração da noite: amor 🌙 Para fechar o dia com Romanos 12:9. Escreva amém se essa oração é sua também. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr"/>
@@ -902,7 +902,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Dia 10 de 365. Provérbios 10:12: O ódio provoca brigas. #fe #amordedeus #amor #palavradodia</t>
+          <t>Dia 10 de 365. Provérbios 10:12: O ódio provoca brigas. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -912,7 +912,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ 1 Pedro 3:8. Amor compassivo. #versiculododia #fe #amor #oracao</t>
+          <t>Pausa do meio-dia ☀️ 1 Pedro 3:8. Amor compassivo. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -922,7 +922,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: amor 🌙 Para fechar o dia com Provérbios 10:12. Comente o nome de quem você quer colocar nesta oração. #oracaodanoite #oracao #fe #amor</t>
+          <t>Oração da noite: amor 🌙 Para fechar o dia com Provérbios 10:12. Comente o nome de quem você quer colocar nesta oração. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr"/>
@@ -945,7 +945,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Dia 11 de 365. 1 João 4:20: Quem diz que ama a Deus. #fe #amordedeus #amor #palavradodia</t>
+          <t>Dia 11 de 365. 1 João 4:20: Quem diz que ama a Deus. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -955,7 +955,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ João 15:10. Amor que permanece. #versiculododia #fe #amor #oracao</t>
+          <t>Pausa do meio-dia ☀️ João 15:10. Amor que permanece. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -965,7 +965,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: amor 🌙 Para fechar o dia com 1 João 4:20. Conte nos comentários pelo que você quer agradecer hoje. #oracaodanoite #oracao #fe #amor</t>
+          <t>Oração da noite: amor 🌙 Para fechar o dia com 1 João 4:20. Conte nos comentários pelo que você quer agradecer hoje. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr"/>
@@ -988,7 +988,7 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Dia 12 de 365. Salmos 86:15: Lento para a ira, grande em amor. #fe #amordedeus #amor #palavradodia</t>
+          <t>Dia 12 de 365. Salmos 86:15: Lento para a ira, grande em amor. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -998,7 +998,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ Salmos 149:4. Deus se agrada de você. #versiculododia #fe #amor #oracao</t>
+          <t>Pausa do meio-dia ☀️ Salmos 149:4. Deus se agrada de você. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1008,7 +1008,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: amor 🌙 Para fechar o dia com Salmos 86:15. Deixe nos comentários o que você quer entregar a Deus esta noite. #oracaodanoite #oracao #fe #amor</t>
+          <t>Oração da noite: amor 🌙 Para fechar o dia com Salmos 86:15. Deixe nos comentários o que você quer entregar a Deus esta noite. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr"/>
@@ -1031,7 +1031,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Dia 13 de 365. Oseias 11:4: Atraí-os com cordas de amor. #fe #amordedeus #amor #palavradodia</t>
+          <t>Dia 13 de 365. Oseias 11:4: Atraí-os com cordas de amor. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -1041,7 +1041,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ Efésios 5:2. Ande em amor. #versiculododia #fe #amor #oracao</t>
+          <t>Pausa do meio-dia ☀️ Efésios 5:2. Ande em amor. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1051,7 +1051,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: amor 🌙 Para fechar o dia com Oseias 11:4. Marque alguém que precisa ouvir esta oração. #oracaodanoite #oracao #fe #amor</t>
+          <t>Oração da noite: amor 🌙 Para fechar o dia com Oseias 11:4. Marque alguém que precisa ouvir esta oração. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr"/>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Dia 14 de 365. Marcos 10:21: Jesus olhou para ele e o amou. #fe #amordedeus #amor #palavradodia</t>
+          <t>Dia 14 de 365. Marcos 10:21: Jesus olhou para ele e o amou. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ Miqueias 6:8. Amor e misericórdia. #versiculododia #fe #amor #oracao</t>
+          <t>Pausa do meio-dia ☀️ Miqueias 6:8. Amor e misericórdia. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: amor 🌙 Para fechar o dia com Marcos 10:21. Comente seu pedido. Vamos orar juntos. #oracaodanoite #oracao #fe #amor</t>
+          <t>Oração da noite: amor 🌙 Para fechar o dia com Marcos 10:21. Comente seu pedido. Vamos orar juntos. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr"/>
@@ -1117,7 +1117,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Dia 15 de 365. João 21:17: Tu sabes que eu te amo. #fe #amordedeus #amor #palavradodia</t>
+          <t>Dia 15 de 365. João 21:17: Tu sabes que eu te amo. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ Provérbios 19:17. Amor ao pobre. #versiculododia #fe #amor #oracao</t>
+          <t>Pausa do meio-dia ☀️ Provérbios 19:17. Amor ao pobre. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1137,7 +1137,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: amor 🌙 Para fechar o dia com João 21:17. Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #amor</t>
+          <t>Oração da noite: amor 🌙 Para fechar o dia com João 21:17. Deixe seu pedido de oração nos comentários. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr"/>
@@ -1160,7 +1160,7 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>Dia 16 de 365. Tito 3:4-5: A bondade e o amor de Deus apareceram. #fe #amordedeus #amor #palavradodia</t>
+          <t>Dia 16 de 365. Tito 3:4-5: A bondade e o amor de Deus apareceram. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -1170,7 +1170,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ 1 João 4:12. Amor que une. #versiculododia #fe #amor #oracao</t>
+          <t>Pausa do meio-dia ☀️ 1 João 4:12. Amor que une. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1180,7 +1180,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: amor 🌙 Para fechar o dia com Tito 3:4-5. Escreva amém se essa oração é sua também. #oracaodanoite #oracao #fe #amor</t>
+          <t>Oração da noite: amor 🌙 Para fechar o dia com Tito 3:4-5. Escreva amém se essa oração é sua também. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr"/>
@@ -1203,7 +1203,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Dia 17 de 365. 1 Coríntios 16:14: Todas as vossas coisas sejam feitas com amor. #fe #amordedeus #amor #palavradodia</t>
+          <t>Dia 17 de 365. 1 Coríntios 16:14: Todas as vossas coisas sejam feitas com amor. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -1213,7 +1213,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ Salmos 117:2. Amor firme. #versiculododia #fe #amor #oracao</t>
+          <t>Pausa do meio-dia ☀️ Salmos 117:2. Amor firme. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: amor 🌙 Para fechar o dia com 1 Coríntios 16:14. Comente o nome de quem você quer colocar nesta oração. #oracaodanoite #oracao #fe #amor</t>
+          <t>Oração da noite: amor 🌙 Para fechar o dia com 1 Coríntios 16:14. Comente o nome de quem você quer colocar nesta oração. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr"/>
@@ -1246,7 +1246,7 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>Dia 18 de 365. Jeremias 33:3: Clama a mim, e responder-te-ei. #fe #oracao #confianca #palavradodia</t>
+          <t>Dia 18 de 365. Jeremias 33:3: Clama a mim, e responder-te-ei. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ Salmos 55:17. Já orou hoje? #versiculododia #fe #oracao #oracao</t>
+          <t>Pausa do meio-dia ☀️ Salmos 55:17. Já orou hoje? #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: oração e confiança 🌙 Para fechar o dia com Jeremias 33:3. Conte nos comentários pelo que você quer agradecer hoje. #oracaodanoite #oracao #fe #oracao</t>
+          <t>Oração da noite: oração e confiança 🌙 Para fechar o dia com Jeremias 33:3. Conte nos comentários pelo que você quer agradecer hoje. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr"/>
@@ -1289,7 +1289,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Dia 19 de 365. Mateus 7:7-8: Pedi, buscai, batei. #fe #oracao #confianca #palavradodia</t>
+          <t>Dia 19 de 365. Mateus 7:7-8: Pedi, buscai, batei. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -1299,7 +1299,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ Salmos 142:2. Ore sem cerimônia. #versiculododia #fe #oracao #oracao</t>
+          <t>Pausa do meio-dia ☀️ Salmos 142:2. Ore sem cerimônia. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1309,7 +1309,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: oração e confiança 🌙 Para fechar o dia com Mateus 7:7-8. Deixe nos comentários o que você quer entregar a Deus esta noite. #oracaodanoite #oracao #fe #oracao</t>
+          <t>Oração da noite: oração e confiança 🌙 Para fechar o dia com Mateus 7:7-8. Deixe nos comentários o que você quer entregar a Deus esta noite. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr"/>
@@ -1332,7 +1332,7 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>Dia 20 de 365. 1 Tessalonicenses 5:17: Orai sem cessar. #fe #oracao #confianca #palavradodia</t>
+          <t>Dia 20 de 365. 1 Tessalonicenses 5:17: Orai sem cessar. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -1342,7 +1342,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ Salmos 34:15. Ele ouve. #versiculododia #fe #oracao #oracao</t>
+          <t>Pausa do meio-dia ☀️ Salmos 34:15. Ele ouve. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -1352,7 +1352,7 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: oração e confiança 🌙 Para fechar o dia com 1 Tessalonicenses 5:17. Marque alguém que precisa ouvir esta oração. #oracaodanoite #oracao #fe #oracao</t>
+          <t>Oração da noite: oração e confiança 🌙 Para fechar o dia com 1 Tessalonicenses 5:17. Marque alguém que precisa ouvir esta oração. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr"/>
@@ -1375,7 +1375,7 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>Dia 21 de 365. Filipenses 4:19: O meu Deus suprirá. #fe #oracao #confianca #palavradodia</t>
+          <t>Dia 21 de 365. Filipenses 4:19: O meu Deus suprirá. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -1385,7 +1385,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ Salmos 13:5. Confie de todo coração. #versiculododia #fe #oracao #oracao</t>
+          <t>Pausa do meio-dia ☀️ Salmos 13:5. Confie de todo coração. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -1395,7 +1395,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: oração e confiança 🌙 Para fechar o dia com Filipenses 4:19. Comente seu pedido. Vamos orar juntos. #oracaodanoite #oracao #fe #oracao</t>
+          <t>Oração da noite: oração e confiança 🌙 Para fechar o dia com Filipenses 4:19. Comente seu pedido. Vamos orar juntos. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr"/>
@@ -1418,7 +1418,7 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>Dia 22 de 365. Salmos 37:4: Deleita-te no Senhor. #fe #oracao #confianca #palavradodia</t>
+          <t>Dia 22 de 365. Salmos 37:4: Deleita-te no Senhor. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ 1 Timóteo 2:1. Ore pelos outros. #versiculododia #fe #oracao #oracao</t>
+          <t>Pausa do meio-dia ☀️ 1 Timóteo 2:1. Ore pelos outros. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -1438,7 +1438,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: oração e confiança 🌙 Para fechar o dia com Salmos 37:4. Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #oracao</t>
+          <t>Oração da noite: oração e confiança 🌙 Para fechar o dia com Salmos 37:4. Deixe seu pedido de oração nos comentários. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr"/>
@@ -1461,7 +1461,7 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>Dia 23 de 365. Salmos 56:8: Deus guarda as suas lágrimas. #fe #oracao #confianca #palavradodia</t>
+          <t>Dia 23 de 365. Salmos 56:8: Deus guarda as suas lágrimas. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ Tiago 5:13. Aflito? Ore. Contente? Cante. #versiculododia #fe #oracao #oracao</t>
+          <t>Pausa do meio-dia ☀️ Tiago 5:13. Aflito? Ore. Contente? Cante. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: oração e confiança 🌙 Para fechar o dia com Salmos 56:8. Escreva amém se essa oração é sua também. #oracaodanoite #oracao #fe #oracao</t>
+          <t>Oração da noite: oração e confiança 🌙 Para fechar o dia com Salmos 56:8. Escreva amém se essa oração é sua também. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr"/>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>Dia 24 de 365. Marcos 11:24: Crede que recebestes. #fe #oracao #confianca #palavradodia</t>
+          <t>Dia 24 de 365. Marcos 11:24: Crede que recebestes. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
@@ -1514,7 +1514,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ João 16:24. Peça. #versiculododia #fe #oracao #oracao</t>
+          <t>Pausa do meio-dia ☀️ João 16:24. Peça. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: oração e confiança 🌙 Para fechar o dia com Marcos 11:24. Comente o nome de quem você quer colocar nesta oração. #oracaodanoite #oracao #fe #oracao</t>
+          <t>Oração da noite: oração e confiança 🌙 Para fechar o dia com Marcos 11:24. Comente o nome de quem você quer colocar nesta oração. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr"/>
@@ -1547,7 +1547,7 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>Dia 25 de 365. Salmos 145:18: Perto está o Senhor. #fe #oracao #confianca #palavradodia</t>
+          <t>Dia 25 de 365. Salmos 145:18: Perto está o Senhor. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -1557,7 +1557,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ Mateus 6:8. Ele sabe do que você precisa. #versiculododia #fe #oracao #oracao</t>
+          <t>Pausa do meio-dia ☀️ Mateus 6:8. Ele sabe do que você precisa. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -1567,7 +1567,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: oração e confiança 🌙 Para fechar o dia com Salmos 145:18. Conte nos comentários pelo que você quer agradecer hoje. #oracaodanoite #oracao #fe #oracao</t>
+          <t>Oração da noite: oração e confiança 🌙 Para fechar o dia com Salmos 145:18. Conte nos comentários pelo que você quer agradecer hoje. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr"/>
@@ -1590,7 +1590,7 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>Dia 26 de 365. Mateus 6:6: Entre no seu quarto e feche a porta. #fe #oracao #confianca #palavradodia</t>
+          <t>Dia 26 de 365. Mateus 6:6: Entre no seu quarto e feche a porta. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
@@ -1600,7 +1600,7 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ Salmos 37:3. Confie e faça o bem. #versiculododia #fe #oracao #oracao</t>
+          <t>Pausa do meio-dia ☀️ Salmos 37:3. Confie e faça o bem. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -1610,7 +1610,7 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: oração e confiança 🌙 Para fechar o dia com Mateus 6:6. Deixe nos comentários o que você quer entregar a Deus esta noite. #oracaodanoite #oracao #fe #oracao</t>
+          <t>Oração da noite: oração e confiança 🌙 Para fechar o dia com Mateus 6:6. Deixe nos comentários o que você quer entregar a Deus esta noite. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr"/>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>Dia 27 de 365. Romanos 8:26: Quando você não sabe o que orar. #fe #oracao #confianca #palavradodia</t>
+          <t>Dia 27 de 365. Romanos 8:26: Quando você não sabe o que orar. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -1643,7 +1643,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ Tiago 1:6. Ore com fé. #versiculododia #fe #oracao #oracao</t>
+          <t>Pausa do meio-dia ☀️ Tiago 1:6. Ore com fé. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -1653,7 +1653,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: oração e confiança 🌙 Para fechar o dia com Romanos 8:26. Marque alguém que precisa ouvir esta oração. #oracaodanoite #oracao #fe #oracao</t>
+          <t>Oração da noite: oração e confiança 🌙 Para fechar o dia com Romanos 8:26. Marque alguém que precisa ouvir esta oração. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr"/>
@@ -1676,7 +1676,7 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>Dia 28 de 365. Hebreus 4:16: Cheguemos com confiança ao trono da graça. #fe #oracao #confianca #palavradodia</t>
+          <t>Dia 28 de 365. Hebreus 4:16: Cheguemos com confiança ao trono da graça. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ 1 Coríntios 1:9. Ele é fiel. #versiculododia #fe #oracao #oracao</t>
+          <t>Pausa do meio-dia ☀️ 1 Coríntios 1:9. Ele é fiel. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -1696,7 +1696,7 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: oração e confiança 🌙 Para fechar o dia com Hebreus 4:16. Comente seu pedido. Vamos orar juntos. #oracaodanoite #oracao #fe #oracao</t>
+          <t>Oração da noite: oração e confiança 🌙 Para fechar o dia com Hebreus 4:16. Comente seu pedido. Vamos orar juntos. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr"/>
@@ -1719,7 +1719,7 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>Dia 29 de 365. Salmos 62:8: Derramai perante Ele o vosso coração. #fe #oracao #confianca #palavradodia</t>
+          <t>Dia 29 de 365. Salmos 62:8: Derramai perante Ele o vosso coração. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ Salmos 118:8. Confie em quem não falha. #versiculododia #fe #oracao #oracao</t>
+          <t>Pausa do meio-dia ☀️ Salmos 118:8. Confie em quem não falha. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -1739,7 +1739,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: oração e confiança 🌙 Para fechar o dia com Salmos 62:8. Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #oracao</t>
+          <t>Oração da noite: oração e confiança 🌙 Para fechar o dia com Salmos 62:8. Deixe seu pedido de oração nos comentários. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr"/>
@@ -1762,7 +1762,7 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>Dia 30 de 365. Tiago 5:16: A oração do justo pode muito. #fe #oracao #confianca #palavradodia</t>
+          <t>Dia 30 de 365. Tiago 5:16: A oração do justo pode muito. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ Efésios 6:18. Ore em todo tempo. #versiculododia #fe #oracao #oracao</t>
+          <t>Pausa do meio-dia ☀️ Efésios 6:18. Ore em todo tempo. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -1782,7 +1782,7 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: oração e confiança 🌙 Para fechar o dia com Tiago 5:16. Escreva amém se essa oração é sua também. #oracaodanoite #oracao #fe #oracao</t>
+          <t>Oração da noite: oração e confiança 🌙 Para fechar o dia com Tiago 5:16. Escreva amém se essa oração é sua também. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr"/>
@@ -1805,7 +1805,7 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>Dia 31 de 365. Mateus 6:9-10: A oração que Jesus ensinou. #fe #oracao #confianca #palavradodia</t>
+          <t>Dia 31 de 365. Mateus 6:9-10: A oração que Jesus ensinou. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
@@ -1815,7 +1815,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ Salmos 27:8. Busque a face dEle. #versiculododia #fe #oracao #oracao</t>
+          <t>Pausa do meio-dia ☀️ Salmos 27:8. Busque a face dEle. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -1825,7 +1825,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: oração e confiança 🌙 Para fechar o dia com Mateus 6:9-10. Comente o nome de quem você quer colocar nesta oração. #oracaodanoite #oracao #fe #oracao</t>
+          <t>Oração da noite: oração e confiança 🌙 Para fechar o dia com Mateus 6:9-10. Comente o nome de quem você quer colocar nesta oração. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr"/>
@@ -1848,7 +1848,7 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>Dia 32 de 365. Salmos 5:3: De manhã ouvirás a minha voz. #fe #oracao #confianca #palavradodia</t>
+          <t>Dia 32 de 365. Salmos 5:3: De manhã ouvirás a minha voz. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
@@ -1858,7 +1858,7 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ Salmos 50:15. Clame. #versiculododia #fe #oracao #oracao</t>
+          <t>Pausa do meio-dia ☀️ Salmos 50:15. Clame. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -1868,7 +1868,7 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: oração e confiança 🌙 Para fechar o dia com Salmos 5:3. Conte nos comentários pelo que você quer agradecer hoje. #oracaodanoite #oracao #fe #oracao</t>
+          <t>Oração da noite: oração e confiança 🌙 Para fechar o dia com Salmos 5:3. Conte nos comentários pelo que você quer agradecer hoje. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr"/>
@@ -1891,7 +1891,7 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>Dia 33 de 365. Lucas 22:42: Não a minha vontade, mas a tua. #fe #oracao #confianca #palavradodia</t>
+          <t>Dia 33 de 365. Lucas 22:42: Não a minha vontade, mas a tua. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
@@ -1901,7 +1901,7 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ Salmos 120:1. Ele responde. #versiculododia #fe #oracao #oracao</t>
+          <t>Pausa do meio-dia ☀️ Salmos 120:1. Ele responde. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -1911,7 +1911,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: oração e confiança 🌙 Para fechar o dia com Lucas 22:42. Deixe nos comentários o que você quer entregar a Deus esta noite. #oracaodanoite #oracao #fe #oracao</t>
+          <t>Oração da noite: oração e confiança 🌙 Para fechar o dia com Lucas 22:42. Deixe nos comentários o que você quer entregar a Deus esta noite. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr"/>
@@ -1934,7 +1934,7 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>Dia 34 de 365. 1 João 5:14: Se pedirmos segundo a sua vontade. #fe #oracao #confianca #palavradodia</t>
+          <t>Dia 34 de 365. 1 João 5:14: Se pedirmos segundo a sua vontade. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
@@ -1944,7 +1944,7 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ Jeremias 17:7. Confie no Senhor. #versiculododia #fe #oracao #oracao</t>
+          <t>Pausa do meio-dia ☀️ Jeremias 17:7. Confie no Senhor. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -1954,7 +1954,7 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: oração e confiança 🌙 Para fechar o dia com 1 João 5:14. Marque alguém que precisa ouvir esta oração. #oracaodanoite #oracao #fe #oracao</t>
+          <t>Oração da noite: oração e confiança 🌙 Para fechar o dia com 1 João 5:14. Marque alguém que precisa ouvir esta oração. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr"/>
@@ -1977,7 +1977,7 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>Dia 35 de 365. Salmos 20:7: Uns confiam em carros, outros em cavalos. #fe #oracao #confianca #palavradodia</t>
+          <t>Dia 35 de 365. Salmos 20:7: Uns confiam em carros, outros em cavalos. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
@@ -1987,7 +1987,7 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ 1 Tessalonicenses 5:16. Alegria na oração. #versiculododia #fe #oracao #oracao</t>
+          <t>Pausa do meio-dia ☀️ 1 Tessalonicenses 5:16. Alegria na oração. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -1997,7 +1997,7 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: oração e confiança 🌙 Para fechar o dia com Salmos 20:7. Comente seu pedido. Vamos orar juntos. #oracaodanoite #oracao #fe #oracao</t>
+          <t>Oração da noite: oração e confiança 🌙 Para fechar o dia com Salmos 20:7. Comente seu pedido. Vamos orar juntos. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr"/>
@@ -2020,7 +2020,7 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>Dia 36 de 365. Isaías 65:24: Antes que clamem, eu responderei. #fe #oracao #confianca #palavradodia</t>
+          <t>Dia 36 de 365. Isaías 65:24: Antes que clamem, eu responderei. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
@@ -2030,7 +2030,7 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ Deuteronômio 4:7. Ele está perto. #versiculododia #fe #oracao #oracao</t>
+          <t>Pausa do meio-dia ☀️ Deuteronômio 4:7. Ele está perto. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -2040,7 +2040,7 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: oração e confiança 🌙 Para fechar o dia com Isaías 65:24. Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #oracao</t>
+          <t>Oração da noite: oração e confiança 🌙 Para fechar o dia com Isaías 65:24. Deixe seu pedido de oração nos comentários. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr"/>
@@ -2063,7 +2063,7 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>Dia 37 de 365. Neemias 1:4: Neemias chorou, jejuou e orou. #fe #oracao #confianca #palavradodia</t>
+          <t>Dia 37 de 365. Neemias 1:4: Neemias chorou, jejuou e orou. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
@@ -2073,7 +2073,7 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ Salmos 31:15. Confie nos planos dEle. #versiculododia #fe #oracao #oracao</t>
+          <t>Pausa do meio-dia ☀️ Salmos 31:15. Confie nos planos dEle. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -2083,7 +2083,7 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: oração e confiança 🌙 Para fechar o dia com Neemias 1:4. Escreva amém se essa oração é sua também. #oracaodanoite #oracao #fe #oracao</t>
+          <t>Oração da noite: oração e confiança 🌙 Para fechar o dia com Neemias 1:4. Escreva amém se essa oração é sua também. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr"/>
@@ -2106,7 +2106,7 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>Dia 38 de 365. Daniel 9:18: Não por nossas justiças. #fe #oracao #confianca #palavradodia</t>
+          <t>Dia 38 de 365. Daniel 9:18: Não por nossas justiças. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
@@ -2116,7 +2116,7 @@
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ Salmos 40:1. Ore e espere. #versiculododia #fe #oracao #oracao</t>
+          <t>Pausa do meio-dia ☀️ Salmos 40:1. Ore e espere. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -2126,7 +2126,7 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: oração e confiança 🌙 Para fechar o dia com Daniel 9:18. Comente o nome de quem você quer colocar nesta oração. #oracaodanoite #oracao #fe #oracao</t>
+          <t>Oração da noite: oração e confiança 🌙 Para fechar o dia com Daniel 9:18. Comente o nome de quem você quer colocar nesta oração. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr"/>
@@ -2149,7 +2149,7 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>Dia 39 de 365. Salmos 37:7: Descansa no Senhor e espera nEle. #fe #oracao #confianca #palavradodia</t>
+          <t>Dia 39 de 365. Salmos 37:7: Descansa no Senhor e espera nEle. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
@@ -2159,7 +2159,7 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ Jeremias 29:7. Ore pela cidade. #versiculododia #fe #oracao #oracao</t>
+          <t>Pausa do meio-dia ☀️ Jeremias 29:7. Ore pela cidade. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -2169,7 +2169,7 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: oração e confiança 🌙 Para fechar o dia com Salmos 37:7. Conte nos comentários pelo que você quer agradecer hoje. #oracaodanoite #oracao #fe #oracao</t>
+          <t>Oração da noite: oração e confiança 🌙 Para fechar o dia com Salmos 37:7. Conte nos comentários pelo que você quer agradecer hoje. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr"/>
@@ -2192,7 +2192,7 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>Dia 40 de 365. Mateus 21:22: Tudo o que pedirdes em oração, crendo. #fe #oracao #confianca #palavradodia</t>
+          <t>Dia 40 de 365. Mateus 21:22: Tudo o que pedirdes em oração, crendo. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
@@ -2202,7 +2202,7 @@
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ Salmos 9:9. Ele não falha. #versiculododia #fe #oracao #oracao</t>
+          <t>Pausa do meio-dia ☀️ Salmos 9:9. Ele não falha. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -2212,7 +2212,7 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: oração e confiança 🌙 Para fechar o dia com Mateus 21:22. Deixe nos comentários o que você quer entregar a Deus esta noite. #oracaodanoite #oracao #fe #oracao</t>
+          <t>Oração da noite: oração e confiança 🌙 Para fechar o dia com Mateus 21:22. Deixe nos comentários o que você quer entregar a Deus esta noite. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr"/>
@@ -2235,7 +2235,7 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>Dia 41 de 365. Salmos 141:2: Minha oração como incenso. #fe #oracao #confianca #palavradodia</t>
+          <t>Dia 41 de 365. Salmos 141:2: Minha oração como incenso. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
@@ -2245,7 +2245,7 @@
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ Lucas 18:13. Ore com humildade. #versiculododia #fe #oracao #oracao</t>
+          <t>Pausa do meio-dia ☀️ Lucas 18:13. Ore com humildade. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -2255,7 +2255,7 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: oração e confiança 🌙 Para fechar o dia com Salmos 141:2. Marque alguém que precisa ouvir esta oração. #oracaodanoite #oracao #fe #oracao</t>
+          <t>Oração da noite: oração e confiança 🌙 Para fechar o dia com Salmos 141:2. Marque alguém que precisa ouvir esta oração. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr"/>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>Dia 42 de 365. Isaías 30:15: Na tranquilidade e na confiança. #fe #oracao #confianca #palavradodia</t>
+          <t>Dia 42 de 365. Isaías 30:15: Na tranquilidade e na confiança. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
@@ -2288,7 +2288,7 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ 2 Coríntios 5:7. Confie sem ver. #versiculododia #fe #oracao #oracao</t>
+          <t>Pausa do meio-dia ☀️ 2 Coríntios 5:7. Confie sem ver. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -2298,7 +2298,7 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: oração e confiança 🌙 Para fechar o dia com Isaías 30:15. Comente seu pedido. Vamos orar juntos. #oracaodanoite #oracao #fe #oracao</t>
+          <t>Oração da noite: oração e confiança 🌙 Para fechar o dia com Isaías 30:15. Comente seu pedido. Vamos orar juntos. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr"/>
@@ -2321,7 +2321,7 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>Dia 43 de 365. Salmos 9:10: Os que conhecem o teu nome confiarão em ti. #fe #oracao #confianca #palavradodia</t>
+          <t>Dia 43 de 365. Salmos 9:10: Os que conhecem o teu nome confiarão em ti. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
@@ -2331,7 +2331,7 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ 1 Timóteo 2:2. Ore pelos líderes. #versiculododia #fe #oracao #oracao</t>
+          <t>Pausa do meio-dia ☀️ 1 Timóteo 2:2. Ore pelos líderes. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: oração e confiança 🌙 Para fechar o dia com Salmos 9:10. Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #oracao</t>
+          <t>Oração da noite: oração e confiança 🌙 Para fechar o dia com Salmos 9:10. Deixe seu pedido de oração nos comentários. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr"/>
@@ -2364,7 +2364,7 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>Dia 44 de 365. Atos 12:5: A igreja orava por Pedro. #fe #oracao #confianca #palavradodia</t>
+          <t>Dia 44 de 365. Atos 12:5: A igreja orava por Pedro. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
@@ -2374,7 +2374,7 @@
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ Judas 1:20. O Espírito ajuda. #versiculododia #fe #oracao #oracao</t>
+          <t>Pausa do meio-dia ☀️ Judas 1:20. O Espírito ajuda. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -2384,7 +2384,7 @@
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: oração e confiança 🌙 Para fechar o dia com Atos 12:5. Escreva amém se essa oração é sua também. #oracaodanoite #oracao #fe #oracao</t>
+          <t>Oração da noite: oração e confiança 🌙 Para fechar o dia com Atos 12:5. Escreva amém se essa oração é sua também. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr"/>
@@ -2407,7 +2407,7 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>Dia 45 de 365. Lucas 11:9-10: Batei, e abrir-se-vos-á. #fe #oracao #confianca #palavradodia</t>
+          <t>Dia 45 de 365. Lucas 11:9-10: Batei, e abrir-se-vos-á. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
@@ -2417,7 +2417,7 @@
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ Salmos 119:114. Confie na palavra. #versiculododia #fe #oracao #oracao</t>
+          <t>Pausa do meio-dia ☀️ Salmos 119:114. Confie na palavra. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -2427,7 +2427,7 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: oração e confiança 🌙 Para fechar o dia com Lucas 11:9-10. Comente o nome de quem você quer colocar nesta oração. #oracaodanoite #oracao #fe #oracao</t>
+          <t>Oração da noite: oração e confiança 🌙 Para fechar o dia com Lucas 11:9-10. Comente o nome de quem você quer colocar nesta oração. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr"/>
@@ -2450,7 +2450,7 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>Dia 46 de 365. Provérbios 29:25: O medo dos homens é um laço. #fe #oracao #confianca #palavradodia</t>
+          <t>Dia 46 de 365. Provérbios 29:25: O medo dos homens é um laço. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
@@ -2460,7 +2460,7 @@
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ Lucas 5:16. Ore a sós. #versiculododia #fe #oracao #oracao</t>
+          <t>Pausa do meio-dia ☀️ Lucas 5:16. Ore a sós. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -2470,7 +2470,7 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: oração e confiança 🌙 Para fechar o dia com Provérbios 29:25. Conte nos comentários pelo que você quer agradecer hoje. #oracaodanoite #oracao #fe #oracao</t>
+          <t>Oração da noite: oração e confiança 🌙 Para fechar o dia com Provérbios 29:25. Conte nos comentários pelo que você quer agradecer hoje. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr"/>
@@ -2493,7 +2493,7 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>Dia 47 de 365. Salmos 57:1-2: À sombra das tuas asas. #fe #oracao #confianca #palavradodia</t>
+          <t>Dia 47 de 365. Salmos 57:1-2: À sombra das tuas asas. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
@@ -2503,7 +2503,7 @@
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ Salmos 4:5. Confie e descanse. #versiculododia #fe #oracao #oracao</t>
+          <t>Pausa do meio-dia ☀️ Salmos 4:5. Confie e descanse. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -2513,7 +2513,7 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: oração e confiança 🌙 Para fechar o dia com Salmos 57:1-2. Deixe nos comentários o que você quer entregar a Deus esta noite. #oracaodanoite #oracao #fe #oracao</t>
+          <t>Oração da noite: oração e confiança 🌙 Para fechar o dia com Salmos 57:1-2. Deixe nos comentários o que você quer entregar a Deus esta noite. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr"/>
@@ -2536,7 +2536,7 @@
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>Dia 48 de 365. Isaías 43:18: Não vos lembreis das coisas passadas. #fe #recomeco #promessas #palavradodia</t>
+          <t>Dia 48 de 365. Isaías 43:18: Não vos lembreis das coisas passadas. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
@@ -2546,7 +2546,7 @@
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ Lamentações 5:21. Precisa recomeçar? #versiculododia #fe #recomeco #oracao</t>
+          <t>Pausa do meio-dia ☀️ Lamentações 5:21. Precisa recomeçar? #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -2556,7 +2556,7 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: recomeço e promessas 🌙 Para fechar o dia com Isaías 43:18. Marque alguém que precisa ouvir esta oração. #oracaodanoite #oracao #fe #recomeco</t>
+          <t>Oração da noite: recomeço e promessas 🌙 Para fechar o dia com Isaías 43:18. Marque alguém que precisa ouvir esta oração. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr"/>
@@ -2579,7 +2579,7 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>Dia 49 de 365. Filipenses 3:13-14: Esquecendo o que fica para trás. #fe #recomeco #promessas #palavradodia</t>
+          <t>Dia 49 de 365. Filipenses 3:13-14: Esquecendo o que fica para trás. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
@@ -2589,7 +2589,7 @@
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ 1 Reis 8:56. Nenhuma palavra dEle falhou. #versiculododia #fe #recomeco #oracao</t>
+          <t>Pausa do meio-dia ☀️ 1 Reis 8:56. Nenhuma palavra dEle falhou. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -2599,7 +2599,7 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: recomeço e promessas 🌙 Para fechar o dia com Filipenses 3:13-14. Comente seu pedido. Vamos orar juntos. #oracaodanoite #oracao #fe #recomeco</t>
+          <t>Oração da noite: recomeço e promessas 🌙 Para fechar o dia com Filipenses 3:13-14. Comente seu pedido. Vamos orar juntos. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr"/>
@@ -2622,7 +2622,7 @@
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>Dia 50 de 365. Ezequiel 36:26: Um coração novo. #fe #recomeco #promessas #palavradodia</t>
+          <t>Dia 50 de 365. Ezequiel 36:26: Um coração novo. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
@@ -2632,7 +2632,7 @@
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ Efésios 4:24. Vista o novo. #versiculododia #fe #recomeco #oracao</t>
+          <t>Pausa do meio-dia ☀️ Efésios 4:24. Vista o novo. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
@@ -2642,7 +2642,7 @@
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: recomeço e promessas 🌙 Para fechar o dia com Ezequiel 36:26. Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #recomeco</t>
+          <t>Oração da noite: recomeço e promessas 🌙 Para fechar o dia com Ezequiel 36:26. Deixe seu pedido de oração nos comentários. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr"/>
@@ -2665,7 +2665,7 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>Dia 51 de 365. Apocalipse 21:5: Eis que faço novas todas as coisas. #fe #recomeco #promessas #palavradodia</t>
+          <t>Dia 51 de 365. Apocalipse 21:5: Eis que faço novas todas as coisas. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
@@ -2675,7 +2675,7 @@
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ Isaías 33:2. Força a cada manhã. #versiculododia #fe #recomeco #oracao</t>
+          <t>Pausa do meio-dia ☀️ Isaías 33:2. Força a cada manhã. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -2685,7 +2685,7 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: recomeço e promessas 🌙 Para fechar o dia com Apocalipse 21:5. Escreva amém se essa oração é sua também. #oracaodanoite #oracao #fe #recomeco</t>
+          <t>Oração da noite: recomeço e promessas 🌙 Para fechar o dia com Apocalipse 21:5. Escreva amém se essa oração é sua também. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr"/>
@@ -2708,7 +2708,7 @@
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>Dia 52 de 365. Salmos 40:3: Um cântico novo. #fe #recomeco #promessas #palavradodia</t>
+          <t>Dia 52 de 365. Salmos 40:3: Um cântico novo. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
@@ -2718,7 +2718,7 @@
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ Isaías 65:17. Ele faz novo. #versiculododia #fe #recomeco #oracao</t>
+          <t>Pausa do meio-dia ☀️ Isaías 65:17. Ele faz novo. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -2728,7 +2728,7 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: recomeço e promessas 🌙 Para fechar o dia com Salmos 40:3. Comente o nome de quem você quer colocar nesta oração. #oracaodanoite #oracao #fe #recomeco</t>
+          <t>Oração da noite: recomeço e promessas 🌙 Para fechar o dia com Salmos 40:3. Comente o nome de quem você quer colocar nesta oração. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr"/>
@@ -2751,7 +2751,7 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>Dia 53 de 365. 2 Coríntios 1:20: Todas as promessas têm o sim nEle. #fe #recomeco #promessas #palavradodia</t>
+          <t>Dia 53 de 365. 2 Coríntios 1:20: Todas as promessas têm o sim nEle. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ Mateus 1:23. Deus conosco. #versiculododia #fe #recomeco #oracao</t>
+          <t>Pausa do meio-dia ☀️ Mateus 1:23. Deus conosco. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: recomeço e promessas 🌙 Para fechar o dia com 2 Coríntios 1:20. Conte nos comentários pelo que você quer agradecer hoje. #oracaodanoite #oracao #fe #recomeco</t>
+          <t>Oração da noite: recomeço e promessas 🌙 Para fechar o dia com 2 Coríntios 1:20. Conte nos comentários pelo que você quer agradecer hoje. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr"/>
@@ -2794,7 +2794,7 @@
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>Dia 54 de 365. Números 23:19: Deus não é homem para que minta. #fe #recomeco #promessas #palavradodia</t>
+          <t>Dia 54 de 365. Números 23:19: Deus não é homem para que minta. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
@@ -2804,7 +2804,7 @@
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ Salmos 34:10. Promessa de cuidado. #versiculododia #fe #recomeco #oracao</t>
+          <t>Pausa do meio-dia ☀️ Salmos 34:10. Promessa de cuidado. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -2814,7 +2814,7 @@
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: recomeço e promessas 🌙 Para fechar o dia com Números 23:19. Deixe nos comentários o que você quer entregar a Deus esta noite. #oracaodanoite #oracao #fe #recomeco</t>
+          <t>Oração da noite: recomeço e promessas 🌙 Para fechar o dia com Números 23:19. Deixe nos comentários o que você quer entregar a Deus esta noite. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr"/>
@@ -2837,7 +2837,7 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>Dia 55 de 365. Josué 21:45: Nenhuma palavra falhou. #fe #recomeco #promessas #palavradodia</t>
+          <t>Dia 55 de 365. Josué 21:45: Nenhuma palavra falhou. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
@@ -2847,7 +2847,7 @@
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ Lucas 15:22. Recomeço do filho. #versiculododia #fe #recomeco #oracao</t>
+          <t>Pausa do meio-dia ☀️ Lucas 15:22. Recomeço do filho. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -2857,7 +2857,7 @@
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: recomeço e promessas 🌙 Para fechar o dia com Josué 21:45. Marque alguém que precisa ouvir esta oração. #oracaodanoite #oracao #fe #recomeco</t>
+          <t>Oração da noite: recomeço e promessas 🌙 Para fechar o dia com Josué 21:45. Marque alguém que precisa ouvir esta oração. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr"/>
@@ -2880,7 +2880,7 @@
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>Dia 56 de 365. Lamentações 3:25: Bom é o Senhor para os que esperam por Ele. #fe #recomeco #promessas #palavradodia</t>
+          <t>Dia 56 de 365. Lamentações 3:25: Bom é o Senhor para os que esperam por Ele. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
@@ -2890,7 +2890,7 @@
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ Salmos 51:12. Alegria restaurada. #versiculododia #fe #recomeco #oracao</t>
+          <t>Pausa do meio-dia ☀️ Salmos 51:12. Alegria restaurada. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
@@ -2900,7 +2900,7 @@
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: recomeço e promessas 🌙 Para fechar o dia com Lamentações 3:25. Comente seu pedido. Vamos orar juntos. #oracaodanoite #oracao #fe #recomeco</t>
+          <t>Oração da noite: recomeço e promessas 🌙 Para fechar o dia com Lamentações 3:25. Comente seu pedido. Vamos orar juntos. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr"/>
@@ -2923,7 +2923,7 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>Dia 57 de 365. Isaías 55:10-11: A palavra de Deus não volta vazia. #fe #recomeco #promessas #palavradodia</t>
+          <t>Dia 57 de 365. Isaías 55:10-11: A palavra de Deus não volta vazia. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
@@ -2933,7 +2933,7 @@
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ Joel 2:26. Ele restitui. #versiculododia #fe #recomeco #oracao</t>
+          <t>Pausa do meio-dia ☀️ Joel 2:26. Ele restitui. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
@@ -2943,7 +2943,7 @@
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: recomeço e promessas 🌙 Para fechar o dia com Isaías 55:10-11. Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #recomeco</t>
+          <t>Oração da noite: recomeço e promessas 🌙 Para fechar o dia com Isaías 55:10-11. Deixe seu pedido de oração nos comentários. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr"/>
@@ -2966,7 +2966,7 @@
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>Dia 58 de 365. Salmos 37:25: Nunca vi o justo desamparado. #fe #recomeco #promessas #palavradodia</t>
+          <t>Dia 58 de 365. Salmos 37:25: Nunca vi o justo desamparado. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
@@ -2976,7 +2976,7 @@
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ Isaías 48:17. Promessa de direção. #versiculododia #fe #recomeco #oracao</t>
+          <t>Pausa do meio-dia ☀️ Isaías 48:17. Promessa de direção. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
@@ -2986,7 +2986,7 @@
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: recomeço e promessas 🌙 Para fechar o dia com Salmos 37:25. Escreva amém se essa oração é sua também. #oracaodanoite #oracao #fe #recomeco</t>
+          <t>Oração da noite: recomeço e promessas 🌙 Para fechar o dia com Salmos 37:25. Escreva amém se essa oração é sua também. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr"/>
@@ -3009,7 +3009,7 @@
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>Dia 59 de 365. Deuteronômio 7:9: O Deus fiel. #fe #recomeco #promessas #palavradodia</t>
+          <t>Dia 59 de 365. Deuteronômio 7:9: O Deus fiel. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
@@ -3019,7 +3019,7 @@
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ Jó 11:16. Deixe o passado passar. #versiculododia #fe #recomeco #oracao</t>
+          <t>Pausa do meio-dia ☀️ Jó 11:16. Deixe o passado passar. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
@@ -3029,7 +3029,7 @@
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: recomeço e promessas 🌙 Para fechar o dia com Deuteronômio 7:9. Comente o nome de quem você quer colocar nesta oração. #oracaodanoite #oracao #fe #recomeco</t>
+          <t>Oração da noite: recomeço e promessas 🌙 Para fechar o dia com Deuteronômio 7:9. Comente o nome de quem você quer colocar nesta oração. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr"/>
@@ -3052,7 +3052,7 @@
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>Dia 60 de 365. Hebreus 10:23: Retenhamos firme a confissão da esperança. #fe #recomeco #promessas #palavradodia</t>
+          <t>Dia 60 de 365. Hebreus 10:23: Retenhamos firme a confissão da esperança. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
@@ -3062,7 +3062,7 @@
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ Salmos 68:35. Promessa de força. #versiculododia #fe #recomeco #oracao</t>
+          <t>Pausa do meio-dia ☀️ Salmos 68:35. Promessa de força. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
@@ -3072,7 +3072,7 @@
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: recomeço e promessas 🌙 Para fechar o dia com Hebreus 10:23. Conte nos comentários pelo que você quer agradecer hoje. #oracaodanoite #oracao #fe #recomeco</t>
+          <t>Oração da noite: recomeço e promessas 🌙 Para fechar o dia com Hebreus 10:23. Conte nos comentários pelo que você quer agradecer hoje. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr"/>
@@ -3095,7 +3095,7 @@
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>Dia 61 de 365. Jonas 2:10: Do fundo do peixe para a terra seca. #fe #recomeco #promessas #palavradodia</t>
+          <t>Dia 61 de 365. Jonas 2:10: Do fundo do peixe para a terra seca. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
@@ -3105,7 +3105,7 @@
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ Apocalipse 2:4. O primeiro amor. #versiculododia #fe #recomeco #oracao</t>
+          <t>Pausa do meio-dia ☀️ Apocalipse 2:4. O primeiro amor. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
@@ -3115,7 +3115,7 @@
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: recomeço e promessas 🌙 Para fechar o dia com Jonas 2:10. Deixe nos comentários o que você quer entregar a Deus esta noite. #oracaodanoite #oracao #fe #recomeco</t>
+          <t>Oração da noite: recomeço e promessas 🌙 Para fechar o dia com Jonas 2:10. Deixe nos comentários o que você quer entregar a Deus esta noite. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr"/>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>Dia 62 de 365. Jonas 3:1: A palavra veio pela segunda vez. #fe #recomeco #promessas #palavradodia</t>
+          <t>Dia 62 de 365. Jonas 3:1: A palavra veio pela segunda vez. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
@@ -3148,7 +3148,7 @@
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ João 10:10. Promessa de vida. #versiculododia #fe #recomeco #oracao</t>
+          <t>Pausa do meio-dia ☀️ João 10:10. Promessa de vida. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
@@ -3158,7 +3158,7 @@
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: recomeço e promessas 🌙 Para fechar o dia com Jonas 3:1. Marque alguém que precisa ouvir esta oração. #oracaodanoite #oracao #fe #recomeco</t>
+          <t>Oração da noite: recomeço e promessas 🌙 Para fechar o dia com Jonas 3:1. Marque alguém que precisa ouvir esta oração. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr"/>
@@ -3181,7 +3181,7 @@
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>Dia 63 de 365. Isaías 58:11: Como jardim regado. #fe #recomeco #promessas #palavradodia</t>
+          <t>Dia 63 de 365. Isaías 58:11: Como jardim regado. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ Isaías 9:6. Promessa de paz. #versiculododia #fe #recomeco #oracao</t>
+          <t>Pausa do meio-dia ☀️ Isaías 9:6. Promessa de paz. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
@@ -3201,7 +3201,7 @@
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: recomeço e promessas 🌙 Para fechar o dia com Isaías 58:11. Comente seu pedido. Vamos orar juntos. #oracaodanoite #oracao #fe #recomeco</t>
+          <t>Oração da noite: recomeço e promessas 🌙 Para fechar o dia com Isaías 58:11. Comente seu pedido. Vamos orar juntos. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr"/>
@@ -3224,7 +3224,7 @@
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>Dia 64 de 365. Salmos 23:6: Bondade e misericórdia me seguirão. #fe #recomeco #promessas #palavradodia</t>
+          <t>Dia 64 de 365. Salmos 23:6: Bondade e misericórdia me seguirão. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
@@ -3234,7 +3234,7 @@
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ Tito 1:2. Deus não mente. #versiculododia #fe #recomeco #oracao</t>
+          <t>Pausa do meio-dia ☀️ Tito 1:2. Deus não mente. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
@@ -3244,7 +3244,7 @@
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: recomeço e promessas 🌙 Para fechar o dia com Salmos 23:6. Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #recomeco</t>
+          <t>Oração da noite: recomeço e promessas 🌙 Para fechar o dia com Salmos 23:6. Deixe seu pedido de oração nos comentários. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr"/>
@@ -3267,7 +3267,7 @@
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>Dia 65 de 365. Gênesis 28:15: Eis que estou contigo. #fe #recomeco #promessas #palavradodia</t>
+          <t>Dia 65 de 365. Gênesis 28:15: Eis que estou contigo. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
@@ -3277,7 +3277,7 @@
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ João 8:12. Promessa de luz. #versiculododia #fe #recomeco #oracao</t>
+          <t>Pausa do meio-dia ☀️ João 8:12. Promessa de luz. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
@@ -3287,7 +3287,7 @@
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: recomeço e promessas 🌙 Para fechar o dia com Gênesis 28:15. Escreva amém se essa oração é sua também. #oracaodanoite #oracao #fe #recomeco</t>
+          <t>Oração da noite: recomeço e promessas 🌙 Para fechar o dia com Gênesis 28:15. Escreva amém se essa oração é sua também. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr"/>
@@ -3310,7 +3310,7 @@
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>Dia 66 de 365. Isaías 42:3: A cana quebrada Ele não esmagará. #fe #recomeco #promessas #palavradodia</t>
+          <t>Dia 66 de 365. Isaías 42:3: A cana quebrada Ele não esmagará. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
@@ -3320,7 +3320,7 @@
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ 2 Timóteo 2:13. Ele é fiel sempre. #versiculododia #fe #recomeco #oracao</t>
+          <t>Pausa do meio-dia ☀️ 2 Timóteo 2:13. Ele é fiel sempre. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
@@ -3330,7 +3330,7 @@
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: recomeço e promessas 🌙 Para fechar o dia com Isaías 42:3. Comente o nome de quem você quer colocar nesta oração. #oracaodanoite #oracao #fe #recomeco</t>
+          <t>Oração da noite: recomeço e promessas 🌙 Para fechar o dia com Isaías 42:3. Comente o nome de quem você quer colocar nesta oração. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr"/>
@@ -3353,7 +3353,7 @@
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>Dia 67 de 365. Salmos 145:14: O Senhor sustenta os que caem. #fe #recomeco #promessas #palavradodia</t>
+          <t>Dia 67 de 365. Salmos 145:14: O Senhor sustenta os que caem. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
@@ -3363,7 +3363,7 @@
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ Jeremias 32:27. Nada é impossível. #versiculododia #fe #recomeco #oracao</t>
+          <t>Pausa do meio-dia ☀️ Jeremias 32:27. Nada é impossível. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
@@ -3373,7 +3373,7 @@
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: recomeço e promessas 🌙 Para fechar o dia com Salmos 145:14. Conte nos comentários pelo que você quer agradecer hoje. #oracaodanoite #oracao #fe #recomeco</t>
+          <t>Oração da noite: recomeço e promessas 🌙 Para fechar o dia com Salmos 145:14. Conte nos comentários pelo que você quer agradecer hoje. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr"/>
@@ -3396,7 +3396,7 @@
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>Dia 68 de 365. Isaías 60:1: Levanta-te, resplandece. #fe #recomeco #promessas #palavradodia</t>
+          <t>Dia 68 de 365. Isaías 60:1: Levanta-te, resplandece. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
@@ -3406,7 +3406,7 @@
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ Provérbios 4:18. Seu caminho vai clareando. #versiculododia #fe #recomeco #oracao</t>
+          <t>Pausa do meio-dia ☀️ Provérbios 4:18. Seu caminho vai clareando. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
@@ -3416,7 +3416,7 @@
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: recomeço e promessas 🌙 Para fechar o dia com Isaías 60:1. Deixe nos comentários o que você quer entregar a Deus esta noite. #oracaodanoite #oracao #fe #recomeco</t>
+          <t>Oração da noite: recomeço e promessas 🌙 Para fechar o dia com Isaías 60:1. Deixe nos comentários o que você quer entregar a Deus esta noite. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr"/>
@@ -3439,7 +3439,7 @@
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>Dia 69 de 365. Atos 9:17-18: Saulo voltou a ver. #fe #recomeco #promessas #palavradodia</t>
+          <t>Dia 69 de 365. Atos 9:17-18: Saulo voltou a ver. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
@@ -3449,7 +3449,7 @@
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ Ezequiel 18:31. Comece de novo. #versiculododia #fe #recomeco #oracao</t>
+          <t>Pausa do meio-dia ☀️ Ezequiel 18:31. Comece de novo. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
@@ -3459,7 +3459,7 @@
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: recomeço e promessas 🌙 Para fechar o dia com Atos 9:17-18. Marque alguém que precisa ouvir esta oração. #oracaodanoite #oracao #fe #recomeco</t>
+          <t>Oração da noite: recomeço e promessas 🌙 Para fechar o dia com Atos 9:17-18. Marque alguém que precisa ouvir esta oração. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr"/>
@@ -3482,7 +3482,7 @@
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>Dia 70 de 365. Lucas 5:5-6: Sobre a tua palavra, lançarei as redes. #fe #recomeco #promessas #palavradodia</t>
+          <t>Dia 70 de 365. Lucas 5:5-6: Sobre a tua palavra, lançarei as redes. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
@@ -3492,7 +3492,7 @@
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ João 1:14. O Verbo se fez carne. #versiculododia #fe #recomeco #oracao</t>
+          <t>Pausa do meio-dia ☀️ João 1:14. O Verbo se fez carne. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
@@ -3502,7 +3502,7 @@
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: recomeço e promessas 🌙 Para fechar o dia com Lucas 5:5-6. Comente seu pedido. Vamos orar juntos. #oracaodanoite #oracao #fe #recomeco</t>
+          <t>Oração da noite: recomeço e promessas 🌙 Para fechar o dia com Lucas 5:5-6. Comente seu pedido. Vamos orar juntos. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr"/>
@@ -3525,7 +3525,7 @@
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>Dia 71 de 365. Oseias 6:3: Como a alva, a sua vinda é certa. #fe #recomeco #promessas #palavradodia</t>
+          <t>Dia 71 de 365. Oseias 6:3: Como a alva, a sua vinda é certa. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
@@ -3535,7 +3535,7 @@
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ Lucas 2:10. Boas novas. #versiculododia #fe #recomeco #oracao</t>
+          <t>Pausa do meio-dia ☀️ Lucas 2:10. Boas novas. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
@@ -3545,7 +3545,7 @@
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: recomeço e promessas 🌙 Para fechar o dia com Oseias 6:3. Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #recomeco</t>
+          <t>Oração da noite: recomeço e promessas 🌙 Para fechar o dia com Oseias 6:3. Deixe seu pedido de oração nos comentários. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr"/>
@@ -3568,7 +3568,7 @@
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>Dia 72 de 365. Ageu 2:9: A glória desta última casa será maior. #fe #recomeco #promessas #palavradodia</t>
+          <t>Dia 72 de 365. Ageu 2:9: A glória desta última casa será maior. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
@@ -3578,7 +3578,7 @@
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ Lucas 2:11. Nasceu o Salvador. #versiculododia #fe #recomeco #oracao</t>
+          <t>Pausa do meio-dia ☀️ Lucas 2:11. Nasceu o Salvador. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
@@ -3588,7 +3588,7 @@
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: recomeço e promessas 🌙 Para fechar o dia com Ageu 2:9. Escreva amém se essa oração é sua também. #oracaodanoite #oracao #fe #recomeco</t>
+          <t>Oração da noite: recomeço e promessas 🌙 Para fechar o dia com Ageu 2:9. Escreva amém se essa oração é sua também. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr"/>
@@ -3611,7 +3611,7 @@
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>Dia 73 de 365. Isaías 54:10: Os montes se retirarão. #fe #recomeco #promessas #palavradodia</t>
+          <t>Dia 73 de 365. Isaías 54:10: Os montes se retirarão. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
@@ -3621,7 +3621,7 @@
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ João 14:3. Promessa de volta. #versiculododia #fe #recomeco #oracao</t>
+          <t>Pausa do meio-dia ☀️ João 14:3. Promessa de volta. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
@@ -3631,7 +3631,7 @@
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: recomeço e promessas 🌙 Para fechar o dia com Isaías 54:10. Comente o nome de quem você quer colocar nesta oração. #oracaodanoite #oracao #fe #recomeco</t>
+          <t>Oração da noite: recomeço e promessas 🌙 Para fechar o dia com Isaías 54:10. Comente o nome de quem você quer colocar nesta oração. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr"/>
@@ -3654,7 +3654,7 @@
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>Dia 74 de 365. Salmos 30:11: Tornaste o meu pranto em dança. #fe #recomeco #promessas #palavradodia</t>
+          <t>Dia 74 de 365. Salmos 30:11: Tornaste o meu pranto em dança. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
@@ -3664,7 +3664,7 @@
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ 2 Pedro 3:13. Ele faz tudo novo. #versiculododia #fe #recomeco #oracao</t>
+          <t>Pausa do meio-dia ☀️ 2 Pedro 3:13. Ele faz tudo novo. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr">
@@ -3674,7 +3674,7 @@
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: recomeço e promessas 🌙 Para fechar o dia com Salmos 30:11. Conte nos comentários pelo que você quer agradecer hoje. #oracaodanoite #oracao #fe #recomeco</t>
+          <t>Oração da noite: recomeço e promessas 🌙 Para fechar o dia com Salmos 30:11. Conte nos comentários pelo que você quer agradecer hoje. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr"/>
@@ -3697,7 +3697,7 @@
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>Dia 75 de 365. 2 Pedro 3:9: O Senhor não retarda a promessa. #fe #recomeco #promessas #palavradodia</t>
+          <t>Dia 75 de 365. 2 Pedro 3:9: O Senhor não retarda a promessa. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
@@ -3707,7 +3707,7 @@
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ Salmos 91:4. Promessa de proteção. #versiculododia #fe #recomeco #oracao</t>
+          <t>Pausa do meio-dia ☀️ Salmos 91:4. Promessa de proteção. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
@@ -3717,7 +3717,7 @@
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: recomeço e promessas 🌙 Para fechar o dia com 2 Pedro 3:9. Deixe nos comentários o que você quer entregar a Deus esta noite. #oracaodanoite #oracao #fe #recomeco</t>
+          <t>Oração da noite: recomeço e promessas 🌙 Para fechar o dia com 2 Pedro 3:9. Deixe nos comentários o que você quer entregar a Deus esta noite. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr"/>
@@ -3740,7 +3740,7 @@
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>Dia 76 de 365. Isaías 46:4: Até a velhice eu te carregarei. #fe #recomeco #promessas #palavradodia</t>
+          <t>Dia 76 de 365. Isaías 46:4: Até a velhice eu te carregarei. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
@@ -3750,7 +3750,7 @@
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ Eclesiastes 3:11. Fim e começo. #versiculododia #fe #recomeco #oracao</t>
+          <t>Pausa do meio-dia ☀️ Eclesiastes 3:11. Fim e começo. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G77" s="2" t="inlineStr">
@@ -3760,7 +3760,7 @@
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: recomeço e promessas 🌙 Para fechar o dia com Isaías 46:4. Marque alguém que precisa ouvir esta oração. #oracaodanoite #oracao #fe #recomeco</t>
+          <t>Oração da noite: recomeço e promessas 🌙 Para fechar o dia com Isaías 46:4. Marque alguém que precisa ouvir esta oração. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr"/>
@@ -3783,7 +3783,7 @@
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>Dia 77 de 365. Números 6:24-26: O Senhor te abençoe e te guarde. #fe #recomeco #promessas #palavradodia</t>
+          <t>Dia 77 de 365. Números 6:24-26: O Senhor te abençoe e te guarde. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
@@ -3793,7 +3793,7 @@
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ Êxodo 33:14. Ele te conduz. #versiculododia #fe #recomeco #oracao</t>
+          <t>Pausa do meio-dia ☀️ Êxodo 33:14. Ele te conduz. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
@@ -3803,7 +3803,7 @@
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: recomeço e promessas 🌙 Para fechar o dia com Números 6:24-26. Comente seu pedido. Vamos orar juntos. #oracaodanoite #oracao #fe #recomeco</t>
+          <t>Oração da noite: recomeço e promessas 🌙 Para fechar o dia com Números 6:24-26. Comente seu pedido. Vamos orar juntos. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr"/>
@@ -3826,7 +3826,7 @@
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>Dia 78 de 365. Judas 1:24-25: Àquele que é poderoso para vos guardar. #fe #recomeco #promessas #palavradodia</t>
+          <t>Dia 78 de 365. Judas 1:24-25: Àquele que é poderoso para vos guardar. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
@@ -3836,7 +3836,7 @@
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ 1 Samuel 7:12. Até aqui o Senhor ajudou. #versiculododia #fe #recomeco #oracao</t>
+          <t>Pausa do meio-dia ☀️ 1 Samuel 7:12. Até aqui o Senhor ajudou. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G79" s="2" t="inlineStr">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: recomeço e promessas 🌙 Para fechar o dia com Judas 1:24-25. Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #recomeco</t>
+          <t>Oração da noite: recomeço e promessas 🌙 Para fechar o dia com Judas 1:24-25. Deixe seu pedido de oração nos comentários. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr"/>
@@ -3869,7 +3869,7 @@
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>Dia 79 de 365. Filipenses 4:6-7: Se a ansiedade te acordou hoje, ouça isso antes de começar o dia. #fe #ansiedade #paz #palavradodia</t>
+          <t>Dia 79 de 365. Filipenses 4:6-7: Se a ansiedade te acordou hoje, ouça isso antes de começar o dia. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
@@ -3879,7 +3879,7 @@
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ Salmos 116:7. A manhã foi corrida? #versiculododia #fe #ansiedade #oracao</t>
+          <t>Pausa do meio-dia ☀️ Salmos 116:7. A manhã foi corrida? #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr">
@@ -3889,7 +3889,7 @@
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: ansiedade e paz 🌙 Para fechar o dia com Filipenses 4:6-7. Escreva amém se essa oração é sua também. #oracaodanoite #oracao #fe #ansiedade</t>
+          <t>Oração da noite: ansiedade e paz 🌙 Para fechar o dia com Filipenses 4:6-7. Escreva amém se essa oração é sua também. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr"/>
@@ -3912,7 +3912,7 @@
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>Dia 80 de 365. Mateus 6:34: Você está sofrendo hoje por algo que ainda nem aconteceu? #fe #ansiedade #paz #palavradodia</t>
+          <t>Dia 80 de 365. Mateus 6:34: Você está sofrendo hoje por algo que ainda nem aconteceu? #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
@@ -3922,7 +3922,7 @@
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ Mateus 6:27. Quanto da sua cabeça está no amanhã? #versiculododia #fe #ansiedade #oracao</t>
+          <t>Pausa do meio-dia ☀️ Mateus 6:27. Quanto da sua cabeça está no amanhã? #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G81" s="2" t="inlineStr">
@@ -3932,7 +3932,7 @@
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: ansiedade e paz 🌙 Para fechar o dia com Mateus 6:34. Comente o nome de quem você quer colocar nesta oração. #oracaodanoite #oracao #fe #ansiedade</t>
+          <t>Oração da noite: ansiedade e paz 🌙 Para fechar o dia com Mateus 6:34. Comente o nome de quem você quer colocar nesta oração. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr"/>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>Dia 81 de 365. 1 Pedro 5:7: Tem uma coisa que você não contou para ninguém. Deus já sabe. #fe #ansiedade #paz #palavradodia</t>
+          <t>Dia 81 de 365. 1 Pedro 5:7: Tem uma coisa que você não contou para ninguém. Deus já sabe. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
@@ -3965,7 +3965,7 @@
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ Marcos 6:31. Já parou hoje? #versiculododia #fe #ansiedade #oracao</t>
+          <t>Pausa do meio-dia ☀️ Marcos 6:31. Já parou hoje? #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G82" s="2" t="inlineStr">
@@ -3975,7 +3975,7 @@
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: ansiedade e paz 🌙 Para fechar o dia com 1 Pedro 5:7. Conte nos comentários pelo que você quer agradecer hoje. #oracaodanoite #oracao #fe #ansiedade</t>
+          <t>Oração da noite: ansiedade e paz 🌙 Para fechar o dia com 1 Pedro 5:7. Conte nos comentários pelo que você quer agradecer hoje. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr"/>
@@ -3998,7 +3998,7 @@
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>Dia 82 de 365. João 14:27: A paz que o mundo vende acaba. Essa não. #fe #ansiedade #paz #palavradodia</t>
+          <t>Dia 82 de 365. João 14:27: A paz que o mundo vende acaba. Essa não. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
@@ -4008,7 +4008,7 @@
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ Romanos 15:33. O Deus de paz está com você. #versiculododia #fe #ansiedade #oracao</t>
+          <t>Pausa do meio-dia ☀️ Romanos 15:33. O Deus de paz está com você. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G83" s="2" t="inlineStr">
@@ -4018,7 +4018,7 @@
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: ansiedade e paz 🌙 Para fechar o dia com João 14:27. Deixe nos comentários o que você quer entregar a Deus esta noite. #oracaodanoite #oracao #fe #ansiedade</t>
+          <t>Oração da noite: ansiedade e paz 🌙 Para fechar o dia com João 14:27. Deixe nos comentários o que você quer entregar a Deus esta noite. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I83" s="2" t="inlineStr"/>
@@ -4041,7 +4041,7 @@
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>Dia 83 de 365. Salmos 94:19: Quando os pensamentos não param, leia isso. #fe #ansiedade #paz #palavradodia</t>
+          <t>Dia 83 de 365. Salmos 94:19: Quando os pensamentos não param, leia isso. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
@@ -4051,7 +4051,7 @@
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ Salmos 62:1. Sentindo o peito apertado? #versiculododia #fe #ansiedade #oracao</t>
+          <t>Pausa do meio-dia ☀️ Salmos 62:1. Sentindo o peito apertado? #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G84" s="2" t="inlineStr">
@@ -4061,7 +4061,7 @@
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: ansiedade e paz 🌙 Para fechar o dia com Salmos 94:19. Marque alguém que precisa ouvir esta oração. #oracaodanoite #oracao #fe #ansiedade</t>
+          <t>Oração da noite: ansiedade e paz 🌙 Para fechar o dia com Salmos 94:19. Marque alguém que precisa ouvir esta oração. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr"/>
@@ -4084,7 +4084,7 @@
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>Dia 84 de 365. Isaías 26:3: Existe um tipo de paz que só vem de um lugar. #fe #ansiedade #paz #palavradodia</t>
+          <t>Dia 84 de 365. Isaías 26:3: Existe um tipo de paz que só vem de um lugar. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr">
@@ -4094,7 +4094,7 @@
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ Salmos 85:8. O que te tirou a paz hoje cedo? #versiculododia #fe #ansiedade #oracao</t>
+          <t>Pausa do meio-dia ☀️ Salmos 85:8. O que te tirou a paz hoje cedo? #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G85" s="2" t="inlineStr">
@@ -4104,7 +4104,7 @@
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: ansiedade e paz 🌙 Para fechar o dia com Isaías 26:3. Comente seu pedido. Vamos orar juntos. #oracaodanoite #oracao #fe #ansiedade</t>
+          <t>Oração da noite: ansiedade e paz 🌙 Para fechar o dia com Isaías 26:3. Comente seu pedido. Vamos orar juntos. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I85" s="2" t="inlineStr"/>
@@ -4127,7 +4127,7 @@
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>Dia 85 de 365. Salmos 46:10: Às vezes a resposta é parar. #fe #ansiedade #paz #palavradodia</t>
+          <t>Dia 85 de 365. Salmos 46:10: Às vezes a resposta é parar. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
@@ -4137,7 +4137,7 @@
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ Salmos 127:2. Ele dá descanso até aos que dormem. #versiculododia #fe #ansiedade #oracao</t>
+          <t>Pausa do meio-dia ☀️ Salmos 127:2. Ele dá descanso até aos que dormem. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G86" s="2" t="inlineStr">
@@ -4147,7 +4147,7 @@
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: ansiedade e paz 🌙 Para fechar o dia com Salmos 46:10. Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #ansiedade</t>
+          <t>Oração da noite: ansiedade e paz 🌙 Para fechar o dia com Salmos 46:10. Deixe seu pedido de oração nos comentários. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I86" s="2" t="inlineStr"/>
@@ -4170,7 +4170,7 @@
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>Dia 86 de 365. Mateus 11:28-30: Cansado de carregar tudo sozinho? #fe #ansiedade #paz #palavradodia</t>
+          <t>Dia 86 de 365. Mateus 11:28-30: Cansado de carregar tudo sozinho? #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr">
@@ -4180,7 +4180,7 @@
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ Salmos 131:2. Coração agitado? #versiculododia #fe #ansiedade #oracao</t>
+          <t>Pausa do meio-dia ☀️ Salmos 131:2. Coração agitado? #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G87" s="2" t="inlineStr">
@@ -4190,7 +4190,7 @@
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: ansiedade e paz 🌙 Para fechar o dia com Mateus 11:28-30. Escreva amém se essa oração é sua também. #oracaodanoite #oracao #fe #ansiedade</t>
+          <t>Oração da noite: ansiedade e paz 🌙 Para fechar o dia com Mateus 11:28-30. Escreva amém se essa oração é sua também. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I87" s="2" t="inlineStr"/>
@@ -4213,7 +4213,7 @@
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>Dia 87 de 365. Salmos 55:22: O que você está carregando que não é seu para carregar? #fe #ansiedade #paz #palavradodia</t>
+          <t>Dia 87 de 365. Salmos 55:22: O que você está carregando que não é seu para carregar? #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
@@ -4223,7 +4223,7 @@
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ Isaías 43:5. Você não está sozinho nessa tarde. #versiculododia #fe #ansiedade #oracao</t>
+          <t>Pausa do meio-dia ☀️ Isaías 43:5. Você não está sozinho nessa tarde. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G88" s="2" t="inlineStr">
@@ -4233,7 +4233,7 @@
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: ansiedade e paz 🌙 Para fechar o dia com Salmos 55:22. Comente o nome de quem você quer colocar nesta oração. #oracaodanoite #oracao #fe #ansiedade</t>
+          <t>Oração da noite: ansiedade e paz 🌙 Para fechar o dia com Salmos 55:22. Comente o nome de quem você quer colocar nesta oração. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I88" s="2" t="inlineStr"/>
@@ -4256,7 +4256,7 @@
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t>Dia 88 de 365. Provérbios 12:25: Uma palavra boa muda o dia de alguém. Inclusive o seu. #fe #ansiedade #paz #palavradodia</t>
+          <t>Dia 88 de 365. Provérbios 12:25: Uma palavra boa muda o dia de alguém. Inclusive o seu. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr">
@@ -4266,7 +4266,7 @@
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ Salmos 27:3. Medo do que vem à tarde? #versiculododia #fe #ansiedade #oracao</t>
+          <t>Pausa do meio-dia ☀️ Salmos 27:3. Medo do que vem à tarde? #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G89" s="2" t="inlineStr">
@@ -4276,7 +4276,7 @@
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: ansiedade e paz 🌙 Para fechar o dia com Provérbios 12:25. Conte nos comentários pelo que você quer agradecer hoje. #oracaodanoite #oracao #fe #ansiedade</t>
+          <t>Oração da noite: ansiedade e paz 🌙 Para fechar o dia com Provérbios 12:25. Conte nos comentários pelo que você quer agradecer hoje. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I89" s="2" t="inlineStr"/>
@@ -4299,7 +4299,7 @@
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>Dia 89 de 365. Salmos 4:8: Para quem não consegue dormir de preocupação. #fe #ansiedade #paz #palavradodia</t>
+          <t>Dia 89 de 365. Salmos 4:8: Para quem não consegue dormir de preocupação. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
@@ -4309,7 +4309,7 @@
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ Salmos 18:2. A sua força tem limite. A dEle não. #versiculododia #fe #ansiedade #oracao</t>
+          <t>Pausa do meio-dia ☀️ Salmos 18:2. A sua força tem limite. A dEle não. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G90" s="2" t="inlineStr">
@@ -4319,7 +4319,7 @@
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: ansiedade e paz 🌙 Para fechar o dia com Salmos 4:8. Deixe nos comentários o que você quer entregar a Deus esta noite. #oracaodanoite #oracao #fe #ansiedade</t>
+          <t>Oração da noite: ansiedade e paz 🌙 Para fechar o dia com Salmos 4:8. Deixe nos comentários o que você quer entregar a Deus esta noite. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I90" s="2" t="inlineStr"/>
@@ -4342,7 +4342,7 @@
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>Dia 90 de 365. Isaías 41:10: Se o medo de hoje parece maior que você, ouça isso. #fe #ansiedade #paz #palavradodia</t>
+          <t>Dia 90 de 365. Isaías 41:10: Se o medo de hoje parece maior que você, ouça isso. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr">
@@ -4352,7 +4352,7 @@
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ Lamentações 3:26. Precisa de calma agora? #versiculododia #fe #ansiedade #oracao</t>
+          <t>Pausa do meio-dia ☀️ Lamentações 3:26. Precisa de calma agora? #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G91" s="2" t="inlineStr">
@@ -4362,7 +4362,7 @@
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: ansiedade e paz 🌙 Para fechar o dia com Isaías 41:10. Marque alguém que precisa ouvir esta oração. #oracaodanoite #oracao #fe #ansiedade</t>
+          <t>Oração da noite: ansiedade e paz 🌙 Para fechar o dia com Isaías 41:10. Marque alguém que precisa ouvir esta oração. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I91" s="2" t="inlineStr"/>
@@ -4385,7 +4385,7 @@
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>Dia 91 de 365. Salmos 23:1-3: O salmo que milhões repetem quando a vida aperta. #fe #ansiedade #paz #palavradodia</t>
+          <t>Dia 91 de 365. Salmos 23:1-3: O salmo que milhões repetem quando a vida aperta. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
@@ -4395,7 +4395,7 @@
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ Salmos 121:3. Quem guarda você não cochila. #versiculododia #fe #ansiedade #oracao</t>
+          <t>Pausa do meio-dia ☀️ Salmos 121:3. Quem guarda você não cochila. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G92" s="2" t="inlineStr">
@@ -4405,7 +4405,7 @@
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: ansiedade e paz 🌙 Para fechar o dia com Salmos 23:1-3. Comente seu pedido. Vamos orar juntos. #oracaodanoite #oracao #fe #ansiedade</t>
+          <t>Oração da noite: ansiedade e paz 🌙 Para fechar o dia com Salmos 23:1-3. Comente seu pedido. Vamos orar juntos. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I92" s="2" t="inlineStr"/>
@@ -4428,7 +4428,7 @@
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>Dia 92 de 365. Romanos 8:28: Nem tudo que acontece é bom. Mas veja o que este versículo diz. #fe #ansiedade #paz #palavradodia</t>
+          <t>Dia 92 de 365. Romanos 8:28: Nem tudo que acontece é bom. Mas veja o que este versículo diz. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E93" s="2" t="inlineStr">
@@ -4438,7 +4438,7 @@
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ Deuteronômio 31:8. Ele vai na sua frente. #versiculododia #fe #ansiedade #oracao</t>
+          <t>Pausa do meio-dia ☀️ Deuteronômio 31:8. Ele vai na sua frente. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G93" s="2" t="inlineStr">
@@ -4448,7 +4448,7 @@
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: ansiedade e paz 🌙 Para fechar o dia com Romanos 8:28. Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #ansiedade</t>
+          <t>Oração da noite: ansiedade e paz 🌙 Para fechar o dia com Romanos 8:28. Deixe seu pedido de oração nos comentários. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I93" s="2" t="inlineStr"/>
@@ -4471,7 +4471,7 @@
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>Dia 93 de 365. 2 Timóteo 1:7: O medo não veio de Deus. #fe #ansiedade #paz #palavradodia</t>
+          <t>Dia 93 de 365. 2 Timóteo 1:7: O medo não veio de Deus. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
@@ -4481,7 +4481,7 @@
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ 2 Tessalonicenses 3:16. A paz que vem do alto. #versiculododia #fe #ansiedade #oracao</t>
+          <t>Pausa do meio-dia ☀️ 2 Tessalonicenses 3:16. A paz que vem do alto. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G94" s="2" t="inlineStr">
@@ -4491,7 +4491,7 @@
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: ansiedade e paz 🌙 Para fechar o dia com 2 Timóteo 1:7. Escreva amém se essa oração é sua também. #oracaodanoite #oracao #fe #ansiedade</t>
+          <t>Oração da noite: ansiedade e paz 🌙 Para fechar o dia com 2 Timóteo 1:7. Escreva amém se essa oração é sua também. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I94" s="2" t="inlineStr"/>
@@ -4514,7 +4514,7 @@
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>Dia 94 de 365. Salmos 34:4: Busquei, e Ele respondeu. #fe #ansiedade #paz #palavradodia</t>
+          <t>Dia 94 de 365. Salmos 34:4: Busquei, e Ele respondeu. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E95" s="2" t="inlineStr">
@@ -4524,7 +4524,7 @@
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ Salmos 94:18. Seu pensamento está acelerado? #versiculododia #fe #ansiedade #oracao</t>
+          <t>Pausa do meio-dia ☀️ Salmos 94:18. Seu pensamento está acelerado? #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G95" s="2" t="inlineStr">
@@ -4534,7 +4534,7 @@
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: ansiedade e paz 🌙 Para fechar o dia com Salmos 34:4. Comente o nome de quem você quer colocar nesta oração. #oracaodanoite #oracao #fe #ansiedade</t>
+          <t>Oração da noite: ansiedade e paz 🌙 Para fechar o dia com Salmos 34:4. Comente o nome de quem você quer colocar nesta oração. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I95" s="2" t="inlineStr"/>
@@ -4557,7 +4557,7 @@
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>Dia 95 de 365. Salmos 61:2: Quando o coração desfalece, para onde você corre? #fe #ansiedade #paz #palavradodia</t>
+          <t>Dia 95 de 365. Salmos 61:2: Quando o coração desfalece, para onde você corre? #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
@@ -4567,7 +4567,7 @@
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ Miqueias 7:7. Olhe para cima. #versiculododia #fe #ansiedade #oracao</t>
+          <t>Pausa do meio-dia ☀️ Miqueias 7:7. Olhe para cima. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G96" s="2" t="inlineStr">
@@ -4577,7 +4577,7 @@
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: ansiedade e paz 🌙 Para fechar o dia com Salmos 61:2. Conte nos comentários pelo que você quer agradecer hoje. #oracaodanoite #oracao #fe #ansiedade</t>
+          <t>Oração da noite: ansiedade e paz 🌙 Para fechar o dia com Salmos 61:2. Conte nos comentários pelo que você quer agradecer hoje. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I96" s="2" t="inlineStr"/>
@@ -4600,7 +4600,7 @@
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t>Dia 96 de 365. Filipenses 4:8: Mude o que você alimenta na mente e o dia muda. #fe #ansiedade #paz #palavradodia</t>
+          <t>Dia 96 de 365. Filipenses 4:8: Mude o que você alimenta na mente e o dia muda. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E97" s="2" t="inlineStr">
@@ -4610,7 +4610,7 @@
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ Lucas 10:41. Muitas coisas pesando? #versiculododia #fe #ansiedade #oracao</t>
+          <t>Pausa do meio-dia ☀️ Lucas 10:41. Muitas coisas pesando? #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G97" s="2" t="inlineStr">
@@ -4620,7 +4620,7 @@
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: ansiedade e paz 🌙 Para fechar o dia com Filipenses 4:8. Deixe nos comentários o que você quer entregar a Deus esta noite. #oracaodanoite #oracao #fe #ansiedade</t>
+          <t>Oração da noite: ansiedade e paz 🌙 Para fechar o dia com Filipenses 4:8. Deixe nos comentários o que você quer entregar a Deus esta noite. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I97" s="2" t="inlineStr"/>
@@ -4643,7 +4643,7 @@
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>Dia 97 de 365. Salmos 139:23-24: Uma oração para quem está com o coração inquieto. #fe #ansiedade #paz #palavradodia</t>
+          <t>Dia 97 de 365. Salmos 139:23-24: Uma oração para quem está com o coração inquieto. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr">
@@ -4653,7 +4653,7 @@
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ Salmos 125:1. Quem confia não se abala. #versiculododia #fe #ansiedade #oracao</t>
+          <t>Pausa do meio-dia ☀️ Salmos 125:1. Quem confia não se abala. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G98" s="2" t="inlineStr">
@@ -4663,7 +4663,7 @@
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: ansiedade e paz 🌙 Para fechar o dia com Salmos 139:23-24. Marque alguém que precisa ouvir esta oração. #oracaodanoite #oracao #fe #ansiedade</t>
+          <t>Oração da noite: ansiedade e paz 🌙 Para fechar o dia com Salmos 139:23-24. Marque alguém que precisa ouvir esta oração. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I98" s="2" t="inlineStr"/>
@@ -4686,7 +4686,7 @@
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t>Dia 98 de 365. Lucas 12:25-26: Preocupação já resolveu algum problema seu? #fe #ansiedade #paz #palavradodia</t>
+          <t>Dia 98 de 365. Lucas 12:25-26: Preocupação já resolveu algum problema seu? #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E99" s="2" t="inlineStr">
@@ -4696,7 +4696,7 @@
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ Salmos 142:3. Ele conhece o seu caminho. #versiculododia #fe #ansiedade #oracao</t>
+          <t>Pausa do meio-dia ☀️ Salmos 142:3. Ele conhece o seu caminho. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G99" s="2" t="inlineStr">
@@ -4706,7 +4706,7 @@
       </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: ansiedade e paz 🌙 Para fechar o dia com Lucas 12:25-26. Comente seu pedido. Vamos orar juntos. #oracaodanoite #oracao #fe #ansiedade</t>
+          <t>Oração da noite: ansiedade e paz 🌙 Para fechar o dia com Lucas 12:25-26. Comente seu pedido. Vamos orar juntos. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I99" s="2" t="inlineStr"/>
@@ -4729,7 +4729,7 @@
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>Dia 99 de 365. Josué 1:9: Uma ordem e uma promessa no mesmo versículo. #fe #ansiedade #paz #palavradodia</t>
+          <t>Dia 99 de 365. Josué 1:9: Uma ordem e uma promessa no mesmo versículo. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr">
@@ -4739,7 +4739,7 @@
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ Salmos 86:7. Uma oração curta resolve muito. #versiculododia #fe #ansiedade #oracao</t>
+          <t>Pausa do meio-dia ☀️ Salmos 86:7. Uma oração curta resolve muito. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G100" s="2" t="inlineStr">
@@ -4749,7 +4749,7 @@
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: ansiedade e paz 🌙 Para fechar o dia com Josué 1:9. Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #ansiedade</t>
+          <t>Oração da noite: ansiedade e paz 🌙 Para fechar o dia com Josué 1:9. Deixe seu pedido de oração nos comentários. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I100" s="2" t="inlineStr"/>
@@ -4772,7 +4772,7 @@
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t>Dia 100 de 365. Salmos 121:1-2: De onde vem o seu socorro? #fe #ansiedade #paz #palavradodia</t>
+          <t>Dia 100 de 365. Salmos 121:1-2: De onde vem o seu socorro? #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E101" s="2" t="inlineStr">
@@ -4782,7 +4782,7 @@
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ Naum 1:7. Ele é refúgio em tempo de aperto. #versiculododia #fe #ansiedade #oracao</t>
+          <t>Pausa do meio-dia ☀️ Naum 1:7. Ele é refúgio em tempo de aperto. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G101" s="2" t="inlineStr">
@@ -4792,7 +4792,7 @@
       </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: ansiedade e paz 🌙 Para fechar o dia com Salmos 121:1-2. Escreva amém se essa oração é sua também. #oracaodanoite #oracao #fe #ansiedade</t>
+          <t>Oração da noite: ansiedade e paz 🌙 Para fechar o dia com Salmos 121:1-2. Escreva amém se essa oração é sua também. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I101" s="2" t="inlineStr"/>
@@ -4815,7 +4815,7 @@
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>Dia 101 de 365. Isaías 40:31: Para quem está sem forças para continuar. #fe #ansiedade #paz #palavradodia</t>
+          <t>Dia 101 de 365. Isaías 40:31: Para quem está sem forças para continuar. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E102" s="2" t="inlineStr">
@@ -4825,7 +4825,7 @@
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ Salmos 69:1. Sente que está afundando? #versiculododia #fe #ansiedade #oracao</t>
+          <t>Pausa do meio-dia ☀️ Salmos 69:1. Sente que está afundando? #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G102" s="2" t="inlineStr">
@@ -4835,7 +4835,7 @@
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: ansiedade e paz 🌙 Para fechar o dia com Isaías 40:31. Comente o nome de quem você quer colocar nesta oração. #oracaodanoite #oracao #fe #ansiedade</t>
+          <t>Oração da noite: ansiedade e paz 🌙 Para fechar o dia com Isaías 40:31. Comente o nome de quem você quer colocar nesta oração. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I102" s="2" t="inlineStr"/>
@@ -4858,7 +4858,7 @@
       </c>
       <c r="D103" s="2" t="inlineStr">
         <is>
-          <t>Dia 102 de 365. Êxodo 14:14: Tem batalhas que não são suas para lutar. #fe #ansiedade #paz #palavradodia</t>
+          <t>Dia 102 de 365. Êxodo 14:14: Tem batalhas que não são suas para lutar. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E103" s="2" t="inlineStr">
@@ -4868,7 +4868,7 @@
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ Romanos 5:1. Paz não é falta de problema. #versiculododia #fe #ansiedade #oracao</t>
+          <t>Pausa do meio-dia ☀️ Romanos 5:1. Paz não é falta de problema. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G103" s="2" t="inlineStr">
@@ -4878,7 +4878,7 @@
       </c>
       <c r="H103" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: ansiedade e paz 🌙 Para fechar o dia com Êxodo 14:14. Conte nos comentários pelo que você quer agradecer hoje. #oracaodanoite #oracao #fe #ansiedade</t>
+          <t>Oração da noite: ansiedade e paz 🌙 Para fechar o dia com Êxodo 14:14. Conte nos comentários pelo que você quer agradecer hoje. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I103" s="2" t="inlineStr"/>
@@ -4901,7 +4901,7 @@
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>Dia 103 de 365. Salmos 56:3: Uma frase curta para repetir quando o medo chegar. #fe #ansiedade #paz #palavradodia</t>
+          <t>Dia 103 de 365. Salmos 56:3: Uma frase curta para repetir quando o medo chegar. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E104" s="2" t="inlineStr">
@@ -4911,7 +4911,7 @@
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ 1 Coríntios 14:33. Você foi chamado para a paz. #versiculododia #fe #ansiedade #oracao</t>
+          <t>Pausa do meio-dia ☀️ 1 Coríntios 14:33. Você foi chamado para a paz. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G104" s="2" t="inlineStr">
@@ -4921,7 +4921,7 @@
       </c>
       <c r="H104" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: ansiedade e paz 🌙 Para fechar o dia com Salmos 56:3. Deixe nos comentários o que você quer entregar a Deus esta noite. #oracaodanoite #oracao #fe #ansiedade</t>
+          <t>Oração da noite: ansiedade e paz 🌙 Para fechar o dia com Salmos 56:3. Deixe nos comentários o que você quer entregar a Deus esta noite. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I104" s="2" t="inlineStr"/>
@@ -4944,7 +4944,7 @@
       </c>
       <c r="D105" s="2" t="inlineStr">
         <is>
-          <t>Dia 104 de 365. Mateus 6:26: Olhe os pássaros lá fora. #fe #ansiedade #paz #palavradodia</t>
+          <t>Dia 104 de 365. Mateus 6:26: Olhe os pássaros lá fora. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E105" s="2" t="inlineStr">
@@ -4954,7 +4954,7 @@
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ Provérbios 17:22. A alegria acalma o coração. #versiculododia #fe #ansiedade #oracao</t>
+          <t>Pausa do meio-dia ☀️ Provérbios 17:22. A alegria acalma o coração. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G105" s="2" t="inlineStr">
@@ -4964,7 +4964,7 @@
       </c>
       <c r="H105" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: ansiedade e paz 🌙 Para fechar o dia com Mateus 6:26. Marque alguém que precisa ouvir esta oração. #oracaodanoite #oracao #fe #ansiedade</t>
+          <t>Oração da noite: ansiedade e paz 🌙 Para fechar o dia com Mateus 6:26. Marque alguém que precisa ouvir esta oração. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I105" s="2" t="inlineStr"/>
@@ -4987,7 +4987,7 @@
       </c>
       <c r="D106" s="2" t="inlineStr">
         <is>
-          <t>Dia 105 de 365. Salmos 3:3: Quando você está de cabeça baixa. #fe #ansiedade #paz #palavradodia</t>
+          <t>Dia 105 de 365. Salmos 3:3: Quando você está de cabeça baixa. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E106" s="2" t="inlineStr">
@@ -4997,7 +4997,7 @@
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ Salmos 91:11. Quantas vezes você já foi guardado? #versiculododia #fe #ansiedade #oracao</t>
+          <t>Pausa do meio-dia ☀️ Salmos 91:11. Quantas vezes você já foi guardado? #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G106" s="2" t="inlineStr">
@@ -5007,7 +5007,7 @@
       </c>
       <c r="H106" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: ansiedade e paz 🌙 Para fechar o dia com Salmos 3:3. Comente seu pedido. Vamos orar juntos. #oracaodanoite #oracao #fe #ansiedade</t>
+          <t>Oração da noite: ansiedade e paz 🌙 Para fechar o dia com Salmos 3:3. Comente seu pedido. Vamos orar juntos. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I106" s="2" t="inlineStr"/>
@@ -5030,7 +5030,7 @@
       </c>
       <c r="D107" s="2" t="inlineStr">
         <is>
-          <t>Dia 106 de 365. Sofonias 3:17: Deus se alegra com você. Já pensou nisso? #fe #ansiedade #paz #palavradodia</t>
+          <t>Dia 106 de 365. Sofonias 3:17: Deus se alegra com você. Já pensou nisso? #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E107" s="2" t="inlineStr">
@@ -5040,7 +5040,7 @@
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ Salmos 63:7. À sombra das asas dEle. #versiculododia #fe #ansiedade #oracao</t>
+          <t>Pausa do meio-dia ☀️ Salmos 63:7. À sombra das asas dEle. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G107" s="2" t="inlineStr">
@@ -5050,7 +5050,7 @@
       </c>
       <c r="H107" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: ansiedade e paz 🌙 Para fechar o dia com Sofonias 3:17. Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #ansiedade</t>
+          <t>Oração da noite: ansiedade e paz 🌙 Para fechar o dia com Sofonias 3:17. Deixe seu pedido de oração nos comentários. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I107" s="2" t="inlineStr"/>
@@ -5073,7 +5073,7 @@
       </c>
       <c r="D108" s="2" t="inlineStr">
         <is>
-          <t>Dia 107 de 365. João 16:33: Jesus nunca prometeu uma vida sem problemas. #fe #ansiedade #paz #palavradodia</t>
+          <t>Dia 107 de 365. João 16:33: Jesus nunca prometeu uma vida sem problemas. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E108" s="2" t="inlineStr">
@@ -5083,7 +5083,7 @@
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ Deuteronômio 1:31. Ele carrega você. #versiculododia #fe #ansiedade #oracao</t>
+          <t>Pausa do meio-dia ☀️ Deuteronômio 1:31. Ele carrega você. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G108" s="2" t="inlineStr">
@@ -5093,7 +5093,7 @@
       </c>
       <c r="H108" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: ansiedade e paz 🌙 Para fechar o dia com João 16:33. Escreva amém se essa oração é sua também. #oracaodanoite #oracao #fe #ansiedade</t>
+          <t>Oração da noite: ansiedade e paz 🌙 Para fechar o dia com João 16:33. Escreva amém se essa oração é sua também. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I108" s="2" t="inlineStr"/>
@@ -5116,7 +5116,7 @@
       </c>
       <c r="D109" s="2" t="inlineStr">
         <is>
-          <t>Dia 108 de 365. Salmos 16:8: O segredo de quem não é abalado. #fe #ansiedade #paz #palavradodia</t>
+          <t>Dia 108 de 365. Salmos 16:8: O segredo de quem não é abalado. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E109" s="2" t="inlineStr">
@@ -5126,7 +5126,7 @@
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ Salmos 124:8. Seu socorro tem nome. #versiculododia #fe #ansiedade #oracao</t>
+          <t>Pausa do meio-dia ☀️ Salmos 124:8. Seu socorro tem nome. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G109" s="2" t="inlineStr">
@@ -5136,7 +5136,7 @@
       </c>
       <c r="H109" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: ansiedade e paz 🌙 Para fechar o dia com Salmos 16:8. Comente o nome de quem você quer colocar nesta oração. #oracaodanoite #oracao #fe #ansiedade</t>
+          <t>Oração da noite: ansiedade e paz 🌙 Para fechar o dia com Salmos 16:8. Comente o nome de quem você quer colocar nesta oração. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I109" s="2" t="inlineStr"/>
@@ -5159,7 +5159,7 @@
       </c>
       <c r="D110" s="2" t="inlineStr">
         <is>
-          <t>Dia 109 de 365. Salmos 27:1: Se Deus é sua luz, de quem você vai ter medo? #fe #ansiedade #paz #palavradodia</t>
+          <t>Dia 109 de 365. Salmos 27:1: Se Deus é sua luz, de quem você vai ter medo? #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E110" s="2" t="inlineStr">
@@ -5169,7 +5169,7 @@
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ Salmos 74:16. A tarde também é do Senhor. #versiculododia #fe #ansiedade #oracao</t>
+          <t>Pausa do meio-dia ☀️ Salmos 74:16. A tarde também é do Senhor. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G110" s="2" t="inlineStr">
@@ -5179,7 +5179,7 @@
       </c>
       <c r="H110" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: ansiedade e paz 🌙 Para fechar o dia com Salmos 27:1. Conte nos comentários pelo que você quer agradecer hoje. #oracaodanoite #oracao #fe #ansiedade</t>
+          <t>Oração da noite: ansiedade e paz 🌙 Para fechar o dia com Salmos 27:1. Conte nos comentários pelo que você quer agradecer hoje. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I110" s="2" t="inlineStr"/>
@@ -5202,7 +5202,7 @@
       </c>
       <c r="D111" s="2" t="inlineStr">
         <is>
-          <t>Dia 110 de 365. Deuteronômio 31:6: Você não vai enfrentar isso sozinho. #fe #coragem #medo #palavradodia</t>
+          <t>Dia 110 de 365. Deuteronômio 31:6: Você não vai enfrentar isso sozinho. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E111" s="2" t="inlineStr">
@@ -5212,7 +5212,7 @@
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ Isaías 51:12. Do que você tem medo hoje? #versiculododia #fe #medo #oracao</t>
+          <t>Pausa do meio-dia ☀️ Isaías 51:12. Do que você tem medo hoje? #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G111" s="2" t="inlineStr">
@@ -5222,7 +5222,7 @@
       </c>
       <c r="H111" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: medo e coragem 🌙 Para fechar o dia com Deuteronômio 31:6. Deixe nos comentários o que você quer entregar a Deus esta noite. #oracaodanoite #oracao #fe #medo</t>
+          <t>Oração da noite: medo e coragem 🌙 Para fechar o dia com Deuteronômio 31:6. Deixe nos comentários o que você quer entregar a Deus esta noite. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I111" s="2" t="inlineStr"/>
@@ -5245,7 +5245,7 @@
       </c>
       <c r="D112" s="2" t="inlineStr">
         <is>
-          <t>Dia 111 de 365. Salmos 118:6: Uma pergunta para quem tem medo do que os outros vão fazer. #fe #coragem #medo #palavradodia</t>
+          <t>Dia 111 de 365. Salmos 118:6: Uma pergunta para quem tem medo do que os outros vão fazer. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E112" s="2" t="inlineStr">
@@ -5255,7 +5255,7 @@
       </c>
       <c r="F112" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ Josué 1:6. Coragem é dar o próximo passo. #versiculododia #fe #medo #oracao</t>
+          <t>Pausa do meio-dia ☀️ Josué 1:6. Coragem é dar o próximo passo. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G112" s="2" t="inlineStr">
@@ -5265,7 +5265,7 @@
       </c>
       <c r="H112" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: medo e coragem 🌙 Para fechar o dia com Salmos 118:6. Marque alguém que precisa ouvir esta oração. #oracaodanoite #oracao #fe #medo</t>
+          <t>Oração da noite: medo e coragem 🌙 Para fechar o dia com Salmos 118:6. Marque alguém que precisa ouvir esta oração. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I112" s="2" t="inlineStr"/>
@@ -5288,7 +5288,7 @@
       </c>
       <c r="D113" s="2" t="inlineStr">
         <is>
-          <t>Dia 112 de 365. Isaías 43:1-2: Você passou pelas águas e não se afogou. #fe #coragem #medo #palavradodia</t>
+          <t>Dia 112 de 365. Isaías 43:1-2: Você passou pelas águas e não se afogou. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E113" s="2" t="inlineStr">
@@ -5298,7 +5298,7 @@
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ Êxodo 3:12. Deus não te mandou sozinho. #versiculododia #fe #medo #oracao</t>
+          <t>Pausa do meio-dia ☀️ Êxodo 3:12. Deus não te mandou sozinho. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G113" s="2" t="inlineStr">
@@ -5308,7 +5308,7 @@
       </c>
       <c r="H113" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: medo e coragem 🌙 Para fechar o dia com Isaías 43:1-2. Comente seu pedido. Vamos orar juntos. #oracaodanoite #oracao #fe #medo</t>
+          <t>Oração da noite: medo e coragem 🌙 Para fechar o dia com Isaías 43:1-2. Comente seu pedido. Vamos orar juntos. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I113" s="2" t="inlineStr"/>
@@ -5331,7 +5331,7 @@
       </c>
       <c r="D114" s="2" t="inlineStr">
         <is>
-          <t>Dia 113 de 365. Salmos 23:4: Para quem está atravessando um vale escuro. #fe #coragem #medo #palavradodia</t>
+          <t>Dia 113 de 365. Salmos 23:4: Para quem está atravessando um vale escuro. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E114" s="2" t="inlineStr">
@@ -5341,7 +5341,7 @@
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ 1 Crônicas 28:20. Seja forte. É uma ordem com promessa. #versiculododia #fe #medo #oracao</t>
+          <t>Pausa do meio-dia ☀️ 1 Crônicas 28:20. Seja forte. É uma ordem com promessa. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G114" s="2" t="inlineStr">
@@ -5351,7 +5351,7 @@
       </c>
       <c r="H114" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: medo e coragem 🌙 Para fechar o dia com Salmos 23:4. Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #medo</t>
+          <t>Oração da noite: medo e coragem 🌙 Para fechar o dia com Salmos 23:4. Deixe seu pedido de oração nos comentários. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I114" s="2" t="inlineStr"/>
@@ -5374,7 +5374,7 @@
       </c>
       <c r="D115" s="2" t="inlineStr">
         <is>
-          <t>Dia 114 de 365. Romanos 8:31: Se Deus é por você, quem será contra? #fe #coragem #medo #palavradodia</t>
+          <t>Dia 114 de 365. Romanos 8:31: Se Deus é por você, quem será contra? #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E115" s="2" t="inlineStr">
@@ -5384,7 +5384,7 @@
       </c>
       <c r="F115" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ Isaías 35:4. O medo grita. Deus fala. #versiculododia #fe #medo #oracao</t>
+          <t>Pausa do meio-dia ☀️ Isaías 35:4. O medo grita. Deus fala. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G115" s="2" t="inlineStr">
@@ -5394,7 +5394,7 @@
       </c>
       <c r="H115" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: medo e coragem 🌙 Para fechar o dia com Romanos 8:31. Escreva amém se essa oração é sua também. #oracaodanoite #oracao #fe #medo</t>
+          <t>Oração da noite: medo e coragem 🌙 Para fechar o dia com Romanos 8:31. Escreva amém se essa oração é sua também. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I115" s="2" t="inlineStr"/>
@@ -5417,7 +5417,7 @@
       </c>
       <c r="D116" s="2" t="inlineStr">
         <is>
-          <t>Dia 115 de 365. Hebreus 13:6: Diga em voz alta: o Senhor é o meu ajudador. #fe #coragem #medo #palavradodia</t>
+          <t>Dia 115 de 365. Hebreus 13:6: Diga em voz alta: o Senhor é o meu ajudador. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E116" s="2" t="inlineStr">
@@ -5427,7 +5427,7 @@
       </c>
       <c r="F116" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ 2 Reis 6:16. Mais são os que estão conosco. #versiculododia #fe #medo #oracao</t>
+          <t>Pausa do meio-dia ☀️ 2 Reis 6:16. Mais são os que estão conosco. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G116" s="2" t="inlineStr">
@@ -5437,7 +5437,7 @@
       </c>
       <c r="H116" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: medo e coragem 🌙 Para fechar o dia com Hebreus 13:6. Comente o nome de quem você quer colocar nesta oração. #oracaodanoite #oracao #fe #medo</t>
+          <t>Oração da noite: medo e coragem 🌙 Para fechar o dia com Hebreus 13:6. Comente o nome de quem você quer colocar nesta oração. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I116" s="2" t="inlineStr"/>
@@ -5460,7 +5460,7 @@
       </c>
       <c r="D117" s="2" t="inlineStr">
         <is>
-          <t>Dia 116 de 365. Provérbios 28:1: Por que algumas pessoas parecem não ter medo? #fe #coragem #medo #palavradodia</t>
+          <t>Dia 116 de 365. Provérbios 28:1: Por que algumas pessoas parecem não ter medo? #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E117" s="2" t="inlineStr">
@@ -5470,7 +5470,7 @@
       </c>
       <c r="F117" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ Deuteronômio 3:22. Ele luta por você. #versiculododia #fe #medo #oracao</t>
+          <t>Pausa do meio-dia ☀️ Deuteronômio 3:22. Ele luta por você. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G117" s="2" t="inlineStr">
@@ -5480,7 +5480,7 @@
       </c>
       <c r="H117" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: medo e coragem 🌙 Para fechar o dia com Provérbios 28:1. Conte nos comentários pelo que você quer agradecer hoje. #oracaodanoite #oracao #fe #medo</t>
+          <t>Oração da noite: medo e coragem 🌙 Para fechar o dia com Provérbios 28:1. Conte nos comentários pelo que você quer agradecer hoje. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I117" s="2" t="inlineStr"/>
@@ -5503,7 +5503,7 @@
       </c>
       <c r="D118" s="2" t="inlineStr">
         <is>
-          <t>Dia 117 de 365. Salmos 91:1-2: O salmo da proteção. #fe #coragem #medo #palavradodia</t>
+          <t>Dia 117 de 365. Salmos 91:1-2: O salmo da proteção. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E118" s="2" t="inlineStr">
@@ -5513,7 +5513,7 @@
       </c>
       <c r="F118" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ 1 Samuel 17:37. Gigantes também caem. #versiculododia #fe #medo #oracao</t>
+          <t>Pausa do meio-dia ☀️ 1 Samuel 17:37. Gigantes também caem. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G118" s="2" t="inlineStr">
@@ -5523,7 +5523,7 @@
       </c>
       <c r="H118" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: medo e coragem 🌙 Para fechar o dia com Salmos 91:1-2. Deixe nos comentários o que você quer entregar a Deus esta noite. #oracaodanoite #oracao #fe #medo</t>
+          <t>Oração da noite: medo e coragem 🌙 Para fechar o dia com Salmos 91:1-2. Deixe nos comentários o que você quer entregar a Deus esta noite. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I118" s="2" t="inlineStr"/>
@@ -5546,7 +5546,7 @@
       </c>
       <c r="D119" s="2" t="inlineStr">
         <is>
-          <t>Dia 118 de 365. Josué 1:7: Coragem para fazer o certo, não só o fácil. #fe #coragem #medo #palavradodia</t>
+          <t>Dia 118 de 365. Josué 1:7: Coragem para fazer o certo, não só o fácil. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E119" s="2" t="inlineStr">
@@ -5556,7 +5556,7 @@
       </c>
       <c r="F119" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ Salmos 121:5. Ele está à sua direita. #versiculododia #fe #medo #oracao</t>
+          <t>Pausa do meio-dia ☀️ Salmos 121:5. Ele está à sua direita. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G119" s="2" t="inlineStr">
@@ -5566,7 +5566,7 @@
       </c>
       <c r="H119" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: medo e coragem 🌙 Para fechar o dia com Josué 1:7. Marque alguém que precisa ouvir esta oração. #oracaodanoite #oracao #fe #medo</t>
+          <t>Oração da noite: medo e coragem 🌙 Para fechar o dia com Josué 1:7. Marque alguém que precisa ouvir esta oração. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I119" s="2" t="inlineStr"/>
@@ -5589,7 +5589,7 @@
       </c>
       <c r="D120" s="2" t="inlineStr">
         <is>
-          <t>Dia 119 de 365. 1 Samuel 17:45: Davi diante do gigante. #fe #coragem #medo #palavradodia</t>
+          <t>Dia 119 de 365. 1 Samuel 17:45: Davi diante do gigante. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E120" s="2" t="inlineStr">
@@ -5599,7 +5599,7 @@
       </c>
       <c r="F120" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ Hebreus 11:8. Não precisa saber tudo para ir. #versiculododia #fe #medo #oracao</t>
+          <t>Pausa do meio-dia ☀️ Hebreus 11:8. Não precisa saber tudo para ir. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G120" s="2" t="inlineStr">
@@ -5609,7 +5609,7 @@
       </c>
       <c r="H120" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: medo e coragem 🌙 Para fechar o dia com 1 Samuel 17:45. Comente seu pedido. Vamos orar juntos. #oracaodanoite #oracao #fe #medo</t>
+          <t>Oração da noite: medo e coragem 🌙 Para fechar o dia com 1 Samuel 17:45. Comente seu pedido. Vamos orar juntos. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I120" s="2" t="inlineStr"/>
@@ -5632,7 +5632,7 @@
       </c>
       <c r="D121" s="2" t="inlineStr">
         <is>
-          <t>Dia 120 de 365. Salmos 27:14: Coragem também é saber esperar. #fe #coragem #medo #palavradodia</t>
+          <t>Dia 120 de 365. Salmos 27:14: Coragem também é saber esperar. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E121" s="2" t="inlineStr">
@@ -5642,7 +5642,7 @@
       </c>
       <c r="F121" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ Gênesis 15:1. Ele é o seu escudo. #versiculododia #fe #medo #oracao</t>
+          <t>Pausa do meio-dia ☀️ Gênesis 15:1. Ele é o seu escudo. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G121" s="2" t="inlineStr">
@@ -5652,7 +5652,7 @@
       </c>
       <c r="H121" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: medo e coragem 🌙 Para fechar o dia com Salmos 27:14. Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #medo</t>
+          <t>Oração da noite: medo e coragem 🌙 Para fechar o dia com Salmos 27:14. Deixe seu pedido de oração nos comentários. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I121" s="2" t="inlineStr"/>
@@ -5675,7 +5675,7 @@
       </c>
       <c r="D122" s="2" t="inlineStr">
         <is>
-          <t>Dia 121 de 365. Isaías 12:2: Confiar sem medo. Dá para treinar isso? #fe #coragem #medo #palavradodia</t>
+          <t>Dia 121 de 365. Isaías 12:2: Confiar sem medo. Dá para treinar isso? #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E122" s="2" t="inlineStr">
@@ -5685,7 +5685,7 @@
       </c>
       <c r="F122" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ Salmos 112:8. O justo é ousado como o leão. #versiculododia #fe #medo #oracao</t>
+          <t>Pausa do meio-dia ☀️ Salmos 112:8. O justo é ousado como o leão. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G122" s="2" t="inlineStr">
@@ -5695,7 +5695,7 @@
       </c>
       <c r="H122" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: medo e coragem 🌙 Para fechar o dia com Isaías 12:2. Escreva amém se essa oração é sua também. #oracaodanoite #oracao #fe #medo</t>
+          <t>Oração da noite: medo e coragem 🌙 Para fechar o dia com Isaías 12:2. Escreva amém se essa oração é sua também. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I122" s="2" t="inlineStr"/>
@@ -5718,7 +5718,7 @@
       </c>
       <c r="D123" s="2" t="inlineStr">
         <is>
-          <t>Dia 122 de 365. 2 Crônicas 20:15: A batalha não é sua. #fe #coragem #medo #palavradodia</t>
+          <t>Dia 122 de 365. 2 Crônicas 20:15: A batalha não é sua. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E123" s="2" t="inlineStr">
@@ -5728,7 +5728,7 @@
       </c>
       <c r="F123" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ Juízes 6:14. Você é mais forte do que pensa? #versiculododia #fe #medo #oracao</t>
+          <t>Pausa do meio-dia ☀️ Juízes 6:14. Você é mais forte do que pensa? #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G123" s="2" t="inlineStr">
@@ -5738,7 +5738,7 @@
       </c>
       <c r="H123" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: medo e coragem 🌙 Para fechar o dia com 2 Crônicas 20:15. Comente o nome de quem você quer colocar nesta oração. #oracaodanoite #oracao #fe #medo</t>
+          <t>Oração da noite: medo e coragem 🌙 Para fechar o dia com 2 Crônicas 20:15. Comente o nome de quem você quer colocar nesta oração. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I123" s="2" t="inlineStr"/>
@@ -5761,7 +5761,7 @@
       </c>
       <c r="D124" s="2" t="inlineStr">
         <is>
-          <t>Dia 123 de 365. Salmos 46:1-2: Mesmo que tudo desabe. #fe #coragem #medo #palavradodia</t>
+          <t>Dia 123 de 365. Salmos 46:1-2: Mesmo que tudo desabe. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E124" s="2" t="inlineStr">
@@ -5771,7 +5771,7 @@
       </c>
       <c r="F124" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ Salmos 56:4. Quem é por nós? #versiculododia #fe #medo #oracao</t>
+          <t>Pausa do meio-dia ☀️ Salmos 56:4. Quem é por nós? #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G124" s="2" t="inlineStr">
@@ -5781,7 +5781,7 @@
       </c>
       <c r="H124" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: medo e coragem 🌙 Para fechar o dia com Salmos 46:1-2. Conte nos comentários pelo que você quer agradecer hoje. #oracaodanoite #oracao #fe #medo</t>
+          <t>Oração da noite: medo e coragem 🌙 Para fechar o dia com Salmos 46:1-2. Conte nos comentários pelo que você quer agradecer hoje. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I124" s="2" t="inlineStr"/>
@@ -5804,7 +5804,7 @@
       </c>
       <c r="D125" s="2" t="inlineStr">
         <is>
-          <t>Dia 124 de 365. Marcos 4:39-40: Jesus dormia no meio da tempestade. #fe #coragem #medo #palavradodia</t>
+          <t>Dia 124 de 365. Marcos 4:39-40: Jesus dormia no meio da tempestade. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E125" s="2" t="inlineStr">
@@ -5814,7 +5814,7 @@
       </c>
       <c r="F125" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ Marcos 5:36. A fé vence o medo. #versiculododia #fe #medo #oracao</t>
+          <t>Pausa do meio-dia ☀️ Marcos 5:36. A fé vence o medo. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G125" s="2" t="inlineStr">
@@ -5824,7 +5824,7 @@
       </c>
       <c r="H125" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: medo e coragem 🌙 Para fechar o dia com Marcos 4:39-40. Deixe nos comentários o que você quer entregar a Deus esta noite. #oracaodanoite #oracao #fe #medo</t>
+          <t>Oração da noite: medo e coragem 🌙 Para fechar o dia com Marcos 4:39-40. Deixe nos comentários o que você quer entregar a Deus esta noite. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I125" s="2" t="inlineStr"/>
@@ -5847,7 +5847,7 @@
       </c>
       <c r="D126" s="2" t="inlineStr">
         <is>
-          <t>Dia 125 de 365. Mateus 14:29-31: Pedro andou sobre as águas. Até olhar para o vento. #fe #coragem #medo #palavradodia</t>
+          <t>Dia 125 de 365. Mateus 14:29-31: Pedro andou sobre as águas. Até olhar para o vento. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E126" s="2" t="inlineStr">
@@ -5857,7 +5857,7 @@
       </c>
       <c r="F126" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ Salmos 27:5. Ele te esconde na hora difícil. #versiculododia #fe #medo #oracao</t>
+          <t>Pausa do meio-dia ☀️ Salmos 27:5. Ele te esconde na hora difícil. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G126" s="2" t="inlineStr">
@@ -5867,7 +5867,7 @@
       </c>
       <c r="H126" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: medo e coragem 🌙 Para fechar o dia com Mateus 14:29-31. Marque alguém que precisa ouvir esta oração. #oracaodanoite #oracao #fe #medo</t>
+          <t>Oração da noite: medo e coragem 🌙 Para fechar o dia com Mateus 14:29-31. Marque alguém que precisa ouvir esta oração. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I126" s="2" t="inlineStr"/>
@@ -5890,7 +5890,7 @@
       </c>
       <c r="D127" s="2" t="inlineStr">
         <is>
-          <t>Dia 126 de 365. Salmos 112:7: Medo de notícia ruim? #fe #coragem #medo #palavradodia</t>
+          <t>Dia 126 de 365. Salmos 112:7: Medo de notícia ruim? #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E127" s="2" t="inlineStr">
@@ -5900,7 +5900,7 @@
       </c>
       <c r="F127" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ Salmos 57:7. Seu coração está firme? #versiculododia #fe #medo #oracao</t>
+          <t>Pausa do meio-dia ☀️ Salmos 57:7. Seu coração está firme? #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G127" s="2" t="inlineStr">
@@ -5910,7 +5910,7 @@
       </c>
       <c r="H127" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: medo e coragem 🌙 Para fechar o dia com Salmos 112:7. Comente seu pedido. Vamos orar juntos. #oracaodanoite #oracao #fe #medo</t>
+          <t>Oração da noite: medo e coragem 🌙 Para fechar o dia com Salmos 112:7. Comente seu pedido. Vamos orar juntos. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I127" s="2" t="inlineStr"/>
@@ -5933,7 +5933,7 @@
       </c>
       <c r="D128" s="2" t="inlineStr">
         <is>
-          <t>Dia 127 de 365. Lucas 1:37: Para quem acha que é tarde demais. #fe #coragem #medo #palavradodia</t>
+          <t>Dia 127 de 365. Lucas 1:37: Para quem acha que é tarde demais. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E128" s="2" t="inlineStr">
@@ -5943,7 +5943,7 @@
       </c>
       <c r="F128" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ Mateus 8:26. Quando a tempestade vem. #versiculododia #fe #medo #oracao</t>
+          <t>Pausa do meio-dia ☀️ Mateus 8:26. Quando a tempestade vem. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G128" s="2" t="inlineStr">
@@ -5953,7 +5953,7 @@
       </c>
       <c r="H128" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: medo e coragem 🌙 Para fechar o dia com Lucas 1:37. Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #medo</t>
+          <t>Oração da noite: medo e coragem 🌙 Para fechar o dia com Lucas 1:37. Deixe seu pedido de oração nos comentários. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I128" s="2" t="inlineStr"/>
@@ -5976,7 +5976,7 @@
       </c>
       <c r="D129" s="2" t="inlineStr">
         <is>
-          <t>Dia 128 de 365. Juízes 6:12: Deus chamou de valente um homem escondido. #fe #coragem #medo #palavradodia</t>
+          <t>Dia 128 de 365. Juízes 6:12: Deus chamou de valente um homem escondido. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E129" s="2" t="inlineStr">
@@ -5986,7 +5986,7 @@
       </c>
       <c r="F129" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ Sofonias 3:16. Não deixe as mãos caírem. #versiculododia #fe #medo #oracao</t>
+          <t>Pausa do meio-dia ☀️ Sofonias 3:16. Não deixe as mãos caírem. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G129" s="2" t="inlineStr">
@@ -5996,7 +5996,7 @@
       </c>
       <c r="H129" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: medo e coragem 🌙 Para fechar o dia com Juízes 6:12. Escreva amém se essa oração é sua também. #oracaodanoite #oracao #fe #medo</t>
+          <t>Oração da noite: medo e coragem 🌙 Para fechar o dia com Juízes 6:12. Escreva amém se essa oração é sua também. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I129" s="2" t="inlineStr"/>
@@ -6019,7 +6019,7 @@
       </c>
       <c r="D130" s="2" t="inlineStr">
         <is>
-          <t>Dia 129 de 365. Salmos 31:24: Uma palavra para todos que esperam no Senhor. #fe #coragem #medo #palavradodia</t>
+          <t>Dia 129 de 365. Salmos 31:24: Uma palavra para todos que esperam no Senhor. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E130" s="2" t="inlineStr">
@@ -6029,7 +6029,7 @@
       </c>
       <c r="F130" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ Provérbios 31:25. Medo do futuro? #versiculododia #fe #medo #oracao</t>
+          <t>Pausa do meio-dia ☀️ Provérbios 31:25. Medo do futuro? #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G130" s="2" t="inlineStr">
@@ -6039,7 +6039,7 @@
       </c>
       <c r="H130" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: medo e coragem 🌙 Para fechar o dia com Salmos 31:24. Comente o nome de quem você quer colocar nesta oração. #oracaodanoite #oracao #fe #medo</t>
+          <t>Oração da noite: medo e coragem 🌙 Para fechar o dia com Salmos 31:24. Comente o nome de quem você quer colocar nesta oração. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I130" s="2" t="inlineStr"/>
@@ -6062,7 +6062,7 @@
       </c>
       <c r="D131" s="2" t="inlineStr">
         <is>
-          <t>Dia 130 de 365. Ester 4:14: Talvez você esteja exatamente onde precisa estar. #fe #coragem #medo #palavradodia</t>
+          <t>Dia 130 de 365. Ester 4:14: Talvez você esteja exatamente onde precisa estar. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E131" s="2" t="inlineStr">
@@ -6072,7 +6072,7 @@
       </c>
       <c r="F131" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ Atos 4:29. Coragem para falar a verdade. #versiculododia #fe #medo #oracao</t>
+          <t>Pausa do meio-dia ☀️ Atos 4:29. Coragem para falar a verdade. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G131" s="2" t="inlineStr">
@@ -6082,7 +6082,7 @@
       </c>
       <c r="H131" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: medo e coragem 🌙 Para fechar o dia com Ester 4:14. Conte nos comentários pelo que você quer agradecer hoje. #oracaodanoite #oracao #fe #medo</t>
+          <t>Oração da noite: medo e coragem 🌙 Para fechar o dia com Ester 4:14. Conte nos comentários pelo que você quer agradecer hoje. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I131" s="2" t="inlineStr"/>
@@ -6105,7 +6105,7 @@
       </c>
       <c r="D132" s="2" t="inlineStr">
         <is>
-          <t>Dia 131 de 365. Daniel 3:17-18: Fé que não depende do resultado. #fe #coragem #medo #palavradodia</t>
+          <t>Dia 131 de 365. Daniel 3:17-18: Fé que não depende do resultado. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E132" s="2" t="inlineStr">
@@ -6115,7 +6115,7 @@
       </c>
       <c r="F132" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ Efésios 3:16. Ele te fortalece por dentro. #versiculododia #fe #medo #oracao</t>
+          <t>Pausa do meio-dia ☀️ Efésios 3:16. Ele te fortalece por dentro. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G132" s="2" t="inlineStr">
@@ -6125,7 +6125,7 @@
       </c>
       <c r="H132" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: medo e coragem 🌙 Para fechar o dia com Daniel 3:17-18. Deixe nos comentários o que você quer entregar a Deus esta noite. #oracaodanoite #oracao #fe #medo</t>
+          <t>Oração da noite: medo e coragem 🌙 Para fechar o dia com Daniel 3:17-18. Deixe nos comentários o que você quer entregar a Deus esta noite. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I132" s="2" t="inlineStr"/>
@@ -6148,7 +6148,7 @@
       </c>
       <c r="D133" s="2" t="inlineStr">
         <is>
-          <t>Dia 132 de 365. Atos 18:9-10: Não se cale. Eu estou com você. #fe #coragem #medo #palavradodia</t>
+          <t>Dia 132 de 365. Atos 18:9-10: Não se cale. Eu estou com você. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E133" s="2" t="inlineStr">
@@ -6158,7 +6158,7 @@
       </c>
       <c r="F133" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ Salmos 18:29. Com Deus você salta muralhas. #versiculododia #fe #medo #oracao</t>
+          <t>Pausa do meio-dia ☀️ Salmos 18:29. Com Deus você salta muralhas. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G133" s="2" t="inlineStr">
@@ -6168,7 +6168,7 @@
       </c>
       <c r="H133" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: medo e coragem 🌙 Para fechar o dia com Atos 18:9-10. Marque alguém que precisa ouvir esta oração. #oracaodanoite #oracao #fe #medo</t>
+          <t>Oração da noite: medo e coragem 🌙 Para fechar o dia com Atos 18:9-10. Marque alguém que precisa ouvir esta oração. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I133" s="2" t="inlineStr"/>
@@ -6191,7 +6191,7 @@
       </c>
       <c r="D134" s="2" t="inlineStr">
         <is>
-          <t>Dia 133 de 365. Salmos 138:3: Ele respondeu no dia em que você clamou. #fe #coragem #medo #palavradodia</t>
+          <t>Dia 133 de 365. Salmos 138:3: Ele respondeu no dia em que você clamou. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E134" s="2" t="inlineStr">
@@ -6201,7 +6201,7 @@
       </c>
       <c r="F134" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ Provérbios 4:12. Medo de errar? #versiculododia #fe #medo #oracao</t>
+          <t>Pausa do meio-dia ☀️ Provérbios 4:12. Medo de errar? #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G134" s="2" t="inlineStr">
@@ -6211,7 +6211,7 @@
       </c>
       <c r="H134" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: medo e coragem 🌙 Para fechar o dia com Salmos 138:3. Comente seu pedido. Vamos orar juntos. #oracaodanoite #oracao #fe #medo</t>
+          <t>Oração da noite: medo e coragem 🌙 Para fechar o dia com Salmos 138:3. Comente seu pedido. Vamos orar juntos. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I134" s="2" t="inlineStr"/>
@@ -6234,7 +6234,7 @@
       </c>
       <c r="D135" s="2" t="inlineStr">
         <is>
-          <t>Dia 134 de 365. Isaías 54:17: Nenhuma arma forjada contra você prosperará. #fe #coragem #medo #palavradodia</t>
+          <t>Dia 134 de 365. Isaías 54:17: Nenhuma arma forjada contra você prosperará. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E135" s="2" t="inlineStr">
@@ -6244,7 +6244,7 @@
       </c>
       <c r="F135" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ Isaías 26:4. Ele é rocha eterna. #versiculododia #fe #medo #oracao</t>
+          <t>Pausa do meio-dia ☀️ Isaías 26:4. Ele é rocha eterna. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G135" s="2" t="inlineStr">
@@ -6254,7 +6254,7 @@
       </c>
       <c r="H135" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: medo e coragem 🌙 Para fechar o dia com Isaías 54:17. Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #medo</t>
+          <t>Oração da noite: medo e coragem 🌙 Para fechar o dia com Isaías 54:17. Deixe seu pedido de oração nos comentários. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I135" s="2" t="inlineStr"/>
@@ -6277,7 +6277,7 @@
       </c>
       <c r="D136" s="2" t="inlineStr">
         <is>
-          <t>Dia 135 de 365. Provérbios 3:25-26: Não tema o pavor repentino. #fe #coragem #medo #palavradodia</t>
+          <t>Dia 135 de 365. Provérbios 3:25-26: Não tema o pavor repentino. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E136" s="2" t="inlineStr">
@@ -6287,7 +6287,7 @@
       </c>
       <c r="F136" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ Salmos 144:1. Deus treina suas mãos. #versiculododia #fe #medo #oracao</t>
+          <t>Pausa do meio-dia ☀️ Salmos 144:1. Deus treina suas mãos. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G136" s="2" t="inlineStr">
@@ -6297,7 +6297,7 @@
       </c>
       <c r="H136" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: medo e coragem 🌙 Para fechar o dia com Provérbios 3:25-26. Escreva amém se essa oração é sua também. #oracaodanoite #oracao #fe #medo</t>
+          <t>Oração da noite: medo e coragem 🌙 Para fechar o dia com Provérbios 3:25-26. Escreva amém se essa oração é sua também. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I136" s="2" t="inlineStr"/>
@@ -6320,7 +6320,7 @@
       </c>
       <c r="D137" s="2" t="inlineStr">
         <is>
-          <t>Dia 136 de 365. Neemias 4:14: Lembre-se de quem é o Senhor. #fe #coragem #medo #palavradodia</t>
+          <t>Dia 136 de 365. Neemias 4:14: Lembre-se de quem é o Senhor. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E137" s="2" t="inlineStr">
@@ -6330,7 +6330,7 @@
       </c>
       <c r="F137" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ Salmos 130:5. Esperar também exige coragem. #versiculododia #fe #medo #oracao</t>
+          <t>Pausa do meio-dia ☀️ Salmos 130:5. Esperar também exige coragem. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G137" s="2" t="inlineStr">
@@ -6340,7 +6340,7 @@
       </c>
       <c r="H137" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: medo e coragem 🌙 Para fechar o dia com Neemias 4:14. Comente o nome de quem você quer colocar nesta oração. #oracaodanoite #oracao #fe #medo</t>
+          <t>Oração da noite: medo e coragem 🌙 Para fechar o dia com Neemias 4:14. Comente o nome de quem você quer colocar nesta oração. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I137" s="2" t="inlineStr"/>
@@ -6363,7 +6363,7 @@
       </c>
       <c r="D138" s="2" t="inlineStr">
         <is>
-          <t>Dia 137 de 365. 2 Coríntios 12:9-10: Quando você é fraco, aí é que é forte. #fe #coragem #medo #palavradodia</t>
+          <t>Dia 137 de 365. 2 Coríntios 12:9-10: Quando você é fraco, aí é que é forte. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E138" s="2" t="inlineStr">
@@ -6373,7 +6373,7 @@
       </c>
       <c r="F138" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ Isaías 12:6. Ele está no meio de você. #versiculododia #fe #medo #oracao</t>
+          <t>Pausa do meio-dia ☀️ Isaías 12:6. Ele está no meio de você. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G138" s="2" t="inlineStr">
@@ -6383,7 +6383,7 @@
       </c>
       <c r="H138" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: medo e coragem 🌙 Para fechar o dia com 2 Coríntios 12:9-10. Conte nos comentários pelo que você quer agradecer hoje. #oracaodanoite #oracao #fe #medo</t>
+          <t>Oração da noite: medo e coragem 🌙 Para fechar o dia com 2 Coríntios 12:9-10. Conte nos comentários pelo que você quer agradecer hoje. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I138" s="2" t="inlineStr"/>
@@ -6406,7 +6406,7 @@
       </c>
       <c r="D139" s="2" t="inlineStr">
         <is>
-          <t>Dia 138 de 365. Lamentações 3:22-23: As misericórdias se renovam toda manhã. Inclusive nesta. #fe #esperanca #forca #palavradodia</t>
+          <t>Dia 138 de 365. Lamentações 3:22-23: As misericórdias se renovam toda manhã. Inclusive nesta. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E139" s="2" t="inlineStr">
@@ -6416,7 +6416,7 @@
       </c>
       <c r="F139" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ Salmos 71:14. Ainda tem esperança? #versiculododia #fe #esperanca #oracao</t>
+          <t>Pausa do meio-dia ☀️ Salmos 71:14. Ainda tem esperança? #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G139" s="2" t="inlineStr">
@@ -6426,7 +6426,7 @@
       </c>
       <c r="H139" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: esperança em tempos difíceis 🌙 Para fechar o dia com Lamentações 3:22-23. Deixe nos comentários o que você quer entregar a Deus esta noite. #oracaodanoite #oracao #fe #esperanca</t>
+          <t>Oração da noite: esperança em tempos difíceis 🌙 Para fechar o dia com Lamentações 3:22-23. Deixe nos comentários o que você quer entregar a Deus esta noite. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I139" s="2" t="inlineStr"/>
@@ -6449,7 +6449,7 @@
       </c>
       <c r="D140" s="2" t="inlineStr">
         <is>
-          <t>Dia 139 de 365. Jeremias 29:11: Deus tem planos para você. Bons. #fe #esperanca #forca #palavradodia</t>
+          <t>Dia 139 de 365. Jeremias 29:11: Deus tem planos para você. Bons. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E140" s="2" t="inlineStr">
@@ -6459,7 +6459,7 @@
       </c>
       <c r="F140" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ Salmos 126:5. O choro tem prazo. #versiculododia #fe #esperanca #oracao</t>
+          <t>Pausa do meio-dia ☀️ Salmos 126:5. O choro tem prazo. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G140" s="2" t="inlineStr">
@@ -6469,7 +6469,7 @@
       </c>
       <c r="H140" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: esperança em tempos difíceis 🌙 Para fechar o dia com Jeremias 29:11. Marque alguém que precisa ouvir esta oração. #oracaodanoite #oracao #fe #esperanca</t>
+          <t>Oração da noite: esperança em tempos difíceis 🌙 Para fechar o dia com Jeremias 29:11. Marque alguém que precisa ouvir esta oração. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I140" s="2" t="inlineStr"/>
@@ -6492,7 +6492,7 @@
       </c>
       <c r="D141" s="2" t="inlineStr">
         <is>
-          <t>Dia 140 de 365. Romanos 15:13: Uma bênção para quem perdeu a esperança. #fe #esperanca #forca #palavradodia</t>
+          <t>Dia 140 de 365. Romanos 15:13: Uma bênção para quem perdeu a esperança. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E141" s="2" t="inlineStr">
@@ -6502,7 +6502,7 @@
       </c>
       <c r="F141" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ Isaías 42:9. Ele está fazendo algo novo. #versiculododia #fe #esperanca #oracao</t>
+          <t>Pausa do meio-dia ☀️ Isaías 42:9. Ele está fazendo algo novo. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G141" s="2" t="inlineStr">
@@ -6512,7 +6512,7 @@
       </c>
       <c r="H141" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: esperança em tempos difíceis 🌙 Para fechar o dia com Romanos 15:13. Comente seu pedido. Vamos orar juntos. #oracaodanoite #oracao #fe #esperanca</t>
+          <t>Oração da noite: esperança em tempos difíceis 🌙 Para fechar o dia com Romanos 15:13. Comente seu pedido. Vamos orar juntos. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I141" s="2" t="inlineStr"/>
@@ -6535,7 +6535,7 @@
       </c>
       <c r="D142" s="2" t="inlineStr">
         <is>
-          <t>Dia 141 de 365. Salmos 42:11: Por que estás abatida, ó minha alma? #fe #esperanca #forca #palavradodia</t>
+          <t>Dia 141 de 365. Salmos 42:11: Por que estás abatida, ó minha alma? #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E142" s="2" t="inlineStr">
@@ -6545,7 +6545,7 @@
       </c>
       <c r="F142" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ Romanos 5:5. A esperança não decepciona. #versiculododia #fe #esperanca #oracao</t>
+          <t>Pausa do meio-dia ☀️ Romanos 5:5. A esperança não decepciona. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G142" s="2" t="inlineStr">
@@ -6555,7 +6555,7 @@
       </c>
       <c r="H142" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: esperança em tempos difíceis 🌙 Para fechar o dia com Salmos 42:11. Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #esperanca</t>
+          <t>Oração da noite: esperança em tempos difíceis 🌙 Para fechar o dia com Salmos 42:11. Deixe seu pedido de oração nos comentários. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I142" s="2" t="inlineStr"/>
@@ -6578,7 +6578,7 @@
       </c>
       <c r="D143" s="2" t="inlineStr">
         <is>
-          <t>Dia 142 de 365. Isaías 43:19: Deus está fazendo algo novo. Você não percebe? #fe #esperanca #forca #palavradodia</t>
+          <t>Dia 142 de 365. Isaías 43:19: Deus está fazendo algo novo. Você não percebe? #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E143" s="2" t="inlineStr">
@@ -6588,7 +6588,7 @@
       </c>
       <c r="F143" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ Salmos 39:7. Deus é o Deus da esperança. #versiculododia #fe #esperanca #oracao</t>
+          <t>Pausa do meio-dia ☀️ Salmos 39:7. Deus é o Deus da esperança. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G143" s="2" t="inlineStr">
@@ -6598,7 +6598,7 @@
       </c>
       <c r="H143" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: esperança em tempos difíceis 🌙 Para fechar o dia com Isaías 43:19. Escreva amém se essa oração é sua também. #oracaodanoite #oracao #fe #esperanca</t>
+          <t>Oração da noite: esperança em tempos difíceis 🌙 Para fechar o dia com Isaías 43:19. Escreva amém se essa oração é sua também. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I143" s="2" t="inlineStr"/>
@@ -6621,7 +6621,7 @@
       </c>
       <c r="D144" s="2" t="inlineStr">
         <is>
-          <t>Dia 143 de 365. Romanos 5:3-5: A dor não é o fim da história. #fe #esperanca #forca #palavradodia</t>
+          <t>Dia 143 de 365. Romanos 5:3-5: A dor não é o fim da história. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E144" s="2" t="inlineStr">
@@ -6631,7 +6631,7 @@
       </c>
       <c r="F144" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ Jó 14:7. O que parece fim pode ser começo. #versiculododia #fe #esperanca #oracao</t>
+          <t>Pausa do meio-dia ☀️ Jó 14:7. O que parece fim pode ser começo. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G144" s="2" t="inlineStr">
@@ -6641,7 +6641,7 @@
       </c>
       <c r="H144" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: esperança em tempos difíceis 🌙 Para fechar o dia com Romanos 5:3-5. Comente o nome de quem você quer colocar nesta oração. #oracaodanoite #oracao #fe #esperanca</t>
+          <t>Oração da noite: esperança em tempos difíceis 🌙 Para fechar o dia com Romanos 5:3-5. Comente o nome de quem você quer colocar nesta oração. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I144" s="2" t="inlineStr"/>
@@ -6664,7 +6664,7 @@
       </c>
       <c r="D145" s="2" t="inlineStr">
         <is>
-          <t>Dia 144 de 365. 2 Coríntios 4:16-18: Por fora você cansa. Por dentro, algo se renova. #fe #esperanca #forca #palavradodia</t>
+          <t>Dia 144 de 365. 2 Coríntios 4:16-18: Por fora você cansa. Por dentro, algo se renova. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E145" s="2" t="inlineStr">
@@ -6674,7 +6674,7 @@
       </c>
       <c r="F145" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ Salmos 19:7. Ele restaura. #versiculododia #fe #esperanca #oracao</t>
+          <t>Pausa do meio-dia ☀️ Salmos 19:7. Ele restaura. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G145" s="2" t="inlineStr">
@@ -6684,7 +6684,7 @@
       </c>
       <c r="H145" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: esperança em tempos difíceis 🌙 Para fechar o dia com 2 Coríntios 4:16-18. Conte nos comentários pelo que você quer agradecer hoje. #oracaodanoite #oracao #fe #esperanca</t>
+          <t>Oração da noite: esperança em tempos difíceis 🌙 Para fechar o dia com 2 Coríntios 4:16-18. Conte nos comentários pelo que você quer agradecer hoje. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I145" s="2" t="inlineStr"/>
@@ -6707,7 +6707,7 @@
       </c>
       <c r="D146" s="2" t="inlineStr">
         <is>
-          <t>Dia 145 de 365. Salmos 30:5: O choro pode durar uma noite. #fe #esperanca #forca #palavradodia</t>
+          <t>Dia 145 de 365. Salmos 30:5: O choro pode durar uma noite. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E146" s="2" t="inlineStr">
@@ -6717,7 +6717,7 @@
       </c>
       <c r="F146" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ Salmos 37:9. Os que esperam herdam. #versiculododia #fe #esperanca #oracao</t>
+          <t>Pausa do meio-dia ☀️ Salmos 37:9. Os que esperam herdam. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G146" s="2" t="inlineStr">
@@ -6727,7 +6727,7 @@
       </c>
       <c r="H146" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: esperança em tempos difíceis 🌙 Para fechar o dia com Salmos 30:5. Deixe nos comentários o que você quer entregar a Deus esta noite. #oracaodanoite #oracao #fe #esperanca</t>
+          <t>Oração da noite: esperança em tempos difíceis 🌙 Para fechar o dia com Salmos 30:5. Deixe nos comentários o que você quer entregar a Deus esta noite. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I146" s="2" t="inlineStr"/>
@@ -6750,7 +6750,7 @@
       </c>
       <c r="D147" s="2" t="inlineStr">
         <is>
-          <t>Dia 146 de 365. Habacuque 3:17-18: Mesmo que nada dê certo. #fe #esperanca #forca #palavradodia</t>
+          <t>Dia 146 de 365. Habacuque 3:17-18: Mesmo que nada dê certo. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E147" s="2" t="inlineStr">
@@ -6760,7 +6760,7 @@
       </c>
       <c r="F147" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ Tiago 5:11. Tempo difícil não é tempo perdido. #versiculododia #fe #esperanca #oracao</t>
+          <t>Pausa do meio-dia ☀️ Tiago 5:11. Tempo difícil não é tempo perdido. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G147" s="2" t="inlineStr">
@@ -6770,7 +6770,7 @@
       </c>
       <c r="H147" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: esperança em tempos difíceis 🌙 Para fechar o dia com Habacuque 3:17-18. Marque alguém que precisa ouvir esta oração. #oracaodanoite #oracao #fe #esperanca</t>
+          <t>Oração da noite: esperança em tempos difíceis 🌙 Para fechar o dia com Habacuque 3:17-18. Marque alguém que precisa ouvir esta oração. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I147" s="2" t="inlineStr"/>
@@ -6793,7 +6793,7 @@
       </c>
       <c r="D148" s="2" t="inlineStr">
         <is>
-          <t>Dia 147 de 365. Hebreus 6:19: Uma âncora para a alma. #fe #esperanca #forca #palavradodia</t>
+          <t>Dia 147 de 365. Hebreus 6:19: Uma âncora para a alma. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E148" s="2" t="inlineStr">
@@ -6803,7 +6803,7 @@
       </c>
       <c r="F148" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ Isaías 25:8. Ele enxuga as lágrimas. #versiculododia #fe #esperanca #oracao</t>
+          <t>Pausa do meio-dia ☀️ Isaías 25:8. Ele enxuga as lágrimas. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G148" s="2" t="inlineStr">
@@ -6813,7 +6813,7 @@
       </c>
       <c r="H148" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: esperança em tempos difíceis 🌙 Para fechar o dia com Hebreus 6:19. Comente seu pedido. Vamos orar juntos. #oracaodanoite #oracao #fe #esperanca</t>
+          <t>Oração da noite: esperança em tempos difíceis 🌙 Para fechar o dia com Hebreus 6:19. Comente seu pedido. Vamos orar juntos. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I148" s="2" t="inlineStr"/>
@@ -6836,7 +6836,7 @@
       </c>
       <c r="D149" s="2" t="inlineStr">
         <is>
-          <t>Dia 148 de 365. Salmos 40:1-2: Esperei com paciência. #fe #esperanca #forca #palavradodia</t>
+          <t>Dia 148 de 365. Salmos 40:1-2: Esperei com paciência. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E149" s="2" t="inlineStr">
@@ -6846,7 +6846,7 @@
       </c>
       <c r="F149" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ Lamentações 3:21. Lembre do que te dá esperança. #versiculododia #fe #esperanca #oracao</t>
+          <t>Pausa do meio-dia ☀️ Lamentações 3:21. Lembre do que te dá esperança. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G149" s="2" t="inlineStr">
@@ -6856,7 +6856,7 @@
       </c>
       <c r="H149" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: esperança em tempos difíceis 🌙 Para fechar o dia com Salmos 40:1-2. Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #esperanca</t>
+          <t>Oração da noite: esperança em tempos difíceis 🌙 Para fechar o dia com Salmos 40:1-2. Deixe seu pedido de oração nos comentários. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I149" s="2" t="inlineStr"/>
@@ -6879,7 +6879,7 @@
       </c>
       <c r="D150" s="2" t="inlineStr">
         <is>
-          <t>Dia 149 de 365. Isaías 61:3: Coroa em vez de cinzas. #fe #esperanca #forca #palavradodia</t>
+          <t>Dia 149 de 365. Isaías 61:3: Coroa em vez de cinzas. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E150" s="2" t="inlineStr">
@@ -6889,7 +6889,7 @@
       </c>
       <c r="F150" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ Salmos 113:7. Ele te ergue. #versiculododia #fe #esperanca #oracao</t>
+          <t>Pausa do meio-dia ☀️ Salmos 113:7. Ele te ergue. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G150" s="2" t="inlineStr">
@@ -6899,7 +6899,7 @@
       </c>
       <c r="H150" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: esperança em tempos difíceis 🌙 Para fechar o dia com Isaías 61:3. Escreva amém se essa oração é sua também. #oracaodanoite #oracao #fe #esperanca</t>
+          <t>Oração da noite: esperança em tempos difíceis 🌙 Para fechar o dia com Isaías 61:3. Escreva amém se essa oração é sua também. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I150" s="2" t="inlineStr"/>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="D151" s="2" t="inlineStr">
         <is>
-          <t>Dia 150 de 365. Romanos 8:18: O que vem é maior do que o que dói. #fe #esperanca #forca #palavradodia</t>
+          <t>Dia 150 de 365. Romanos 8:18: O que vem é maior do que o que dói. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E151" s="2" t="inlineStr">
@@ -6932,7 +6932,7 @@
       </c>
       <c r="F151" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ Hebreus 10:35. A esperança é âncora. #versiculododia #fe #esperanca #oracao</t>
+          <t>Pausa do meio-dia ☀️ Hebreus 10:35. A esperança é âncora. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G151" s="2" t="inlineStr">
@@ -6942,7 +6942,7 @@
       </c>
       <c r="H151" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: esperança em tempos difíceis 🌙 Para fechar o dia com Romanos 8:18. Comente o nome de quem você quer colocar nesta oração. #oracaodanoite #oracao #fe #esperanca</t>
+          <t>Oração da noite: esperança em tempos difíceis 🌙 Para fechar o dia com Romanos 8:18. Comente o nome de quem você quer colocar nesta oração. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I151" s="2" t="inlineStr"/>
@@ -6965,7 +6965,7 @@
       </c>
       <c r="D152" s="2" t="inlineStr">
         <is>
-          <t>Dia 151 de 365. Miqueias 7:8: Caí, mas vou me levantar. #fe #esperanca #forca #palavradodia</t>
+          <t>Dia 151 de 365. Miqueias 7:8: Caí, mas vou me levantar. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E152" s="2" t="inlineStr">
@@ -6975,7 +6975,7 @@
       </c>
       <c r="F152" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ Salmos 143:8. Depois da noite vem a manhã. #versiculododia #fe #esperanca #oracao</t>
+          <t>Pausa do meio-dia ☀️ Salmos 143:8. Depois da noite vem a manhã. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G152" s="2" t="inlineStr">
@@ -6985,7 +6985,7 @@
       </c>
       <c r="H152" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: esperança em tempos difíceis 🌙 Para fechar o dia com Miqueias 7:8. Conte nos comentários pelo que você quer agradecer hoje. #oracaodanoite #oracao #fe #esperanca</t>
+          <t>Oração da noite: esperança em tempos difíceis 🌙 Para fechar o dia com Miqueias 7:8. Conte nos comentários pelo que você quer agradecer hoje. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I152" s="2" t="inlineStr"/>
@@ -7008,7 +7008,7 @@
       </c>
       <c r="D153" s="2" t="inlineStr">
         <is>
-          <t>Dia 152 de 365. Salmos 147:3: Para quem está de coração partido. #fe #esperanca #forca #palavradodia</t>
+          <t>Dia 152 de 365. Salmos 147:3: Para quem está de coração partido. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E153" s="2" t="inlineStr">
@@ -7018,7 +7018,7 @@
       </c>
       <c r="F153" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ Salmos 51:17. Ele não despreza o coração quebrado. #versiculododia #fe #esperanca #oracao</t>
+          <t>Pausa do meio-dia ☀️ Salmos 51:17. Ele não despreza o coração quebrado. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G153" s="2" t="inlineStr">
@@ -7028,7 +7028,7 @@
       </c>
       <c r="H153" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: esperança em tempos difíceis 🌙 Para fechar o dia com Salmos 147:3. Deixe nos comentários o que você quer entregar a Deus esta noite. #oracaodanoite #oracao #fe #esperanca</t>
+          <t>Oração da noite: esperança em tempos difíceis 🌙 Para fechar o dia com Salmos 147:3. Deixe nos comentários o que você quer entregar a Deus esta noite. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I153" s="2" t="inlineStr"/>
@@ -7051,7 +7051,7 @@
       </c>
       <c r="D154" s="2" t="inlineStr">
         <is>
-          <t>Dia 153 de 365. Joel 2:25: Deus pode restituir os anos perdidos. #fe #esperanca #forca #palavradodia</t>
+          <t>Dia 153 de 365. Joel 2:25: Deus pode restituir os anos perdidos. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E154" s="2" t="inlineStr">
@@ -7061,7 +7061,7 @@
       </c>
       <c r="F154" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ João 10:28. Ninguém se perde nas mãos dEle. #versiculododia #fe #esperanca #oracao</t>
+          <t>Pausa do meio-dia ☀️ João 10:28. Ninguém se perde nas mãos dEle. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G154" s="2" t="inlineStr">
@@ -7071,7 +7071,7 @@
       </c>
       <c r="H154" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: esperança em tempos difíceis 🌙 Para fechar o dia com Joel 2:25. Marque alguém que precisa ouvir esta oração. #oracaodanoite #oracao #fe #esperanca</t>
+          <t>Oração da noite: esperança em tempos difíceis 🌙 Para fechar o dia com Joel 2:25. Marque alguém que precisa ouvir esta oração. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I154" s="2" t="inlineStr"/>
@@ -7094,7 +7094,7 @@
       </c>
       <c r="D155" s="2" t="inlineStr">
         <is>
-          <t>Dia 154 de 365. Jó 42:10: A história de Jó não termina na perda. #fe #esperanca #forca #palavradodia</t>
+          <t>Dia 154 de 365. Jó 42:10: A história de Jó não termina na perda. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E155" s="2" t="inlineStr">
@@ -7104,7 +7104,7 @@
       </c>
       <c r="F155" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ Jeremias 31:17. Sua história não acabou. #versiculododia #fe #esperanca #oracao</t>
+          <t>Pausa do meio-dia ☀️ Jeremias 31:17. Sua história não acabou. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G155" s="2" t="inlineStr">
@@ -7114,7 +7114,7 @@
       </c>
       <c r="H155" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: esperança em tempos difíceis 🌙 Para fechar o dia com Jó 42:10. Comente seu pedido. Vamos orar juntos. #oracaodanoite #oracao #fe #esperanca</t>
+          <t>Oração da noite: esperança em tempos difíceis 🌙 Para fechar o dia com Jó 42:10. Comente seu pedido. Vamos orar juntos. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I155" s="2" t="inlineStr"/>
@@ -7137,7 +7137,7 @@
       </c>
       <c r="D156" s="2" t="inlineStr">
         <is>
-          <t>Dia 155 de 365. Salmos 34:18: Deus está perto. Especialmente agora. #fe #esperanca #forca #palavradodia</t>
+          <t>Dia 155 de 365. Salmos 34:18: Deus está perto. Especialmente agora. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E156" s="2" t="inlineStr">
@@ -7147,7 +7147,7 @@
       </c>
       <c r="F156" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ Gênesis 16:13. Deus vê o que você passa. #versiculododia #fe #esperanca #oracao</t>
+          <t>Pausa do meio-dia ☀️ Gênesis 16:13. Deus vê o que você passa. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G156" s="2" t="inlineStr">
@@ -7157,7 +7157,7 @@
       </c>
       <c r="H156" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: esperança em tempos difíceis 🌙 Para fechar o dia com Salmos 34:18. Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #esperanca</t>
+          <t>Oração da noite: esperança em tempos difíceis 🌙 Para fechar o dia com Salmos 34:18. Deixe seu pedido de oração nos comentários. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I156" s="2" t="inlineStr"/>
@@ -7180,7 +7180,7 @@
       </c>
       <c r="D157" s="2" t="inlineStr">
         <is>
-          <t>Dia 156 de 365. Apocalipse 21:4: Um dia sem lágrimas. #fe #esperanca #forca #palavradodia</t>
+          <t>Dia 156 de 365. Apocalipse 21:4: Um dia sem lágrimas. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E157" s="2" t="inlineStr">
@@ -7190,7 +7190,7 @@
       </c>
       <c r="F157" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ Salmos 130:7. Esperança tem fundamento. #versiculododia #fe #esperanca #oracao</t>
+          <t>Pausa do meio-dia ☀️ Salmos 130:7. Esperança tem fundamento. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G157" s="2" t="inlineStr">
@@ -7200,7 +7200,7 @@
       </c>
       <c r="H157" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: esperança em tempos difíceis 🌙 Para fechar o dia com Apocalipse 21:4. Escreva amém se essa oração é sua também. #oracaodanoite #oracao #fe #esperanca</t>
+          <t>Oração da noite: esperança em tempos difíceis 🌙 Para fechar o dia com Apocalipse 21:4. Escreva amém se essa oração é sua também. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I157" s="2" t="inlineStr"/>
@@ -7223,7 +7223,7 @@
       </c>
       <c r="D158" s="2" t="inlineStr">
         <is>
-          <t>Dia 157 de 365. Romanos 12:12: Três atitudes para dias difíceis. #fe #esperanca #forca #palavradodia</t>
+          <t>Dia 157 de 365. Romanos 12:12: Três atitudes para dias difíceis. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E158" s="2" t="inlineStr">
@@ -7233,7 +7233,7 @@
       </c>
       <c r="F158" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ Salmos 42:8. Ele dá cântico na noite. #versiculododia #fe #esperanca #oracao</t>
+          <t>Pausa do meio-dia ☀️ Salmos 42:8. Ele dá cântico na noite. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G158" s="2" t="inlineStr">
@@ -7243,7 +7243,7 @@
       </c>
       <c r="H158" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: esperança em tempos difíceis 🌙 Para fechar o dia com Romanos 12:12. Comente o nome de quem você quer colocar nesta oração. #oracaodanoite #oracao #fe #esperanca</t>
+          <t>Oração da noite: esperança em tempos difíceis 🌙 Para fechar o dia com Romanos 12:12. Comente o nome de quem você quer colocar nesta oração. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I158" s="2" t="inlineStr"/>
@@ -7266,7 +7266,7 @@
       </c>
       <c r="D159" s="2" t="inlineStr">
         <is>
-          <t>Dia 158 de 365. Isaías 40:29: Ele dá força ao cansado. #fe #esperanca #forca #palavradodia</t>
+          <t>Dia 158 de 365. Isaías 40:29: Ele dá força ao cansado. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E159" s="2" t="inlineStr">
@@ -7276,7 +7276,7 @@
       </c>
       <c r="F159" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ 1 Pedro 5:10. O sofrimento passa. #versiculododia #fe #esperanca #oracao</t>
+          <t>Pausa do meio-dia ☀️ 1 Pedro 5:10. O sofrimento passa. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G159" s="2" t="inlineStr">
@@ -7286,7 +7286,7 @@
       </c>
       <c r="H159" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: esperança em tempos difíceis 🌙 Para fechar o dia com Isaías 40:29. Conte nos comentários pelo que você quer agradecer hoje. #oracaodanoite #oracao #fe #esperanca</t>
+          <t>Oração da noite: esperança em tempos difíceis 🌙 Para fechar o dia com Isaías 40:29. Conte nos comentários pelo que você quer agradecer hoje. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I159" s="2" t="inlineStr"/>
@@ -7309,7 +7309,7 @@
       </c>
       <c r="D160" s="2" t="inlineStr">
         <is>
-          <t>Dia 159 de 365. Salmos 71:20: Você vai voltar a viver. #fe #esperanca #forca #palavradodia</t>
+          <t>Dia 159 de 365. Salmos 71:20: Você vai voltar a viver. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E160" s="2" t="inlineStr">
@@ -7319,7 +7319,7 @@
       </c>
       <c r="F160" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ Salmos 30:3. Ele tira do poço. #versiculododia #fe #esperanca #oracao</t>
+          <t>Pausa do meio-dia ☀️ Salmos 30:3. Ele tira do poço. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G160" s="2" t="inlineStr">
@@ -7329,7 +7329,7 @@
       </c>
       <c r="H160" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: esperança em tempos difíceis 🌙 Para fechar o dia com Salmos 71:20. Deixe nos comentários o que você quer entregar a Deus esta noite. #oracaodanoite #oracao #fe #esperanca</t>
+          <t>Oração da noite: esperança em tempos difíceis 🌙 Para fechar o dia com Salmos 71:20. Deixe nos comentários o que você quer entregar a Deus esta noite. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I160" s="2" t="inlineStr"/>
@@ -7352,7 +7352,7 @@
       </c>
       <c r="D161" s="2" t="inlineStr">
         <is>
-          <t>Dia 160 de 365. 1 Pedro 1:3: Uma esperança viva. #fe #esperanca #forca #palavradodia</t>
+          <t>Dia 160 de 365. 1 Pedro 1:3: Uma esperança viva. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E161" s="2" t="inlineStr">
@@ -7362,7 +7362,7 @@
       </c>
       <c r="F161" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ Hebreus 11:1. A fé vê além. #versiculododia #fe #esperanca #oracao</t>
+          <t>Pausa do meio-dia ☀️ Hebreus 11:1. A fé vê além. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G161" s="2" t="inlineStr">
@@ -7372,7 +7372,7 @@
       </c>
       <c r="H161" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: esperança em tempos difíceis 🌙 Para fechar o dia com 1 Pedro 1:3. Marque alguém que precisa ouvir esta oração. #oracaodanoite #oracao #fe #esperanca</t>
+          <t>Oração da noite: esperança em tempos difíceis 🌙 Para fechar o dia com 1 Pedro 1:3. Marque alguém que precisa ouvir esta oração. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I161" s="2" t="inlineStr"/>
@@ -7395,7 +7395,7 @@
       </c>
       <c r="D162" s="2" t="inlineStr">
         <is>
-          <t>Dia 161 de 365. Gênesis 50:20: O mal que planejaram contra você. #fe #esperanca #forca #palavradodia</t>
+          <t>Dia 161 de 365. Gênesis 50:20: O mal que planejaram contra você. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E162" s="2" t="inlineStr">
@@ -7405,7 +7405,7 @@
       </c>
       <c r="F162" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ Rute 4:15. Há vida depois da perda. #versiculododia #fe #esperanca #oracao</t>
+          <t>Pausa do meio-dia ☀️ Rute 4:15. Há vida depois da perda. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G162" s="2" t="inlineStr">
@@ -7415,7 +7415,7 @@
       </c>
       <c r="H162" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: esperança em tempos difíceis 🌙 Para fechar o dia com Gênesis 50:20. Comente seu pedido. Vamos orar juntos. #oracaodanoite #oracao #fe #esperanca</t>
+          <t>Oração da noite: esperança em tempos difíceis 🌙 Para fechar o dia com Gênesis 50:20. Comente seu pedido. Vamos orar juntos. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I162" s="2" t="inlineStr"/>
@@ -7438,7 +7438,7 @@
       </c>
       <c r="D163" s="2" t="inlineStr">
         <is>
-          <t>Dia 162 de 365. Salmos 126:5-6: Quem semeia com lágrimas. #fe #esperanca #forca #palavradodia</t>
+          <t>Dia 162 de 365. Salmos 126:5-6: Quem semeia com lágrimas. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E163" s="2" t="inlineStr">
@@ -7448,7 +7448,7 @@
       </c>
       <c r="F163" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ Isaías 58:8. Ele renova. #versiculododia #fe #esperanca #oracao</t>
+          <t>Pausa do meio-dia ☀️ Isaías 58:8. Ele renova. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G163" s="2" t="inlineStr">
@@ -7458,7 +7458,7 @@
       </c>
       <c r="H163" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: esperança em tempos difíceis 🌙 Para fechar o dia com Salmos 126:5-6. Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #esperanca</t>
+          <t>Oração da noite: esperança em tempos difíceis 🌙 Para fechar o dia com Salmos 126:5-6. Deixe seu pedido de oração nos comentários. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I163" s="2" t="inlineStr"/>
@@ -7481,7 +7481,7 @@
       </c>
       <c r="D164" s="2" t="inlineStr">
         <is>
-          <t>Dia 163 de 365. Isaías 9:2: Uma luz no meio da escuridão. #fe #esperanca #forca #palavradodia</t>
+          <t>Dia 163 de 365. Isaías 9:2: Uma luz no meio da escuridão. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E164" s="2" t="inlineStr">
@@ -7491,7 +7491,7 @@
       </c>
       <c r="F164" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ Isaías 40:11. Ele te carrega no colo. #versiculododia #fe #esperanca #oracao</t>
+          <t>Pausa do meio-dia ☀️ Isaías 40:11. Ele te carrega no colo. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G164" s="2" t="inlineStr">
@@ -7501,7 +7501,7 @@
       </c>
       <c r="H164" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: esperança em tempos difíceis 🌙 Para fechar o dia com Isaías 9:2. Escreva amém se essa oração é sua também. #oracaodanoite #oracao #fe #esperanca</t>
+          <t>Oração da noite: esperança em tempos difíceis 🌙 Para fechar o dia com Isaías 9:2. Escreva amém se essa oração é sua também. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I164" s="2" t="inlineStr"/>
@@ -7524,7 +7524,7 @@
       </c>
       <c r="D165" s="2" t="inlineStr">
         <is>
-          <t>Dia 164 de 365. Salmos 62:5: Descanse, ó minha alma. #fe #esperanca #forca #palavradodia</t>
+          <t>Dia 164 de 365. Salmos 62:5: Descanse, ó minha alma. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E165" s="2" t="inlineStr">
@@ -7534,7 +7534,7 @@
       </c>
       <c r="F165" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ Isaías 49:16. Deus não esqueceu você. #versiculododia #fe #esperanca #oracao</t>
+          <t>Pausa do meio-dia ☀️ Isaías 49:16. Deus não esqueceu você. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G165" s="2" t="inlineStr">
@@ -7544,7 +7544,7 @@
       </c>
       <c r="H165" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: esperança em tempos difíceis 🌙 Para fechar o dia com Salmos 62:5. Comente o nome de quem você quer colocar nesta oração. #oracaodanoite #oracao #fe #esperanca</t>
+          <t>Oração da noite: esperança em tempos difíceis 🌙 Para fechar o dia com Salmos 62:5. Comente o nome de quem você quer colocar nesta oração. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I165" s="2" t="inlineStr"/>
@@ -7567,7 +7567,7 @@
       </c>
       <c r="D166" s="2" t="inlineStr">
         <is>
-          <t>Dia 165 de 365. Isaías 35:3-4: Fortalecei as mãos fracas. #fe #esperanca #forca #palavradodia</t>
+          <t>Dia 165 de 365. Isaías 35:3-4: Fortalecei as mãos fracas. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E166" s="2" t="inlineStr">
@@ -7577,7 +7577,7 @@
       </c>
       <c r="F166" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ Isaías 35:1. O deserto floresce. #versiculododia #fe #esperanca #oracao</t>
+          <t>Pausa do meio-dia ☀️ Isaías 35:1. O deserto floresce. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G166" s="2" t="inlineStr">
@@ -7587,7 +7587,7 @@
       </c>
       <c r="H166" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: esperança em tempos difíceis 🌙 Para fechar o dia com Isaías 35:3-4. Conte nos comentários pelo que você quer agradecer hoje. #oracaodanoite #oracao #fe #esperanca</t>
+          <t>Oração da noite: esperança em tempos difíceis 🌙 Para fechar o dia com Isaías 35:3-4. Conte nos comentários pelo que você quer agradecer hoje. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I166" s="2" t="inlineStr"/>
@@ -7610,7 +7610,7 @@
       </c>
       <c r="D167" s="2" t="inlineStr">
         <is>
-          <t>Dia 166 de 365. 2 Coríntios 4:8-9: Apertado, mas não esmagado. #fe #esperanca #forca #palavradodia</t>
+          <t>Dia 166 de 365. 2 Coríntios 4:8-9: Apertado, mas não esmagado. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E167" s="2" t="inlineStr">
@@ -7620,7 +7620,7 @@
       </c>
       <c r="F167" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ Salmos 37:34. Volte a esperar. #versiculododia #fe #esperanca #oracao</t>
+          <t>Pausa do meio-dia ☀️ Salmos 37:34. Volte a esperar. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G167" s="2" t="inlineStr">
@@ -7630,7 +7630,7 @@
       </c>
       <c r="H167" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: esperança em tempos difíceis 🌙 Para fechar o dia com 2 Coríntios 4:8-9. Deixe nos comentários o que você quer entregar a Deus esta noite. #oracaodanoite #oracao #fe #esperanca</t>
+          <t>Oração da noite: esperança em tempos difíceis 🌙 Para fechar o dia com 2 Coríntios 4:8-9. Deixe nos comentários o que você quer entregar a Deus esta noite. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I167" s="2" t="inlineStr"/>
@@ -7653,7 +7653,7 @@
       </c>
       <c r="D168" s="2" t="inlineStr">
         <is>
-          <t>Dia 167 de 365. Salmos 33:20-22: Nossa alma espera no Senhor. #fe #esperanca #forca #palavradodia</t>
+          <t>Dia 167 de 365. Salmos 33:20-22: Nossa alma espera no Senhor. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E168" s="2" t="inlineStr">
@@ -7663,7 +7663,7 @@
       </c>
       <c r="F168" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ Provérbios 23:18. Ele te dá um futuro. #versiculododia #fe #esperanca #oracao</t>
+          <t>Pausa do meio-dia ☀️ Provérbios 23:18. Ele te dá um futuro. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G168" s="2" t="inlineStr">
@@ -7673,7 +7673,7 @@
       </c>
       <c r="H168" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: esperança em tempos difíceis 🌙 Para fechar o dia com Salmos 33:20-22. Marque alguém que precisa ouvir esta oração. #oracaodanoite #oracao #fe #esperanca</t>
+          <t>Oração da noite: esperança em tempos difíceis 🌙 Para fechar o dia com Salmos 33:20-22. Marque alguém que precisa ouvir esta oração. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I168" s="2" t="inlineStr"/>
@@ -7696,7 +7696,7 @@
       </c>
       <c r="D169" s="2" t="inlineStr">
         <is>
-          <t>Dia 168 de 365. Mateus 28:20: Até o fim. Todos os dias. #fe #esperanca #forca #palavradodia</t>
+          <t>Dia 168 de 365. Mateus 28:20: Até o fim. Todos os dias. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E169" s="2" t="inlineStr">
@@ -7706,7 +7706,7 @@
       </c>
       <c r="F169" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ Salmos 31:19. A bondade dEle te acompanha. #versiculododia #fe #esperanca #oracao</t>
+          <t>Pausa do meio-dia ☀️ Salmos 31:19. A bondade dEle te acompanha. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G169" s="2" t="inlineStr">
@@ -7716,7 +7716,7 @@
       </c>
       <c r="H169" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: esperança em tempos difíceis 🌙 Para fechar o dia com Mateus 28:20. Comente seu pedido. Vamos orar juntos. #oracaodanoite #oracao #fe #esperanca</t>
+          <t>Oração da noite: esperança em tempos difíceis 🌙 Para fechar o dia com Mateus 28:20. Comente seu pedido. Vamos orar juntos. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I169" s="2" t="inlineStr"/>
@@ -7739,7 +7739,7 @@
       </c>
       <c r="D170" s="2" t="inlineStr">
         <is>
-          <t>Dia 169 de 365. Efésios 4:32: Perdoar não é dizer que não doeu. #fe #perdao #graca #palavradodia</t>
+          <t>Dia 169 de 365. Efésios 4:32: Perdoar não é dizer que não doeu. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E170" s="2" t="inlineStr">
@@ -7749,7 +7749,7 @@
       </c>
       <c r="F170" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ Mateus 6:12. Tem alguém para perdoar? #versiculododia #fe #perdao #oracao</t>
+          <t>Pausa do meio-dia ☀️ Mateus 6:12. Tem alguém para perdoar? #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G170" s="2" t="inlineStr">
@@ -7759,7 +7759,7 @@
       </c>
       <c r="H170" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: perdão 🌙 Para fechar o dia com Efésios 4:32. Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #perdao</t>
+          <t>Oração da noite: perdão 🌙 Para fechar o dia com Efésios 4:32. Deixe seu pedido de oração nos comentários. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I170" s="2" t="inlineStr"/>
@@ -7782,7 +7782,7 @@
       </c>
       <c r="D171" s="2" t="inlineStr">
         <is>
-          <t>Dia 170 de 365. Colossenses 3:13: Tem alguém que você ainda não perdoou? #fe #perdao #graca #palavradodia</t>
+          <t>Dia 170 de 365. Colossenses 3:13: Tem alguém que você ainda não perdoou? #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E171" s="2" t="inlineStr">
@@ -7792,7 +7792,7 @@
       </c>
       <c r="F171" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ Colossenses 3:12. Perdão não é sentimento, é decisão. #versiculododia #fe #perdao #oracao</t>
+          <t>Pausa do meio-dia ☀️ Colossenses 3:12. Perdão não é sentimento, é decisão. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G171" s="2" t="inlineStr">
@@ -7802,7 +7802,7 @@
       </c>
       <c r="H171" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: perdão 🌙 Para fechar o dia com Colossenses 3:13. Escreva amém se essa oração é sua também. #oracaodanoite #oracao #fe #perdao</t>
+          <t>Oração da noite: perdão 🌙 Para fechar o dia com Colossenses 3:13. Escreva amém se essa oração é sua também. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I171" s="2" t="inlineStr"/>
@@ -7825,7 +7825,7 @@
       </c>
       <c r="D172" s="2" t="inlineStr">
         <is>
-          <t>Dia 93 de 365. Mateus 6:14-15: Uma frase da oração que muita gente pula. #fe #perdao #graca #palavradodia</t>
+          <t>Dia 93 de 365. Mateus 6:14-15: Uma frase da oração que muita gente pula. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E172" s="2" t="inlineStr">
@@ -7835,7 +7835,7 @@
       </c>
       <c r="F172" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ Isaías 38:17. Deus esquece o que você confessa. #versiculododia #fe #perdao #oracao</t>
+          <t>Pausa do meio-dia ☀️ Isaías 38:17. Deus esquece o que você confessa. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G172" s="2" t="inlineStr">
@@ -7845,7 +7845,7 @@
       </c>
       <c r="H172" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: perdão 🌙 Para fechar o dia com Mateus 6:14-15. Comente o nome de quem você quer colocar nesta oração. #oracaodanoite #oracao #fe #perdao</t>
+          <t>Oração da noite: perdão 🌙 Para fechar o dia com Mateus 6:14-15. Comente o nome de quem você quer colocar nesta oração. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I172" s="2" t="inlineStr"/>
@@ -7868,7 +7868,7 @@
       </c>
       <c r="D173" s="2" t="inlineStr">
         <is>
-          <t>Dia 172 de 365. Mateus 18:21-22: Quantas vezes eu tenho que perdoar? #fe #perdao #graca #palavradodia</t>
+          <t>Dia 172 de 365. Mateus 18:21-22: Quantas vezes eu tenho que perdoar? #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E173" s="2" t="inlineStr">
@@ -7878,7 +7878,7 @@
       </c>
       <c r="F173" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ Efésios 1:7. Você foi perdoado primeiro. #versiculododia #fe #perdao #oracao</t>
+          <t>Pausa do meio-dia ☀️ Efésios 1:7. Você foi perdoado primeiro. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G173" s="2" t="inlineStr">
@@ -7888,7 +7888,7 @@
       </c>
       <c r="H173" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: perdão 🌙 Para fechar o dia com Mateus 18:21-22. Conte nos comentários pelo que você quer agradecer hoje. #oracaodanoite #oracao #fe #perdao</t>
+          <t>Oração da noite: perdão 🌙 Para fechar o dia com Mateus 18:21-22. Conte nos comentários pelo que você quer agradecer hoje. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I173" s="2" t="inlineStr"/>
@@ -7911,7 +7911,7 @@
       </c>
       <c r="D174" s="2" t="inlineStr">
         <is>
-          <t>Dia 173 de 365. 1 João 1:9: Para quem acha que errou demais. #fe #perdao #graca #palavradodia</t>
+          <t>Dia 173 de 365. 1 João 1:9: Para quem acha que errou demais. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E174" s="2" t="inlineStr">
@@ -7921,7 +7921,7 @@
       </c>
       <c r="F174" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ Tiago 1:20. A raiva tem prazo curto. #versiculododia #fe #perdao #oracao</t>
+          <t>Pausa do meio-dia ☀️ Tiago 1:20. A raiva tem prazo curto. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G174" s="2" t="inlineStr">
@@ -7931,7 +7931,7 @@
       </c>
       <c r="H174" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: perdão 🌙 Para fechar o dia com 1 João 1:9. Deixe nos comentários o que você quer entregar a Deus esta noite. #oracaodanoite #oracao #fe #perdao</t>
+          <t>Oração da noite: perdão 🌙 Para fechar o dia com 1 João 1:9. Deixe nos comentários o que você quer entregar a Deus esta noite. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I174" s="2" t="inlineStr"/>
@@ -7954,7 +7954,7 @@
       </c>
       <c r="D175" s="2" t="inlineStr">
         <is>
-          <t>Dia 174 de 365. Salmos 103:12: Até onde Deus jogou os seus erros? #fe #perdao #graca #palavradodia</t>
+          <t>Dia 174 de 365. Salmos 103:12: Até onde Deus jogou os seus erros? #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E175" s="2" t="inlineStr">
@@ -7964,7 +7964,7 @@
       </c>
       <c r="F175" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ Mateus 18:35. Perdoar liberta você. #versiculododia #fe #perdao #oracao</t>
+          <t>Pausa do meio-dia ☀️ Mateus 18:35. Perdoar liberta você. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G175" s="2" t="inlineStr">
@@ -7974,7 +7974,7 @@
       </c>
       <c r="H175" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: perdão 🌙 Para fechar o dia com Salmos 103:12. Marque alguém que precisa ouvir esta oração. #oracaodanoite #oracao #fe #perdao</t>
+          <t>Oração da noite: perdão 🌙 Para fechar o dia com Salmos 103:12. Marque alguém que precisa ouvir esta oração. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I175" s="2" t="inlineStr"/>
@@ -7997,7 +7997,7 @@
       </c>
       <c r="D176" s="2" t="inlineStr">
         <is>
-          <t>Dia 175 de 365. Isaías 1:18: Ainda que seus pecados sejam como escarlate. #fe #perdao #graca #palavradodia</t>
+          <t>Dia 175 de 365. Isaías 1:18: Ainda que seus pecados sejam como escarlate. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E176" s="2" t="inlineStr">
@@ -8007,7 +8007,7 @@
       </c>
       <c r="F176" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ Salmos 86:5. Ele é fiel para perdoar. #versiculododia #fe #perdao #oracao</t>
+          <t>Pausa do meio-dia ☀️ Salmos 86:5. Ele é fiel para perdoar. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G176" s="2" t="inlineStr">
@@ -8017,7 +8017,7 @@
       </c>
       <c r="H176" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: perdão 🌙 Para fechar o dia com Isaías 1:18. Comente seu pedido. Vamos orar juntos. #oracaodanoite #oracao #fe #perdao</t>
+          <t>Oração da noite: perdão 🌙 Para fechar o dia com Isaías 1:18. Comente seu pedido. Vamos orar juntos. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I176" s="2" t="inlineStr"/>
@@ -8040,7 +8040,7 @@
       </c>
       <c r="D177" s="2" t="inlineStr">
         <is>
-          <t>Dia 176 de 365. Lucas 15:20: O pai correu. #fe #perdao #graca #palavradodia</t>
+          <t>Dia 176 de 365. Lucas 15:20: O pai correu. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E177" s="2" t="inlineStr">
@@ -8050,7 +8050,7 @@
       </c>
       <c r="F177" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ Hebreus 12:15. A mágoa contamina. #versiculododia #fe #perdao #oracao</t>
+          <t>Pausa do meio-dia ☀️ Hebreus 12:15. A mágoa contamina. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G177" s="2" t="inlineStr">
@@ -8060,7 +8060,7 @@
       </c>
       <c r="H177" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: perdão 🌙 Para fechar o dia com Lucas 15:20. Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #perdao</t>
+          <t>Oração da noite: perdão 🌙 Para fechar o dia com Lucas 15:20. Deixe seu pedido de oração nos comentários. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I177" s="2" t="inlineStr"/>
@@ -8083,7 +8083,7 @@
       </c>
       <c r="D178" s="2" t="inlineStr">
         <is>
-          <t>Dia 177 de 365. Lucas 23:34: Jesus perdoou enquanto ainda doía. #fe #perdao #graca #palavradodia</t>
+          <t>Dia 177 de 365. Lucas 23:34: Jesus perdoou enquanto ainda doía. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E178" s="2" t="inlineStr">
@@ -8093,7 +8093,7 @@
       </c>
       <c r="F178" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ Romanos 12:21. Pague o mal com o bem. #versiculododia #fe #perdao #oracao</t>
+          <t>Pausa do meio-dia ☀️ Romanos 12:21. Pague o mal com o bem. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G178" s="2" t="inlineStr">
@@ -8103,7 +8103,7 @@
       </c>
       <c r="H178" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: perdão 🌙 Para fechar o dia com Lucas 23:34. Escreva amém se essa oração é sua também. #oracaodanoite #oracao #fe #perdao</t>
+          <t>Oração da noite: perdão 🌙 Para fechar o dia com Lucas 23:34. Escreva amém se essa oração é sua também. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I178" s="2" t="inlineStr"/>
@@ -8126,7 +8126,7 @@
       </c>
       <c r="D179" s="2" t="inlineStr">
         <is>
-          <t>Dia 178 de 365. Miqueias 7:18-19: Deus lança os pecados no fundo do mar. #fe #perdao #graca #palavradodia</t>
+          <t>Dia 178 de 365. Miqueias 7:18-19: Deus lança os pecados no fundo do mar. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E179" s="2" t="inlineStr">
@@ -8136,7 +8136,7 @@
       </c>
       <c r="F179" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ Salmos 103:10. Ele não te trata segundo seus erros. #versiculododia #fe #perdao #oracao</t>
+          <t>Pausa do meio-dia ☀️ Salmos 103:10. Ele não te trata segundo seus erros. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G179" s="2" t="inlineStr">
@@ -8146,7 +8146,7 @@
       </c>
       <c r="H179" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: perdão 🌙 Para fechar o dia com Miqueias 7:18-19. Comente o nome de quem você quer colocar nesta oração. #oracaodanoite #oracao #fe #perdao</t>
+          <t>Oração da noite: perdão 🌙 Para fechar o dia com Miqueias 7:18-19. Comente o nome de quem você quer colocar nesta oração. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I179" s="2" t="inlineStr"/>
@@ -8169,7 +8169,7 @@
       </c>
       <c r="D180" s="2" t="inlineStr">
         <is>
-          <t>Dia 179 de 365. Romanos 12:17-19: Não pague o mal com mal. #fe #perdao #graca #palavradodia</t>
+          <t>Dia 179 de 365. Romanos 12:17-19: Não pague o mal com mal. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E180" s="2" t="inlineStr">
@@ -8179,7 +8179,7 @@
       </c>
       <c r="F180" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ Salmos 32:5. Confessar alivia. #versiculododia #fe #perdao #oracao</t>
+          <t>Pausa do meio-dia ☀️ Salmos 32:5. Confessar alivia. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G180" s="2" t="inlineStr">
@@ -8189,7 +8189,7 @@
       </c>
       <c r="H180" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: perdão 🌙 Para fechar o dia com Romanos 12:17-19. Conte nos comentários pelo que você quer agradecer hoje. #oracaodanoite #oracao #fe #perdao</t>
+          <t>Oração da noite: perdão 🌙 Para fechar o dia com Romanos 12:17-19. Conte nos comentários pelo que você quer agradecer hoje. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I180" s="2" t="inlineStr"/>
@@ -8212,7 +8212,7 @@
       </c>
       <c r="D181" s="2" t="inlineStr">
         <is>
-          <t>Dia 180 de 365. Salmos 32:1-2: Feliz é quem foi perdoado. #fe #perdao #graca #palavradodia</t>
+          <t>Dia 180 de 365. Salmos 32:1-2: Feliz é quem foi perdoado. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E181" s="2" t="inlineStr">
@@ -8222,7 +8222,7 @@
       </c>
       <c r="F181" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ Provérbios 17:9. Amor cobre ofensas. #versiculododia #fe #perdao #oracao</t>
+          <t>Pausa do meio-dia ☀️ Provérbios 17:9. Amor cobre ofensas. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G181" s="2" t="inlineStr">
@@ -8232,7 +8232,7 @@
       </c>
       <c r="H181" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: perdão 🌙 Para fechar o dia com Salmos 32:1-2. Deixe nos comentários o que você quer entregar a Deus esta noite. #oracaodanoite #oracao #fe #perdao</t>
+          <t>Oração da noite: perdão 🌙 Para fechar o dia com Salmos 32:1-2. Deixe nos comentários o que você quer entregar a Deus esta noite. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I181" s="2" t="inlineStr"/>
@@ -8255,7 +8255,7 @@
       </c>
       <c r="D182" s="2" t="inlineStr">
         <is>
-          <t>Dia 181 de 365. Marcos 11:25: Antes de orar, solte. #fe #perdao #graca #palavradodia</t>
+          <t>Dia 181 de 365. Marcos 11:25: Antes de orar, solte. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E182" s="2" t="inlineStr">
@@ -8265,7 +8265,7 @@
       </c>
       <c r="F182" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ Isaías 44:22. Deus apaga. #versiculododia #fe #perdao #oracao</t>
+          <t>Pausa do meio-dia ☀️ Isaías 44:22. Deus apaga. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G182" s="2" t="inlineStr">
@@ -8275,7 +8275,7 @@
       </c>
       <c r="H182" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: perdão 🌙 Para fechar o dia com Marcos 11:25. Marque alguém que precisa ouvir esta oração. #oracaodanoite #oracao #fe #perdao</t>
+          <t>Oração da noite: perdão 🌙 Para fechar o dia com Marcos 11:25. Marque alguém que precisa ouvir esta oração. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I182" s="2" t="inlineStr"/>
@@ -8298,7 +8298,7 @@
       </c>
       <c r="D183" s="2" t="inlineStr">
         <is>
-          <t>Dia 182 de 365. Hebreus 8:12: Deus decide esquecer. #fe #perdao #graca #palavradodia</t>
+          <t>Dia 182 de 365. Hebreus 8:12: Deus decide esquecer. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E183" s="2" t="inlineStr">
@@ -8308,7 +8308,7 @@
       </c>
       <c r="F183" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ Mateus 5:44. Ore por quem te persegue. #versiculododia #fe #perdao #oracao</t>
+          <t>Pausa do meio-dia ☀️ Mateus 5:44. Ore por quem te persegue. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G183" s="2" t="inlineStr">
@@ -8318,7 +8318,7 @@
       </c>
       <c r="H183" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: perdão 🌙 Para fechar o dia com Hebreus 8:12. Comente seu pedido. Vamos orar juntos. #oracaodanoite #oracao #fe #perdao</t>
+          <t>Oração da noite: perdão 🌙 Para fechar o dia com Hebreus 8:12. Comente seu pedido. Vamos orar juntos. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I183" s="2" t="inlineStr"/>
@@ -8341,7 +8341,7 @@
       </c>
       <c r="D184" s="2" t="inlineStr">
         <is>
-          <t>Dia 183 de 365. Gênesis 45:4-5: José perdoou os irmãos que o venderam. #fe #perdao #graca #palavradodia</t>
+          <t>Dia 183 de 365. Gênesis 45:4-5: José perdoou os irmãos que o venderam. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E184" s="2" t="inlineStr">
@@ -8351,7 +8351,7 @@
       </c>
       <c r="F184" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ Romanos 3:23. Ninguém é sem pecado. #versiculododia #fe #perdao #oracao</t>
+          <t>Pausa do meio-dia ☀️ Romanos 3:23. Ninguém é sem pecado. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G184" s="2" t="inlineStr">
@@ -8361,7 +8361,7 @@
       </c>
       <c r="H184" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: perdão 🌙 Para fechar o dia com Gênesis 45:4-5. Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #perdao</t>
+          <t>Oração da noite: perdão 🌙 Para fechar o dia com Gênesis 45:4-5. Deixe seu pedido de oração nos comentários. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I184" s="2" t="inlineStr"/>
@@ -8384,7 +8384,7 @@
       </c>
       <c r="D185" s="2" t="inlineStr">
         <is>
-          <t>Dia 184 de 365. Provérbios 19:11: Saber deixar passar é sabedoria. #fe #perdao #graca #palavradodia</t>
+          <t>Dia 184 de 365. Provérbios 19:11: Saber deixar passar é sabedoria. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E185" s="2" t="inlineStr">
@@ -8394,7 +8394,7 @@
       </c>
       <c r="F185" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ Lucas 15:24. O pai correu para abraçar. #versiculododia #fe #perdao #oracao</t>
+          <t>Pausa do meio-dia ☀️ Lucas 15:24. O pai correu para abraçar. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G185" s="2" t="inlineStr">
@@ -8404,7 +8404,7 @@
       </c>
       <c r="H185" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: perdão 🌙 Para fechar o dia com Provérbios 19:11. Escreva amém se essa oração é sua também. #oracaodanoite #oracao #fe #perdao</t>
+          <t>Oração da noite: perdão 🌙 Para fechar o dia com Provérbios 19:11. Escreva amém se essa oração é sua também. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I185" s="2" t="inlineStr"/>
@@ -8427,7 +8427,7 @@
       </c>
       <c r="D186" s="2" t="inlineStr">
         <is>
-          <t>Dia 185 de 365. 2 Coríntios 5:17: Você não é mais quem era. #fe #perdao #graca #palavradodia</t>
+          <t>Dia 185 de 365. 2 Coríntios 5:17: Você não é mais quem era. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E186" s="2" t="inlineStr">
@@ -8437,7 +8437,7 @@
       </c>
       <c r="F186" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ João 3:17. Sem condenação. #versiculododia #fe #perdao #oracao</t>
+          <t>Pausa do meio-dia ☀️ João 3:17. Sem condenação. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G186" s="2" t="inlineStr">
@@ -8447,7 +8447,7 @@
       </c>
       <c r="H186" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: perdão 🌙 Para fechar o dia com 2 Coríntios 5:17. Comente o nome de quem você quer colocar nesta oração. #oracaodanoite #oracao #fe #perdao</t>
+          <t>Oração da noite: perdão 🌙 Para fechar o dia com 2 Coríntios 5:17. Comente o nome de quem você quer colocar nesta oração. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I186" s="2" t="inlineStr"/>
@@ -8470,7 +8470,7 @@
       </c>
       <c r="D187" s="2" t="inlineStr">
         <is>
-          <t>Dia 186 de 365. Romanos 8:1: Nenhuma condenação. #fe #perdao #graca #palavradodia</t>
+          <t>Dia 186 de 365. Romanos 8:1: Nenhuma condenação. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E187" s="2" t="inlineStr">
@@ -8480,7 +8480,7 @@
       </c>
       <c r="F187" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ Mateus 10:8. Dê graça como recebeu. #versiculododia #fe #perdao #oracao</t>
+          <t>Pausa do meio-dia ☀️ Mateus 10:8. Dê graça como recebeu. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G187" s="2" t="inlineStr">
@@ -8490,7 +8490,7 @@
       </c>
       <c r="H187" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: perdão 🌙 Para fechar o dia com Romanos 8:1. Conte nos comentários pelo que você quer agradecer hoje. #oracaodanoite #oracao #fe #perdao</t>
+          <t>Oração da noite: perdão 🌙 Para fechar o dia com Romanos 8:1. Conte nos comentários pelo que você quer agradecer hoje. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I187" s="2" t="inlineStr"/>
@@ -8513,7 +8513,7 @@
       </c>
       <c r="D188" s="2" t="inlineStr">
         <is>
-          <t>Dia 187 de 365. Lucas 6:37: Não julgue, e não será julgado. #fe #perdao #graca #palavradodia</t>
+          <t>Dia 187 de 365. Lucas 6:37: Não julgue, e não será julgado. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E188" s="2" t="inlineStr">
@@ -8523,7 +8523,7 @@
       </c>
       <c r="F188" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ Provérbios 25:15. Brandura acalma. #versiculododia #fe #perdao #oracao</t>
+          <t>Pausa do meio-dia ☀️ Provérbios 25:15. Brandura acalma. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G188" s="2" t="inlineStr">
@@ -8533,7 +8533,7 @@
       </c>
       <c r="H188" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: perdão 🌙 Para fechar o dia com Lucas 6:37. Deixe nos comentários o que você quer entregar a Deus esta noite. #oracaodanoite #oracao #fe #perdao</t>
+          <t>Oração da noite: perdão 🌙 Para fechar o dia com Lucas 6:37. Deixe nos comentários o que você quer entregar a Deus esta noite. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I188" s="2" t="inlineStr"/>
@@ -8556,7 +8556,7 @@
       </c>
       <c r="D189" s="2" t="inlineStr">
         <is>
-          <t>Dia 188 de 365. Salmos 51:10: Uma oração para recomeçar por dentro. #fe #perdao #graca #palavradodia</t>
+          <t>Dia 188 de 365. Salmos 51:10: Uma oração para recomeçar por dentro. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E189" s="2" t="inlineStr">
@@ -8566,7 +8566,7 @@
       </c>
       <c r="F189" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ Gálatas 6:1. Restaure com mansidão. #versiculododia #fe #perdao #oracao</t>
+          <t>Pausa do meio-dia ☀️ Gálatas 6:1. Restaure com mansidão. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G189" s="2" t="inlineStr">
@@ -8576,7 +8576,7 @@
       </c>
       <c r="H189" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: perdão 🌙 Para fechar o dia com Salmos 51:10. Marque alguém que precisa ouvir esta oração. #oracaodanoite #oracao #fe #perdao</t>
+          <t>Oração da noite: perdão 🌙 Para fechar o dia com Salmos 51:10. Marque alguém que precisa ouvir esta oração. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I189" s="2" t="inlineStr"/>
@@ -8599,7 +8599,7 @@
       </c>
       <c r="D190" s="2" t="inlineStr">
         <is>
-          <t>Dia 189 de 365. Atos 3:19: Arrepender e ser renovado. #fe #perdao #graca #palavradodia</t>
+          <t>Dia 189 de 365. Atos 3:19: Arrepender e ser renovado. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E190" s="2" t="inlineStr">
@@ -8609,7 +8609,7 @@
       </c>
       <c r="F190" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ Salmos 103:9. Ele não guarda rancor. #versiculododia #fe #perdao #oracao</t>
+          <t>Pausa do meio-dia ☀️ Salmos 103:9. Ele não guarda rancor. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G190" s="2" t="inlineStr">
@@ -8619,7 +8619,7 @@
       </c>
       <c r="H190" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: perdão 🌙 Para fechar o dia com Atos 3:19. Comente seu pedido. Vamos orar juntos. #oracaodanoite #oracao #fe #perdao</t>
+          <t>Oração da noite: perdão 🌙 Para fechar o dia com Atos 3:19. Comente seu pedido. Vamos orar juntos. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I190" s="2" t="inlineStr"/>
@@ -8642,7 +8642,7 @@
       </c>
       <c r="D191" s="2" t="inlineStr">
         <is>
-          <t>Dia 190 de 365. Mateus 5:23-24: Antes da oferta, a reconciliação. #fe #perdao #graca #palavradodia</t>
+          <t>Dia 190 de 365. Mateus 5:23-24: Antes da oferta, a reconciliação. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E191" s="2" t="inlineStr">
@@ -8652,7 +8652,7 @@
       </c>
       <c r="F191" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ Salmos 51:7. Coração limpo. #versiculododia #fe #perdao #oracao</t>
+          <t>Pausa do meio-dia ☀️ Salmos 51:7. Coração limpo. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G191" s="2" t="inlineStr">
@@ -8662,7 +8662,7 @@
       </c>
       <c r="H191" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: perdão 🌙 Para fechar o dia com Mateus 5:23-24. Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #perdao</t>
+          <t>Oração da noite: perdão 🌙 Para fechar o dia com Mateus 5:23-24. Deixe seu pedido de oração nos comentários. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I191" s="2" t="inlineStr"/>
@@ -8685,7 +8685,7 @@
       </c>
       <c r="D192" s="2" t="inlineStr">
         <is>
-          <t>Dia 191 de 365. Efésios 4:26-27: Não deixe o sol se pôr sobre a sua ira. #fe #perdao #graca #palavradodia</t>
+          <t>Dia 191 de 365. Efésios 4:26-27: Não deixe o sol se pôr sobre a sua ira. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E192" s="2" t="inlineStr">
@@ -8695,7 +8695,7 @@
       </c>
       <c r="F192" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ Oseias 14:4. Ele te recebe de volta. #versiculododia #fe #perdao #oracao</t>
+          <t>Pausa do meio-dia ☀️ Oseias 14:4. Ele te recebe de volta. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G192" s="2" t="inlineStr">
@@ -8705,7 +8705,7 @@
       </c>
       <c r="H192" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: perdão 🌙 Para fechar o dia com Efésios 4:26-27. Escreva amém se essa oração é sua também. #oracaodanoite #oracao #fe #perdao</t>
+          <t>Oração da noite: perdão 🌙 Para fechar o dia com Efésios 4:26-27. Escreva amém se essa oração é sua também. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I192" s="2" t="inlineStr"/>
@@ -8728,7 +8728,7 @@
       </c>
       <c r="D193" s="2" t="inlineStr">
         <is>
-          <t>Dia 192 de 365. Lucas 7:47: Quem foi muito perdoado, ama muito. #fe #perdao #graca #palavradodia</t>
+          <t>Dia 192 de 365. Lucas 7:47: Quem foi muito perdoado, ama muito. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E193" s="2" t="inlineStr">
@@ -8738,7 +8738,7 @@
       </c>
       <c r="F193" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ Provérbios 14:29. Paciência é inteligência. #versiculododia #fe #perdao #oracao</t>
+          <t>Pausa do meio-dia ☀️ Provérbios 14:29. Paciência é inteligência. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G193" s="2" t="inlineStr">
@@ -8748,7 +8748,7 @@
       </c>
       <c r="H193" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: perdão 🌙 Para fechar o dia com Lucas 7:47. Comente o nome de quem você quer colocar nesta oração. #oracaodanoite #oracao #fe #perdao</t>
+          <t>Oração da noite: perdão 🌙 Para fechar o dia com Lucas 7:47. Comente o nome de quem você quer colocar nesta oração. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I193" s="2" t="inlineStr"/>
@@ -8771,7 +8771,7 @@
       </c>
       <c r="D194" s="2" t="inlineStr">
         <is>
-          <t>Dia 193 de 365. João 8:10-11: Nem eu te condeno. #fe #perdao #graca #palavradodia</t>
+          <t>Dia 193 de 365. João 8:10-11: Nem eu te condeno. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E194" s="2" t="inlineStr">
@@ -8781,7 +8781,7 @@
       </c>
       <c r="F194" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ Lucas 6:36. Perdão sem limite. #versiculododia #fe #perdao #oracao</t>
+          <t>Pausa do meio-dia ☀️ Lucas 6:36. Perdão sem limite. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G194" s="2" t="inlineStr">
@@ -8791,7 +8791,7 @@
       </c>
       <c r="H194" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: perdão 🌙 Para fechar o dia com João 8:10-11. Conte nos comentários pelo que você quer agradecer hoje. #oracaodanoite #oracao #fe #perdao</t>
+          <t>Oração da noite: perdão 🌙 Para fechar o dia com João 8:10-11. Conte nos comentários pelo que você quer agradecer hoje. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I194" s="2" t="inlineStr"/>
@@ -8814,7 +8814,7 @@
       </c>
       <c r="D195" s="2" t="inlineStr">
         <is>
-          <t>Dia 194 de 365. Isaías 43:25: Deus apaga por amor a si mesmo. #fe #perdao #graca #palavradodia</t>
+          <t>Dia 194 de 365. Isaías 43:25: Deus apaga por amor a si mesmo. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E195" s="2" t="inlineStr">
@@ -8824,7 +8824,7 @@
       </c>
       <c r="F195" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ 1 Pedro 2:23. Não pague na mesma moeda. #versiculododia #fe #perdao #oracao</t>
+          <t>Pausa do meio-dia ☀️ 1 Pedro 2:23. Não pague na mesma moeda. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G195" s="2" t="inlineStr">
@@ -8834,7 +8834,7 @@
       </c>
       <c r="H195" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: perdão 🌙 Para fechar o dia com Isaías 43:25. Deixe nos comentários o que você quer entregar a Deus esta noite. #oracaodanoite #oracao #fe #perdao</t>
+          <t>Oração da noite: perdão 🌙 Para fechar o dia com Isaías 43:25. Deixe nos comentários o que você quer entregar a Deus esta noite. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I195" s="2" t="inlineStr"/>
@@ -8857,7 +8857,7 @@
       </c>
       <c r="D196" s="2" t="inlineStr">
         <is>
-          <t>Dia 195 de 365. Salmos 130:3-4: Se Deus guardasse a lista. #fe #perdao #graca #palavradodia</t>
+          <t>Dia 195 de 365. Salmos 130:3-4: Se Deus guardasse a lista. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E196" s="2" t="inlineStr">
@@ -8867,7 +8867,7 @@
       </c>
       <c r="F196" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ Romanos 12:18. Paz com todos. #versiculododia #fe #perdao #oracao</t>
+          <t>Pausa do meio-dia ☀️ Romanos 12:18. Paz com todos. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G196" s="2" t="inlineStr">
@@ -8877,7 +8877,7 @@
       </c>
       <c r="H196" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: perdão 🌙 Para fechar o dia com Salmos 130:3-4. Marque alguém que precisa ouvir esta oração. #oracaodanoite #oracao #fe #perdao</t>
+          <t>Oração da noite: perdão 🌙 Para fechar o dia com Salmos 130:3-4. Marque alguém que precisa ouvir esta oração. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I196" s="2" t="inlineStr"/>
@@ -8900,7 +8900,7 @@
       </c>
       <c r="D197" s="2" t="inlineStr">
         <is>
-          <t>Dia 196 de 365. Colossenses 2:13-14: A dívida foi pregada na cruz. #fe #perdao #graca #palavradodia</t>
+          <t>Dia 196 de 365. Colossenses 2:13-14: A dívida foi pregada na cruz. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E197" s="2" t="inlineStr">
@@ -8910,7 +8910,7 @@
       </c>
       <c r="F197" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ Romanos 5:20. Graça abundante. #versiculododia #fe #perdao #oracao</t>
+          <t>Pausa do meio-dia ☀️ Romanos 5:20. Graça abundante. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G197" s="2" t="inlineStr">
@@ -8920,7 +8920,7 @@
       </c>
       <c r="H197" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: perdão 🌙 Para fechar o dia com Colossenses 2:13-14. Comente seu pedido. Vamos orar juntos. #oracaodanoite #oracao #fe #perdao</t>
+          <t>Oração da noite: perdão 🌙 Para fechar o dia com Colossenses 2:13-14. Comente seu pedido. Vamos orar juntos. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I197" s="2" t="inlineStr"/>
@@ -8943,7 +8943,7 @@
       </c>
       <c r="D198" s="2" t="inlineStr">
         <is>
-          <t>Dia 197 de 365. 1 Pedro 3:9: Responda com bênção. #fe #perdao #graca #palavradodia</t>
+          <t>Dia 197 de 365. 1 Pedro 3:9: Responda com bênção. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E198" s="2" t="inlineStr">
@@ -8953,7 +8953,7 @@
       </c>
       <c r="F198" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ 2 Crônicas 7:14. Ele perdoa e cura. #versiculododia #fe #perdao #oracao</t>
+          <t>Pausa do meio-dia ☀️ 2 Crônicas 7:14. Ele perdoa e cura. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G198" s="2" t="inlineStr">
@@ -8963,7 +8963,7 @@
       </c>
       <c r="H198" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: perdão 🌙 Para fechar o dia com 1 Pedro 3:9. Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #perdao</t>
+          <t>Oração da noite: perdão 🌙 Para fechar o dia com 1 Pedro 3:9. Deixe seu pedido de oração nos comentários. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I198" s="2" t="inlineStr"/>
@@ -8986,7 +8986,7 @@
       </c>
       <c r="D199" s="2" t="inlineStr">
         <is>
-          <t>Dia 198 de 365. Lucas 17:3-4: Perdoar também quando se repete. #fe #perdao #graca #palavradodia</t>
+          <t>Dia 198 de 365. Lucas 17:3-4: Perdoar também quando se repete. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E199" s="2" t="inlineStr">
@@ -8996,7 +8996,7 @@
       </c>
       <c r="F199" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ 1 João 2:1. Recomece limpo. #versiculododia #fe #perdao #oracao</t>
+          <t>Pausa do meio-dia ☀️ 1 João 2:1. Recomece limpo. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G199" s="2" t="inlineStr">
@@ -9006,7 +9006,7 @@
       </c>
       <c r="H199" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: perdão 🌙 Para fechar o dia com Lucas 17:3-4. Escreva amém se essa oração é sua também. #oracaodanoite #oracao #fe #perdao</t>
+          <t>Oração da noite: perdão 🌙 Para fechar o dia com Lucas 17:3-4. Escreva amém se essa oração é sua também. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I199" s="2" t="inlineStr"/>
@@ -9029,7 +9029,7 @@
       </c>
       <c r="D200" s="2" t="inlineStr">
         <is>
-          <t>Dia 199 de 365. Josué 24:15: Eu e a minha casa serviremos ao Senhor. #fe #familia #relacionamentos #palavradodia</t>
+          <t>Dia 199 de 365. Josué 24:15: Eu e a minha casa serviremos ao Senhor. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E200" s="2" t="inlineStr">
@@ -9039,7 +9039,7 @@
       </c>
       <c r="F200" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ Provérbios 17:6. Já mandou mensagem para alguém da família hoje? #versiculododia #fe #familia #oracao</t>
+          <t>Pausa do meio-dia ☀️ Provérbios 17:6. Já mandou mensagem para alguém da família hoje? #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G200" s="2" t="inlineStr">
@@ -9049,7 +9049,7 @@
       </c>
       <c r="H200" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: família e relacionamentos 🌙 Para fechar o dia com Josué 24:15. Comente o nome de quem você quer colocar nesta oração. #oracaodanoite #oracao #fe #familia</t>
+          <t>Oração da noite: família e relacionamentos 🌙 Para fechar o dia com Josué 24:15. Comente o nome de quem você quer colocar nesta oração. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I200" s="2" t="inlineStr"/>
@@ -9072,7 +9072,7 @@
       </c>
       <c r="D201" s="2" t="inlineStr">
         <is>
-          <t>Dia 200 de 365. Salmos 127:1: Se o Senhor não edificar a casa. #fe #familia #relacionamentos #palavradodia</t>
+          <t>Dia 200 de 365. Salmos 127:1: Se o Senhor não edificar a casa. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E201" s="2" t="inlineStr">
@@ -9082,7 +9082,7 @@
       </c>
       <c r="F201" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ Provérbios 17:1. Sua casa tem paz? #versiculododia #fe #familia #oracao</t>
+          <t>Pausa do meio-dia ☀️ Provérbios 17:1. Sua casa tem paz? #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G201" s="2" t="inlineStr">
@@ -9092,7 +9092,7 @@
       </c>
       <c r="H201" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: família e relacionamentos 🌙 Para fechar o dia com Salmos 127:1. Conte nos comentários pelo que você quer agradecer hoje. #oracaodanoite #oracao #fe #familia</t>
+          <t>Oração da noite: família e relacionamentos 🌙 Para fechar o dia com Salmos 127:1. Conte nos comentários pelo que você quer agradecer hoje. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I201" s="2" t="inlineStr"/>
@@ -9115,7 +9115,7 @@
       </c>
       <c r="D202" s="2" t="inlineStr">
         <is>
-          <t>Dia 201 de 365. Provérbios 22:6: Ensina a criança no caminho. #fe #familia #relacionamentos #palavradodia</t>
+          <t>Dia 201 de 365. Provérbios 22:6: Ensina a criança no caminho. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E202" s="2" t="inlineStr">
@@ -9125,7 +9125,7 @@
       </c>
       <c r="F202" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ Provérbios 16:24. Palavra branda cura. #versiculododia #fe #familia #oracao</t>
+          <t>Pausa do meio-dia ☀️ Provérbios 16:24. Palavra branda cura. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G202" s="2" t="inlineStr">
@@ -9135,7 +9135,7 @@
       </c>
       <c r="H202" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: família e relacionamentos 🌙 Para fechar o dia com Provérbios 22:6. Deixe nos comentários o que você quer entregar a Deus esta noite. #oracaodanoite #oracao #fe #familia</t>
+          <t>Oração da noite: família e relacionamentos 🌙 Para fechar o dia com Provérbios 22:6. Deixe nos comentários o que você quer entregar a Deus esta noite. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I202" s="2" t="inlineStr"/>
@@ -9158,7 +9158,7 @@
       </c>
       <c r="D203" s="2" t="inlineStr">
         <is>
-          <t>Dia 202 de 365. Efésios 6:1-3: Honrar pai e mãe tem uma promessa. #fe #familia #relacionamentos #palavradodia</t>
+          <t>Dia 202 de 365. Efésios 6:1-3: Honrar pai e mãe tem uma promessa. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E203" s="2" t="inlineStr">
@@ -9168,7 +9168,7 @@
       </c>
       <c r="F203" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ Êxodo 20:12. Honre quem te criou. #versiculododia #fe #familia #oracao</t>
+          <t>Pausa do meio-dia ☀️ Êxodo 20:12. Honre quem te criou. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G203" s="2" t="inlineStr">
@@ -9178,7 +9178,7 @@
       </c>
       <c r="H203" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: família e relacionamentos 🌙 Para fechar o dia com Efésios 6:1-3. Marque alguém que precisa ouvir esta oração. #oracaodanoite #oracao #fe #familia</t>
+          <t>Oração da noite: família e relacionamentos 🌙 Para fechar o dia com Efésios 6:1-3. Marque alguém que precisa ouvir esta oração. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I203" s="2" t="inlineStr"/>
@@ -9201,7 +9201,7 @@
       </c>
       <c r="D204" s="2" t="inlineStr">
         <is>
-          <t>Dia 203 de 365. Eclesiastes 4:9-10: Dois são melhores que um. #fe #familia #relacionamentos #palavradodia</t>
+          <t>Dia 203 de 365. Eclesiastes 4:9-10: Dois são melhores que um. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E204" s="2" t="inlineStr">
@@ -9211,7 +9211,7 @@
       </c>
       <c r="F204" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ Provérbios 27:10. Amigo de verdade. #versiculododia #fe #familia #oracao</t>
+          <t>Pausa do meio-dia ☀️ Provérbios 27:10. Amigo de verdade. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G204" s="2" t="inlineStr">
@@ -9221,7 +9221,7 @@
       </c>
       <c r="H204" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: família e relacionamentos 🌙 Para fechar o dia com Eclesiastes 4:9-10. Comente seu pedido. Vamos orar juntos. #oracaodanoite #oracao #fe #familia</t>
+          <t>Oração da noite: família e relacionamentos 🌙 Para fechar o dia com Eclesiastes 4:9-10. Comente seu pedido. Vamos orar juntos. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I204" s="2" t="inlineStr"/>
@@ -9244,7 +9244,7 @@
       </c>
       <c r="D205" s="2" t="inlineStr">
         <is>
-          <t>Dia 204 de 365. Eclesiastes 4:12: O cordão de três dobras. #fe #familia #relacionamentos #palavradodia</t>
+          <t>Dia 204 de 365. Eclesiastes 4:12: O cordão de três dobras. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E205" s="2" t="inlineStr">
@@ -9254,7 +9254,7 @@
       </c>
       <c r="F205" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ Provérbios 18:21. A língua tem poder. #versiculododia #fe #familia #oracao</t>
+          <t>Pausa do meio-dia ☀️ Provérbios 18:21. A língua tem poder. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G205" s="2" t="inlineStr">
@@ -9264,7 +9264,7 @@
       </c>
       <c r="H205" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: família e relacionamentos 🌙 Para fechar o dia com Eclesiastes 4:12. Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #familia</t>
+          <t>Oração da noite: família e relacionamentos 🌙 Para fechar o dia com Eclesiastes 4:12. Deixe seu pedido de oração nos comentários. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I205" s="2" t="inlineStr"/>
@@ -9287,7 +9287,7 @@
       </c>
       <c r="D206" s="2" t="inlineStr">
         <is>
-          <t>Dia 205 de 365. Rute 1:16-17: Aonde quer que fores, irei. #fe #familia #relacionamentos #palavradodia</t>
+          <t>Dia 205 de 365. Rute 1:16-17: Aonde quer que fores, irei. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E206" s="2" t="inlineStr">
@@ -9297,7 +9297,7 @@
       </c>
       <c r="F206" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ Romanos 12:13. Ame com obras. #versiculododia #fe #familia #oracao</t>
+          <t>Pausa do meio-dia ☀️ Romanos 12:13. Ame com obras. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G206" s="2" t="inlineStr">
@@ -9307,7 +9307,7 @@
       </c>
       <c r="H206" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: família e relacionamentos 🌙 Para fechar o dia com Rute 1:16-17. Escreva amém se essa oração é sua também. #oracaodanoite #oracao #fe #familia</t>
+          <t>Oração da noite: família e relacionamentos 🌙 Para fechar o dia com Rute 1:16-17. Escreva amém se essa oração é sua também. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I206" s="2" t="inlineStr"/>
@@ -9330,7 +9330,7 @@
       </c>
       <c r="D207" s="2" t="inlineStr">
         <is>
-          <t>Dia 206 de 365. Provérbios 17:17: O amigo ama em todo tempo. #fe #familia #relacionamentos #palavradodia</t>
+          <t>Dia 206 de 365. Provérbios 17:17: O amigo ama em todo tempo. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E207" s="2" t="inlineStr">
@@ -9340,7 +9340,7 @@
       </c>
       <c r="F207" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ Efésios 4:2. Suporte uns aos outros. #versiculododia #fe #familia #oracao</t>
+          <t>Pausa do meio-dia ☀️ Efésios 4:2. Suporte uns aos outros. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G207" s="2" t="inlineStr">
@@ -9350,7 +9350,7 @@
       </c>
       <c r="H207" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: família e relacionamentos 🌙 Para fechar o dia com Provérbios 17:17. Comente o nome de quem você quer colocar nesta oração. #oracaodanoite #oracao #fe #familia</t>
+          <t>Oração da noite: família e relacionamentos 🌙 Para fechar o dia com Provérbios 17:17. Comente o nome de quem você quer colocar nesta oração. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I207" s="2" t="inlineStr"/>
@@ -9373,7 +9373,7 @@
       </c>
       <c r="D208" s="2" t="inlineStr">
         <is>
-          <t>Dia 207 de 365. Colossenses 3:14: Acima de tudo, o amor. #fe #familia #relacionamentos #palavradodia</t>
+          <t>Dia 207 de 365. Colossenses 3:14: Acima de tudo, o amor. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E208" s="2" t="inlineStr">
@@ -9383,7 +9383,7 @@
       </c>
       <c r="F208" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ Efésios 4:3. Unidade é bênção. #versiculododia #fe #familia #oracao</t>
+          <t>Pausa do meio-dia ☀️ Efésios 4:3. Unidade é bênção. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G208" s="2" t="inlineStr">
@@ -9393,7 +9393,7 @@
       </c>
       <c r="H208" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: família e relacionamentos 🌙 Para fechar o dia com Colossenses 3:14. Conte nos comentários pelo que você quer agradecer hoje. #oracaodanoite #oracao #fe #familia</t>
+          <t>Oração da noite: família e relacionamentos 🌙 Para fechar o dia com Colossenses 3:14. Conte nos comentários pelo que você quer agradecer hoje. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I208" s="2" t="inlineStr"/>
@@ -9416,7 +9416,7 @@
       </c>
       <c r="D209" s="2" t="inlineStr">
         <is>
-          <t>Dia 130 de 365. 1 Coríntios 13:4-5: O amor é paciente. #fe #familia #relacionamentos #palavradodia</t>
+          <t>Dia 130 de 365. 1 Coríntios 13:4-5: O amor é paciente. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E209" s="2" t="inlineStr">
@@ -9426,7 +9426,7 @@
       </c>
       <c r="F209" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ Salmos 127:3. Filhos são presente. #versiculododia #fe #familia #oracao</t>
+          <t>Pausa do meio-dia ☀️ Salmos 127:3. Filhos são presente. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G209" s="2" t="inlineStr">
@@ -9436,7 +9436,7 @@
       </c>
       <c r="H209" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: família e relacionamentos 🌙 Para fechar o dia com 1 Coríntios 13:4-5. Deixe nos comentários o que você quer entregar a Deus esta noite. #oracaodanoite #oracao #fe #familia</t>
+          <t>Oração da noite: família e relacionamentos 🌙 Para fechar o dia com 1 Coríntios 13:4-5. Deixe nos comentários o que você quer entregar a Deus esta noite. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I209" s="2" t="inlineStr"/>
@@ -9459,7 +9459,7 @@
       </c>
       <c r="D210" s="2" t="inlineStr">
         <is>
-          <t>Dia 209 de 365. Gênesis 2:24: Deixar e unir. #fe #familia #relacionamentos #palavradodia</t>
+          <t>Dia 209 de 365. Gênesis 2:24: Deixar e unir. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E210" s="2" t="inlineStr">
@@ -9469,7 +9469,7 @@
       </c>
       <c r="F210" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ Efésios 4:15. Fale a verdade com amor. #versiculododia #fe #familia #oracao</t>
+          <t>Pausa do meio-dia ☀️ Efésios 4:15. Fale a verdade com amor. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G210" s="2" t="inlineStr">
@@ -9479,7 +9479,7 @@
       </c>
       <c r="H210" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: família e relacionamentos 🌙 Para fechar o dia com Gênesis 2:24. Marque alguém que precisa ouvir esta oração. #oracaodanoite #oracao #fe #familia</t>
+          <t>Oração da noite: família e relacionamentos 🌙 Para fechar o dia com Gênesis 2:24. Marque alguém que precisa ouvir esta oração. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I210" s="2" t="inlineStr"/>
@@ -9502,7 +9502,7 @@
       </c>
       <c r="D211" s="2" t="inlineStr">
         <is>
-          <t>Dia 210 de 365. Provérbios 31:10-11: Quem achará uma mulher virtuosa? #fe #familia #relacionamentos #palavradodia</t>
+          <t>Dia 210 de 365. Provérbios 31:10-11: Quem achará uma mulher virtuosa? #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E211" s="2" t="inlineStr">
@@ -9512,7 +9512,7 @@
       </c>
       <c r="F211" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ Provérbios 18:2. Quem só fala não aprende. #versiculododia #fe #familia #oracao</t>
+          <t>Pausa do meio-dia ☀️ Provérbios 18:2. Quem só fala não aprende. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G211" s="2" t="inlineStr">
@@ -9522,7 +9522,7 @@
       </c>
       <c r="H211" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: família e relacionamentos 🌙 Para fechar o dia com Provérbios 31:10-11. Comente seu pedido. Vamos orar juntos. #oracaodanoite #oracao #fe #familia</t>
+          <t>Oração da noite: família e relacionamentos 🌙 Para fechar o dia com Provérbios 31:10-11. Comente seu pedido. Vamos orar juntos. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I211" s="2" t="inlineStr"/>
@@ -9545,7 +9545,7 @@
       </c>
       <c r="D212" s="2" t="inlineStr">
         <is>
-          <t>Dia 211 de 365. Efésios 5:25: Amar como Cristo amou a igreja. #fe #familia #relacionamentos #palavradodia</t>
+          <t>Dia 211 de 365. Efésios 5:25: Amar como Cristo amou a igreja. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E212" s="2" t="inlineStr">
@@ -9555,7 +9555,7 @@
       </c>
       <c r="F212" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ Filipenses 2:4. O amor não busca o seu. #versiculododia #fe #familia #oracao</t>
+          <t>Pausa do meio-dia ☀️ Filipenses 2:4. O amor não busca o seu. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G212" s="2" t="inlineStr">
@@ -9565,7 +9565,7 @@
       </c>
       <c r="H212" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: família e relacionamentos 🌙 Para fechar o dia com Efésios 5:25. Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #familia</t>
+          <t>Oração da noite: família e relacionamentos 🌙 Para fechar o dia com Efésios 5:25. Deixe seu pedido de oração nos comentários. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I212" s="2" t="inlineStr"/>
@@ -9588,7 +9588,7 @@
       </c>
       <c r="D213" s="2" t="inlineStr">
         <is>
-          <t>Dia 212 de 365. Salmos 133:1: Como é bom viver em união. #fe #familia #relacionamentos #palavradodia</t>
+          <t>Dia 212 de 365. Salmos 133:1: Como é bom viver em união. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E213" s="2" t="inlineStr">
@@ -9598,7 +9598,7 @@
       </c>
       <c r="F213" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ Provérbios 24:3. Casa firme. #versiculododia #fe #familia #oracao</t>
+          <t>Pausa do meio-dia ☀️ Provérbios 24:3. Casa firme. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G213" s="2" t="inlineStr">
@@ -9608,7 +9608,7 @@
       </c>
       <c r="H213" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: família e relacionamentos 🌙 Para fechar o dia com Salmos 133:1. Escreva amém se essa oração é sua também. #oracaodanoite #oracao #fe #familia</t>
+          <t>Oração da noite: família e relacionamentos 🌙 Para fechar o dia com Salmos 133:1. Escreva amém se essa oração é sua também. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I213" s="2" t="inlineStr"/>
@@ -9631,7 +9631,7 @@
       </c>
       <c r="D214" s="2" t="inlineStr">
         <is>
-          <t>Dia 213 de 365. Provérbios 15:1: A resposta branda desvia o furor. #fe #familia #relacionamentos #palavradodia</t>
+          <t>Dia 213 de 365. Provérbios 15:1: A resposta branda desvia o furor. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E214" s="2" t="inlineStr">
@@ -9641,7 +9641,7 @@
       </c>
       <c r="F214" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ Eclesiastes 4:11. Juntos é melhor. #versiculododia #fe #familia #oracao</t>
+          <t>Pausa do meio-dia ☀️ Eclesiastes 4:11. Juntos é melhor. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G214" s="2" t="inlineStr">
@@ -9651,7 +9651,7 @@
       </c>
       <c r="H214" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: família e relacionamentos 🌙 Para fechar o dia com Provérbios 15:1. Comente o nome de quem você quer colocar nesta oração. #oracaodanoite #oracao #fe #familia</t>
+          <t>Oração da noite: família e relacionamentos 🌙 Para fechar o dia com Provérbios 15:1. Comente o nome de quem você quer colocar nesta oração. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I214" s="2" t="inlineStr"/>
@@ -9674,7 +9674,7 @@
       </c>
       <c r="D215" s="2" t="inlineStr">
         <is>
-          <t>Dia 214 de 365. Tiago 1:19: Ouvir mais, falar menos. #fe #familia #relacionamentos #palavradodia</t>
+          <t>Dia 214 de 365. Tiago 1:19: Ouvir mais, falar menos. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E215" s="2" t="inlineStr">
@@ -9684,7 +9684,7 @@
       </c>
       <c r="F215" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ Colossenses 3:19. Bondade em casa. #versiculododia #fe #familia #oracao</t>
+          <t>Pausa do meio-dia ☀️ Colossenses 3:19. Bondade em casa. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G215" s="2" t="inlineStr">
@@ -9694,7 +9694,7 @@
       </c>
       <c r="H215" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: família e relacionamentos 🌙 Para fechar o dia com Tiago 1:19. Conte nos comentários pelo que você quer agradecer hoje. #oracaodanoite #oracao #fe #familia</t>
+          <t>Oração da noite: família e relacionamentos 🌙 Para fechar o dia com Tiago 1:19. Conte nos comentários pelo que você quer agradecer hoje. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I215" s="2" t="inlineStr"/>
@@ -9717,7 +9717,7 @@
       </c>
       <c r="D216" s="2" t="inlineStr">
         <is>
-          <t>Dia 215 de 365. 1 Pedro 4:8: O amor cobre muitos pecados. #fe #familia #relacionamentos #palavradodia</t>
+          <t>Dia 215 de 365. 1 Pedro 4:8: O amor cobre muitos pecados. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E216" s="2" t="inlineStr">
@@ -9727,7 +9727,7 @@
       </c>
       <c r="F216" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ Provérbios 23:22. Paciência com os pais. #versiculododia #fe #familia #oracao</t>
+          <t>Pausa do meio-dia ☀️ Provérbios 23:22. Paciência com os pais. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G216" s="2" t="inlineStr">
@@ -9737,7 +9737,7 @@
       </c>
       <c r="H216" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: família e relacionamentos 🌙 Para fechar o dia com 1 Pedro 4:8. Deixe nos comentários o que você quer entregar a Deus esta noite. #oracaodanoite #oracao #fe #familia</t>
+          <t>Oração da noite: família e relacionamentos 🌙 Para fechar o dia com 1 Pedro 4:8. Deixe nos comentários o que você quer entregar a Deus esta noite. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I216" s="2" t="inlineStr"/>
@@ -9760,7 +9760,7 @@
       </c>
       <c r="D217" s="2" t="inlineStr">
         <is>
-          <t>Dia 216 de 365. Malaquias 4:6: Corações que voltam. #fe #familia #relacionamentos #palavradodia</t>
+          <t>Dia 216 de 365. Malaquias 4:6: Corações que voltam. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E217" s="2" t="inlineStr">
@@ -9770,7 +9770,7 @@
       </c>
       <c r="F217" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ Deuteronômio 6:7. Ensine pelo exemplo. #versiculododia #fe #familia #oracao</t>
+          <t>Pausa do meio-dia ☀️ Deuteronômio 6:7. Ensine pelo exemplo. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G217" s="2" t="inlineStr">
@@ -9780,7 +9780,7 @@
       </c>
       <c r="H217" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: família e relacionamentos 🌙 Para fechar o dia com Malaquias 4:6. Marque alguém que precisa ouvir esta oração. #oracaodanoite #oracao #fe #familia</t>
+          <t>Oração da noite: família e relacionamentos 🌙 Para fechar o dia com Malaquias 4:6. Marque alguém que precisa ouvir esta oração. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I217" s="2" t="inlineStr"/>
@@ -9803,7 +9803,7 @@
       </c>
       <c r="D218" s="2" t="inlineStr">
         <is>
-          <t>Dia 217 de 365. Salmos 68:6: Deus faz o solitário habitar em família. #fe #familia #relacionamentos #palavradodia</t>
+          <t>Dia 217 de 365. Salmos 68:6: Deus faz o solitário habitar em família. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E218" s="2" t="inlineStr">
@@ -9813,7 +9813,7 @@
       </c>
       <c r="F218" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ Gênesis 50:21. Perdoe em família. #versiculododia #fe #familia #oracao</t>
+          <t>Pausa do meio-dia ☀️ Gênesis 50:21. Perdoe em família. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G218" s="2" t="inlineStr">
@@ -9823,7 +9823,7 @@
       </c>
       <c r="H218" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: família e relacionamentos 🌙 Para fechar o dia com Salmos 68:6. Comente seu pedido. Vamos orar juntos. #oracaodanoite #oracao #fe #familia</t>
+          <t>Oração da noite: família e relacionamentos 🌙 Para fechar o dia com Salmos 68:6. Comente seu pedido. Vamos orar juntos. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I218" s="2" t="inlineStr"/>
@@ -9846,7 +9846,7 @@
       </c>
       <c r="D219" s="2" t="inlineStr">
         <is>
-          <t>Dia 218 de 365. Provérbios 27:17: Ferro afia ferro. #fe #familia #relacionamentos #palavradodia</t>
+          <t>Dia 218 de 365. Provérbios 27:17: Ferro afia ferro. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E219" s="2" t="inlineStr">
@@ -9856,7 +9856,7 @@
       </c>
       <c r="F219" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ Romanos 12:15. Alegrem-se juntos. #versiculododia #fe #familia #oracao</t>
+          <t>Pausa do meio-dia ☀️ Romanos 12:15. Alegrem-se juntos. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G219" s="2" t="inlineStr">
@@ -9866,7 +9866,7 @@
       </c>
       <c r="H219" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: família e relacionamentos 🌙 Para fechar o dia com Provérbios 27:17. Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #familia</t>
+          <t>Oração da noite: família e relacionamentos 🌙 Para fechar o dia com Provérbios 27:17. Deixe seu pedido de oração nos comentários. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I219" s="2" t="inlineStr"/>
@@ -9889,7 +9889,7 @@
       </c>
       <c r="D220" s="2" t="inlineStr">
         <is>
-          <t>Dia 219 de 365. Romanos 12:10: Amai-vos cordialmente. #fe #familia #relacionamentos #palavradodia</t>
+          <t>Dia 219 de 365. Romanos 12:10: Amai-vos cordialmente. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E220" s="2" t="inlineStr">
@@ -9899,7 +9899,7 @@
       </c>
       <c r="F220" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ 1 Pedro 4:9. Seja hospitaleiro. #versiculododia #fe #familia #oracao</t>
+          <t>Pausa do meio-dia ☀️ 1 Pedro 4:9. Seja hospitaleiro. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G220" s="2" t="inlineStr">
@@ -9909,7 +9909,7 @@
       </c>
       <c r="H220" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: família e relacionamentos 🌙 Para fechar o dia com Romanos 12:10. Escreva amém se essa oração é sua também. #oracaodanoite #oracao #fe #familia</t>
+          <t>Oração da noite: família e relacionamentos 🌙 Para fechar o dia com Romanos 12:10. Escreva amém se essa oração é sua também. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I220" s="2" t="inlineStr"/>
@@ -9932,7 +9932,7 @@
       </c>
       <c r="D221" s="2" t="inlineStr">
         <is>
-          <t>Dia 220 de 365. 1 Tessalonicenses 5:11: Encorajem uns aos outros. #fe #familia #relacionamentos #palavradodia</t>
+          <t>Dia 220 de 365. 1 Tessalonicenses 5:11: Encorajem uns aos outros. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E221" s="2" t="inlineStr">
@@ -9942,7 +9942,7 @@
       </c>
       <c r="F221" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ Provérbios 25:11. Palavra na hora certa. #versiculododia #fe #familia #oracao</t>
+          <t>Pausa do meio-dia ☀️ Provérbios 25:11. Palavra na hora certa. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G221" s="2" t="inlineStr">
@@ -9952,7 +9952,7 @@
       </c>
       <c r="H221" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: família e relacionamentos 🌙 Para fechar o dia com 1 Tessalonicenses 5:11. Comente o nome de quem você quer colocar nesta oração. #oracaodanoite #oracao #fe #familia</t>
+          <t>Oração da noite: família e relacionamentos 🌙 Para fechar o dia com 1 Tessalonicenses 5:11. Comente o nome de quem você quer colocar nesta oração. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I221" s="2" t="inlineStr"/>
@@ -9975,7 +9975,7 @@
       </c>
       <c r="D222" s="2" t="inlineStr">
         <is>
-          <t>Dia 221 de 365. Lucas 2:51-52: Jesus também viveu em família. #fe #familia #relacionamentos #palavradodia</t>
+          <t>Dia 221 de 365. Lucas 2:51-52: Jesus também viveu em família. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E222" s="2" t="inlineStr">
@@ -9985,7 +9985,7 @@
       </c>
       <c r="F222" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ 1 Coríntios 15:33. Cuidado com as companhias. #versiculododia #fe #familia #oracao</t>
+          <t>Pausa do meio-dia ☀️ 1 Coríntios 15:33. Cuidado com as companhias. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G222" s="2" t="inlineStr">
@@ -9995,7 +9995,7 @@
       </c>
       <c r="H222" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: família e relacionamentos 🌙 Para fechar o dia com Lucas 2:51-52. Conte nos comentários pelo que você quer agradecer hoje. #oracaodanoite #oracao #fe #familia</t>
+          <t>Oração da noite: família e relacionamentos 🌙 Para fechar o dia com Lucas 2:51-52. Conte nos comentários pelo que você quer agradecer hoje. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I222" s="2" t="inlineStr"/>
@@ -10018,7 +10018,7 @@
       </c>
       <c r="D223" s="2" t="inlineStr">
         <is>
-          <t>Dia 222 de 365. Provérbios 18:24: Há amigo mais chegado que um irmão. #fe #familia #relacionamentos #palavradodia</t>
+          <t>Dia 222 de 365. Provérbios 18:24: Há amigo mais chegado que um irmão. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E223" s="2" t="inlineStr">
@@ -10028,7 +10028,7 @@
       </c>
       <c r="F223" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ Provérbios 15:4. Palavra boa é árvore de vida. #versiculododia #fe #familia #oracao</t>
+          <t>Pausa do meio-dia ☀️ Provérbios 15:4. Palavra boa é árvore de vida. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G223" s="2" t="inlineStr">
@@ -10038,7 +10038,7 @@
       </c>
       <c r="H223" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: família e relacionamentos 🌙 Para fechar o dia com Provérbios 18:24. Deixe nos comentários o que você quer entregar a Deus esta noite. #oracaodanoite #oracao #fe #familia</t>
+          <t>Oração da noite: família e relacionamentos 🌙 Para fechar o dia com Provérbios 18:24. Deixe nos comentários o que você quer entregar a Deus esta noite. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I223" s="2" t="inlineStr"/>
@@ -10061,7 +10061,7 @@
       </c>
       <c r="D224" s="2" t="inlineStr">
         <is>
-          <t>Dia 223 de 365. João 15:13: Maior amor não há. #fe #familia #relacionamentos #palavradodia</t>
+          <t>Dia 223 de 365. João 15:13: Maior amor não há. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E224" s="2" t="inlineStr">
@@ -10071,7 +10071,7 @@
       </c>
       <c r="F224" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ João 13:14. Amor que serve. #versiculododia #fe #familia #oracao</t>
+          <t>Pausa do meio-dia ☀️ João 13:14. Amor que serve. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G224" s="2" t="inlineStr">
@@ -10081,7 +10081,7 @@
       </c>
       <c r="H224" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: família e relacionamentos 🌙 Para fechar o dia com João 15:13. Marque alguém que precisa ouvir esta oração. #oracaodanoite #oracao #fe #familia</t>
+          <t>Oração da noite: família e relacionamentos 🌙 Para fechar o dia com João 15:13. Marque alguém que precisa ouvir esta oração. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I224" s="2" t="inlineStr"/>
@@ -10104,7 +10104,7 @@
       </c>
       <c r="D225" s="2" t="inlineStr">
         <is>
-          <t>Dia 224 de 365. Gálatas 6:2: Levai as cargas uns dos outros. #fe #familia #relacionamentos #palavradodia</t>
+          <t>Dia 224 de 365. Gálatas 6:2: Levai as cargas uns dos outros. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E225" s="2" t="inlineStr">
@@ -10114,7 +10114,7 @@
       </c>
       <c r="F225" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ Provérbios 14:1. A mulher sábia edifica. #versiculododia #fe #familia #oracao</t>
+          <t>Pausa do meio-dia ☀️ Provérbios 14:1. A mulher sábia edifica. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G225" s="2" t="inlineStr">
@@ -10124,7 +10124,7 @@
       </c>
       <c r="H225" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: família e relacionamentos 🌙 Para fechar o dia com Gálatas 6:2. Comente seu pedido. Vamos orar juntos. #oracaodanoite #oracao #fe #familia</t>
+          <t>Oração da noite: família e relacionamentos 🌙 Para fechar o dia com Gálatas 6:2. Comente seu pedido. Vamos orar juntos. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I225" s="2" t="inlineStr"/>
@@ -10147,7 +10147,7 @@
       </c>
       <c r="D226" s="2" t="inlineStr">
         <is>
-          <t>Dia 225 de 365. Filipenses 2:3-4: Considere os outros superiores a si mesmo. #fe #familia #relacionamentos #palavradodia</t>
+          <t>Dia 225 de 365. Filipenses 2:3-4: Considere os outros superiores a si mesmo. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E226" s="2" t="inlineStr">
@@ -10157,7 +10157,7 @@
       </c>
       <c r="F226" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ Salmos 68:5. Pai dos órfãos. #versiculododia #fe #familia #oracao</t>
+          <t>Pausa do meio-dia ☀️ Salmos 68:5. Pai dos órfãos. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G226" s="2" t="inlineStr">
@@ -10167,7 +10167,7 @@
       </c>
       <c r="H226" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: família e relacionamentos 🌙 Para fechar o dia com Filipenses 2:3-4. Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #familia</t>
+          <t>Oração da noite: família e relacionamentos 🌙 Para fechar o dia com Filipenses 2:3-4. Deixe seu pedido de oração nos comentários. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I226" s="2" t="inlineStr"/>
@@ -10190,7 +10190,7 @@
       </c>
       <c r="D227" s="2" t="inlineStr">
         <is>
-          <t>Dia 226 de 365. Salmos 103:13: Como um pai se compadece dos filhos. #fe #familia #relacionamentos #palavradodia</t>
+          <t>Dia 226 de 365. Salmos 103:13: Como um pai se compadece dos filhos. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E227" s="2" t="inlineStr">
@@ -10200,7 +10200,7 @@
       </c>
       <c r="F227" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ Provérbios 16:31. Coroa dos velhos. #versiculododia #fe #familia #oracao</t>
+          <t>Pausa do meio-dia ☀️ Provérbios 16:31. Coroa dos velhos. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G227" s="2" t="inlineStr">
@@ -10210,7 +10210,7 @@
       </c>
       <c r="H227" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: família e relacionamentos 🌙 Para fechar o dia com Salmos 103:13. Escreva amém se essa oração é sua também. #oracaodanoite #oracao #fe #familia</t>
+          <t>Oração da noite: família e relacionamentos 🌙 Para fechar o dia com Salmos 103:13. Escreva amém se essa oração é sua também. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I227" s="2" t="inlineStr"/>
@@ -10233,7 +10233,7 @@
       </c>
       <c r="D228" s="2" t="inlineStr">
         <is>
-          <t>Dia 227 de 365. Isaías 49:15: Uma mãe pode esquecer o filho? #fe #familia #relacionamentos #palavradodia</t>
+          <t>Dia 227 de 365. Isaías 49:15: Uma mãe pode esquecer o filho? #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E228" s="2" t="inlineStr">
@@ -10243,7 +10243,7 @@
       </c>
       <c r="F228" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ 1 Samuel 18:1. Amizade de alma. #versiculododia #fe #familia #oracao</t>
+          <t>Pausa do meio-dia ☀️ 1 Samuel 18:1. Amizade de alma. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G228" s="2" t="inlineStr">
@@ -10253,7 +10253,7 @@
       </c>
       <c r="H228" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: família e relacionamentos 🌙 Para fechar o dia com Isaías 49:15. Comente o nome de quem você quer colocar nesta oração. #oracaodanoite #oracao #fe #familia</t>
+          <t>Oração da noite: família e relacionamentos 🌙 Para fechar o dia com Isaías 49:15. Comente o nome de quem você quer colocar nesta oração. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I228" s="2" t="inlineStr"/>
@@ -10276,7 +10276,7 @@
       </c>
       <c r="D229" s="2" t="inlineStr">
         <is>
-          <t>Dia 228 de 365. 1 João 4:11: Se Deus nos amou assim. #fe #familia #relacionamentos #palavradodia</t>
+          <t>Dia 228 de 365. 1 João 4:11: Se Deus nos amou assim. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E229" s="2" t="inlineStr">
@@ -10286,7 +10286,7 @@
       </c>
       <c r="F229" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ Gálatas 5:22. Paciência é fruto. #versiculododia #fe #familia #oracao</t>
+          <t>Pausa do meio-dia ☀️ Gálatas 5:22. Paciência é fruto. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G229" s="2" t="inlineStr">
@@ -10296,7 +10296,7 @@
       </c>
       <c r="H229" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: família e relacionamentos 🌙 Para fechar o dia com 1 João 4:11. Conte nos comentários pelo que você quer agradecer hoje. #oracaodanoite #oracao #fe #familia</t>
+          <t>Oração da noite: família e relacionamentos 🌙 Para fechar o dia com 1 João 4:11. Conte nos comentários pelo que você quer agradecer hoje. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I229" s="2" t="inlineStr"/>
@@ -10319,7 +10319,7 @@
       </c>
       <c r="D230" s="2" t="inlineStr">
         <is>
-          <t>Dia 229 de 365. Hebreus 13:1: Permaneça o amor fraternal. #fe #familia #relacionamentos #palavradodia</t>
+          <t>Dia 229 de 365. Hebreus 13:1: Permaneça o amor fraternal. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E230" s="2" t="inlineStr">
@@ -10329,7 +10329,7 @@
       </c>
       <c r="F230" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ Atos 16:31. Uma casa que serve a Deus. #versiculododia #fe #familia #oracao</t>
+          <t>Pausa do meio-dia ☀️ Atos 16:31. Uma casa que serve a Deus. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G230" s="2" t="inlineStr">
@@ -10339,7 +10339,7 @@
       </c>
       <c r="H230" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: família e relacionamentos 🌙 Para fechar o dia com Hebreus 13:1. Deixe nos comentários o que você quer entregar a Deus esta noite. #oracaodanoite #oracao #fe #familia</t>
+          <t>Oração da noite: família e relacionamentos 🌙 Para fechar o dia com Hebreus 13:1. Deixe nos comentários o que você quer entregar a Deus esta noite. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I230" s="2" t="inlineStr"/>
@@ -10362,7 +10362,7 @@
       </c>
       <c r="D231" s="2" t="inlineStr">
         <is>
-          <t>Dia 230 de 365. 1 Tessalonicenses 5:18: Em tudo dai graças. #fe #gratidao #louvor #palavradodia</t>
+          <t>Dia 230 de 365. 1 Tessalonicenses 5:18: Em tudo dai graças. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E231" s="2" t="inlineStr">
@@ -10372,7 +10372,7 @@
       </c>
       <c r="F231" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ Salmos 103:1. Pelo que você agradece hoje? #versiculododia #fe #gratidao #oracao</t>
+          <t>Pausa do meio-dia ☀️ Salmos 103:1. Pelo que você agradece hoje? #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G231" s="2" t="inlineStr">
@@ -10382,7 +10382,7 @@
       </c>
       <c r="H231" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: gratidão 🌙 Para fechar o dia com 1 Tessalonicenses 5:18. Marque alguém que precisa ouvir esta oração. #oracaodanoite #oracao #fe #gratidao</t>
+          <t>Oração da noite: gratidão 🌙 Para fechar o dia com 1 Tessalonicenses 5:18. Marque alguém que precisa ouvir esta oração. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I231" s="2" t="inlineStr"/>
@@ -10405,7 +10405,7 @@
       </c>
       <c r="D232" s="2" t="inlineStr">
         <is>
-          <t>Dia 231 de 365. Salmos 118:24: Este é o dia que o Senhor fez. #fe #gratidao #louvor #palavradodia</t>
+          <t>Dia 231 de 365. Salmos 118:24: Este é o dia que o Senhor fez. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E232" s="2" t="inlineStr">
@@ -10415,7 +10415,7 @@
       </c>
       <c r="F232" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ 1 Timóteo 4:4. Agradeça pela comida. #versiculododia #fe #gratidao #oracao</t>
+          <t>Pausa do meio-dia ☀️ 1 Timóteo 4:4. Agradeça pela comida. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G232" s="2" t="inlineStr">
@@ -10425,7 +10425,7 @@
       </c>
       <c r="H232" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: gratidão 🌙 Para fechar o dia com Salmos 118:24. Comente seu pedido. Vamos orar juntos. #oracaodanoite #oracao #fe #gratidao</t>
+          <t>Oração da noite: gratidão 🌙 Para fechar o dia com Salmos 118:24. Comente seu pedido. Vamos orar juntos. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I232" s="2" t="inlineStr"/>
@@ -10448,7 +10448,7 @@
       </c>
       <c r="D233" s="2" t="inlineStr">
         <is>
-          <t>Dia 232 de 365. Salmos 100:4: Entre pelas portas com ação de graças. #fe #gratidao #louvor #palavradodia</t>
+          <t>Dia 232 de 365. Salmos 100:4: Entre pelas portas com ação de graças. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E233" s="2" t="inlineStr">
@@ -10458,7 +10458,7 @@
       </c>
       <c r="F233" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ Salmos 106:1. Gratidão muda o olhar. #versiculododia #fe #gratidao #oracao</t>
+          <t>Pausa do meio-dia ☀️ Salmos 106:1. Gratidão muda o olhar. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G233" s="2" t="inlineStr">
@@ -10468,7 +10468,7 @@
       </c>
       <c r="H233" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: gratidão 🌙 Para fechar o dia com Salmos 100:4. Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #gratidao</t>
+          <t>Oração da noite: gratidão 🌙 Para fechar o dia com Salmos 100:4. Deixe seu pedido de oração nos comentários. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I233" s="2" t="inlineStr"/>
@@ -10491,7 +10491,7 @@
       </c>
       <c r="D234" s="2" t="inlineStr">
         <is>
-          <t>Dia 233 de 365. Colossenses 3:15: E sede agradecidos. #fe #gratidao #louvor #palavradodia</t>
+          <t>Dia 233 de 365. Colossenses 3:15: E sede agradecidos. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E234" s="2" t="inlineStr">
@@ -10501,7 +10501,7 @@
       </c>
       <c r="F234" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ Salmos 68:19. Bênçãos de cada dia. #versiculododia #fe #gratidao #oracao</t>
+          <t>Pausa do meio-dia ☀️ Salmos 68:19. Bênçãos de cada dia. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G234" s="2" t="inlineStr">
@@ -10511,7 +10511,7 @@
       </c>
       <c r="H234" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: gratidão 🌙 Para fechar o dia com Colossenses 3:15. Escreva amém se essa oração é sua também. #oracaodanoite #oracao #fe #gratidao</t>
+          <t>Oração da noite: gratidão 🌙 Para fechar o dia com Colossenses 3:15. Escreva amém se essa oração é sua também. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I234" s="2" t="inlineStr"/>
@@ -10534,7 +10534,7 @@
       </c>
       <c r="D235" s="2" t="inlineStr">
         <is>
-          <t>Dia 234 de 365. Salmos 103:2: Não te esqueças de nenhum dos seus benefícios. #fe #gratidao #louvor #palavradodia</t>
+          <t>Dia 234 de 365. Salmos 103:2: Não te esqueças de nenhum dos seus benefícios. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E235" s="2" t="inlineStr">
@@ -10544,7 +10544,7 @@
       </c>
       <c r="F235" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ Salmos 34:8. Prove que Ele é bom. #versiculododia #fe #gratidao #oracao</t>
+          <t>Pausa do meio-dia ☀️ Salmos 34:8. Prove que Ele é bom. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G235" s="2" t="inlineStr">
@@ -10554,7 +10554,7 @@
       </c>
       <c r="H235" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: gratidão 🌙 Para fechar o dia com Salmos 103:2. Comente o nome de quem você quer colocar nesta oração. #oracaodanoite #oracao #fe #gratidao</t>
+          <t>Oração da noite: gratidão 🌙 Para fechar o dia com Salmos 103:2. Comente o nome de quem você quer colocar nesta oração. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I235" s="2" t="inlineStr"/>
@@ -10577,7 +10577,7 @@
       </c>
       <c r="D236" s="2" t="inlineStr">
         <is>
-          <t>Dia 235 de 365. Lucas 17:15-16: Dos dez curados, só um voltou para agradecer. #fe #gratidao #louvor #palavradodia</t>
+          <t>Dia 235 de 365. Lucas 17:15-16: Dos dez curados, só um voltou para agradecer. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E236" s="2" t="inlineStr">
@@ -10587,7 +10587,7 @@
       </c>
       <c r="F236" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ Salmos 113:3. Louve do nascer ao pôr do sol. #versiculododia #fe #gratidao #oracao</t>
+          <t>Pausa do meio-dia ☀️ Salmos 113:3. Louve do nascer ao pôr do sol. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G236" s="2" t="inlineStr">
@@ -10597,7 +10597,7 @@
       </c>
       <c r="H236" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: gratidão 🌙 Para fechar o dia com Lucas 17:15-16. Conte nos comentários pelo que você quer agradecer hoje. #oracaodanoite #oracao #fe #gratidao</t>
+          <t>Oração da noite: gratidão 🌙 Para fechar o dia com Lucas 17:15-16. Conte nos comentários pelo que você quer agradecer hoje. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I236" s="2" t="inlineStr"/>
@@ -10620,7 +10620,7 @@
       </c>
       <c r="D237" s="2" t="inlineStr">
         <is>
-          <t>Dia 236 de 365. Tiago 1:17: Todo bem vem do alto. #fe #gratidao #louvor #palavradodia</t>
+          <t>Dia 236 de 365. Tiago 1:17: Todo bem vem do alto. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E237" s="2" t="inlineStr">
@@ -10630,7 +10630,7 @@
       </c>
       <c r="F237" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ Filipenses 1:3. Obrigado por quem você tem. #versiculododia #fe #gratidao #oracao</t>
+          <t>Pausa do meio-dia ☀️ Filipenses 1:3. Obrigado por quem você tem. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G237" s="2" t="inlineStr">
@@ -10640,7 +10640,7 @@
       </c>
       <c r="H237" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: gratidão 🌙 Para fechar o dia com Tiago 1:17. Deixe nos comentários o que você quer entregar a Deus esta noite. #oracaodanoite #oracao #fe #gratidao</t>
+          <t>Oração da noite: gratidão 🌙 Para fechar o dia com Tiago 1:17. Deixe nos comentários o que você quer entregar a Deus esta noite. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I237" s="2" t="inlineStr"/>
@@ -10663,7 +10663,7 @@
       </c>
       <c r="D238" s="2" t="inlineStr">
         <is>
-          <t>Dia 237 de 365. Salmos 136:1: A misericórdia dEle dura para sempre. #fe #gratidao #louvor #palavradodia</t>
+          <t>Dia 237 de 365. Salmos 136:1: A misericórdia dEle dura para sempre. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E238" s="2" t="inlineStr">
@@ -10673,7 +10673,7 @@
       </c>
       <c r="F238" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ 1 Timóteo 6:6. Contentamento é riqueza. #versiculododia #fe #gratidao #oracao</t>
+          <t>Pausa do meio-dia ☀️ 1 Timóteo 6:6. Contentamento é riqueza. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G238" s="2" t="inlineStr">
@@ -10683,7 +10683,7 @@
       </c>
       <c r="H238" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: gratidão 🌙 Para fechar o dia com Salmos 136:1. Marque alguém que precisa ouvir esta oração. #oracaodanoite #oracao #fe #gratidao</t>
+          <t>Oração da noite: gratidão 🌙 Para fechar o dia com Salmos 136:1. Marque alguém que precisa ouvir esta oração. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I238" s="2" t="inlineStr"/>
@@ -10706,7 +10706,7 @@
       </c>
       <c r="D239" s="2" t="inlineStr">
         <is>
-          <t>Dia 238 de 365. Filipenses 4:11-12: Aprendi a contentar-me. #fe #gratidao #louvor #palavradodia</t>
+          <t>Dia 238 de 365. Filipenses 4:11-12: Aprendi a contentar-me. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E239" s="2" t="inlineStr">
@@ -10716,7 +10716,7 @@
       </c>
       <c r="F239" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ Salmos 23:5. O cálice transborda. #versiculododia #fe #gratidao #oracao</t>
+          <t>Pausa do meio-dia ☀️ Salmos 23:5. O cálice transborda. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G239" s="2" t="inlineStr">
@@ -10726,7 +10726,7 @@
       </c>
       <c r="H239" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: gratidão 🌙 Para fechar o dia com Filipenses 4:11-12. Comente seu pedido. Vamos orar juntos. #oracaodanoite #oracao #fe #gratidao</t>
+          <t>Oração da noite: gratidão 🌙 Para fechar o dia com Filipenses 4:11-12. Comente seu pedido. Vamos orar juntos. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I239" s="2" t="inlineStr"/>
@@ -10749,7 +10749,7 @@
       </c>
       <c r="D240" s="2" t="inlineStr">
         <is>
-          <t>Dia 239 de 365. Salmos 9:1: De todo o coração. #fe #gratidao #louvor #palavradodia</t>
+          <t>Dia 239 de 365. Salmos 9:1: De todo o coração. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E240" s="2" t="inlineStr">
@@ -10759,7 +10759,7 @@
       </c>
       <c r="F240" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ Salmos 147:7. Cante agradecido. #versiculododia #fe #gratidao #oracao</t>
+          <t>Pausa do meio-dia ☀️ Salmos 147:7. Cante agradecido. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G240" s="2" t="inlineStr">
@@ -10769,7 +10769,7 @@
       </c>
       <c r="H240" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: gratidão 🌙 Para fechar o dia com Salmos 9:1. Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #gratidao</t>
+          <t>Oração da noite: gratidão 🌙 Para fechar o dia com Salmos 9:1. Deixe seu pedido de oração nos comentários. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I240" s="2" t="inlineStr"/>
@@ -10792,7 +10792,7 @@
       </c>
       <c r="D241" s="2" t="inlineStr">
         <is>
-          <t>Dia 240 de 365. Salmos 107:1: Dai graças ao Senhor, porque Ele é bom. #fe #gratidao #louvor #palavradodia</t>
+          <t>Dia 240 de 365. Salmos 107:1: Dai graças ao Senhor, porque Ele é bom. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E241" s="2" t="inlineStr">
@@ -10802,7 +10802,7 @@
       </c>
       <c r="F241" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ Habacuque 3:18. Agradeça na dificuldade. #versiculododia #fe #gratidao #oracao</t>
+          <t>Pausa do meio-dia ☀️ Habacuque 3:18. Agradeça na dificuldade. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G241" s="2" t="inlineStr">
@@ -10812,7 +10812,7 @@
       </c>
       <c r="H241" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: gratidão 🌙 Para fechar o dia com Salmos 107:1. Escreva amém se essa oração é sua também. #oracaodanoite #oracao #fe #gratidao</t>
+          <t>Oração da noite: gratidão 🌙 Para fechar o dia com Salmos 107:1. Escreva amém se essa oração é sua também. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I241" s="2" t="inlineStr"/>
@@ -10835,7 +10835,7 @@
       </c>
       <c r="D242" s="2" t="inlineStr">
         <is>
-          <t>Dia 241 de 365. Efésios 5:20: Dando sempre graças por tudo. #fe #gratidao #louvor #palavradodia</t>
+          <t>Dia 241 de 365. Efésios 5:20: Dando sempre graças por tudo. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E242" s="2" t="inlineStr">
@@ -10845,7 +10845,7 @@
       </c>
       <c r="F242" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ Mateus 6:11. O pão de cada dia. #versiculododia #fe #gratidao #oracao</t>
+          <t>Pausa do meio-dia ☀️ Mateus 6:11. O pão de cada dia. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G242" s="2" t="inlineStr">
@@ -10855,7 +10855,7 @@
       </c>
       <c r="H242" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: gratidão 🌙 Para fechar o dia com Efésios 5:20. Comente o nome de quem você quer colocar nesta oração. #oracaodanoite #oracao #fe #gratidao</t>
+          <t>Oração da noite: gratidão 🌙 Para fechar o dia com Efésios 5:20. Comente o nome de quem você quer colocar nesta oração. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I242" s="2" t="inlineStr"/>
@@ -10878,7 +10878,7 @@
       </c>
       <c r="D243" s="2" t="inlineStr">
         <is>
-          <t>Dia 242 de 365. Hebreus 12:28: Um reino que não pode ser abalado. #fe #gratidao #louvor #palavradodia</t>
+          <t>Dia 242 de 365. Hebreus 12:28: Um reino que não pode ser abalado. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E243" s="2" t="inlineStr">
@@ -10888,7 +10888,7 @@
       </c>
       <c r="F243" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ Salmos 84:11. Dádivas perfeitas. #versiculododia #fe #gratidao #oracao</t>
+          <t>Pausa do meio-dia ☀️ Salmos 84:11. Dádivas perfeitas. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G243" s="2" t="inlineStr">
@@ -10898,7 +10898,7 @@
       </c>
       <c r="H243" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: gratidão 🌙 Para fechar o dia com Hebreus 12:28. Conte nos comentários pelo que você quer agradecer hoje. #oracaodanoite #oracao #fe #gratidao</t>
+          <t>Oração da noite: gratidão 🌙 Para fechar o dia com Hebreus 12:28. Conte nos comentários pelo que você quer agradecer hoje. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I243" s="2" t="inlineStr"/>
@@ -10921,7 +10921,7 @@
       </c>
       <c r="D244" s="2" t="inlineStr">
         <is>
-          <t>Dia 243 de 365. Salmos 92:1-2: Bom é render graças de manhã e de noite. #fe #gratidao #louvor #palavradodia</t>
+          <t>Dia 243 de 365. Salmos 92:1-2: Bom é render graças de manhã e de noite. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E244" s="2" t="inlineStr">
@@ -10931,7 +10931,7 @@
       </c>
       <c r="F244" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ Provérbios 15:13. Coração alegre. #versiculododia #fe #gratidao #oracao</t>
+          <t>Pausa do meio-dia ☀️ Provérbios 15:13. Coração alegre. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G244" s="2" t="inlineStr">
@@ -10941,7 +10941,7 @@
       </c>
       <c r="H244" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: gratidão 🌙 Para fechar o dia com Salmos 92:1-2. Deixe nos comentários o que você quer entregar a Deus esta noite. #oracaodanoite #oracao #fe #gratidao</t>
+          <t>Oração da noite: gratidão 🌙 Para fechar o dia com Salmos 92:1-2. Deixe nos comentários o que você quer entregar a Deus esta noite. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I244" s="2" t="inlineStr"/>
@@ -10964,7 +10964,7 @@
       </c>
       <c r="D245" s="2" t="inlineStr">
         <is>
-          <t>Dia 244 de 365. 1 Crônicas 16:34: Rendei graças ao Senhor. #fe #gratidao #louvor #palavradodia</t>
+          <t>Dia 244 de 365. 1 Crônicas 16:34: Rendei graças ao Senhor. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E245" s="2" t="inlineStr">
@@ -10974,7 +10974,7 @@
       </c>
       <c r="F245" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ Salmos 8:5. Ele te coroou de honra. #versiculododia #fe #gratidao #oracao</t>
+          <t>Pausa do meio-dia ☀️ Salmos 8:5. Ele te coroou de honra. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G245" s="2" t="inlineStr">
@@ -10984,7 +10984,7 @@
       </c>
       <c r="H245" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: gratidão 🌙 Para fechar o dia com 1 Crônicas 16:34. Marque alguém que precisa ouvir esta oração. #oracaodanoite #oracao #fe #gratidao</t>
+          <t>Oração da noite: gratidão 🌙 Para fechar o dia com 1 Crônicas 16:34. Marque alguém que precisa ouvir esta oração. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I245" s="2" t="inlineStr"/>
@@ -11007,7 +11007,7 @@
       </c>
       <c r="D246" s="2" t="inlineStr">
         <is>
-          <t>Dia 245 de 365. 2 Coríntios 9:15: Graças a Deus pelo seu dom inefável. #fe #gratidao #louvor #palavradodia</t>
+          <t>Dia 245 de 365. 2 Coríntios 9:15: Graças a Deus pelo seu dom inefável. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E246" s="2" t="inlineStr">
@@ -11017,7 +11017,7 @@
       </c>
       <c r="F246" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ Salmos 13:6. Grato pela salvação. #versiculododia #fe #gratidao #oracao</t>
+          <t>Pausa do meio-dia ☀️ Salmos 13:6. Grato pela salvação. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G246" s="2" t="inlineStr">
@@ -11027,7 +11027,7 @@
       </c>
       <c r="H246" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: gratidão 🌙 Para fechar o dia com 2 Coríntios 9:15. Comente seu pedido. Vamos orar juntos. #oracaodanoite #oracao #fe #gratidao</t>
+          <t>Oração da noite: gratidão 🌙 Para fechar o dia com 2 Coríntios 9:15. Comente seu pedido. Vamos orar juntos. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I246" s="2" t="inlineStr"/>
@@ -11050,7 +11050,7 @@
       </c>
       <c r="D247" s="2" t="inlineStr">
         <is>
-          <t>Dia 246 de 365. Salmos 34:1: Bendirei o Senhor em todo o tempo. #fe #gratidao #louvor #palavradodia</t>
+          <t>Dia 246 de 365. Salmos 34:1: Bendirei o Senhor em todo o tempo. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E247" s="2" t="inlineStr">
@@ -11060,7 +11060,7 @@
       </c>
       <c r="F247" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ Deuteronômio 8:10. Lembre dos benefícios. #versiculododia #fe #gratidao #oracao</t>
+          <t>Pausa do meio-dia ☀️ Deuteronômio 8:10. Lembre dos benefícios. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G247" s="2" t="inlineStr">
@@ -11070,7 +11070,7 @@
       </c>
       <c r="H247" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: gratidão 🌙 Para fechar o dia com Salmos 34:1. Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #gratidao</t>
+          <t>Oração da noite: gratidão 🌙 Para fechar o dia com Salmos 34:1. Deixe seu pedido de oração nos comentários. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I247" s="2" t="inlineStr"/>
@@ -11093,7 +11093,7 @@
       </c>
       <c r="D248" s="2" t="inlineStr">
         <is>
-          <t>Dia 247 de 365. Daniel 6:10: Daniel orava e dava graças três vezes ao dia. #fe #gratidao #louvor #palavradodia</t>
+          <t>Dia 247 de 365. Daniel 6:10: Daniel orava e dava graças três vezes ao dia. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E248" s="2" t="inlineStr">
@@ -11103,7 +11103,7 @@
       </c>
       <c r="F248" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ Salmos 33:5. A terra está cheia de bondade. #versiculododia #fe #gratidao #oracao</t>
+          <t>Pausa do meio-dia ☀️ Salmos 33:5. A terra está cheia de bondade. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G248" s="2" t="inlineStr">
@@ -11113,7 +11113,7 @@
       </c>
       <c r="H248" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: gratidão 🌙 Para fechar o dia com Daniel 6:10. Escreva amém se essa oração é sua também. #oracaodanoite #oracao #fe #gratidao</t>
+          <t>Oração da noite: gratidão 🌙 Para fechar o dia com Daniel 6:10. Escreva amém se essa oração é sua também. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I248" s="2" t="inlineStr"/>
@@ -11136,7 +11136,7 @@
       </c>
       <c r="D249" s="2" t="inlineStr">
         <is>
-          <t>Dia 248 de 365. Salmos 50:23: A gratidão honra a Deus. #fe #gratidao #louvor #palavradodia</t>
+          <t>Dia 248 de 365. Salmos 50:23: A gratidão honra a Deus. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E249" s="2" t="inlineStr">
@@ -11146,7 +11146,7 @@
       </c>
       <c r="F249" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ Hebreus 4:9. Grato pelo descanso. #versiculododia #fe #gratidao #oracao</t>
+          <t>Pausa do meio-dia ☀️ Hebreus 4:9. Grato pelo descanso. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G249" s="2" t="inlineStr">
@@ -11156,7 +11156,7 @@
       </c>
       <c r="H249" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: gratidão 🌙 Para fechar o dia com Salmos 50:23. Comente o nome de quem você quer colocar nesta oração. #oracaodanoite #oracao #fe #gratidao</t>
+          <t>Oração da noite: gratidão 🌙 Para fechar o dia com Salmos 50:23. Comente o nome de quem você quer colocar nesta oração. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I249" s="2" t="inlineStr"/>
@@ -11179,7 +11179,7 @@
       </c>
       <c r="D250" s="2" t="inlineStr">
         <is>
-          <t>Dia 249 de 365. Romanos 1:21: O perigo de esquecer de agradecer. #fe #gratidao #louvor #palavradodia</t>
+          <t>Dia 249 de 365. Romanos 1:21: O perigo de esquecer de agradecer. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E250" s="2" t="inlineStr">
@@ -11189,7 +11189,7 @@
       </c>
       <c r="F250" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ Provérbios 27:9. Grato pelos amigos. #versiculododia #fe #gratidao #oracao</t>
+          <t>Pausa do meio-dia ☀️ Provérbios 27:9. Grato pelos amigos. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G250" s="2" t="inlineStr">
@@ -11199,7 +11199,7 @@
       </c>
       <c r="H250" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: gratidão 🌙 Para fechar o dia com Romanos 1:21. Conte nos comentários pelo que você quer agradecer hoje. #oracaodanoite #oracao #fe #gratidao</t>
+          <t>Oração da noite: gratidão 🌙 Para fechar o dia com Romanos 1:21. Conte nos comentários pelo que você quer agradecer hoje. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I250" s="2" t="inlineStr"/>
@@ -11222,7 +11222,7 @@
       </c>
       <c r="D251" s="2" t="inlineStr">
         <is>
-          <t>Dia 250 de 365. Salmos 16:6: As cordas caíram em lugares deliciosos. #fe #gratidao #louvor #palavradodia</t>
+          <t>Dia 250 de 365. Salmos 16:6: As cordas caíram em lugares deliciosos. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E251" s="2" t="inlineStr">
@@ -11232,7 +11232,7 @@
       </c>
       <c r="F251" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ 1 Crônicas 29:14. Tudo vem dEle. #versiculododia #fe #gratidao #oracao</t>
+          <t>Pausa do meio-dia ☀️ 1 Crônicas 29:14. Tudo vem dEle. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G251" s="2" t="inlineStr">
@@ -11242,7 +11242,7 @@
       </c>
       <c r="H251" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: gratidão 🌙 Para fechar o dia com Salmos 16:6. Deixe nos comentários o que você quer entregar a Deus esta noite. #oracaodanoite #oracao #fe #gratidao</t>
+          <t>Oração da noite: gratidão 🌙 Para fechar o dia com Salmos 16:6. Deixe nos comentários o que você quer entregar a Deus esta noite. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I251" s="2" t="inlineStr"/>
@@ -11265,7 +11265,7 @@
       </c>
       <c r="D252" s="2" t="inlineStr">
         <is>
-          <t>Dia 251 de 365. Salmos 145:9: O Senhor é bom para todos. #fe #gratidao #louvor #palavradodia</t>
+          <t>Dia 251 de 365. Salmos 145:9: O Senhor é bom para todos. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E252" s="2" t="inlineStr">
@@ -11275,7 +11275,7 @@
       </c>
       <c r="F252" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ Gênesis 1:3. Grato pela luz. #versiculododia #fe #gratidao #oracao</t>
+          <t>Pausa do meio-dia ☀️ Gênesis 1:3. Grato pela luz. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G252" s="2" t="inlineStr">
@@ -11285,7 +11285,7 @@
       </c>
       <c r="H252" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: gratidão 🌙 Para fechar o dia com Salmos 145:9. Marque alguém que precisa ouvir esta oração. #oracaodanoite #oracao #fe #gratidao</t>
+          <t>Oração da noite: gratidão 🌙 Para fechar o dia com Salmos 145:9. Marque alguém que precisa ouvir esta oração. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I252" s="2" t="inlineStr"/>
@@ -11308,7 +11308,7 @@
       </c>
       <c r="D253" s="2" t="inlineStr">
         <is>
-          <t>Dia 252 de 365. João 6:11: Jesus deu graças antes do milagre. #fe #gratidao #louvor #palavradodia</t>
+          <t>Dia 252 de 365. João 6:11: Jesus deu graças antes do milagre. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E253" s="2" t="inlineStr">
@@ -11318,7 +11318,7 @@
       </c>
       <c r="F253" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ Salmos 18:1. Grato pela força. #versiculododia #fe #gratidao #oracao</t>
+          <t>Pausa do meio-dia ☀️ Salmos 18:1. Grato pela força. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G253" s="2" t="inlineStr">
@@ -11328,7 +11328,7 @@
       </c>
       <c r="H253" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: gratidão 🌙 Para fechar o dia com João 6:11. Comente seu pedido. Vamos orar juntos. #oracaodanoite #oracao #fe #gratidao</t>
+          <t>Oração da noite: gratidão 🌙 Para fechar o dia com João 6:11. Comente seu pedido. Vamos orar juntos. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I253" s="2" t="inlineStr"/>
@@ -11351,7 +11351,7 @@
       </c>
       <c r="D254" s="2" t="inlineStr">
         <is>
-          <t>Dia 253 de 365. Salmos 95:2: Cheguemos com ações de graças. #fe #gratidao #louvor #palavradodia</t>
+          <t>Dia 253 de 365. Salmos 95:2: Cheguemos com ações de graças. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E254" s="2" t="inlineStr">
@@ -11361,7 +11361,7 @@
       </c>
       <c r="F254" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ Salmos 118:1. Grato pela misericórdia. #versiculododia #fe #gratidao #oracao</t>
+          <t>Pausa do meio-dia ☀️ Salmos 118:1. Grato pela misericórdia. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G254" s="2" t="inlineStr">
@@ -11371,7 +11371,7 @@
       </c>
       <c r="H254" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: gratidão 🌙 Para fechar o dia com Salmos 95:2. Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #gratidao</t>
+          <t>Oração da noite: gratidão 🌙 Para fechar o dia com Salmos 95:2. Deixe seu pedido de oração nos comentários. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I254" s="2" t="inlineStr"/>
@@ -11394,7 +11394,7 @@
       </c>
       <c r="D255" s="2" t="inlineStr">
         <is>
-          <t>Dia 254 de 365. Lamentações 3:24: A minha porção é o Senhor. #fe #gratidao #louvor #palavradodia</t>
+          <t>Dia 254 de 365. Lamentações 3:24: A minha porção é o Senhor. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E255" s="2" t="inlineStr">
@@ -11404,7 +11404,7 @@
       </c>
       <c r="F255" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ Filipenses 2:14. Gratidão espanta a murmuração. #versiculododia #fe #gratidao #oracao</t>
+          <t>Pausa do meio-dia ☀️ Filipenses 2:14. Gratidão espanta a murmuração. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G255" s="2" t="inlineStr">
@@ -11414,7 +11414,7 @@
       </c>
       <c r="H255" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: gratidão 🌙 Para fechar o dia com Lamentações 3:24. Escreva amém se essa oração é sua também. #oracaodanoite #oracao #fe #gratidao</t>
+          <t>Oração da noite: gratidão 🌙 Para fechar o dia com Lamentações 3:24. Escreva amém se essa oração é sua também. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I255" s="2" t="inlineStr"/>
@@ -11437,7 +11437,7 @@
       </c>
       <c r="D256" s="2" t="inlineStr">
         <is>
-          <t>Dia 255 de 365. Salmos 116:12: Que darei ao Senhor por todos os benefícios? #fe #gratidao #louvor #palavradodia</t>
+          <t>Dia 255 de 365. Salmos 116:12: Que darei ao Senhor por todos os benefícios? #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E256" s="2" t="inlineStr">
@@ -11447,7 +11447,7 @@
       </c>
       <c r="F256" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ Salmos 104:24. Grato pela criação. #versiculododia #fe #gratidao #oracao</t>
+          <t>Pausa do meio-dia ☀️ Salmos 104:24. Grato pela criação. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G256" s="2" t="inlineStr">
@@ -11457,7 +11457,7 @@
       </c>
       <c r="H256" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: gratidão 🌙 Para fechar o dia com Salmos 116:12. Comente o nome de quem você quer colocar nesta oração. #oracaodanoite #oracao #fe #gratidao</t>
+          <t>Oração da noite: gratidão 🌙 Para fechar o dia com Salmos 116:12. Comente o nome de quem você quer colocar nesta oração. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I256" s="2" t="inlineStr"/>
@@ -11480,7 +11480,7 @@
       </c>
       <c r="D257" s="2" t="inlineStr">
         <is>
-          <t>Dia 256 de 365. Atos 16:25: Paulo e Silas cantavam presos. #fe #gratidao #louvor #palavradodia</t>
+          <t>Dia 256 de 365. Atos 16:25: Paulo e Silas cantavam presos. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E257" s="2" t="inlineStr">
@@ -11490,7 +11490,7 @@
       </c>
       <c r="F257" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ Eclesiastes 5:19. Grato pelo trabalho. #versiculododia #fe #gratidao #oracao</t>
+          <t>Pausa do meio-dia ☀️ Eclesiastes 5:19. Grato pelo trabalho. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G257" s="2" t="inlineStr">
@@ -11500,7 +11500,7 @@
       </c>
       <c r="H257" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: gratidão 🌙 Para fechar o dia com Atos 16:25. Conte nos comentários pelo que você quer agradecer hoje. #oracaodanoite #oracao #fe #gratidao</t>
+          <t>Oração da noite: gratidão 🌙 Para fechar o dia com Atos 16:25. Conte nos comentários pelo que você quer agradecer hoje. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I257" s="2" t="inlineStr"/>
@@ -11523,7 +11523,7 @@
       </c>
       <c r="D258" s="2" t="inlineStr">
         <is>
-          <t>Dia 257 de 365. Salmos 103:3-5: Ele perdoa, sara, resgata, coroa, farta. #fe #gratidao #louvor #palavradodia</t>
+          <t>Dia 257 de 365. Salmos 103:3-5: Ele perdoa, sara, resgata, coroa, farta. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E258" s="2" t="inlineStr">
@@ -11533,7 +11533,7 @@
       </c>
       <c r="F258" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ Salmos 66:20. Grato por ser ouvido. #versiculododia #fe #gratidao #oracao</t>
+          <t>Pausa do meio-dia ☀️ Salmos 66:20. Grato por ser ouvido. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G258" s="2" t="inlineStr">
@@ -11543,7 +11543,7 @@
       </c>
       <c r="H258" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: gratidão 🌙 Para fechar o dia com Salmos 103:3-5. Deixe nos comentários o que você quer entregar a Deus esta noite. #oracaodanoite #oracao #fe #gratidao</t>
+          <t>Oração da noite: gratidão 🌙 Para fechar o dia com Salmos 103:3-5. Deixe nos comentários o que você quer entregar a Deus esta noite. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I258" s="2" t="inlineStr"/>
@@ -11566,7 +11566,7 @@
       </c>
       <c r="D259" s="2" t="inlineStr">
         <is>
-          <t>Dia 258 de 365. Salmos 65:11: Coroas o ano com a tua bondade. #fe #gratidao #louvor #palavradodia</t>
+          <t>Dia 258 de 365. Salmos 65:11: Coroas o ano com a tua bondade. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E259" s="2" t="inlineStr">
@@ -11576,7 +11576,7 @@
       </c>
       <c r="F259" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ Isaías 55:7. Grato pelo perdão. #versiculododia #fe #gratidao #oracao</t>
+          <t>Pausa do meio-dia ☀️ Isaías 55:7. Grato pelo perdão. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G259" s="2" t="inlineStr">
@@ -11586,7 +11586,7 @@
       </c>
       <c r="H259" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: gratidão 🌙 Para fechar o dia com Salmos 65:11. Marque alguém que precisa ouvir esta oração. #oracaodanoite #oracao #fe #gratidao</t>
+          <t>Oração da noite: gratidão 🌙 Para fechar o dia com Salmos 65:11. Marque alguém que precisa ouvir esta oração. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I259" s="2" t="inlineStr"/>
@@ -11609,7 +11609,7 @@
       </c>
       <c r="D260" s="2" t="inlineStr">
         <is>
-          <t>Dia 259 de 365. Neemias 8:10: A alegria do Senhor é a vossa força. #fe #gratidao #louvor #palavradodia</t>
+          <t>Dia 259 de 365. Neemias 8:10: A alegria do Senhor é a vossa força. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E260" s="2" t="inlineStr">
@@ -11619,7 +11619,7 @@
       </c>
       <c r="F260" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ Salmos 145:2. Grato todos os dias. #versiculododia #fe #gratidao #oracao</t>
+          <t>Pausa do meio-dia ☀️ Salmos 145:2. Grato todos os dias. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G260" s="2" t="inlineStr">
@@ -11629,7 +11629,7 @@
       </c>
       <c r="H260" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: gratidão 🌙 Para fechar o dia com Neemias 8:10. Comente seu pedido. Vamos orar juntos. #oracaodanoite #oracao #fe #gratidao</t>
+          <t>Oração da noite: gratidão 🌙 Para fechar o dia com Neemias 8:10. Comente seu pedido. Vamos orar juntos. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I260" s="2" t="inlineStr"/>
@@ -11652,7 +11652,7 @@
       </c>
       <c r="D261" s="2" t="inlineStr">
         <is>
-          <t>Dia 260 de 365. Colossenses 3:23: Trabalhe como se fosse para Deus. #fe #proposito #trabalho #palavradodia</t>
+          <t>Dia 260 de 365. Colossenses 3:23: Trabalhe como se fosse para Deus. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E261" s="2" t="inlineStr">
@@ -11662,7 +11662,7 @@
       </c>
       <c r="F261" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ Eclesiastes 2:24. Seu trabalho tem valor? #versiculododia #fe #proposito #oracao</t>
+          <t>Pausa do meio-dia ☀️ Eclesiastes 2:24. Seu trabalho tem valor? #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G261" s="2" t="inlineStr">
@@ -11672,7 +11672,7 @@
       </c>
       <c r="H261" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: propósito e trabalho 🌙 Para fechar o dia com Colossenses 3:23. Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #proposito</t>
+          <t>Oração da noite: propósito e trabalho 🌙 Para fechar o dia com Colossenses 3:23. Deixe seu pedido de oração nos comentários. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I261" s="2" t="inlineStr"/>
@@ -11695,7 +11695,7 @@
       </c>
       <c r="D262" s="2" t="inlineStr">
         <is>
-          <t>Dia 261 de 365. Provérbios 16:3: Entregue ao Senhor as suas obras. #fe #proposito #trabalho #palavradodia</t>
+          <t>Dia 261 de 365. Provérbios 16:3: Entregue ao Senhor as suas obras. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E262" s="2" t="inlineStr">
@@ -11705,7 +11705,7 @@
       </c>
       <c r="F262" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ Efésios 6:7. Trabalhe para Deus. #versiculododia #fe #proposito #oracao</t>
+          <t>Pausa do meio-dia ☀️ Efésios 6:7. Trabalhe para Deus. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G262" s="2" t="inlineStr">
@@ -11715,7 +11715,7 @@
       </c>
       <c r="H262" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: propósito e trabalho 🌙 Para fechar o dia com Provérbios 16:3. Escreva amém se essa oração é sua também. #oracaodanoite #oracao #fe #proposito</t>
+          <t>Oração da noite: propósito e trabalho 🌙 Para fechar o dia com Provérbios 16:3. Escreva amém se essa oração é sua também. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I262" s="2" t="inlineStr"/>
@@ -11738,7 +11738,7 @@
       </c>
       <c r="D263" s="2" t="inlineStr">
         <is>
-          <t>Dia 262 de 365. Efésios 2:10: Você foi feito com propósito. #fe #proposito #trabalho #palavradodia</t>
+          <t>Dia 262 de 365. Efésios 2:10: Você foi feito com propósito. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E263" s="2" t="inlineStr">
@@ -11748,7 +11748,7 @@
       </c>
       <c r="F263" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ Salmos 139:14. Você foi feito com propósito. #versiculododia #fe #proposito #oracao</t>
+          <t>Pausa do meio-dia ☀️ Salmos 139:14. Você foi feito com propósito. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G263" s="2" t="inlineStr">
@@ -11758,7 +11758,7 @@
       </c>
       <c r="H263" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: propósito e trabalho 🌙 Para fechar o dia com Efésios 2:10. Comente o nome de quem você quer colocar nesta oração. #oracaodanoite #oracao #fe #proposito</t>
+          <t>Oração da noite: propósito e trabalho 🌙 Para fechar o dia com Efésios 2:10. Comente o nome de quem você quer colocar nesta oração. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I263" s="2" t="inlineStr"/>
@@ -11781,7 +11781,7 @@
       </c>
       <c r="D264" s="2" t="inlineStr">
         <is>
-          <t>Dia 263 de 365. Jeremias 1:5: Antes de te formar, eu te conheci. #fe #proposito #trabalho #palavradodia</t>
+          <t>Dia 263 de 365. Jeremias 1:5: Antes de te formar, eu te conheci. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E264" s="2" t="inlineStr">
@@ -11791,7 +11791,7 @@
       </c>
       <c r="F264" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ Provérbios 16:1. Planeje com Deus. #versiculododia #fe #proposito #oracao</t>
+          <t>Pausa do meio-dia ☀️ Provérbios 16:1. Planeje com Deus. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G264" s="2" t="inlineStr">
@@ -11801,7 +11801,7 @@
       </c>
       <c r="H264" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: propósito e trabalho 🌙 Para fechar o dia com Jeremias 1:5. Conte nos comentários pelo que você quer agradecer hoje. #oracaodanoite #oracao #fe #proposito</t>
+          <t>Oração da noite: propósito e trabalho 🌙 Para fechar o dia com Jeremias 1:5. Conte nos comentários pelo que você quer agradecer hoje. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I264" s="2" t="inlineStr"/>
@@ -11824,7 +11824,7 @@
       </c>
       <c r="D265" s="2" t="inlineStr">
         <is>
-          <t>Dia 264 de 365. Provérbios 14:23: Em todo trabalho há proveito. #fe #proposito #trabalho #palavradodia</t>
+          <t>Dia 264 de 365. Provérbios 14:23: Em todo trabalho há proveito. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E265" s="2" t="inlineStr">
@@ -11834,7 +11834,7 @@
       </c>
       <c r="F265" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ Jó 8:7. Pequeno começo. #versiculododia #fe #proposito #oracao</t>
+          <t>Pausa do meio-dia ☀️ Jó 8:7. Pequeno começo. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G265" s="2" t="inlineStr">
@@ -11844,7 +11844,7 @@
       </c>
       <c r="H265" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: propósito e trabalho 🌙 Para fechar o dia com Provérbios 14:23. Deixe nos comentários o que você quer entregar a Deus esta noite. #oracaodanoite #oracao #fe #proposito</t>
+          <t>Oração da noite: propósito e trabalho 🌙 Para fechar o dia com Provérbios 14:23. Deixe nos comentários o que você quer entregar a Deus esta noite. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I265" s="2" t="inlineStr"/>
@@ -11867,7 +11867,7 @@
       </c>
       <c r="D266" s="2" t="inlineStr">
         <is>
-          <t>Dia 265 de 365. Eclesiastes 9:10: Faça com todas as suas forças. #fe #proposito #trabalho #palavradodia</t>
+          <t>Dia 265 de 365. Eclesiastes 9:10: Faça com todas as suas forças. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E266" s="2" t="inlineStr">
@@ -11877,7 +11877,7 @@
       </c>
       <c r="F266" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ Provérbios 12:24. Mãos diligentes. #versiculododia #fe #proposito #oracao</t>
+          <t>Pausa do meio-dia ☀️ Provérbios 12:24. Mãos diligentes. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G266" s="2" t="inlineStr">
@@ -11887,7 +11887,7 @@
       </c>
       <c r="H266" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: propósito e trabalho 🌙 Para fechar o dia com Eclesiastes 9:10. Marque alguém que precisa ouvir esta oração. #oracaodanoite #oracao #fe #proposito</t>
+          <t>Oração da noite: propósito e trabalho 🌙 Para fechar o dia com Eclesiastes 9:10. Marque alguém que precisa ouvir esta oração. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I266" s="2" t="inlineStr"/>
@@ -11910,7 +11910,7 @@
       </c>
       <c r="D267" s="2" t="inlineStr">
         <is>
-          <t>Dia 266 de 365. Provérbios 22:29: O diligente servirá diante de reis. #fe #proposito #trabalho #palavradodia</t>
+          <t>Dia 266 de 365. Provérbios 22:29: O diligente servirá diante de reis. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E267" s="2" t="inlineStr">
@@ -11920,7 +11920,7 @@
       </c>
       <c r="F267" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ Êxodo 20:9. Trabalho tem medida. #versiculododia #fe #proposito #oracao</t>
+          <t>Pausa do meio-dia ☀️ Êxodo 20:9. Trabalho tem medida. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G267" s="2" t="inlineStr">
@@ -11930,7 +11930,7 @@
       </c>
       <c r="H267" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: propósito e trabalho 🌙 Para fechar o dia com Provérbios 22:29. Comente seu pedido. Vamos orar juntos. #oracaodanoite #oracao #fe #proposito</t>
+          <t>Oração da noite: propósito e trabalho 🌙 Para fechar o dia com Provérbios 22:29. Comente seu pedido. Vamos orar juntos. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I267" s="2" t="inlineStr"/>
@@ -11953,7 +11953,7 @@
       </c>
       <c r="D268" s="2" t="inlineStr">
         <is>
-          <t>Dia 267 de 365. Filipenses 1:6: Deus termina o que começa. #fe #proposito #trabalho #palavradodia</t>
+          <t>Dia 267 de 365. Filipenses 1:6: Deus termina o que começa. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E268" s="2" t="inlineStr">
@@ -11963,7 +11963,7 @@
       </c>
       <c r="F268" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ Lucas 16:10. Seja fiel no pouco. #versiculododia #fe #proposito #oracao</t>
+          <t>Pausa do meio-dia ☀️ Lucas 16:10. Seja fiel no pouco. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G268" s="2" t="inlineStr">
@@ -11973,7 +11973,7 @@
       </c>
       <c r="H268" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: propósito e trabalho 🌙 Para fechar o dia com Filipenses 1:6. Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #proposito</t>
+          <t>Oração da noite: propósito e trabalho 🌙 Para fechar o dia com Filipenses 1:6. Deixe seu pedido de oração nos comentários. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I268" s="2" t="inlineStr"/>
@@ -11996,7 +11996,7 @@
       </c>
       <c r="D269" s="2" t="inlineStr">
         <is>
-          <t>Dia 268 de 365. Gálatas 6:9: Não se canse de fazer o bem. #fe #proposito #trabalho #palavradodia</t>
+          <t>Dia 268 de 365. Gálatas 6:9: Não se canse de fazer o bem. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E269" s="2" t="inlineStr">
@@ -12006,7 +12006,7 @@
       </c>
       <c r="F269" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ Romanos 12:11. Dons para servir. #versiculododia #fe #proposito #oracao</t>
+          <t>Pausa do meio-dia ☀️ Romanos 12:11. Dons para servir. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G269" s="2" t="inlineStr">
@@ -12016,7 +12016,7 @@
       </c>
       <c r="H269" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: propósito e trabalho 🌙 Para fechar o dia com Gálatas 6:9. Escreva amém se essa oração é sua também. #oracaodanoite #oracao #fe #proposito</t>
+          <t>Oração da noite: propósito e trabalho 🌙 Para fechar o dia com Gálatas 6:9. Escreva amém se essa oração é sua também. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I269" s="2" t="inlineStr"/>
@@ -12039,7 +12039,7 @@
       </c>
       <c r="D270" s="2" t="inlineStr">
         <is>
-          <t>Dia 269 de 365. Salmos 90:17: Confirma a obra das nossas mãos. #fe #proposito #trabalho #palavradodia</t>
+          <t>Dia 269 de 365. Salmos 90:17: Confirma a obra das nossas mãos. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E270" s="2" t="inlineStr">
@@ -12049,7 +12049,7 @@
       </c>
       <c r="F270" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ Provérbios 10:22. A bênção dEle no seu trabalho. #versiculododia #fe #proposito #oracao</t>
+          <t>Pausa do meio-dia ☀️ Provérbios 10:22. A bênção dEle no seu trabalho. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G270" s="2" t="inlineStr">
@@ -12059,7 +12059,7 @@
       </c>
       <c r="H270" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: propósito e trabalho 🌙 Para fechar o dia com Salmos 90:17. Comente o nome de quem você quer colocar nesta oração. #oracaodanoite #oracao #fe #proposito</t>
+          <t>Oração da noite: propósito e trabalho 🌙 Para fechar o dia com Salmos 90:17. Comente o nome de quem você quer colocar nesta oração. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I270" s="2" t="inlineStr"/>
@@ -12082,7 +12082,7 @@
       </c>
       <c r="D271" s="2" t="inlineStr">
         <is>
-          <t>Dia 270 de 365. Romanos 12:6-8: Cada um tem um dom diferente. #fe #proposito #trabalho #palavradodia</t>
+          <t>Dia 270 de 365. Romanos 12:6-8: Cada um tem um dom diferente. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E271" s="2" t="inlineStr">
@@ -12092,7 +12092,7 @@
       </c>
       <c r="F271" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ Salmos 57:2. Ele cumpre o propósito por você. #versiculododia #fe #proposito #oracao</t>
+          <t>Pausa do meio-dia ☀️ Salmos 57:2. Ele cumpre o propósito por você. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G271" s="2" t="inlineStr">
@@ -12102,7 +12102,7 @@
       </c>
       <c r="H271" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: propósito e trabalho 🌙 Para fechar o dia com Romanos 12:6-8. Conte nos comentários pelo que você quer agradecer hoje. #oracaodanoite #oracao #fe #proposito</t>
+          <t>Oração da noite: propósito e trabalho 🌙 Para fechar o dia com Romanos 12:6-8. Conte nos comentários pelo que você quer agradecer hoje. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I271" s="2" t="inlineStr"/>
@@ -12125,7 +12125,7 @@
       </c>
       <c r="D272" s="2" t="inlineStr">
         <is>
-          <t>Dia 271 de 365. 1 Pedro 4:10: Seu dom é para servir. #fe #proposito #trabalho #palavradodia</t>
+          <t>Dia 271 de 365. 1 Pedro 4:10: Seu dom é para servir. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E272" s="2" t="inlineStr">
@@ -12135,7 +12135,7 @@
       </c>
       <c r="F272" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ Êxodo 31:3. Deus dá habilidade. #versiculododia #fe #proposito #oracao</t>
+          <t>Pausa do meio-dia ☀️ Êxodo 31:3. Deus dá habilidade. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G272" s="2" t="inlineStr">
@@ -12145,7 +12145,7 @@
       </c>
       <c r="H272" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: propósito e trabalho 🌙 Para fechar o dia com 1 Pedro 4:10. Deixe nos comentários o que você quer entregar a Deus esta noite. #oracaodanoite #oracao #fe #proposito</t>
+          <t>Oração da noite: propósito e trabalho 🌙 Para fechar o dia com 1 Pedro 4:10. Deixe nos comentários o que você quer entregar a Deus esta noite. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I272" s="2" t="inlineStr"/>
@@ -12168,7 +12168,7 @@
       </c>
       <c r="D273" s="2" t="inlineStr">
         <is>
-          <t>Dia 272 de 365. Provérbios 6:6-8: Olhe para a formiga. #fe #proposito #trabalho #palavradodia</t>
+          <t>Dia 272 de 365. Provérbios 6:6-8: Olhe para a formiga. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E273" s="2" t="inlineStr">
@@ -12178,7 +12178,7 @@
       </c>
       <c r="F273" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ Salmos 100:2. Sirva com alegria. #versiculododia #fe #proposito #oracao</t>
+          <t>Pausa do meio-dia ☀️ Salmos 100:2. Sirva com alegria. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G273" s="2" t="inlineStr">
@@ -12188,7 +12188,7 @@
       </c>
       <c r="H273" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: propósito e trabalho 🌙 Para fechar o dia com Provérbios 6:6-8. Marque alguém que precisa ouvir esta oração. #oracaodanoite #oracao #fe #proposito</t>
+          <t>Oração da noite: propósito e trabalho 🌙 Para fechar o dia com Provérbios 6:6-8. Marque alguém que precisa ouvir esta oração. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I273" s="2" t="inlineStr"/>
@@ -12211,7 +12211,7 @@
       </c>
       <c r="D274" s="2" t="inlineStr">
         <is>
-          <t>Dia 273 de 365. Mateus 25:21: Fiel no pouco. #fe #proposito #trabalho #palavradodia</t>
+          <t>Dia 273 de 365. Mateus 25:21: Fiel no pouco. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E274" s="2" t="inlineStr">
@@ -12221,7 +12221,7 @@
       </c>
       <c r="F274" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ Provérbios 24:27. Prepare-se. #versiculododia #fe #proposito #oracao</t>
+          <t>Pausa do meio-dia ☀️ Provérbios 24:27. Prepare-se. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G274" s="2" t="inlineStr">
@@ -12231,7 +12231,7 @@
       </c>
       <c r="H274" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: propósito e trabalho 🌙 Para fechar o dia com Mateus 25:21. Comente seu pedido. Vamos orar juntos. #oracaodanoite #oracao #fe #proposito</t>
+          <t>Oração da noite: propósito e trabalho 🌙 Para fechar o dia com Mateus 25:21. Comente seu pedido. Vamos orar juntos. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I274" s="2" t="inlineStr"/>
@@ -12254,7 +12254,7 @@
       </c>
       <c r="D275" s="2" t="inlineStr">
         <is>
-          <t>Dia 274 de 365. Neemias 2:20: O Deus dos céus nos fará prosperar. #fe #proposito #trabalho #palavradodia</t>
+          <t>Dia 274 de 365. Neemias 2:20: O Deus dos céus nos fará prosperar. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E275" s="2" t="inlineStr">
@@ -12264,7 +12264,7 @@
       </c>
       <c r="F275" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ Provérbios 19:2. Sem pressa errada. #versiculododia #fe #proposito #oracao</t>
+          <t>Pausa do meio-dia ☀️ Provérbios 19:2. Sem pressa errada. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G275" s="2" t="inlineStr">
@@ -12274,7 +12274,7 @@
       </c>
       <c r="H275" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: propósito e trabalho 🌙 Para fechar o dia com Neemias 2:20. Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #proposito</t>
+          <t>Oração da noite: propósito e trabalho 🌙 Para fechar o dia com Neemias 2:20. Deixe seu pedido de oração nos comentários. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I275" s="2" t="inlineStr"/>
@@ -12297,7 +12297,7 @@
       </c>
       <c r="D276" s="2" t="inlineStr">
         <is>
-          <t>Dia 275 de 365. Provérbios 13:4: O desejo do preguiçoso não se realiza. #fe #proposito #trabalho #palavradodia</t>
+          <t>Dia 275 de 365. Provérbios 13:4: O desejo do preguiçoso não se realiza. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E276" s="2" t="inlineStr">
@@ -12307,7 +12307,7 @@
       </c>
       <c r="F276" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ Gálatas 6:10. Faça o bem. #versiculododia #fe #proposito #oracao</t>
+          <t>Pausa do meio-dia ☀️ Gálatas 6:10. Faça o bem. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G276" s="2" t="inlineStr">
@@ -12317,7 +12317,7 @@
       </c>
       <c r="H276" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: propósito e trabalho 🌙 Para fechar o dia com Provérbios 13:4. Escreva amém se essa oração é sua também. #oracaodanoite #oracao #fe #proposito</t>
+          <t>Oração da noite: propósito e trabalho 🌙 Para fechar o dia com Provérbios 13:4. Escreva amém se essa oração é sua também. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I276" s="2" t="inlineStr"/>
@@ -12340,7 +12340,7 @@
       </c>
       <c r="D277" s="2" t="inlineStr">
         <is>
-          <t>Dia 276 de 365. Mateus 5:14-16: Você é a luz do mundo. #fe #proposito #trabalho #palavradodia</t>
+          <t>Dia 276 de 365. Mateus 5:14-16: Você é a luz do mundo. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E277" s="2" t="inlineStr">
@@ -12350,7 +12350,7 @@
       </c>
       <c r="F277" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ Isaías 46:10. Os planos dEle. #versiculododia #fe #proposito #oracao</t>
+          <t>Pausa do meio-dia ☀️ Isaías 46:10. Os planos dEle. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G277" s="2" t="inlineStr">
@@ -12360,7 +12360,7 @@
       </c>
       <c r="H277" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: propósito e trabalho 🌙 Para fechar o dia com Mateus 5:14-16. Comente o nome de quem você quer colocar nesta oração. #oracaodanoite #oracao #fe #proposito</t>
+          <t>Oração da noite: propósito e trabalho 🌙 Para fechar o dia com Mateus 5:14-16. Comente o nome de quem você quer colocar nesta oração. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I277" s="2" t="inlineStr"/>
@@ -12383,7 +12383,7 @@
       </c>
       <c r="D278" s="2" t="inlineStr">
         <is>
-          <t>Dia 277 de 365. 1 Coríntios 15:58: Seu trabalho no Senhor não é em vão. #fe #proposito #trabalho #palavradodia</t>
+          <t>Dia 277 de 365. 1 Coríntios 15:58: Seu trabalho no Senhor não é em vão. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E278" s="2" t="inlineStr">
@@ -12393,7 +12393,7 @@
       </c>
       <c r="F278" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ Mateus 5:13. Sal da terra. #versiculododia #fe #proposito #oracao</t>
+          <t>Pausa do meio-dia ☀️ Mateus 5:13. Sal da terra. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G278" s="2" t="inlineStr">
@@ -12403,7 +12403,7 @@
       </c>
       <c r="H278" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: propósito e trabalho 🌙 Para fechar o dia com 1 Coríntios 15:58. Conte nos comentários pelo que você quer agradecer hoje. #oracaodanoite #oracao #fe #proposito</t>
+          <t>Oração da noite: propósito e trabalho 🌙 Para fechar o dia com 1 Coríntios 15:58. Conte nos comentários pelo que você quer agradecer hoje. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I278" s="2" t="inlineStr"/>
@@ -12426,7 +12426,7 @@
       </c>
       <c r="D279" s="2" t="inlineStr">
         <is>
-          <t>Dia 278 de 365. Deuteronômio 8:18: É Ele quem dá força para conquistar. #fe #proposito #trabalho #palavradodia</t>
+          <t>Dia 278 de 365. Deuteronômio 8:18: É Ele quem dá força para conquistar. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E279" s="2" t="inlineStr">
@@ -12436,7 +12436,7 @@
       </c>
       <c r="F279" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ Provérbios 11:1. Honestidade. #versiculododia #fe #proposito #oracao</t>
+          <t>Pausa do meio-dia ☀️ Provérbios 11:1. Honestidade. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G279" s="2" t="inlineStr">
@@ -12446,7 +12446,7 @@
       </c>
       <c r="H279" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: propósito e trabalho 🌙 Para fechar o dia com Deuteronômio 8:18. Deixe nos comentários o que você quer entregar a Deus esta noite. #oracaodanoite #oracao #fe #proposito</t>
+          <t>Oração da noite: propósito e trabalho 🌙 Para fechar o dia com Deuteronômio 8:18. Deixe nos comentários o que você quer entregar a Deus esta noite. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I279" s="2" t="inlineStr"/>
@@ -12469,7 +12469,7 @@
       </c>
       <c r="D280" s="2" t="inlineStr">
         <is>
-          <t>Dia 279 de 365. Provérbios 10:4: A mão diligente enriquece. #fe #proposito #trabalho #palavradodia</t>
+          <t>Dia 279 de 365. Provérbios 10:4: A mão diligente enriquece. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E280" s="2" t="inlineStr">
@@ -12479,7 +12479,7 @@
       </c>
       <c r="F280" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ Mateus 14:19. Ele multiplica. #versiculododia #fe #proposito #oracao</t>
+          <t>Pausa do meio-dia ☀️ Mateus 14:19. Ele multiplica. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G280" s="2" t="inlineStr">
@@ -12489,7 +12489,7 @@
       </c>
       <c r="H280" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: propósito e trabalho 🌙 Para fechar o dia com Provérbios 10:4. Marque alguém que precisa ouvir esta oração. #oracaodanoite #oracao #fe #proposito</t>
+          <t>Oração da noite: propósito e trabalho 🌙 Para fechar o dia com Provérbios 10:4. Marque alguém que precisa ouvir esta oração. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I280" s="2" t="inlineStr"/>
@@ -12512,7 +12512,7 @@
       </c>
       <c r="D281" s="2" t="inlineStr">
         <is>
-          <t>Dia 280 de 365. Eclesiastes 3:1: Tudo tem o seu tempo. #fe #proposito #trabalho #palavradodia</t>
+          <t>Dia 280 de 365. Eclesiastes 3:1: Tudo tem o seu tempo. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E281" s="2" t="inlineStr">
@@ -12522,7 +12522,7 @@
       </c>
       <c r="F281" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ Tiago 2:17. Trabalho e fé. #versiculododia #fe #proposito #oracao</t>
+          <t>Pausa do meio-dia ☀️ Tiago 2:17. Trabalho e fé. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G281" s="2" t="inlineStr">
@@ -12532,7 +12532,7 @@
       </c>
       <c r="H281" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: propósito e trabalho 🌙 Para fechar o dia com Eclesiastes 3:1. Comente seu pedido. Vamos orar juntos. #oracaodanoite #oracao #fe #proposito</t>
+          <t>Oração da noite: propósito e trabalho 🌙 Para fechar o dia com Eclesiastes 3:1. Comente seu pedido. Vamos orar juntos. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I281" s="2" t="inlineStr"/>
@@ -12555,7 +12555,7 @@
       </c>
       <c r="D282" s="2" t="inlineStr">
         <is>
-          <t>Dia 281 de 365. 2 Tessalonicenses 3:10-13: Não vos canseis de fazer o bem. #fe #proposito #trabalho #palavradodia</t>
+          <t>Dia 281 de 365. 2 Tessalonicenses 3:10-13: Não vos canseis de fazer o bem. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E282" s="2" t="inlineStr">
@@ -12565,7 +12565,7 @@
       </c>
       <c r="F282" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ Jeremias 17:8. Fruto no tempo certo. #versiculododia #fe #proposito #oracao</t>
+          <t>Pausa do meio-dia ☀️ Jeremias 17:8. Fruto no tempo certo. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G282" s="2" t="inlineStr">
@@ -12575,7 +12575,7 @@
       </c>
       <c r="H282" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: propósito e trabalho 🌙 Para fechar o dia com 2 Tessalonicenses 3:10-13. Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #proposito</t>
+          <t>Oração da noite: propósito e trabalho 🌙 Para fechar o dia com 2 Tessalonicenses 3:10-13. Deixe seu pedido de oração nos comentários. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I282" s="2" t="inlineStr"/>
@@ -12598,7 +12598,7 @@
       </c>
       <c r="D283" s="2" t="inlineStr">
         <is>
-          <t>Dia 282 de 365. Isaías 64:8: Somos o barro, Tu és o oleiro. #fe #proposito #trabalho #palavradodia</t>
+          <t>Dia 282 de 365. Isaías 64:8: Somos o barro, Tu és o oleiro. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E283" s="2" t="inlineStr">
@@ -12608,7 +12608,7 @@
       </c>
       <c r="F283" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ Isaías 6:8. Chamado para hoje. #versiculododia #fe #proposito #oracao</t>
+          <t>Pausa do meio-dia ☀️ Isaías 6:8. Chamado para hoje. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G283" s="2" t="inlineStr">
@@ -12618,7 +12618,7 @@
       </c>
       <c r="H283" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: propósito e trabalho 🌙 Para fechar o dia com Isaías 64:8. Escreva amém se essa oração é sua também. #oracaodanoite #oracao #fe #proposito</t>
+          <t>Oração da noite: propósito e trabalho 🌙 Para fechar o dia com Isaías 64:8. Escreva amém se essa oração é sua também. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I283" s="2" t="inlineStr"/>
@@ -12641,7 +12641,7 @@
       </c>
       <c r="D284" s="2" t="inlineStr">
         <is>
-          <t>Dia 283 de 365. Atos 20:35: Mais bem-aventurado é dar. #fe #proposito #trabalho #palavradodia</t>
+          <t>Dia 283 de 365. Atos 20:35: Mais bem-aventurado é dar. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E284" s="2" t="inlineStr">
@@ -12651,7 +12651,7 @@
       </c>
       <c r="F284" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ 1 Coríntios 4:2. Mordomo fiel. #versiculododia #fe #proposito #oracao</t>
+          <t>Pausa do meio-dia ☀️ 1 Coríntios 4:2. Mordomo fiel. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G284" s="2" t="inlineStr">
@@ -12661,7 +12661,7 @@
       </c>
       <c r="H284" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: propósito e trabalho 🌙 Para fechar o dia com Atos 20:35. Comente o nome de quem você quer colocar nesta oração. #oracaodanoite #oracao #fe #proposito</t>
+          <t>Oração da noite: propósito e trabalho 🌙 Para fechar o dia com Atos 20:35. Comente o nome de quem você quer colocar nesta oração. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I284" s="2" t="inlineStr"/>
@@ -12684,7 +12684,7 @@
       </c>
       <c r="D285" s="2" t="inlineStr">
         <is>
-          <t>Dia 284 de 365. Provérbios 16:9: Você planeja, Deus dirige. #fe #proposito #trabalho #palavradodia</t>
+          <t>Dia 284 de 365. Provérbios 16:9: Você planeja, Deus dirige. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E285" s="2" t="inlineStr">
@@ -12694,7 +12694,7 @@
       </c>
       <c r="F285" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ Provérbios 20:24. Ele dirige os passos. #versiculododia #fe #proposito #oracao</t>
+          <t>Pausa do meio-dia ☀️ Provérbios 20:24. Ele dirige os passos. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G285" s="2" t="inlineStr">
@@ -12704,7 +12704,7 @@
       </c>
       <c r="H285" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: propósito e trabalho 🌙 Para fechar o dia com Provérbios 16:9. Conte nos comentários pelo que você quer agradecer hoje. #oracaodanoite #oracao #fe #proposito</t>
+          <t>Oração da noite: propósito e trabalho 🌙 Para fechar o dia com Provérbios 16:9. Conte nos comentários pelo que você quer agradecer hoje. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I285" s="2" t="inlineStr"/>
@@ -12727,7 +12727,7 @@
       </c>
       <c r="D286" s="2" t="inlineStr">
         <is>
-          <t>Dia 285 de 365. Habacuque 2:2-3: Escreva a visão. #fe #proposito #trabalho #palavradodia</t>
+          <t>Dia 285 de 365. Habacuque 2:2-3: Escreva a visão. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E286" s="2" t="inlineStr">
@@ -12737,7 +12737,7 @@
       </c>
       <c r="F286" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ Provérbios 22:1. O bom nome. #versiculododia #fe #proposito #oracao</t>
+          <t>Pausa do meio-dia ☀️ Provérbios 22:1. O bom nome. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G286" s="2" t="inlineStr">
@@ -12747,7 +12747,7 @@
       </c>
       <c r="H286" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: propósito e trabalho 🌙 Para fechar o dia com Habacuque 2:2-3. Deixe nos comentários o que você quer entregar a Deus esta noite. #oracaodanoite #oracao #fe #proposito</t>
+          <t>Oração da noite: propósito e trabalho 🌙 Para fechar o dia com Habacuque 2:2-3. Deixe nos comentários o que você quer entregar a Deus esta noite. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I286" s="2" t="inlineStr"/>
@@ -12770,7 +12770,7 @@
       </c>
       <c r="D287" s="2" t="inlineStr">
         <is>
-          <t>Dia 286 de 365. Gênesis 39:2-3: O Senhor estava com José. #fe #proposito #trabalho #palavradodia</t>
+          <t>Dia 286 de 365. Gênesis 39:2-3: O Senhor estava com José. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E287" s="2" t="inlineStr">
@@ -12780,7 +12780,7 @@
       </c>
       <c r="F287" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ Provérbios 20:13. Sem preguiça. #versiculododia #fe #proposito #oracao</t>
+          <t>Pausa do meio-dia ☀️ Provérbios 20:13. Sem preguiça. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G287" s="2" t="inlineStr">
@@ -12790,7 +12790,7 @@
       </c>
       <c r="H287" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: propósito e trabalho 🌙 Para fechar o dia com Gênesis 39:2-3. Marque alguém que precisa ouvir esta oração. #oracaodanoite #oracao #fe #proposito</t>
+          <t>Oração da noite: propósito e trabalho 🌙 Para fechar o dia com Gênesis 39:2-3. Marque alguém que precisa ouvir esta oração. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I287" s="2" t="inlineStr"/>
@@ -12813,7 +12813,7 @@
       </c>
       <c r="D288" s="2" t="inlineStr">
         <is>
-          <t>Dia 287 de 365. 1 Coríntios 10:31: Para a glória de Deus. #fe #proposito #trabalho #palavradodia</t>
+          <t>Dia 287 de 365. 1 Coríntios 10:31: Para a glória de Deus. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E288" s="2" t="inlineStr">
@@ -12823,7 +12823,7 @@
       </c>
       <c r="F288" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ 2 Coríntios 3:5. Ele te capacita. #versiculododia #fe #proposito #oracao</t>
+          <t>Pausa do meio-dia ☀️ 2 Coríntios 3:5. Ele te capacita. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G288" s="2" t="inlineStr">
@@ -12833,7 +12833,7 @@
       </c>
       <c r="H288" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: propósito e trabalho 🌙 Para fechar o dia com 1 Coríntios 10:31. Comente seu pedido. Vamos orar juntos. #oracaodanoite #oracao #fe #proposito</t>
+          <t>Oração da noite: propósito e trabalho 🌙 Para fechar o dia com 1 Coríntios 10:31. Comente seu pedido. Vamos orar juntos. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I288" s="2" t="inlineStr"/>
@@ -12856,7 +12856,7 @@
       </c>
       <c r="D289" s="2" t="inlineStr">
         <is>
-          <t>Dia 288 de 365. Salmos 37:5: Entrega o teu caminho. #fe #proposito #trabalho #palavradodia</t>
+          <t>Dia 288 de 365. Salmos 37:5: Entrega o teu caminho. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E289" s="2" t="inlineStr">
@@ -12866,7 +12866,7 @@
       </c>
       <c r="F289" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ Filipenses 2:15. Luz no trabalho. #versiculododia #fe #proposito #oracao</t>
+          <t>Pausa do meio-dia ☀️ Filipenses 2:15. Luz no trabalho. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G289" s="2" t="inlineStr">
@@ -12876,7 +12876,7 @@
       </c>
       <c r="H289" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: propósito e trabalho 🌙 Para fechar o dia com Salmos 37:5. Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #proposito</t>
+          <t>Oração da noite: propósito e trabalho 🌙 Para fechar o dia com Salmos 37:5. Deixe seu pedido de oração nos comentários. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I289" s="2" t="inlineStr"/>
@@ -12899,7 +12899,7 @@
       </c>
       <c r="D290" s="2" t="inlineStr">
         <is>
-          <t>Dia 289 de 365. Zacarias 4:10: Não despreze os pequenos começos. #fe #proposito #trabalho #palavradodia</t>
+          <t>Dia 289 de 365. Zacarias 4:10: Não despreze os pequenos começos. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E290" s="2" t="inlineStr">
@@ -12909,7 +12909,7 @@
       </c>
       <c r="F290" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ Ageu 2:4. Coragem para começar. #versiculododia #fe #proposito #oracao</t>
+          <t>Pausa do meio-dia ☀️ Ageu 2:4. Coragem para começar. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G290" s="2" t="inlineStr">
@@ -12919,7 +12919,7 @@
       </c>
       <c r="H290" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: propósito e trabalho 🌙 Para fechar o dia com Zacarias 4:10. Escreva amém se essa oração é sua também. #oracaodanoite #oracao #fe #proposito</t>
+          <t>Oração da noite: propósito e trabalho 🌙 Para fechar o dia com Zacarias 4:10. Escreva amém se essa oração é sua também. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I290" s="2" t="inlineStr"/>
@@ -12942,7 +12942,7 @@
       </c>
       <c r="D291" s="2" t="inlineStr">
         <is>
-          <t>Dia 290 de 365. Mateus 6:33: Busque primeiro. #fe #proposito #trabalho #palavradodia</t>
+          <t>Dia 290 de 365. Mateus 6:33: Busque primeiro. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E291" s="2" t="inlineStr">
@@ -12952,7 +12952,7 @@
       </c>
       <c r="F291" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ Salmos 138:8. Ele completa. #versiculododia #fe #proposito #oracao</t>
+          <t>Pausa do meio-dia ☀️ Salmos 138:8. Ele completa. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G291" s="2" t="inlineStr">
@@ -12962,7 +12962,7 @@
       </c>
       <c r="H291" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: propósito e trabalho 🌙 Para fechar o dia com Mateus 6:33. Comente o nome de quem você quer colocar nesta oração. #oracaodanoite #oracao #fe #proposito</t>
+          <t>Oração da noite: propósito e trabalho 🌙 Para fechar o dia com Mateus 6:33. Comente o nome de quem você quer colocar nesta oração. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I291" s="2" t="inlineStr"/>
@@ -12985,7 +12985,7 @@
       </c>
       <c r="D292" s="2" t="inlineStr">
         <is>
-          <t>Dia 291 de 365. Tiago 1:5: Precisa decidir algo e não sabe o quê? #fe #sabedoria #decisoes #palavradodia</t>
+          <t>Dia 291 de 365. Tiago 1:5: Precisa decidir algo e não sabe o quê? #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E292" s="2" t="inlineStr">
@@ -12995,7 +12995,7 @@
       </c>
       <c r="F292" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ Provérbios 3:7. Indeciso hoje? #versiculododia #fe #sabedoria #oracao</t>
+          <t>Pausa do meio-dia ☀️ Provérbios 3:7. Indeciso hoje? #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G292" s="2" t="inlineStr">
@@ -13005,7 +13005,7 @@
       </c>
       <c r="H292" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: sabedoria e decisões 🌙 Para fechar o dia com Tiago 1:5. Conte nos comentários pelo que você quer agradecer hoje. #oracaodanoite #oracao #fe #sabedoria</t>
+          <t>Oração da noite: sabedoria e decisões 🌙 Para fechar o dia com Tiago 1:5. Conte nos comentários pelo que você quer agradecer hoje. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I292" s="2" t="inlineStr"/>
@@ -13028,7 +13028,7 @@
       </c>
       <c r="D293" s="2" t="inlineStr">
         <is>
-          <t>Dia 292 de 365. Provérbios 3:5-6: Não se apoie só no seu entendimento. #fe #sabedoria #decisoes #palavradodia</t>
+          <t>Dia 292 de 365. Provérbios 3:5-6: Não se apoie só no seu entendimento. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E293" s="2" t="inlineStr">
@@ -13038,7 +13038,7 @@
       </c>
       <c r="F293" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ Provérbios 2:3. Peça sabedoria. #versiculododia #fe #sabedoria #oracao</t>
+          <t>Pausa do meio-dia ☀️ Provérbios 2:3. Peça sabedoria. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G293" s="2" t="inlineStr">
@@ -13048,7 +13048,7 @@
       </c>
       <c r="H293" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: sabedoria e decisões 🌙 Para fechar o dia com Provérbios 3:5-6. Deixe nos comentários o que você quer entregar a Deus esta noite. #oracaodanoite #oracao #fe #sabedoria</t>
+          <t>Oração da noite: sabedoria e decisões 🌙 Para fechar o dia com Provérbios 3:5-6. Deixe nos comentários o que você quer entregar a Deus esta noite. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I293" s="2" t="inlineStr"/>
@@ -13071,7 +13071,7 @@
       </c>
       <c r="D294" s="2" t="inlineStr">
         <is>
-          <t>Dia 293 de 365. Salmos 119:105: Uma lâmpada para os pés. #fe #sabedoria #decisoes #palavradodia</t>
+          <t>Dia 293 de 365. Salmos 119:105: Uma lâmpada para os pés. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E294" s="2" t="inlineStr">
@@ -13081,7 +13081,7 @@
       </c>
       <c r="F294" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ Provérbios 29:20. Pense antes de falar. #versiculododia #fe #sabedoria #oracao</t>
+          <t>Pausa do meio-dia ☀️ Provérbios 29:20. Pense antes de falar. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G294" s="2" t="inlineStr">
@@ -13091,7 +13091,7 @@
       </c>
       <c r="H294" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: sabedoria e decisões 🌙 Para fechar o dia com Salmos 119:105. Marque alguém que precisa ouvir esta oração. #oracaodanoite #oracao #fe #sabedoria</t>
+          <t>Oração da noite: sabedoria e decisões 🌙 Para fechar o dia com Salmos 119:105. Marque alguém que precisa ouvir esta oração. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I294" s="2" t="inlineStr"/>
@@ -13114,7 +13114,7 @@
       </c>
       <c r="D295" s="2" t="inlineStr">
         <is>
-          <t>Dia 294 de 365. Provérbios 1:7: Onde a sabedoria começa. #fe #sabedoria #decisoes #palavradodia</t>
+          <t>Dia 294 de 365. Provérbios 1:7: Onde a sabedoria começa. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E295" s="2" t="inlineStr">
@@ -13124,7 +13124,7 @@
       </c>
       <c r="F295" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ Salmos 143:10. O caminho certo. #versiculododia #fe #sabedoria #oracao</t>
+          <t>Pausa do meio-dia ☀️ Salmos 143:10. O caminho certo. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G295" s="2" t="inlineStr">
@@ -13134,7 +13134,7 @@
       </c>
       <c r="H295" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: sabedoria e decisões 🌙 Para fechar o dia com Provérbios 1:7. Comente seu pedido. Vamos orar juntos. #oracaodanoite #oracao #fe #sabedoria</t>
+          <t>Oração da noite: sabedoria e decisões 🌙 Para fechar o dia com Provérbios 1:7. Comente seu pedido. Vamos orar juntos. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I295" s="2" t="inlineStr"/>
@@ -13157,7 +13157,7 @@
       </c>
       <c r="D296" s="2" t="inlineStr">
         <is>
-          <t>Dia 295 de 365. Provérbios 11:14: Na multidão de conselheiros há segurança. #fe #sabedoria #decisoes #palavradodia</t>
+          <t>Dia 295 de 365. Provérbios 11:14: Na multidão de conselheiros há segurança. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E296" s="2" t="inlineStr">
@@ -13167,7 +13167,7 @@
       </c>
       <c r="F296" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ Provérbios 19:20. Ouça conselho. #versiculododia #fe #sabedoria #oracao</t>
+          <t>Pausa do meio-dia ☀️ Provérbios 19:20. Ouça conselho. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G296" s="2" t="inlineStr">
@@ -13177,7 +13177,7 @@
       </c>
       <c r="H296" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: sabedoria e decisões 🌙 Para fechar o dia com Provérbios 11:14. Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #sabedoria</t>
+          <t>Oração da noite: sabedoria e decisões 🌙 Para fechar o dia com Provérbios 11:14. Deixe seu pedido de oração nos comentários. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I296" s="2" t="inlineStr"/>
@@ -13200,7 +13200,7 @@
       </c>
       <c r="D297" s="2" t="inlineStr">
         <is>
-          <t>Dia 296 de 365. Salmos 32:8: Eu te instruirei. #fe #sabedoria #decisoes #palavradodia</t>
+          <t>Dia 296 de 365. Salmos 32:8: Eu te instruirei. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E297" s="2" t="inlineStr">
@@ -13210,7 +13210,7 @@
       </c>
       <c r="F297" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ Provérbios 3:13. Sabedoria vale ouro. #versiculododia #fe #sabedoria #oracao</t>
+          <t>Pausa do meio-dia ☀️ Provérbios 3:13. Sabedoria vale ouro. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G297" s="2" t="inlineStr">
@@ -13220,7 +13220,7 @@
       </c>
       <c r="H297" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: sabedoria e decisões 🌙 Para fechar o dia com Salmos 32:8. Escreva amém se essa oração é sua também. #oracaodanoite #oracao #fe #sabedoria</t>
+          <t>Oração da noite: sabedoria e decisões 🌙 Para fechar o dia com Salmos 32:8. Escreva amém se essa oração é sua também. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I297" s="2" t="inlineStr"/>
@@ -13243,7 +13243,7 @@
       </c>
       <c r="D298" s="2" t="inlineStr">
         <is>
-          <t>Dia 297 de 365. Provérbios 4:23: Guarde o coração. #fe #sabedoria #decisoes #palavradodia</t>
+          <t>Dia 297 de 365. Provérbios 4:23: Guarde o coração. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E298" s="2" t="inlineStr">
@@ -13253,7 +13253,7 @@
       </c>
       <c r="F298" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ Eclesiastes 7:9. Ira atrapalha decisões. #versiculododia #fe #sabedoria #oracao</t>
+          <t>Pausa do meio-dia ☀️ Eclesiastes 7:9. Ira atrapalha decisões. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G298" s="2" t="inlineStr">
@@ -13263,7 +13263,7 @@
       </c>
       <c r="H298" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: sabedoria e decisões 🌙 Para fechar o dia com Provérbios 4:23. Comente o nome de quem você quer colocar nesta oração. #oracaodanoite #oracao #fe #sabedoria</t>
+          <t>Oração da noite: sabedoria e decisões 🌙 Para fechar o dia com Provérbios 4:23. Comente o nome de quem você quer colocar nesta oração. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I298" s="2" t="inlineStr"/>
@@ -13286,7 +13286,7 @@
       </c>
       <c r="D299" s="2" t="inlineStr">
         <is>
-          <t>Dia 298 de 365. Isaías 30:21: Este é o caminho, andai nele. #fe #sabedoria #decisoes #palavradodia</t>
+          <t>Dia 298 de 365. Isaías 30:21: Este é o caminho, andai nele. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E299" s="2" t="inlineStr">
@@ -13296,7 +13296,7 @@
       </c>
       <c r="F299" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ Salmos 119:130. A palavra ilumina. #versiculododia #fe #sabedoria #oracao</t>
+          <t>Pausa do meio-dia ☀️ Salmos 119:130. A palavra ilumina. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G299" s="2" t="inlineStr">
@@ -13306,7 +13306,7 @@
       </c>
       <c r="H299" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: sabedoria e decisões 🌙 Para fechar o dia com Isaías 30:21. Conte nos comentários pelo que você quer agradecer hoje. #oracaodanoite #oracao #fe #sabedoria</t>
+          <t>Oração da noite: sabedoria e decisões 🌙 Para fechar o dia com Isaías 30:21. Conte nos comentários pelo que você quer agradecer hoje. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I299" s="2" t="inlineStr"/>
@@ -13329,7 +13329,7 @@
       </c>
       <c r="D300" s="2" t="inlineStr">
         <is>
-          <t>Dia 299 de 365. Provérbios 2:6: O Senhor dá a sabedoria. #fe #sabedoria #decisoes #palavradodia</t>
+          <t>Dia 299 de 365. Provérbios 2:6: O Senhor dá a sabedoria. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E300" s="2" t="inlineStr">
@@ -13339,7 +13339,7 @@
       </c>
       <c r="F300" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ Provérbios 11:2. Humildade é sabedoria. #versiculododia #fe #sabedoria #oracao</t>
+          <t>Pausa do meio-dia ☀️ Provérbios 11:2. Humildade é sabedoria. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G300" s="2" t="inlineStr">
@@ -13349,7 +13349,7 @@
       </c>
       <c r="H300" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: sabedoria e decisões 🌙 Para fechar o dia com Provérbios 2:6. Deixe nos comentários o que você quer entregar a Deus esta noite. #oracaodanoite #oracao #fe #sabedoria</t>
+          <t>Oração da noite: sabedoria e decisões 🌙 Para fechar o dia com Provérbios 2:6. Deixe nos comentários o que você quer entregar a Deus esta noite. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I300" s="2" t="inlineStr"/>
@@ -13372,7 +13372,7 @@
       </c>
       <c r="D301" s="2" t="inlineStr">
         <is>
-          <t>Dia 300 de 365. Tiago 3:17: Como reconhecer a sabedoria que vem do alto. #fe #sabedoria #decisoes #palavradodia</t>
+          <t>Dia 300 de 365. Tiago 3:17: Como reconhecer a sabedoria que vem do alto. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E301" s="2" t="inlineStr">
@@ -13382,7 +13382,7 @@
       </c>
       <c r="F301" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ Provérbios 9:10. O temor do Senhor. #versiculododia #fe #sabedoria #oracao</t>
+          <t>Pausa do meio-dia ☀️ Provérbios 9:10. O temor do Senhor. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G301" s="2" t="inlineStr">
@@ -13392,7 +13392,7 @@
       </c>
       <c r="H301" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: sabedoria e decisões 🌙 Para fechar o dia com Tiago 3:17. Marque alguém que precisa ouvir esta oração. #oracaodanoite #oracao #fe #sabedoria</t>
+          <t>Oração da noite: sabedoria e decisões 🌙 Para fechar o dia com Tiago 3:17. Marque alguém que precisa ouvir esta oração. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I301" s="2" t="inlineStr"/>
@@ -13415,7 +13415,7 @@
       </c>
       <c r="D302" s="2" t="inlineStr">
         <is>
-          <t>Dia 301 de 365. Provérbios 15:22: Sem conselho, os planos falham. #fe #sabedoria #decisoes #palavradodia</t>
+          <t>Dia 301 de 365. Provérbios 15:22: Sem conselho, os planos falham. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E302" s="2" t="inlineStr">
@@ -13425,7 +13425,7 @@
       </c>
       <c r="F302" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ Provérbios 21:20. Dinheiro com sabedoria. #versiculododia #fe #sabedoria #oracao</t>
+          <t>Pausa do meio-dia ☀️ Provérbios 21:20. Dinheiro com sabedoria. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G302" s="2" t="inlineStr">
@@ -13435,7 +13435,7 @@
       </c>
       <c r="H302" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: sabedoria e decisões 🌙 Para fechar o dia com Provérbios 15:22. Comente seu pedido. Vamos orar juntos. #oracaodanoite #oracao #fe #sabedoria</t>
+          <t>Oração da noite: sabedoria e decisões 🌙 Para fechar o dia com Provérbios 15:22. Comente seu pedido. Vamos orar juntos. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I302" s="2" t="inlineStr"/>
@@ -13458,7 +13458,7 @@
       </c>
       <c r="D303" s="2" t="inlineStr">
         <is>
-          <t>Dia 302 de 365. Salmos 25:4-5: Mostra-me os teus caminhos. #fe #sabedoria #decisoes #palavradodia</t>
+          <t>Dia 302 de 365. Salmos 25:4-5: Mostra-me os teus caminhos. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E303" s="2" t="inlineStr">
@@ -13468,7 +13468,7 @@
       </c>
       <c r="F303" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ Provérbios 17:28. Silêncio sábio. #versiculododia #fe #sabedoria #oracao</t>
+          <t>Pausa do meio-dia ☀️ Provérbios 17:28. Silêncio sábio. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G303" s="2" t="inlineStr">
@@ -13478,7 +13478,7 @@
       </c>
       <c r="H303" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: sabedoria e decisões 🌙 Para fechar o dia com Salmos 25:4-5. Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #sabedoria</t>
+          <t>Oração da noite: sabedoria e decisões 🌙 Para fechar o dia com Salmos 25:4-5. Deixe seu pedido de oração nos comentários. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I303" s="2" t="inlineStr"/>
@@ -13501,7 +13501,7 @@
       </c>
       <c r="D304" s="2" t="inlineStr">
         <is>
-          <t>Dia 303 de 365. Provérbios 16:16: Melhor que ouro. #fe #sabedoria #decisoes #palavradodia</t>
+          <t>Dia 303 de 365. Provérbios 16:16: Melhor que ouro. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E304" s="2" t="inlineStr">
@@ -13511,7 +13511,7 @@
       </c>
       <c r="F304" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ Salmos 32:9. Não seja teimoso. #versiculododia #fe #sabedoria #oracao</t>
+          <t>Pausa do meio-dia ☀️ Salmos 32:9. Não seja teimoso. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G304" s="2" t="inlineStr">
@@ -13521,7 +13521,7 @@
       </c>
       <c r="H304" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: sabedoria e decisões 🌙 Para fechar o dia com Provérbios 16:16. Escreva amém se essa oração é sua também. #oracaodanoite #oracao #fe #sabedoria</t>
+          <t>Oração da noite: sabedoria e decisões 🌙 Para fechar o dia com Provérbios 16:16. Escreva amém se essa oração é sua também. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I304" s="2" t="inlineStr"/>
@@ -13544,7 +13544,7 @@
       </c>
       <c r="D305" s="2" t="inlineStr">
         <is>
-          <t>Dia 304 de 365. Colossenses 3:16: Que a Palavra habite em você ricamente. #fe #sabedoria #decisoes #palavradodia</t>
+          <t>Dia 304 de 365. Colossenses 3:16: Que a Palavra habite em você ricamente. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E305" s="2" t="inlineStr">
@@ -13554,7 +13554,7 @@
       </c>
       <c r="F305" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ Provérbios 20:21. Não se apresse. #versiculododia #fe #sabedoria #oracao</t>
+          <t>Pausa do meio-dia ☀️ Provérbios 20:21. Não se apresse. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G305" s="2" t="inlineStr">
@@ -13564,7 +13564,7 @@
       </c>
       <c r="H305" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: sabedoria e decisões 🌙 Para fechar o dia com Colossenses 3:16. Comente o nome de quem você quer colocar nesta oração. #oracaodanoite #oracao #fe #sabedoria</t>
+          <t>Oração da noite: sabedoria e decisões 🌙 Para fechar o dia com Colossenses 3:16. Comente o nome de quem você quer colocar nesta oração. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I305" s="2" t="inlineStr"/>
@@ -13587,7 +13587,7 @@
       </c>
       <c r="D306" s="2" t="inlineStr">
         <is>
-          <t>Dia 305 de 365. Provérbios 14:12: Há caminho que parece direito. #fe #sabedoria #decisoes #palavradodia</t>
+          <t>Dia 305 de 365. Provérbios 14:12: Há caminho que parece direito. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E306" s="2" t="inlineStr">
@@ -13597,7 +13597,7 @@
       </c>
       <c r="F306" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ Mateus 7:13. Escolha o caminho estreito. #versiculododia #fe #sabedoria #oracao</t>
+          <t>Pausa do meio-dia ☀️ Mateus 7:13. Escolha o caminho estreito. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G306" s="2" t="inlineStr">
@@ -13607,7 +13607,7 @@
       </c>
       <c r="H306" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: sabedoria e decisões 🌙 Para fechar o dia com Provérbios 14:12. Conte nos comentários pelo que você quer agradecer hoje. #oracaodanoite #oracao #fe #sabedoria</t>
+          <t>Oração da noite: sabedoria e decisões 🌙 Para fechar o dia com Provérbios 14:12. Conte nos comentários pelo que você quer agradecer hoje. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I306" s="2" t="inlineStr"/>
@@ -13630,7 +13630,7 @@
       </c>
       <c r="D307" s="2" t="inlineStr">
         <is>
-          <t>Dia 306 de 365. 1 Reis 3:9: O pedido de Salomão. #fe #sabedoria #decisoes #palavradodia</t>
+          <t>Dia 306 de 365. 1 Reis 3:9: O pedido de Salomão. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E307" s="2" t="inlineStr">
@@ -13640,7 +13640,7 @@
       </c>
       <c r="F307" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ Tiago 3:18. Sabedoria do alto é pacífica. #versiculododia #fe #sabedoria #oracao</t>
+          <t>Pausa do meio-dia ☀️ Tiago 3:18. Sabedoria do alto é pacífica. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G307" s="2" t="inlineStr">
@@ -13650,7 +13650,7 @@
       </c>
       <c r="H307" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: sabedoria e decisões 🌙 Para fechar o dia com 1 Reis 3:9. Deixe nos comentários o que você quer entregar a Deus esta noite. #oracaodanoite #oracao #fe #sabedoria</t>
+          <t>Oração da noite: sabedoria e decisões 🌙 Para fechar o dia com 1 Reis 3:9. Deixe nos comentários o que você quer entregar a Deus esta noite. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I307" s="2" t="inlineStr"/>
@@ -13673,7 +13673,7 @@
       </c>
       <c r="D308" s="2" t="inlineStr">
         <is>
-          <t>Dia 307 de 365. Provérbios 19:21: Muitos planos, um propósito. #fe #sabedoria #decisoes #palavradodia</t>
+          <t>Dia 307 de 365. Provérbios 19:21: Muitos planos, um propósito. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E308" s="2" t="inlineStr">
@@ -13683,7 +13683,7 @@
       </c>
       <c r="F308" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ Provérbios 21:23. Guarde a língua. #versiculododia #fe #sabedoria #oracao</t>
+          <t>Pausa do meio-dia ☀️ Provérbios 21:23. Guarde a língua. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G308" s="2" t="inlineStr">
@@ -13693,7 +13693,7 @@
       </c>
       <c r="H308" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: sabedoria e decisões 🌙 Para fechar o dia com Provérbios 19:21. Marque alguém que precisa ouvir esta oração. #oracaodanoite #oracao #fe #sabedoria</t>
+          <t>Oração da noite: sabedoria e decisões 🌙 Para fechar o dia com Provérbios 19:21. Marque alguém que precisa ouvir esta oração. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I308" s="2" t="inlineStr"/>
@@ -13716,7 +13716,7 @@
       </c>
       <c r="D309" s="2" t="inlineStr">
         <is>
-          <t>Dia 308 de 365. Romanos 12:2: Não se conforme com este mundo. #fe #sabedoria #decisoes #palavradodia</t>
+          <t>Dia 308 de 365. Romanos 12:2: Não se conforme com este mundo. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E309" s="2" t="inlineStr">
@@ -13726,7 +13726,7 @@
       </c>
       <c r="F309" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ Provérbios 22:3. Prudente vê o perigo. #versiculododia #fe #sabedoria #oracao</t>
+          <t>Pausa do meio-dia ☀️ Provérbios 22:3. Prudente vê o perigo. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G309" s="2" t="inlineStr">
@@ -13736,7 +13736,7 @@
       </c>
       <c r="H309" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: sabedoria e decisões 🌙 Para fechar o dia com Romanos 12:2. Comente seu pedido. Vamos orar juntos. #oracaodanoite #oracao #fe #sabedoria</t>
+          <t>Oração da noite: sabedoria e decisões 🌙 Para fechar o dia com Romanos 12:2. Comente seu pedido. Vamos orar juntos. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I309" s="2" t="inlineStr"/>
@@ -13759,7 +13759,7 @@
       </c>
       <c r="D310" s="2" t="inlineStr">
         <is>
-          <t>Dia 309 de 365. Salmos 1:1-3: Feliz quem não segue o conselho dos ímpios. #fe #sabedoria #decisoes #palavradodia</t>
+          <t>Dia 309 de 365. Salmos 1:1-3: Feliz quem não segue o conselho dos ímpios. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E310" s="2" t="inlineStr">
@@ -13769,7 +13769,7 @@
       </c>
       <c r="F310" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ Hebreus 5:14. Discerna. #versiculododia #fe #sabedoria #oracao</t>
+          <t>Pausa do meio-dia ☀️ Hebreus 5:14. Discerna. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G310" s="2" t="inlineStr">
@@ -13779,7 +13779,7 @@
       </c>
       <c r="H310" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: sabedoria e decisões 🌙 Para fechar o dia com Salmos 1:1-3. Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #sabedoria</t>
+          <t>Oração da noite: sabedoria e decisões 🌙 Para fechar o dia com Salmos 1:1-3. Deixe seu pedido de oração nos comentários. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I310" s="2" t="inlineStr"/>
@@ -13802,7 +13802,7 @@
       </c>
       <c r="D311" s="2" t="inlineStr">
         <is>
-          <t>Dia 310 de 365. Provérbios 13:20: Ande com os sábios. #fe #sabedoria #decisoes #palavradodia</t>
+          <t>Dia 310 de 365. Provérbios 13:20: Ande com os sábios. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E311" s="2" t="inlineStr">
@@ -13812,7 +13812,7 @@
       </c>
       <c r="F311" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ Eclesiastes 8:5. Sabedoria na hora certa. #versiculododia #fe #sabedoria #oracao</t>
+          <t>Pausa do meio-dia ☀️ Eclesiastes 8:5. Sabedoria na hora certa. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G311" s="2" t="inlineStr">
@@ -13822,7 +13822,7 @@
       </c>
       <c r="H311" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: sabedoria e decisões 🌙 Para fechar o dia com Provérbios 13:20. Escreva amém se essa oração é sua também. #oracaodanoite #oracao #fe #sabedoria</t>
+          <t>Oração da noite: sabedoria e decisões 🌙 Para fechar o dia com Provérbios 13:20. Escreva amém se essa oração é sua também. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I311" s="2" t="inlineStr"/>
@@ -13845,7 +13845,7 @@
       </c>
       <c r="D312" s="2" t="inlineStr">
         <is>
-          <t>Dia 311 de 365. Eclesiastes 7:8: Melhor é o fim do que o começo. #fe #sabedoria #decisoes #palavradodia</t>
+          <t>Dia 311 de 365. Eclesiastes 7:8: Melhor é o fim do que o começo. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E312" s="2" t="inlineStr">
@@ -13855,7 +13855,7 @@
       </c>
       <c r="F312" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ Salmos 90:12. Ensine-me a contar os dias. #versiculododia #fe #sabedoria #oracao</t>
+          <t>Pausa do meio-dia ☀️ Salmos 90:12. Ensine-me a contar os dias. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G312" s="2" t="inlineStr">
@@ -13865,7 +13865,7 @@
       </c>
       <c r="H312" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: sabedoria e decisões 🌙 Para fechar o dia com Eclesiastes 7:8. Comente o nome de quem você quer colocar nesta oração. #oracaodanoite #oracao #fe #sabedoria</t>
+          <t>Oração da noite: sabedoria e decisões 🌙 Para fechar o dia com Eclesiastes 7:8. Comente o nome de quem você quer colocar nesta oração. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I312" s="2" t="inlineStr"/>
@@ -13888,7 +13888,7 @@
       </c>
       <c r="D313" s="2" t="inlineStr">
         <is>
-          <t>Dia 312 de 365. Provérbios 12:15: O tolo acha que está sempre certo. #fe #sabedoria #decisoes #palavradodia</t>
+          <t>Dia 312 de 365. Provérbios 12:15: O tolo acha que está sempre certo. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E313" s="2" t="inlineStr">
@@ -13898,7 +13898,7 @@
       </c>
       <c r="F313" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ Provérbios 4:25. Os olhos no caminho. #versiculododia #fe #sabedoria #oracao</t>
+          <t>Pausa do meio-dia ☀️ Provérbios 4:25. Os olhos no caminho. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G313" s="2" t="inlineStr">
@@ -13908,7 +13908,7 @@
       </c>
       <c r="H313" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: sabedoria e decisões 🌙 Para fechar o dia com Provérbios 12:15. Conte nos comentários pelo que você quer agradecer hoje. #oracaodanoite #oracao #fe #sabedoria</t>
+          <t>Oração da noite: sabedoria e decisões 🌙 Para fechar o dia com Provérbios 12:15. Conte nos comentários pelo que você quer agradecer hoje. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I313" s="2" t="inlineStr"/>
@@ -13931,7 +13931,7 @@
       </c>
       <c r="D314" s="2" t="inlineStr">
         <is>
-          <t>Dia 313 de 365. Salmos 37:23: O Senhor firma os passos do homem bom. #fe #sabedoria #decisoes #palavradodia</t>
+          <t>Dia 313 de 365. Salmos 37:23: O Senhor firma os passos do homem bom. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E314" s="2" t="inlineStr">
@@ -13941,7 +13941,7 @@
       </c>
       <c r="F314" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ Salmos 33:11. Conselho de Deus permanece. #versiculododia #fe #sabedoria #oracao</t>
+          <t>Pausa do meio-dia ☀️ Salmos 33:11. Conselho de Deus permanece. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G314" s="2" t="inlineStr">
@@ -13951,7 +13951,7 @@
       </c>
       <c r="H314" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: sabedoria e decisões 🌙 Para fechar o dia com Salmos 37:23. Deixe nos comentários o que você quer entregar a Deus esta noite. #oracaodanoite #oracao #fe #sabedoria</t>
+          <t>Oração da noite: sabedoria e decisões 🌙 Para fechar o dia com Salmos 37:23. Deixe nos comentários o que você quer entregar a Deus esta noite. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I314" s="2" t="inlineStr"/>
@@ -13974,7 +13974,7 @@
       </c>
       <c r="D315" s="2" t="inlineStr">
         <is>
-          <t>Dia 314 de 365. Provérbios 21:5: Os planos do diligente levam à fartura. #fe #sabedoria #decisoes #palavradodia</t>
+          <t>Dia 314 de 365. Provérbios 21:5: Os planos do diligente levam à fartura. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E315" s="2" t="inlineStr">
@@ -13984,7 +13984,7 @@
       </c>
       <c r="F315" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ Provérbios 10:31. A boca do justo. #versiculododia #fe #sabedoria #oracao</t>
+          <t>Pausa do meio-dia ☀️ Provérbios 10:31. A boca do justo. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G315" s="2" t="inlineStr">
@@ -13994,7 +13994,7 @@
       </c>
       <c r="H315" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: sabedoria e decisões 🌙 Para fechar o dia com Provérbios 21:5. Marque alguém que precisa ouvir esta oração. #oracaodanoite #oracao #fe #sabedoria</t>
+          <t>Oração da noite: sabedoria e decisões 🌙 Para fechar o dia com Provérbios 21:5. Marque alguém que precisa ouvir esta oração. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I315" s="2" t="inlineStr"/>
@@ -14017,7 +14017,7 @@
       </c>
       <c r="D316" s="2" t="inlineStr">
         <is>
-          <t>Dia 315 de 365. Filipenses 1:9-10: Discernir o que é excelente. #fe #sabedoria #decisoes #palavradodia</t>
+          <t>Dia 315 de 365. Filipenses 1:9-10: Discernir o que é excelente. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E316" s="2" t="inlineStr">
@@ -14027,7 +14027,7 @@
       </c>
       <c r="F316" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ Provérbios 1:20. Sabedoria nas ruas. #versiculododia #fe #sabedoria #oracao</t>
+          <t>Pausa do meio-dia ☀️ Provérbios 1:20. Sabedoria nas ruas. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G316" s="2" t="inlineStr">
@@ -14037,7 +14037,7 @@
       </c>
       <c r="H316" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: sabedoria e decisões 🌙 Para fechar o dia com Filipenses 1:9-10. Comente seu pedido. Vamos orar juntos. #oracaodanoite #oracao #fe #sabedoria</t>
+          <t>Oração da noite: sabedoria e decisões 🌙 Para fechar o dia com Filipenses 1:9-10. Comente seu pedido. Vamos orar juntos. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I316" s="2" t="inlineStr"/>
@@ -14060,7 +14060,7 @@
       </c>
       <c r="D317" s="2" t="inlineStr">
         <is>
-          <t>Dia 316 de 365. Provérbios 18:13: Responder antes de ouvir é tolice. #fe #sabedoria #decisoes #palavradodia</t>
+          <t>Dia 316 de 365. Provérbios 18:13: Responder antes de ouvir é tolice. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E317" s="2" t="inlineStr">
@@ -14070,7 +14070,7 @@
       </c>
       <c r="F317" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ Colossenses 4:5. Ande com sabedoria. #versiculododia #fe #sabedoria #oracao</t>
+          <t>Pausa do meio-dia ☀️ Colossenses 4:5. Ande com sabedoria. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G317" s="2" t="inlineStr">
@@ -14080,7 +14080,7 @@
       </c>
       <c r="H317" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: sabedoria e decisões 🌙 Para fechar o dia com Provérbios 18:13. Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #sabedoria</t>
+          <t>Oração da noite: sabedoria e decisões 🌙 Para fechar o dia com Provérbios 18:13. Deixe seu pedido de oração nos comentários. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I317" s="2" t="inlineStr"/>
@@ -14103,7 +14103,7 @@
       </c>
       <c r="D318" s="2" t="inlineStr">
         <is>
-          <t>Dia 317 de 365. Mateus 7:24-25: Construa sobre a rocha. #fe #sabedoria #decisoes #palavradodia</t>
+          <t>Dia 317 de 365. Mateus 7:24-25: Construa sobre a rocha. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E318" s="2" t="inlineStr">
@@ -14113,7 +14113,7 @@
       </c>
       <c r="F318" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ Efésios 5:17. Busque a vontade dEle. #versiculododia #fe #sabedoria #oracao</t>
+          <t>Pausa do meio-dia ☀️ Efésios 5:17. Busque a vontade dEle. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G318" s="2" t="inlineStr">
@@ -14123,7 +14123,7 @@
       </c>
       <c r="H318" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: sabedoria e decisões 🌙 Para fechar o dia com Mateus 7:24-25. Escreva amém se essa oração é sua também. #oracaodanoite #oracao #fe #sabedoria</t>
+          <t>Oração da noite: sabedoria e decisões 🌙 Para fechar o dia com Mateus 7:24-25. Escreva amém se essa oração é sua também. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I318" s="2" t="inlineStr"/>
@@ -14146,7 +14146,7 @@
       </c>
       <c r="D319" s="2" t="inlineStr">
         <is>
-          <t>Dia 318 de 365. Salmos 111:10: O temor do Senhor é o princípio da sabedoria. #fe #sabedoria #decisoes #palavradodia</t>
+          <t>Dia 318 de 365. Salmos 111:10: O temor do Senhor é o princípio da sabedoria. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E319" s="2" t="inlineStr">
@@ -14156,7 +14156,7 @@
       </c>
       <c r="F319" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ Provérbios 4:13. Instrução é vida. #versiculododia #fe #sabedoria #oracao</t>
+          <t>Pausa do meio-dia ☀️ Provérbios 4:13. Instrução é vida. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G319" s="2" t="inlineStr">
@@ -14166,7 +14166,7 @@
       </c>
       <c r="H319" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: sabedoria e decisões 🌙 Para fechar o dia com Salmos 111:10. Comente o nome de quem você quer colocar nesta oração. #oracaodanoite #oracao #fe #sabedoria</t>
+          <t>Oração da noite: sabedoria e decisões 🌙 Para fechar o dia com Salmos 111:10. Comente o nome de quem você quer colocar nesta oração. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I319" s="2" t="inlineStr"/>
@@ -14189,7 +14189,7 @@
       </c>
       <c r="D320" s="2" t="inlineStr">
         <is>
-          <t>Dia 319 de 365. Provérbios 27:12: O prudente vê o perigo e se esconde. #fe #sabedoria #decisoes #palavradodia</t>
+          <t>Dia 319 de 365. Provérbios 27:12: O prudente vê o perigo e se esconde. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E320" s="2" t="inlineStr">
@@ -14199,7 +14199,7 @@
       </c>
       <c r="F320" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ Provérbios 1:5. O sábio ouve. #versiculododia #fe #sabedoria #oracao</t>
+          <t>Pausa do meio-dia ☀️ Provérbios 1:5. O sábio ouve. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G320" s="2" t="inlineStr">
@@ -14209,7 +14209,7 @@
       </c>
       <c r="H320" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: sabedoria e decisões 🌙 Para fechar o dia com Provérbios 27:12. Conte nos comentários pelo que você quer agradecer hoje. #oracaodanoite #oracao #fe #sabedoria</t>
+          <t>Oração da noite: sabedoria e decisões 🌙 Para fechar o dia com Provérbios 27:12. Conte nos comentários pelo que você quer agradecer hoje. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I320" s="2" t="inlineStr"/>
@@ -14232,7 +14232,7 @@
       </c>
       <c r="D321" s="2" t="inlineStr">
         <is>
-          <t>Dia 320 de 365. Eclesiastes 12:13: A conclusão de tudo. #fe #sabedoria #decisoes #palavradodia</t>
+          <t>Dia 320 de 365. Eclesiastes 12:13: A conclusão de tudo. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E321" s="2" t="inlineStr">
@@ -14242,7 +14242,7 @@
       </c>
       <c r="F321" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ Efésios 4:23. Mente renovada. #versiculododia #fe #sabedoria #oracao</t>
+          <t>Pausa do meio-dia ☀️ Efésios 4:23. Mente renovada. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G321" s="2" t="inlineStr">
@@ -14252,7 +14252,7 @@
       </c>
       <c r="H321" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: sabedoria e decisões 🌙 Para fechar o dia com Eclesiastes 12:13. Deixe nos comentários o que você quer entregar a Deus esta noite. #oracaodanoite #oracao #fe #sabedoria</t>
+          <t>Oração da noite: sabedoria e decisões 🌙 Para fechar o dia com Eclesiastes 12:13. Deixe nos comentários o que você quer entregar a Deus esta noite. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I321" s="2" t="inlineStr"/>
@@ -14275,7 +14275,7 @@
       </c>
       <c r="D322" s="2" t="inlineStr">
         <is>
-          <t>Dia 321 de 365. Daniel 2:20-21: Ele dá sabedoria aos sábios. #fe #sabedoria #decisoes #palavradodia</t>
+          <t>Dia 321 de 365. Daniel 2:20-21: Ele dá sabedoria aos sábios. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E322" s="2" t="inlineStr">
@@ -14285,7 +14285,7 @@
       </c>
       <c r="F322" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ Salmos 119:133. Luz para o caminho. #versiculododia #fe #sabedoria #oracao</t>
+          <t>Pausa do meio-dia ☀️ Salmos 119:133. Luz para o caminho. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G322" s="2" t="inlineStr">
@@ -14295,7 +14295,7 @@
       </c>
       <c r="H322" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: sabedoria e decisões 🌙 Para fechar o dia com Daniel 2:20-21. Marque alguém que precisa ouvir esta oração. #oracaodanoite #oracao #fe #sabedoria</t>
+          <t>Oração da noite: sabedoria e decisões 🌙 Para fechar o dia com Daniel 2:20-21. Marque alguém que precisa ouvir esta oração. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I322" s="2" t="inlineStr"/>
@@ -14318,7 +14318,7 @@
       </c>
       <c r="D323" s="2" t="inlineStr">
         <is>
-          <t>Dia 322 de 365. Filipenses 4:13: Tudo posso naquele que me fortalece. #fe #perseveranca #forca #palavradodia</t>
+          <t>Dia 322 de 365. Filipenses 4:13: Tudo posso naquele que me fortalece. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E323" s="2" t="inlineStr">
@@ -14328,7 +14328,7 @@
       </c>
       <c r="F323" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ Isaías 40:30. Cansado no meio do dia? #versiculododia #fe #forca #oracao</t>
+          <t>Pausa do meio-dia ☀️ Isaías 40:30. Cansado no meio do dia? #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G323" s="2" t="inlineStr">
@@ -14338,7 +14338,7 @@
       </c>
       <c r="H323" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: força e perseverança 🌙 Para fechar o dia com Filipenses 4:13. Comente seu pedido. Vamos orar juntos. #oracaodanoite #oracao #fe #forca</t>
+          <t>Oração da noite: força e perseverança 🌙 Para fechar o dia com Filipenses 4:13. Comente seu pedido. Vamos orar juntos. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I323" s="2" t="inlineStr"/>
@@ -14361,7 +14361,7 @@
       </c>
       <c r="D324" s="2" t="inlineStr">
         <is>
-          <t>Dia 323 de 365. Hebreus 12:1-2: Corra com perseverança. #fe #perseveranca #forca #palavradodia</t>
+          <t>Dia 323 de 365. Hebreus 12:1-2: Corra com perseverança. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E324" s="2" t="inlineStr">
@@ -14371,7 +14371,7 @@
       </c>
       <c r="F324" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ Hebreus 12:3. Não desista. #versiculododia #fe #forca #oracao</t>
+          <t>Pausa do meio-dia ☀️ Hebreus 12:3. Não desista. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G324" s="2" t="inlineStr">
@@ -14381,7 +14381,7 @@
       </c>
       <c r="H324" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: força e perseverança 🌙 Para fechar o dia com Hebreus 12:1-2. Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #forca</t>
+          <t>Oração da noite: força e perseverança 🌙 Para fechar o dia com Hebreus 12:1-2. Deixe seu pedido de oração nos comentários. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I324" s="2" t="inlineStr"/>
@@ -14404,7 +14404,7 @@
       </c>
       <c r="D325" s="2" t="inlineStr">
         <is>
-          <t>Dia 324 de 365. Salmos 27:13: Eu creio que verei a bondade do Senhor. #fe #perseveranca #forca #palavradodia</t>
+          <t>Dia 324 de 365. Salmos 27:13: Eu creio que verei a bondade do Senhor. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E325" s="2" t="inlineStr">
@@ -14414,7 +14414,7 @@
       </c>
       <c r="F325" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ Joel 3:10. A força dEle na fraqueza. #versiculododia #fe #forca #oracao</t>
+          <t>Pausa do meio-dia ☀️ Joel 3:10. A força dEle na fraqueza. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G325" s="2" t="inlineStr">
@@ -14424,7 +14424,7 @@
       </c>
       <c r="H325" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: força e perseverança 🌙 Para fechar o dia com Salmos 27:13. Escreva amém se essa oração é sua também. #oracaodanoite #oracao #fe #forca</t>
+          <t>Oração da noite: força e perseverança 🌙 Para fechar o dia com Salmos 27:13. Escreva amém se essa oração é sua também. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I325" s="2" t="inlineStr"/>
@@ -14447,7 +14447,7 @@
       </c>
       <c r="D326" s="2" t="inlineStr">
         <is>
-          <t>Dia 325 de 365. Tiago 1:2-4: Alegria nas provações? #fe #perseveranca #forca #palavradodia</t>
+          <t>Dia 325 de 365. Tiago 1:2-4: Alegria nas provações? #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E326" s="2" t="inlineStr">
@@ -14457,7 +14457,7 @@
       </c>
       <c r="F326" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ Hebreus 10:39. Não recue. #versiculododia #fe #forca #oracao</t>
+          <t>Pausa do meio-dia ☀️ Hebreus 10:39. Não recue. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G326" s="2" t="inlineStr">
@@ -14467,7 +14467,7 @@
       </c>
       <c r="H326" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: força e perseverança 🌙 Para fechar o dia com Tiago 1:2-4. Comente o nome de quem você quer colocar nesta oração. #oracaodanoite #oracao #fe #forca</t>
+          <t>Oração da noite: força e perseverança 🌙 Para fechar o dia com Tiago 1:2-4. Comente o nome de quem você quer colocar nesta oração. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I326" s="2" t="inlineStr"/>
@@ -14490,7 +14490,7 @@
       </c>
       <c r="D327" s="2" t="inlineStr">
         <is>
-          <t>Dia 326 de 365. Provérbios 24:16: O justo cai sete vezes e se levanta. #fe #perseveranca #forca #palavradodia</t>
+          <t>Dia 326 de 365. Provérbios 24:16: O justo cai sete vezes e se levanta. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E327" s="2" t="inlineStr">
@@ -14500,7 +14500,7 @@
       </c>
       <c r="F327" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ Salmos 20:8. Caiu? Levante. #versiculododia #fe #forca #oracao</t>
+          <t>Pausa do meio-dia ☀️ Salmos 20:8. Caiu? Levante. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G327" s="2" t="inlineStr">
@@ -14510,7 +14510,7 @@
       </c>
       <c r="H327" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: força e perseverança 🌙 Para fechar o dia com Provérbios 24:16. Conte nos comentários pelo que você quer agradecer hoje. #oracaodanoite #oracao #fe #forca</t>
+          <t>Oração da noite: força e perseverança 🌙 Para fechar o dia com Provérbios 24:16. Conte nos comentários pelo que você quer agradecer hoje. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I327" s="2" t="inlineStr"/>
@@ -14533,7 +14533,7 @@
       </c>
       <c r="D328" s="2" t="inlineStr">
         <is>
-          <t>Dia 327 de 365. 2 Timóteo 4:7: Combati o bom combate. #fe #perseveranca #forca #palavradodia</t>
+          <t>Dia 327 de 365. 2 Timóteo 4:7: Combati o bom combate. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E328" s="2" t="inlineStr">
@@ -14543,7 +14543,7 @@
       </c>
       <c r="F328" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ Colossenses 1:11. Firme e constante. #versiculododia #fe #forca #oracao</t>
+          <t>Pausa do meio-dia ☀️ Colossenses 1:11. Firme e constante. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G328" s="2" t="inlineStr">
@@ -14553,7 +14553,7 @@
       </c>
       <c r="H328" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: força e perseverança 🌙 Para fechar o dia com 2 Timóteo 4:7. Deixe nos comentários o que você quer entregar a Deus esta noite. #oracaodanoite #oracao #fe #forca</t>
+          <t>Oração da noite: força e perseverança 🌙 Para fechar o dia com 2 Timóteo 4:7. Deixe nos comentários o que você quer entregar a Deus esta noite. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I328" s="2" t="inlineStr"/>
@@ -14576,7 +14576,7 @@
       </c>
       <c r="D329" s="2" t="inlineStr">
         <is>
-          <t>Dia 328 de 365. Salmos 18:32: Deus me reveste de força. #fe #perseveranca #forca #palavradodia</t>
+          <t>Dia 328 de 365. Salmos 18:32: Deus me reveste de força. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E329" s="2" t="inlineStr">
@@ -14586,7 +14586,7 @@
       </c>
       <c r="F329" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ Êxodo 15:2. O Senhor é a minha força. #versiculododia #fe #forca #oracao</t>
+          <t>Pausa do meio-dia ☀️ Êxodo 15:2. O Senhor é a minha força. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G329" s="2" t="inlineStr">
@@ -14596,7 +14596,7 @@
       </c>
       <c r="H329" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: força e perseverança 🌙 Para fechar o dia com Salmos 18:32. Marque alguém que precisa ouvir esta oração. #oracaodanoite #oracao #fe #forca</t>
+          <t>Oração da noite: força e perseverança 🌙 Para fechar o dia com Salmos 18:32. Marque alguém que precisa ouvir esta oração. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I329" s="2" t="inlineStr"/>
@@ -14619,7 +14619,7 @@
       </c>
       <c r="D330" s="2" t="inlineStr">
         <is>
-          <t>Dia 329 de 365. Salmos 66:10-12: Passamos pelo fogo e pela água. #fe #perseveranca #forca #palavradodia</t>
+          <t>Dia 329 de 365. Salmos 66:10-12: Passamos pelo fogo e pela água. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E330" s="2" t="inlineStr">
@@ -14629,7 +14629,7 @@
       </c>
       <c r="F330" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ Deuteronômio 33:25. Força para hoje. #versiculododia #fe #forca #oracao</t>
+          <t>Pausa do meio-dia ☀️ Deuteronômio 33:25. Força para hoje. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G330" s="2" t="inlineStr">
@@ -14639,7 +14639,7 @@
       </c>
       <c r="H330" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: força e perseverança 🌙 Para fechar o dia com Salmos 66:10-12. Comente seu pedido. Vamos orar juntos. #oracaodanoite #oracao #fe #forca</t>
+          <t>Oração da noite: força e perseverança 🌙 Para fechar o dia com Salmos 66:10-12. Comente seu pedido. Vamos orar juntos. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I330" s="2" t="inlineStr"/>
@@ -14662,7 +14662,7 @@
       </c>
       <c r="D331" s="2" t="inlineStr">
         <is>
-          <t>Dia 330 de 365. Salmos 73:26: Quando o corpo e o coração falham. #fe #perseveranca #forca #palavradodia</t>
+          <t>Dia 330 de 365. Salmos 73:26: Quando o corpo e o coração falham. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E331" s="2" t="inlineStr">
@@ -14672,7 +14672,7 @@
       </c>
       <c r="F331" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ Romanos 5:3. Prova produz paciência. #versiculododia #fe #forca #oracao</t>
+          <t>Pausa do meio-dia ☀️ Romanos 5:3. Prova produz paciência. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G331" s="2" t="inlineStr">
@@ -14682,7 +14682,7 @@
       </c>
       <c r="H331" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: força e perseverança 🌙 Para fechar o dia com Salmos 73:26. Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #forca</t>
+          <t>Oração da noite: força e perseverança 🌙 Para fechar o dia com Salmos 73:26. Deixe seu pedido de oração nos comentários. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I331" s="2" t="inlineStr"/>
@@ -14705,7 +14705,7 @@
       </c>
       <c r="D332" s="2" t="inlineStr">
         <is>
-          <t>Dia 331 de 365. Isaías 41:13: Eu te ajudo. #fe #perseveranca #forca #palavradodia</t>
+          <t>Dia 331 de 365. Isaías 41:13: Eu te ajudo. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E332" s="2" t="inlineStr">
@@ -14715,7 +14715,7 @@
       </c>
       <c r="F332" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ Colossenses 4:2. Persevere em oração. #versiculododia #fe #forca #oracao</t>
+          <t>Pausa do meio-dia ☀️ Colossenses 4:2. Persevere em oração. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G332" s="2" t="inlineStr">
@@ -14725,7 +14725,7 @@
       </c>
       <c r="H332" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: força e perseverança 🌙 Para fechar o dia com Isaías 41:13. Escreva amém se essa oração é sua também. #oracaodanoite #oracao #fe #forca</t>
+          <t>Oração da noite: força e perseverança 🌙 Para fechar o dia com Isaías 41:13. Escreva amém se essa oração é sua também. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I332" s="2" t="inlineStr"/>
@@ -14748,7 +14748,7 @@
       </c>
       <c r="D333" s="2" t="inlineStr">
         <is>
-          <t>Dia 332 de 365. 1 Coríntios 16:13: Sede fortes. #fe #perseveranca #forca #palavradodia</t>
+          <t>Dia 332 de 365. 1 Coríntios 16:13: Sede fortes. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E333" s="2" t="inlineStr">
@@ -14758,7 +14758,7 @@
       </c>
       <c r="F333" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ Salmos 54:4. Ele sustenta. #versiculododia #fe #forca #oracao</t>
+          <t>Pausa do meio-dia ☀️ Salmos 54:4. Ele sustenta. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G333" s="2" t="inlineStr">
@@ -14768,7 +14768,7 @@
       </c>
       <c r="H333" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: força e perseverança 🌙 Para fechar o dia com 1 Coríntios 16:13. Comente o nome de quem você quer colocar nesta oração. #oracaodanoite #oracao #fe #forca</t>
+          <t>Oração da noite: força e perseverança 🌙 Para fechar o dia com 1 Coríntios 16:13. Comente o nome de quem você quer colocar nesta oração. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I333" s="2" t="inlineStr"/>
@@ -14791,7 +14791,7 @@
       </c>
       <c r="D334" s="2" t="inlineStr">
         <is>
-          <t>Dia 333 de 365. Efésios 6:10: Fortalecei-vos no Senhor. #fe #perseveranca #forca #palavradodia</t>
+          <t>Dia 333 de 365. Efésios 6:10: Fortalecei-vos no Senhor. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E334" s="2" t="inlineStr">
@@ -14801,7 +14801,7 @@
       </c>
       <c r="F334" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ Efésios 6:13. Fique firme. #versiculododia #fe #forca #oracao</t>
+          <t>Pausa do meio-dia ☀️ Efésios 6:13. Fique firme. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G334" s="2" t="inlineStr">
@@ -14811,7 +14811,7 @@
       </c>
       <c r="H334" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: força e perseverança 🌙 Para fechar o dia com Efésios 6:10. Conte nos comentários pelo que você quer agradecer hoje. #oracaodanoite #oracao #fe #forca</t>
+          <t>Oração da noite: força e perseverança 🌙 Para fechar o dia com Efésios 6:10. Conte nos comentários pelo que você quer agradecer hoje. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I334" s="2" t="inlineStr"/>
@@ -14834,7 +14834,7 @@
       </c>
       <c r="D335" s="2" t="inlineStr">
         <is>
-          <t>Dia 334 de 365. Salmos 28:7: O Senhor é a minha força e o meu escudo. #fe #perseveranca #forca #palavradodia</t>
+          <t>Dia 334 de 365. Salmos 28:7: O Senhor é a minha força e o meu escudo. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E335" s="2" t="inlineStr">
@@ -14844,7 +14844,7 @@
       </c>
       <c r="F335" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ 1 João 5:4. Vencedor. #versiculododia #fe #forca #oracao</t>
+          <t>Pausa do meio-dia ☀️ 1 João 5:4. Vencedor. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G335" s="2" t="inlineStr">
@@ -14854,7 +14854,7 @@
       </c>
       <c r="H335" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: força e perseverança 🌙 Para fechar o dia com Salmos 28:7. Deixe nos comentários o que você quer entregar a Deus esta noite. #oracaodanoite #oracao #fe #forca</t>
+          <t>Oração da noite: força e perseverança 🌙 Para fechar o dia com Salmos 28:7. Deixe nos comentários o que você quer entregar a Deus esta noite. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I335" s="2" t="inlineStr"/>
@@ -14877,7 +14877,7 @@
       </c>
       <c r="D336" s="2" t="inlineStr">
         <is>
-          <t>Dia 335 de 365. Hebreus 10:36: Vocês precisam de perseverança. #fe #perseveranca #forca #palavradodia</t>
+          <t>Dia 335 de 365. Hebreus 10:36: Vocês precisam de perseverança. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E336" s="2" t="inlineStr">
@@ -14887,7 +14887,7 @@
       </c>
       <c r="F336" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ Salmos 41:3. Ele fortalece os fracos. #versiculododia #fe #forca #oracao</t>
+          <t>Pausa do meio-dia ☀️ Salmos 41:3. Ele fortalece os fracos. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G336" s="2" t="inlineStr">
@@ -14897,7 +14897,7 @@
       </c>
       <c r="H336" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: força e perseverança 🌙 Para fechar o dia com Hebreus 10:36. Marque alguém que precisa ouvir esta oração. #oracaodanoite #oracao #fe #forca</t>
+          <t>Oração da noite: força e perseverança 🌙 Para fechar o dia com Hebreus 10:36. Marque alguém que precisa ouvir esta oração. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I336" s="2" t="inlineStr"/>
@@ -14920,7 +14920,7 @@
       </c>
       <c r="D337" s="2" t="inlineStr">
         <is>
-          <t>Dia 336 de 365. Zacarias 4:6: Não por força, nem por violência. #fe #perseveranca #forca #palavradodia</t>
+          <t>Dia 336 de 365. Zacarias 4:6: Não por força, nem por violência. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E337" s="2" t="inlineStr">
@@ -14930,7 +14930,7 @@
       </c>
       <c r="F337" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ Salmos 40:2. Firme na rocha. #versiculododia #fe #forca #oracao</t>
+          <t>Pausa do meio-dia ☀️ Salmos 40:2. Firme na rocha. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G337" s="2" t="inlineStr">
@@ -14940,7 +14940,7 @@
       </c>
       <c r="H337" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: força e perseverança 🌙 Para fechar o dia com Zacarias 4:6. Comente seu pedido. Vamos orar juntos. #oracaodanoite #oracao #fe #forca</t>
+          <t>Oração da noite: força e perseverança 🌙 Para fechar o dia com Zacarias 4:6. Comente seu pedido. Vamos orar juntos. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I337" s="2" t="inlineStr"/>
@@ -14963,7 +14963,7 @@
       </c>
       <c r="D338" s="2" t="inlineStr">
         <is>
-          <t>Dia 337 de 365. Isaías 50:7: Pus o meu rosto como pedra. #fe #perseveranca #forca #palavradodia</t>
+          <t>Dia 337 de 365. Isaías 50:7: Pus o meu rosto como pedra. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E338" s="2" t="inlineStr">
@@ -14973,7 +14973,7 @@
       </c>
       <c r="F338" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ 2 Tessalonicenses 3:13. Não se canse. #versiculododia #fe #forca #oracao</t>
+          <t>Pausa do meio-dia ☀️ 2 Tessalonicenses 3:13. Não se canse. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G338" s="2" t="inlineStr">
@@ -14983,7 +14983,7 @@
       </c>
       <c r="H338" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: força e perseverança 🌙 Para fechar o dia com Isaías 50:7. Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #forca</t>
+          <t>Oração da noite: força e perseverança 🌙 Para fechar o dia com Isaías 50:7. Deixe seu pedido de oração nos comentários. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I338" s="2" t="inlineStr"/>
@@ -15006,7 +15006,7 @@
       </c>
       <c r="D339" s="2" t="inlineStr">
         <is>
-          <t>Dia 338 de 365. Salmos 138:7: Ainda que eu ande no meio da angústia. #fe #perseveranca #forca #palavradodia</t>
+          <t>Dia 338 de 365. Salmos 138:7: Ainda que eu ande no meio da angústia. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E339" s="2" t="inlineStr">
@@ -15016,7 +15016,7 @@
       </c>
       <c r="F339" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ Salmos 16:11. Gozo é força. #versiculododia #fe #forca #oracao</t>
+          <t>Pausa do meio-dia ☀️ Salmos 16:11. Gozo é força. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G339" s="2" t="inlineStr">
@@ -15026,7 +15026,7 @@
       </c>
       <c r="H339" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: força e perseverança 🌙 Para fechar o dia com Salmos 138:7. Escreva amém se essa oração é sua também. #oracaodanoite #oracao #fe #forca</t>
+          <t>Oração da noite: força e perseverança 🌙 Para fechar o dia com Salmos 138:7. Escreva amém se essa oração é sua também. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I339" s="2" t="inlineStr"/>
@@ -15049,7 +15049,7 @@
       </c>
       <c r="D340" s="2" t="inlineStr">
         <is>
-          <t>Dia 339 de 365. Neemias 6:3: Estou fazendo uma grande obra. #fe #perseveranca #forca #palavradodia</t>
+          <t>Dia 339 de 365. Neemias 6:3: Estou fazendo uma grande obra. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E340" s="2" t="inlineStr">
@@ -15059,7 +15059,7 @@
       </c>
       <c r="F340" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ Salmos 92:14. Ele dá vigor. #versiculododia #fe #forca #oracao</t>
+          <t>Pausa do meio-dia ☀️ Salmos 92:14. Ele dá vigor. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G340" s="2" t="inlineStr">
@@ -15069,7 +15069,7 @@
       </c>
       <c r="H340" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: força e perseverança 🌙 Para fechar o dia com Neemias 6:3. Comente o nome de quem você quer colocar nesta oração. #oracaodanoite #oracao #fe #forca</t>
+          <t>Oração da noite: força e perseverança 🌙 Para fechar o dia com Neemias 6:3. Comente o nome de quem você quer colocar nesta oração. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I340" s="2" t="inlineStr"/>
@@ -15092,7 +15092,7 @@
       </c>
       <c r="D341" s="2" t="inlineStr">
         <is>
-          <t>Dia 340 de 365. Tiago 1:12: Feliz o que suporta a provação. #fe #perseveranca #forca #palavradodia</t>
+          <t>Dia 340 de 365. Tiago 1:12: Feliz o que suporta a provação. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E341" s="2" t="inlineStr">
@@ -15102,7 +15102,7 @@
       </c>
       <c r="F341" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ Jó 17:9. O justo segue o caminho. #versiculododia #fe #forca #oracao</t>
+          <t>Pausa do meio-dia ☀️ Jó 17:9. O justo segue o caminho. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G341" s="2" t="inlineStr">
@@ -15112,7 +15112,7 @@
       </c>
       <c r="H341" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: força e perseverança 🌙 Para fechar o dia com Tiago 1:12. Conte nos comentários pelo que você quer agradecer hoje. #oracaodanoite #oracao #fe #forca</t>
+          <t>Oração da noite: força e perseverança 🌙 Para fechar o dia com Tiago 1:12. Conte nos comentários pelo que você quer agradecer hoje. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I341" s="2" t="inlineStr"/>
@@ -15135,7 +15135,7 @@
       </c>
       <c r="D342" s="2" t="inlineStr">
         <is>
-          <t>Dia 341 de 365. Salmos 46:5: Deus está no meio dela. #fe #perseveranca #forca #palavradodia</t>
+          <t>Dia 341 de 365. Salmos 46:5: Deus está no meio dela. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E342" s="2" t="inlineStr">
@@ -15145,7 +15145,7 @@
       </c>
       <c r="F342" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ Salmos 59:16. Fortaleza no dia da angústia. #versiculododia #fe #forca #oracao</t>
+          <t>Pausa do meio-dia ☀️ Salmos 59:16. Fortaleza no dia da angústia. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G342" s="2" t="inlineStr">
@@ -15155,7 +15155,7 @@
       </c>
       <c r="H342" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: força e perseverança 🌙 Para fechar o dia com Salmos 46:5. Deixe nos comentários o que você quer entregar a Deus esta noite. #oracaodanoite #oracao #fe #forca</t>
+          <t>Oração da noite: força e perseverança 🌙 Para fechar o dia com Salmos 46:5. Deixe nos comentários o que você quer entregar a Deus esta noite. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I342" s="2" t="inlineStr"/>
@@ -15178,7 +15178,7 @@
       </c>
       <c r="D343" s="2" t="inlineStr">
         <is>
-          <t>Dia 342 de 365. Hebreus 12:11: A disciplina dói, depois dá fruto. #fe #perseveranca #forca #palavradodia</t>
+          <t>Dia 342 de 365. Hebreus 12:11: A disciplina dói, depois dá fruto. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E343" s="2" t="inlineStr">
@@ -15188,7 +15188,7 @@
       </c>
       <c r="F343" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ Salmos 66:9. Ele não te deixa cair. #versiculododia #fe #forca #oracao</t>
+          <t>Pausa do meio-dia ☀️ Salmos 66:9. Ele não te deixa cair. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G343" s="2" t="inlineStr">
@@ -15198,7 +15198,7 @@
       </c>
       <c r="H343" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: força e perseverança 🌙 Para fechar o dia com Hebreus 12:11. Marque alguém que precisa ouvir esta oração. #oracaodanoite #oracao #fe #forca</t>
+          <t>Oração da noite: força e perseverança 🌙 Para fechar o dia com Hebreus 12:11. Marque alguém que precisa ouvir esta oração. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I343" s="2" t="inlineStr"/>
@@ -15221,7 +15221,7 @@
       </c>
       <c r="D344" s="2" t="inlineStr">
         <is>
-          <t>Dia 343 de 365. Lucas 18:1: Orar sempre e nunca desistir. #fe #perseveranca #forca #palavradodia</t>
+          <t>Dia 343 de 365. Lucas 18:1: Orar sempre e nunca desistir. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E344" s="2" t="inlineStr">
@@ -15231,7 +15231,7 @@
       </c>
       <c r="F344" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ Provérbios 21:31. A vitória é dEle. #versiculododia #fe #forca #oracao</t>
+          <t>Pausa do meio-dia ☀️ Provérbios 21:31. A vitória é dEle. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G344" s="2" t="inlineStr">
@@ -15241,7 +15241,7 @@
       </c>
       <c r="H344" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: força e perseverança 🌙 Para fechar o dia com Lucas 18:1. Comente seu pedido. Vamos orar juntos. #oracaodanoite #oracao #fe #forca</t>
+          <t>Oração da noite: força e perseverança 🌙 Para fechar o dia com Lucas 18:1. Comente seu pedido. Vamos orar juntos. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I344" s="2" t="inlineStr"/>
@@ -15264,7 +15264,7 @@
       </c>
       <c r="D345" s="2" t="inlineStr">
         <is>
-          <t>Dia 344 de 365. Salmos 37:24: Ainda que caia, não ficará prostrado. #fe #perseveranca #forca #palavradodia</t>
+          <t>Dia 344 de 365. Salmos 37:24: Ainda que caia, não ficará prostrado. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E345" s="2" t="inlineStr">
@@ -15274,7 +15274,7 @@
       </c>
       <c r="F345" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ 2 Samuel 10:12. Esforce-se. #versiculododia #fe #forca #oracao</t>
+          <t>Pausa do meio-dia ☀️ 2 Samuel 10:12. Esforce-se. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G345" s="2" t="inlineStr">
@@ -15284,7 +15284,7 @@
       </c>
       <c r="H345" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: força e perseverança 🌙 Para fechar o dia com Salmos 37:24. Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #forca</t>
+          <t>Oração da noite: força e perseverança 🌙 Para fechar o dia com Salmos 37:24. Deixe seu pedido de oração nos comentários. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I345" s="2" t="inlineStr"/>
@@ -15307,7 +15307,7 @@
       </c>
       <c r="D346" s="2" t="inlineStr">
         <is>
-          <t>Dia 345 de 365. 2 Coríntios 4:7: Um tesouro em vasos de barro. #fe #perseveranca #forca #palavradodia</t>
+          <t>Dia 345 de 365. 2 Coríntios 4:7: Um tesouro em vasos de barro. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E346" s="2" t="inlineStr">
@@ -15317,7 +15317,7 @@
       </c>
       <c r="F346" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ Salmos 84:7. Ande e não se canse. #versiculododia #fe #forca #oracao</t>
+          <t>Pausa do meio-dia ☀️ Salmos 84:7. Ande e não se canse. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G346" s="2" t="inlineStr">
@@ -15327,7 +15327,7 @@
       </c>
       <c r="H346" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: força e perseverança 🌙 Para fechar o dia com 2 Coríntios 4:7. Escreva amém se essa oração é sua também. #oracaodanoite #oracao #fe #forca</t>
+          <t>Oração da noite: força e perseverança 🌙 Para fechar o dia com 2 Coríntios 4:7. Escreva amém se essa oração é sua também. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I346" s="2" t="inlineStr"/>
@@ -15350,7 +15350,7 @@
       </c>
       <c r="D347" s="2" t="inlineStr">
         <is>
-          <t>Dia 346 de 365. Josué 14:11: Calebe com 85 anos. #fe #perseveranca #forca #palavradodia</t>
+          <t>Dia 346 de 365. Josué 14:11: Calebe com 85 anos. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E347" s="2" t="inlineStr">
@@ -15360,7 +15360,7 @@
       </c>
       <c r="F347" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ Salmos 29:11. Ele dá força ao cansado. #versiculododia #fe #forca #oracao</t>
+          <t>Pausa do meio-dia ☀️ Salmos 29:11. Ele dá força ao cansado. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G347" s="2" t="inlineStr">
@@ -15370,7 +15370,7 @@
       </c>
       <c r="H347" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: força e perseverança 🌙 Para fechar o dia com Josué 14:11. Comente o nome de quem você quer colocar nesta oração. #oracaodanoite #oracao #fe #forca</t>
+          <t>Oração da noite: força e perseverança 🌙 Para fechar o dia com Josué 14:11. Comente o nome de quem você quer colocar nesta oração. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I347" s="2" t="inlineStr"/>
@@ -15393,7 +15393,7 @@
       </c>
       <c r="D348" s="2" t="inlineStr">
         <is>
-          <t>Dia 347 de 365. Isaías 40:28: Deus não se cansa. #fe #perseveranca #forca #palavradodia</t>
+          <t>Dia 347 de 365. Isaías 40:28: Deus não se cansa. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E348" s="2" t="inlineStr">
@@ -15403,7 +15403,7 @@
       </c>
       <c r="F348" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ Romanos 15:4. Vida de resistência. #versiculododia #fe #forca #oracao</t>
+          <t>Pausa do meio-dia ☀️ Romanos 15:4. Vida de resistência. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G348" s="2" t="inlineStr">
@@ -15413,7 +15413,7 @@
       </c>
       <c r="H348" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: força e perseverança 🌙 Para fechar o dia com Isaías 40:28. Conte nos comentários pelo que você quer agradecer hoje. #oracaodanoite #oracao #fe #forca</t>
+          <t>Oração da noite: força e perseverança 🌙 Para fechar o dia com Isaías 40:28. Conte nos comentários pelo que você quer agradecer hoje. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I348" s="2" t="inlineStr"/>
@@ -15436,7 +15436,7 @@
       </c>
       <c r="D349" s="2" t="inlineStr">
         <is>
-          <t>Dia 348 de 365. Romanos 8:37: Mais que vencedores. #fe #perseveranca #forca #palavradodia</t>
+          <t>Dia 348 de 365. Romanos 8:37: Mais que vencedores. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E349" s="2" t="inlineStr">
@@ -15446,7 +15446,7 @@
       </c>
       <c r="F349" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ Lucas 9:62. Não volte atrás. #versiculododia #fe #forca #oracao</t>
+          <t>Pausa do meio-dia ☀️ Lucas 9:62. Não volte atrás. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G349" s="2" t="inlineStr">
@@ -15456,7 +15456,7 @@
       </c>
       <c r="H349" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: força e perseverança 🌙 Para fechar o dia com Romanos 8:37. Deixe nos comentários o que você quer entregar a Deus esta noite. #oracaodanoite #oracao #fe #forca</t>
+          <t>Oração da noite: força e perseverança 🌙 Para fechar o dia com Romanos 8:37. Deixe nos comentários o que você quer entregar a Deus esta noite. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I349" s="2" t="inlineStr"/>
@@ -15479,7 +15479,7 @@
       </c>
       <c r="D350" s="2" t="inlineStr">
         <is>
-          <t>Dia 349 de 365. Habacuque 3:19: Pés como os das corças. #fe #perseveranca #forca #palavradodia</t>
+          <t>Dia 349 de 365. Habacuque 3:19: Pés como os das corças. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E350" s="2" t="inlineStr">
@@ -15489,7 +15489,7 @@
       </c>
       <c r="F350" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ Isaías 49:4. Seu esforço não é em vão. #versiculododia #fe #forca #oracao</t>
+          <t>Pausa do meio-dia ☀️ Isaías 49:4. Seu esforço não é em vão. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G350" s="2" t="inlineStr">
@@ -15499,7 +15499,7 @@
       </c>
       <c r="H350" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: força e perseverança 🌙 Para fechar o dia com Habacuque 3:19. Marque alguém que precisa ouvir esta oração. #oracaodanoite #oracao #fe #forca</t>
+          <t>Oração da noite: força e perseverança 🌙 Para fechar o dia com Habacuque 3:19. Marque alguém que precisa ouvir esta oração. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I350" s="2" t="inlineStr"/>
@@ -15522,7 +15522,7 @@
       </c>
       <c r="D351" s="2" t="inlineStr">
         <is>
-          <t>Dia 350 de 365. Apocalipse 2:10: Sê fiel até a morte. #fe #perseveranca #forca #palavradodia</t>
+          <t>Dia 350 de 365. Apocalipse 2:10: Sê fiel até a morte. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E351" s="2" t="inlineStr">
@@ -15532,7 +15532,7 @@
       </c>
       <c r="F351" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ 1 Coríntios 15:57. Mais que vencedor. #versiculododia #fe #forca #oracao</t>
+          <t>Pausa do meio-dia ☀️ 1 Coríntios 15:57. Mais que vencedor. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G351" s="2" t="inlineStr">
@@ -15542,7 +15542,7 @@
       </c>
       <c r="H351" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: força e perseverança 🌙 Para fechar o dia com Apocalipse 2:10. Comente seu pedido. Vamos orar juntos. #oracaodanoite #oracao #fe #forca</t>
+          <t>Oração da noite: força e perseverança 🌙 Para fechar o dia com Apocalipse 2:10. Comente seu pedido. Vamos orar juntos. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I351" s="2" t="inlineStr"/>
@@ -15565,7 +15565,7 @@
       </c>
       <c r="D352" s="2" t="inlineStr">
         <is>
-          <t>Dia 351 de 365. 2 Crônicas 15:7: Não desfaleçam as vossas mãos. #fe #perseveranca #forca #palavradodia</t>
+          <t>Dia 351 de 365. 2 Crônicas 15:7: Não desfaleçam as vossas mãos. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E352" s="2" t="inlineStr">
@@ -15575,7 +15575,7 @@
       </c>
       <c r="F352" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ Mateus 24:13. Até o fim. #versiculododia #fe #forca #oracao</t>
+          <t>Pausa do meio-dia ☀️ Mateus 24:13. Até o fim. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G352" s="2" t="inlineStr">
@@ -15585,7 +15585,7 @@
       </c>
       <c r="H352" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: força e perseverança 🌙 Para fechar o dia com 2 Crônicas 15:7. Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #forca</t>
+          <t>Oração da noite: força e perseverança 🌙 Para fechar o dia com 2 Crônicas 15:7. Deixe seu pedido de oração nos comentários. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I352" s="2" t="inlineStr"/>
@@ -15608,7 +15608,7 @@
       </c>
       <c r="D353" s="2" t="inlineStr">
         <is>
-          <t>Dia 352 de 365. João 3:16: O versículo mais conhecido da Bíblia. #fe #amordedeus #amor #palavradodia</t>
+          <t>Dia 352 de 365. João 3:16: O versículo mais conhecido da Bíblia. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E353" s="2" t="inlineStr">
@@ -15618,7 +15618,7 @@
       </c>
       <c r="F353" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ 1 João 4:7. Já demonstrou amor hoje? #versiculododia #fe #amor #oracao</t>
+          <t>Pausa do meio-dia ☀️ 1 João 4:7. Já demonstrou amor hoje? #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G353" s="2" t="inlineStr">
@@ -15628,7 +15628,7 @@
       </c>
       <c r="H353" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: amor 🌙 Para fechar o dia com João 3:16. Escreva amém se essa oração é sua também. #oracaodanoite #oracao #fe #amor</t>
+          <t>Oração da noite: amor 🌙 Para fechar o dia com João 3:16. Escreva amém se essa oração é sua também. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I353" s="2" t="inlineStr"/>
@@ -15651,7 +15651,7 @@
       </c>
       <c r="D354" s="2" t="inlineStr">
         <is>
-          <t>Dia 353 de 365. 1 João 4:8: Deus é amor. #fe #amordedeus #amor #palavradodia</t>
+          <t>Dia 353 de 365. 1 João 4:8: Deus é amor. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E354" s="2" t="inlineStr">
@@ -15661,7 +15661,7 @@
       </c>
       <c r="F354" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ 1 João 4:16. Deus é amor. #versiculododia #fe #amor #oracao</t>
+          <t>Pausa do meio-dia ☀️ 1 João 4:16. Deus é amor. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G354" s="2" t="inlineStr">
@@ -15671,7 +15671,7 @@
       </c>
       <c r="H354" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: amor 🌙 Para fechar o dia com 1 João 4:8. Comente o nome de quem você quer colocar nesta oração. #oracaodanoite #oracao #fe #amor</t>
+          <t>Oração da noite: amor 🌙 Para fechar o dia com 1 João 4:8. Comente o nome de quem você quer colocar nesta oração. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I354" s="2" t="inlineStr"/>
@@ -15694,7 +15694,7 @@
       </c>
       <c r="D355" s="2" t="inlineStr">
         <is>
-          <t>Dia 354 de 365. Romanos 5:8: Ele te amou no seu pior momento. #fe #amordedeus #amor #palavradodia</t>
+          <t>Dia 354 de 365. Romanos 5:8: Ele te amou no seu pior momento. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E355" s="2" t="inlineStr">
@@ -15704,7 +15704,7 @@
       </c>
       <c r="F355" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ Salmos 100:5. Amor que não acaba. #versiculododia #fe #amor #oracao</t>
+          <t>Pausa do meio-dia ☀️ Salmos 100:5. Amor que não acaba. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G355" s="2" t="inlineStr">
@@ -15714,7 +15714,7 @@
       </c>
       <c r="H355" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: amor 🌙 Para fechar o dia com Romanos 5:8. Conte nos comentários pelo que você quer agradecer hoje. #oracaodanoite #oracao #fe #amor</t>
+          <t>Oração da noite: amor 🌙 Para fechar o dia com Romanos 5:8. Conte nos comentários pelo que você quer agradecer hoje. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I355" s="2" t="inlineStr"/>
@@ -15737,7 +15737,7 @@
       </c>
       <c r="D356" s="2" t="inlineStr">
         <is>
-          <t>Dia 355 de 365. Romanos 8:38-39: Nada pode te separar. #fe #amordedeus #amor #palavradodia</t>
+          <t>Dia 355 de 365. Romanos 8:38-39: Nada pode te separar. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E356" s="2" t="inlineStr">
@@ -15747,7 +15747,7 @@
       </c>
       <c r="F356" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ Levítico 19:18. Ame o próximo. #versiculododia #fe #amor #oracao</t>
+          <t>Pausa do meio-dia ☀️ Levítico 19:18. Ame o próximo. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G356" s="2" t="inlineStr">
@@ -15757,7 +15757,7 @@
       </c>
       <c r="H356" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: amor 🌙 Para fechar o dia com Romanos 8:38-39. Deixe nos comentários o que você quer entregar a Deus esta noite. #oracaodanoite #oracao #fe #amor</t>
+          <t>Oração da noite: amor 🌙 Para fechar o dia com Romanos 8:38-39. Deixe nos comentários o que você quer entregar a Deus esta noite. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I356" s="2" t="inlineStr"/>
@@ -15780,7 +15780,7 @@
       </c>
       <c r="D357" s="2" t="inlineStr">
         <is>
-          <t>Dia 356 de 365. 1 João 4:19: Nós amamos porque Ele nos amou primeiro. #fe #amordedeus #amor #palavradodia</t>
+          <t>Dia 356 de 365. 1 João 4:19: Nós amamos porque Ele nos amou primeiro. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E357" s="2" t="inlineStr">
@@ -15790,7 +15790,7 @@
       </c>
       <c r="F357" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ Tiago 2:15-16. Amor prático. #versiculododia #fe #amor #oracao</t>
+          <t>Pausa do meio-dia ☀️ Tiago 2:15-16. Amor prático. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G357" s="2" t="inlineStr">
@@ -15800,7 +15800,7 @@
       </c>
       <c r="H357" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: amor 🌙 Para fechar o dia com 1 João 4:19. Marque alguém que precisa ouvir esta oração. #oracaodanoite #oracao #fe #amor</t>
+          <t>Oração da noite: amor 🌙 Para fechar o dia com 1 João 4:19. Marque alguém que precisa ouvir esta oração. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I357" s="2" t="inlineStr"/>
@@ -15823,7 +15823,7 @@
       </c>
       <c r="D358" s="2" t="inlineStr">
         <is>
-          <t>Dia 357 de 365. Jeremias 31:3: Com amor eterno eu te amei. #fe #amordedeus #amor #palavradodia</t>
+          <t>Dia 357 de 365. Jeremias 31:3: Com amor eterno eu te amei. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E358" s="2" t="inlineStr">
@@ -15833,7 +15833,7 @@
       </c>
       <c r="F358" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ Romanos 13:8. Amor é dívida eterna. #versiculododia #fe #amor #oracao</t>
+          <t>Pausa do meio-dia ☀️ Romanos 13:8. Amor é dívida eterna. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G358" s="2" t="inlineStr">
@@ -15843,7 +15843,7 @@
       </c>
       <c r="H358" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: amor 🌙 Para fechar o dia com Jeremias 31:3. Comente seu pedido. Vamos orar juntos. #oracaodanoite #oracao #fe #amor</t>
+          <t>Oração da noite: amor 🌙 Para fechar o dia com Jeremias 31:3. Comente seu pedido. Vamos orar juntos. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I358" s="2" t="inlineStr"/>
@@ -15866,7 +15866,7 @@
       </c>
       <c r="D359" s="2" t="inlineStr">
         <is>
-          <t>Dia 358 de 365. 1 Coríntios 13:7: Tudo sofre, tudo crê, tudo espera, tudo suporta. #fe #amordedeus #amor #palavradodia</t>
+          <t>Dia 358 de 365. 1 Coríntios 13:7: Tudo sofre, tudo crê, tudo espera, tudo suporta. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E359" s="2" t="inlineStr">
@@ -15876,7 +15876,7 @@
       </c>
       <c r="F359" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ Isaías 43:4. Você é amado. #versiculododia #fe #amor #oracao</t>
+          <t>Pausa do meio-dia ☀️ Isaías 43:4. Você é amado. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G359" s="2" t="inlineStr">
@@ -15886,7 +15886,7 @@
       </c>
       <c r="H359" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: amor 🌙 Para fechar o dia com 1 Coríntios 13:7. Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #amor</t>
+          <t>Oração da noite: amor 🌙 Para fechar o dia com 1 Coríntios 13:7. Deixe seu pedido de oração nos comentários. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I359" s="2" t="inlineStr"/>
@@ -15909,7 +15909,7 @@
       </c>
       <c r="D360" s="2" t="inlineStr">
         <is>
-          <t>Dia 359 de 365. 1 Coríntios 13:13: O maior deles é o amor. #fe #amordedeus #amor #palavradodia</t>
+          <t>Dia 359 de 365. 1 Coríntios 13:13: O maior deles é o amor. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E360" s="2" t="inlineStr">
@@ -15919,7 +15919,7 @@
       </c>
       <c r="F360" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ João 15:12. Amor maior. #versiculododia #fe #amor #oracao</t>
+          <t>Pausa do meio-dia ☀️ João 15:12. Amor maior. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G360" s="2" t="inlineStr">
@@ -15929,7 +15929,7 @@
       </c>
       <c r="H360" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: amor 🌙 Para fechar o dia com 1 Coríntios 13:13. Escreva amém se essa oração é sua também. #oracaodanoite #oracao #fe #amor</t>
+          <t>Oração da noite: amor 🌙 Para fechar o dia com 1 Coríntios 13:13. Escreva amém se essa oração é sua também. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I360" s="2" t="inlineStr"/>
@@ -15952,7 +15952,7 @@
       </c>
       <c r="D361" s="2" t="inlineStr">
         <is>
-          <t>Dia 360 de 365. Mateus 22:37-39: Os dois maiores mandamentos. #fe #amordedeus #amor #palavradodia</t>
+          <t>Dia 360 de 365. Mateus 22:37-39: Os dois maiores mandamentos. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E361" s="2" t="inlineStr">
@@ -15962,7 +15962,7 @@
       </c>
       <c r="F361" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ 1 João 4:9. Amor que se mostra. #versiculododia #fe #amor #oracao</t>
+          <t>Pausa do meio-dia ☀️ 1 João 4:9. Amor que se mostra. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G361" s="2" t="inlineStr">
@@ -15972,7 +15972,7 @@
       </c>
       <c r="H361" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: amor 🌙 Para fechar o dia com Mateus 22:37-39. Comente o nome de quem você quer colocar nesta oração. #oracaodanoite #oracao #fe #amor</t>
+          <t>Oração da noite: amor 🌙 Para fechar o dia com Mateus 22:37-39. Comente o nome de quem você quer colocar nesta oração. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I361" s="2" t="inlineStr"/>
@@ -15995,7 +15995,7 @@
       </c>
       <c r="D362" s="2" t="inlineStr">
         <is>
-          <t>Dia 361 de 365. João 13:34-35: Um mandamento novo. #fe #amordedeus #amor #palavradodia</t>
+          <t>Dia 361 de 365. João 13:34-35: Um mandamento novo. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E362" s="2" t="inlineStr">
@@ -16005,7 +16005,7 @@
       </c>
       <c r="F362" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ 1 Pedro 1:22. Amor sem fingimento. #versiculododia #fe #amor #oracao</t>
+          <t>Pausa do meio-dia ☀️ 1 Pedro 1:22. Amor sem fingimento. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G362" s="2" t="inlineStr">
@@ -16015,7 +16015,7 @@
       </c>
       <c r="H362" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: amor 🌙 Para fechar o dia com João 13:34-35. Conte nos comentários pelo que você quer agradecer hoje. #oracaodanoite #oracao #fe #amor</t>
+          <t>Oração da noite: amor 🌙 Para fechar o dia com João 13:34-35. Conte nos comentários pelo que você quer agradecer hoje. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I362" s="2" t="inlineStr"/>
@@ -16038,7 +16038,7 @@
       </c>
       <c r="D363" s="2" t="inlineStr">
         <is>
-          <t>Dia 362 de 365. Lucas 6:27-28: Amai os vossos inimigos. #fe #amordedeus #amor #palavradodia</t>
+          <t>Dia 362 de 365. Lucas 6:27-28: Amai os vossos inimigos. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E363" s="2" t="inlineStr">
@@ -16048,7 +16048,7 @@
       </c>
       <c r="F363" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ 1 João 3:11. Amor na família de Deus. #versiculododia #fe #amor #oracao</t>
+          <t>Pausa do meio-dia ☀️ 1 João 3:11. Amor na família de Deus. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G363" s="2" t="inlineStr">
@@ -16058,7 +16058,7 @@
       </c>
       <c r="H363" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: amor 🌙 Para fechar o dia com Lucas 6:27-28. Deixe nos comentários o que você quer entregar a Deus esta noite. #oracaodanoite #oracao #fe #amor</t>
+          <t>Oração da noite: amor 🌙 Para fechar o dia com Lucas 6:27-28. Deixe nos comentários o que você quer entregar a Deus esta noite. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I363" s="2" t="inlineStr"/>
@@ -16081,7 +16081,7 @@
       </c>
       <c r="D364" s="2" t="inlineStr">
         <is>
-          <t>Dia 363 de 365. Efésios 3:17-19: Largura, comprimento, altura e profundidade. #fe #amordedeus #amor #palavradodia</t>
+          <t>Dia 363 de 365. Efésios 3:17-19: Largura, comprimento, altura e profundidade. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E364" s="2" t="inlineStr">
@@ -16091,7 +16091,7 @@
       </c>
       <c r="F364" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ 1 Coríntios 13:6. Amor que se alegra. #versiculododia #fe #amor #oracao</t>
+          <t>Pausa do meio-dia ☀️ 1 Coríntios 13:6. Amor que se alegra. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G364" s="2" t="inlineStr">
@@ -16101,7 +16101,7 @@
       </c>
       <c r="H364" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: amor 🌙 Para fechar o dia com Efésios 3:17-19. Marque alguém que precisa ouvir esta oração. #oracaodanoite #oracao #fe #amor</t>
+          <t>Oração da noite: amor 🌙 Para fechar o dia com Efésios 3:17-19. Marque alguém que precisa ouvir esta oração. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I364" s="2" t="inlineStr"/>
@@ -16124,7 +16124,7 @@
       </c>
       <c r="D365" s="2" t="inlineStr">
         <is>
-          <t>Dia 364 de 365. 1 João 3:18: Amor de verdade aparece em ações. #fe #amordedeus #amor #palavradodia</t>
+          <t>Dia 364 de 365. 1 João 3:18: Amor de verdade aparece em ações. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E365" s="2" t="inlineStr">
@@ -16134,7 +16134,7 @@
       </c>
       <c r="F365" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ Lucas 6:35. Amor pelos inimigos. #versiculododia #fe #amor #oracao</t>
+          <t>Pausa do meio-dia ☀️ Lucas 6:35. Amor pelos inimigos. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G365" s="2" t="inlineStr">
@@ -16144,7 +16144,7 @@
       </c>
       <c r="H365" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: amor 🌙 Para fechar o dia com 1 João 3:18. Comente seu pedido. Vamos orar juntos. #oracaodanoite #oracao #fe #amor</t>
+          <t>Oração da noite: amor 🌙 Para fechar o dia com 1 João 3:18. Comente seu pedido. Vamos orar juntos. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I365" s="2" t="inlineStr"/>
@@ -16167,7 +16167,7 @@
       </c>
       <c r="D366" s="2" t="inlineStr">
         <is>
-          <t>Dia 365 de 365. Romanos 13:10: O amor não faz mal ao próximo. #fe #amordedeus #amor #palavradodia</t>
+          <t>Dia 365 de 365. Romanos 13:10: O amor não faz mal ao próximo. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="E366" s="2" t="inlineStr">
@@ -16177,7 +16177,7 @@
       </c>
       <c r="F366" s="2" t="inlineStr">
         <is>
-          <t>Pausa do meio-dia ☀️ 1 Coríntios 8:1. O amor edifica. #versiculododia #fe #amor #oracao</t>
+          <t>Pausa do meio-dia ☀️ 1 Coríntios 8:1. O amor edifica. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="G366" s="2" t="inlineStr">
@@ -16187,7 +16187,7 @@
       </c>
       <c r="H366" s="2" t="inlineStr">
         <is>
-          <t>Oração da noite: amor 🌙 Para fechar o dia com Romanos 13:10. Deixe seu pedido de oração nos comentários. #oracaodanoite #oracao #fe #amor</t>
+          <t>Oração da noite: amor 🌙 Para fechar o dia com Romanos 13:10. Deixe seu pedido de oração nos comentários. #fe #deus #minutodereflexão #versiculosbiblicos #biblia</t>
         </is>
       </c>
       <c r="I366" s="2" t="inlineStr"/>
